--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88165D7-310D-454F-B891-6AC437F52E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C1844B-428A-441B-96AE-A33D1171F6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,18 +1403,102 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_AUS_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_AUS_048</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 48</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_AUS_035</t>
   </si>
   <si>
@@ -1427,6 +1511,174 @@
     <t>connecting solar to buses in cluster 93</t>
   </si>
   <si>
+    <t>distr_solelc_spv_AUS_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_AUS_040</t>
   </si>
   <si>
@@ -1457,28 +1709,70 @@
     <t>connecting solar to buses in cluster 96</t>
   </si>
   <si>
-    <t>distr_solelc_spv_AUS_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
+    <t>distr_solelc_spv_AUS_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
   </si>
   <si>
     <t>distr_solelc_spv_AUS_070</t>
@@ -1511,178 +1805,154 @@
     <t>connecting solar to buses in cluster 68</t>
   </si>
   <si>
-    <t>distr_solelc_spv_AUS_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
+    <t>distr_solelc_spv_AUS_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
   </si>
   <si>
     <t>distr_solelc_spv_AUS_047</t>
@@ -1721,282 +1991,51 @@
     <t>connecting solar to buses in cluster 87</t>
   </si>
   <si>
-    <t>distr_solelc_spv_AUS_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_TomPriceMine_AUS,e_Yandin_AUS,e_AUS22p9S118p7E_AUS,e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>e_Strathmore_AUS,e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>e_w229759860-220_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_w229759860-220_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_Robertstown_AUS,e_Para_AUS</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>e_SouthMorang_AUS,e_Sheffield_AUS,e_Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>e_Strathmore_AUS,e_Nebo_AUS,e_Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>e_Murray_AUS,e_Wagga_AUS,e_UpperTumut_AUS</t>
+  </si>
+  <si>
+    <t>e_Strathmore_AUS,e_Nebo_AUS,e_Broadsound_AUS,e_Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>e_BulliCreek_AUS,e_Tarong_AUS,e_Armidale_AUS,e_Blackwall_AUS</t>
+  </si>
+  <si>
     <t>e_AUS22p9S118p7E_AUS,e_Kalgoorlie_AUS</t>
   </si>
   <si>
@@ -2006,36 +2045,87 @@
     <t>e_BrokenHill_AUS,e_WandoanSouth_AUS,e_MountPiper_AUS</t>
   </si>
   <si>
+    <t>e_Australind_AUS</t>
+  </si>
+  <si>
+    <t>e_Yandin_AUS,e_Merredin_AUS,e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_Kalgoorlie_AUS,e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>e_AUS22p9S118p7E_AUS,e_w229759860-220_AUS,e_Davenport_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_Robertstown_AUS,e_Para_AUS,e_Balranald_AUS,e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>e_w229759860-220_AUS,e_Broadsound_AUS,e_Strathmore_AUS</t>
+  </si>
+  <si>
+    <t>e_SydneyWest_AUS,e_MountPiper_AUS,e_CentralCoast_AUS</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS,e_Merredin_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS</t>
+  </si>
+  <si>
+    <t>e_CentralCoast_AUS,e_Armidale_AUS</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS,e_TomPriceMine_AUS,e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS,e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>e_MountPiper_AUS,e_Armidale_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_Robertstown_AUS,e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS,e_Para_AUS</t>
+  </si>
+  <si>
+    <t>e_MountPiper_AUS,e_Armidale_AUS,e_BulliCreek_AUS,e_CentralCoast_AUS</t>
+  </si>
+  <si>
     <t>e_Yandin_AUS,e_Kalgoorlie_AUS</t>
   </si>
   <si>
     <t>e_Karratha_AUS,e_AUS22p9S118p7E_AUS,e_w229759860-220_AUS,e_Chalumbin_AUS</t>
   </si>
   <si>
-    <t>e_Davenport_AUS</t>
-  </si>
-  <si>
     <t>e_w229759860-220_AUS,e_Chalumbin_AUS</t>
   </si>
   <si>
     <t>e_DarlingtonPoint_AUS,e_Wagga_AUS,e_MountPiper_AUS</t>
   </si>
   <si>
-    <t>e_Karratha_AUS,e_TomPriceMine_AUS,e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS,e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>e_MountPiper_AUS,e_Armidale_AUS</t>
+    <t>e_Yandin_AUS</t>
+  </si>
+  <si>
+    <t>e_Yandin_AUS,e_TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>e_Horsham_AUS,e_Balranald_AUS,e_Ballarat_AUS,e_Rowville_AUS,e_SouthMorang_AUS,e_Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>e_BrokenHill_AUS,e_Balranald_AUS,e_DarlingtonPoint_AUS,e_MountPiper_AUS</t>
+  </si>
+  <si>
+    <t>e_Palmerston_AUS,e_Sheffield_AUS</t>
+  </si>
+  <si>
+    <t>e_Broadsound_AUS,e_Calvale_AUS,e_Bouldercombe_AUS,e_Tarong_AUS,e_GinGin_AUS,e_CalliopeRiver_AUS,e_Blackwall_AUS</t>
   </si>
   <si>
     <t>e_Merredin_AUS,e_Kalgoorlie_AUS</t>
   </si>
   <si>
-    <t>e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
     <t>e_Para_AUS</t>
   </si>
   <si>
@@ -2045,55 +2135,58 @@
     <t>e_Palmerston_AUS</t>
   </si>
   <si>
-    <t>e_Australind_AUS</t>
-  </si>
-  <si>
-    <t>e_Yandin_AUS,e_Merredin_AUS,e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>e_Kalgoorlie_AUS,e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>e_AUS22p9S118p7E_AUS,e_w229759860-220_AUS,e_Davenport_AUS</t>
-  </si>
-  <si>
-    <t>e_w229759860-220_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_Robertstown_AUS,e_Para_AUS,e_Balranald_AUS,e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>e_w229759860-220_AUS,e_Broadsound_AUS,e_Strathmore_AUS</t>
-  </si>
-  <si>
-    <t>e_SydneyWest_AUS,e_MountPiper_AUS,e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_Robertstown_AUS,e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS,e_Para_AUS</t>
-  </si>
-  <si>
-    <t>e_MountPiper_AUS,e_Armidale_AUS,e_BulliCreek_AUS,e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>e_TomPriceMine_AUS,e_Yandin_AUS,e_AUS22p9S118p7E_AUS,e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>e_Strathmore_AUS,e_Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>e_Australind_AUS,e_Merredin_AUS</t>
-  </si>
-  <si>
-    <t>e_Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>e_CentralCoast_AUS,e_Armidale_AUS</t>
+    <t>e_Perth_AUS,e_Yandin_AUS,e_Australind_AUS</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS,e_Merredin_AUS,e_Yandin_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_w229759860-220_AUS,e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>e_Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>e_Yandin_AUS,e_TomPriceMine_AUS,e_Karratha_AUS</t>
+  </si>
+  <si>
+    <t>e_TomPriceMine_AUS,e_Karratha_AUS,e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>e_AUS22p9S118p7E_AUS,e_Karratha_AUS,e_w229759860-220_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS,e_Ballarat_AUS,e_SouthMorang_AUS</t>
+  </si>
+  <si>
+    <t>e_Ballarat_AUS,e_Rowville_AUS,e_SouthMorang_AUS,e_Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>e_SouthMorang_AUS,e_DarlingtonPoint_AUS,e_Wagga_AUS</t>
+  </si>
+  <si>
+    <t>e_Murray_AUS,e_Canberra_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS,e_Horsham_AUS,e_Ballarat_AUS</t>
+  </si>
+  <si>
+    <t>e_Balranald_AUS,e_SouthMorang_AUS,e_DarlingtonPoint_AUS</t>
+  </si>
+  <si>
+    <t>e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS,e_BulliCreek_AUS</t>
+  </si>
+  <si>
+    <t>e_Balranald_AUS,e_BrokenHill_AUS,e_DarlingtonPoint_AUS</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS,e_Broadsound_AUS,e_Calvale_AUS,e_Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>e_Canberra_AUS,e_MountPiper_AUS,e_SydneyWest_AUS</t>
   </si>
   <si>
     <t>e_w229759860-220_AUS,e_BrokenHill_AUS,e_Broadsound_AUS,e_WandoanSouth_AUS</t>
@@ -2105,97 +2198,250 @@
     <t>e_Broadsound_AUS,e_WandoanSouth_AUS</t>
   </si>
   <si>
-    <t>e_Perth_AUS,e_Yandin_AUS,e_Australind_AUS</t>
-  </si>
-  <si>
-    <t>e_Australind_AUS,e_Merredin_AUS,e_Yandin_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_w229759860-220_AUS,e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>e_Hazelwood_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_w229759860-220_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_Robertstown_AUS,e_Para_AUS</t>
-  </si>
-  <si>
-    <t>e_SouthMorang_AUS,e_Sheffield_AUS,e_Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>e_Strathmore_AUS,e_Nebo_AUS,e_Broadsound_AUS</t>
-  </si>
-  <si>
-    <t>e_Murray_AUS,e_Wagga_AUS,e_UpperTumut_AUS</t>
-  </si>
-  <si>
-    <t>e_Strathmore_AUS,e_Nebo_AUS,e_Broadsound_AUS,e_Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>e_BulliCreek_AUS,e_Tarong_AUS,e_Armidale_AUS,e_Blackwall_AUS</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS,e_Horsham_AUS,e_Ballarat_AUS</t>
-  </si>
-  <si>
-    <t>e_Balranald_AUS,e_SouthMorang_AUS,e_DarlingtonPoint_AUS</t>
-  </si>
-  <si>
-    <t>e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS,e_BulliCreek_AUS</t>
-  </si>
-  <si>
-    <t>e_Balranald_AUS,e_BrokenHill_AUS,e_DarlingtonPoint_AUS</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS,e_Broadsound_AUS,e_Calvale_AUS,e_Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>e_Canberra_AUS,e_MountPiper_AUS,e_SydneyWest_AUS</t>
-  </si>
-  <si>
-    <t>e_Yandin_AUS</t>
-  </si>
-  <si>
-    <t>e_Yandin_AUS,e_TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>e_Horsham_AUS,e_Balranald_AUS,e_Ballarat_AUS,e_Rowville_AUS,e_SouthMorang_AUS,e_Hazelwood_AUS</t>
-  </si>
-  <si>
-    <t>e_BrokenHill_AUS,e_Balranald_AUS,e_DarlingtonPoint_AUS,e_MountPiper_AUS</t>
-  </si>
-  <si>
-    <t>e_Palmerston_AUS,e_Sheffield_AUS</t>
-  </si>
-  <si>
-    <t>e_Broadsound_AUS,e_Calvale_AUS,e_Bouldercombe_AUS,e_Tarong_AUS,e_GinGin_AUS,e_CalliopeRiver_AUS,e_Blackwall_AUS</t>
-  </si>
-  <si>
-    <t>e_Yandin_AUS,e_TomPriceMine_AUS,e_Karratha_AUS</t>
-  </si>
-  <si>
-    <t>e_TomPriceMine_AUS,e_Karratha_AUS,e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>e_AUS22p9S118p7E_AUS,e_Karratha_AUS,e_w229759860-220_AUS</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS,e_Ballarat_AUS,e_SouthMorang_AUS</t>
-  </si>
-  <si>
-    <t>e_Ballarat_AUS,e_Rowville_AUS,e_SouthMorang_AUS,e_Hazelwood_AUS</t>
-  </si>
-  <si>
-    <t>e_SouthMorang_AUS,e_DarlingtonPoint_AUS,e_Wagga_AUS</t>
-  </si>
-  <si>
-    <t>e_Murray_AUS,e_Canberra_AUS</t>
+    <t>distr_wonelc_won_AUS_097</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_070</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_088</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_071</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_082</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_087</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_075</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_091</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_085</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_077</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_093</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_081</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_AUS_095</t>
@@ -2228,6 +2474,84 @@
     <t>connecting wind onshore to buses in cluster 60</t>
   </si>
   <si>
+    <t>distr_wonelc_won_AUS_072</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_094</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_092</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_AUS_074</t>
   </si>
   <si>
@@ -2258,66 +2582,6 @@
     <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_082</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_087</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_093</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_081</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_AUS_083</t>
   </si>
   <si>
@@ -2348,82 +2612,82 @@
     <t>connecting wind onshore to buses in cluster 63</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_097</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_070</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_088</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
+    <t>distr_wonelc_won_AUS_084</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_078</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_090</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
   </si>
   <si>
     <t>distr_wonelc_won_AUS_080</t>
@@ -2486,156 +2750,6 @@
     <t>connecting wind onshore to buses in cluster 61</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_075</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_091</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_085</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_077</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_084</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_071</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_AUS_096</t>
   </si>
   <si>
@@ -2666,118 +2780,169 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_094</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_092</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_078</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_090</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_072</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
+    <t>elc_won_AUS_097</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_070</t>
+  </si>
+  <si>
+    <t>e_Yandin_AUS,e_Merredin_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_017</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_088</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_AUS22p9S118p7E_AUS,e_w229759860-220_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_052</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_037</t>
+  </si>
+  <si>
+    <t>e_Balranald_AUS,e_Horsham_AUS,e_Ballarat_AUS,e_SouthMorang_AUS,e_DarlingtonPoint_AUS,e_Wagga_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_002</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_006</t>
+  </si>
+  <si>
+    <t>e_w229759860-220_AUS,e_Strathmore_AUS,e_Chalumbin_AUS,e_Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_067</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_071</t>
+  </si>
+  <si>
+    <t>e_Perth_AUS,e_Yandin_AUS,e_Merredin_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_029</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_016</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_014</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_021</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_011</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_041</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_066</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS,e_MountPiper_AUS,e_BulliCreek_AUS,e_Armidale_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_056</t>
+  </si>
+  <si>
+    <t>e_Armidale_AUS,e_BulliCreek_AUS,e_Tarong_AUS,e_Blackwall_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_069</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_082</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_087</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_028</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_044</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_053</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_042</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_001</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_005</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS,e_Strathmore_AUS,e_Nebo_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_059</t>
+  </si>
+  <si>
+    <t>e_Broadsound_AUS,e_Bouldercombe_AUS,e_GinGin_AUS,e_CalliopeRiver_AUS,e_Tarong_AUS,e_Blackwall_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_075</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_091</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_085</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_077</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_050</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_051</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_030</t>
+  </si>
+  <si>
+    <t>e_Rowville_AUS,e_Hazelwood_AUS,e_SouthMorang_AUS,e_Murray_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_068</t>
+  </si>
+  <si>
+    <t>e_MountPiper_AUS,e_UpperTumut_AUS,e_Wagga_AUS,e_Canberra_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_093</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS,e_TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_081</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_026</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_015</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_007</t>
   </si>
   <si>
     <t>elc_won_AUS_095</t>
@@ -2801,6 +2966,72 @@
     <t>elc_won_AUS_060</t>
   </si>
   <si>
+    <t>elc_won_AUS_072</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_049</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_008</t>
+  </si>
+  <si>
+    <t>e_Broadsound_AUS,e_Nebo_AUS,e_Strathmore_AUS,e_Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_057</t>
+  </si>
+  <si>
+    <t>e_Armidale_AUS,e_Blackwall_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_035</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_036</t>
+  </si>
+  <si>
+    <t>e_BrokenHill_AUS,e_Balranald_AUS,e_DarlingtonPoint_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_033</t>
+  </si>
+  <si>
+    <t>e_SouthMorang_AUS,e_Sheffield_AUS,e_Rowville_AUS,e_Hazelwood_AUS,e_Palmerston_AUS,e_Murray_AUS,e_Canberra_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_065</t>
+  </si>
+  <si>
+    <t>e_BrokenHill_AUS,e_DarlingtonPoint_AUS,e_MountPiper_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_094</t>
+  </si>
+  <si>
+    <t>e_TomPriceMine_AUS,e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_092</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_038</t>
+  </si>
+  <si>
+    <t>e_Para_AUS,e_Robertstown_AUS,e_Davenport_AUS,e_BrokenHill_AUS,e_Balranald_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_032</t>
+  </si>
+  <si>
+    <t>e_Sheffield_AUS,e_Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_054</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS,e_BulliCreek_AUS,e_Armidale_AUS,e_Tarong_AUS</t>
+  </si>
+  <si>
     <t>elc_won_AUS_074</t>
   </si>
   <si>
@@ -2819,39 +3050,6 @@
     <t>e_w229759860-220_AUS,e_Davenport_AUS,e_BrokenHill_AUS</t>
   </si>
   <si>
-    <t>elc_won_AUS_069</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_082</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_087</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_028</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_044</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_093</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS,e_TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_081</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_026</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_015</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_007</t>
-  </si>
-  <si>
     <t>elc_won_AUS_083</t>
   </si>
   <si>
@@ -2873,64 +3071,55 @@
     <t>elc_won_AUS_063</t>
   </si>
   <si>
-    <t>elc_won_AUS_035</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_036</t>
-  </si>
-  <si>
-    <t>e_BrokenHill_AUS,e_Balranald_AUS,e_DarlingtonPoint_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_033</t>
-  </si>
-  <si>
-    <t>e_SouthMorang_AUS,e_Sheffield_AUS,e_Rowville_AUS,e_Hazelwood_AUS,e_Palmerston_AUS,e_Murray_AUS,e_Canberra_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_065</t>
-  </si>
-  <si>
-    <t>e_BrokenHill_AUS,e_DarlingtonPoint_AUS,e_MountPiper_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_097</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_070</t>
-  </si>
-  <si>
-    <t>e_Yandin_AUS,e_Merredin_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_017</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_088</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_AUS22p9S118p7E_AUS,e_w229759860-220_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_052</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_037</t>
-  </si>
-  <si>
-    <t>e_Balranald_AUS,e_Horsham_AUS,e_Ballarat_AUS,e_SouthMorang_AUS,e_DarlingtonPoint_AUS,e_Wagga_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_002</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_006</t>
-  </si>
-  <si>
-    <t>e_w229759860-220_AUS,e_Strathmore_AUS,e_Chalumbin_AUS,e_Broadsound_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_067</t>
+    <t>elc_won_AUS_084</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_013</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_046</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_078</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_090</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_020</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_045</t>
+  </si>
+  <si>
+    <t>e_w229759860-220_AUS,e_Davenport_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_012</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_034</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS,e_Para_AUS,e_Horsham_AUS,e_Balranald_AUS,e_Ballarat_AUS,e_SouthMorang_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_010</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_003</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_055</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS,e_BulliCreek_AUS,e_Armidale_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_062</t>
+  </si>
+  <si>
+    <t>e_Canberra_AUS,e_MountPiper_AUS,e_SydneyWest_AUS,e_CentralCoast_AUS</t>
   </si>
   <si>
     <t>elc_won_AUS_080</t>
@@ -2957,9 +3146,6 @@
     <t>elc_won_AUS_039</t>
   </si>
   <si>
-    <t>e_Davenport_AUS,e_BrokenHill_AUS</t>
-  </si>
-  <si>
     <t>elc_won_AUS_043</t>
   </si>
   <si>
@@ -2978,105 +3164,6 @@
     <t>e_MountPiper_AUS,e_Armidale_AUS,e_CentralCoast_AUS</t>
   </si>
   <si>
-    <t>elc_won_AUS_075</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_091</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_085</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_077</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_050</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_051</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_030</t>
-  </si>
-  <si>
-    <t>e_Rowville_AUS,e_Hazelwood_AUS,e_SouthMorang_AUS,e_Murray_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_068</t>
-  </si>
-  <si>
-    <t>e_MountPiper_AUS,e_UpperTumut_AUS,e_Wagga_AUS,e_Canberra_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_084</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_013</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_046</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_071</t>
-  </si>
-  <si>
-    <t>e_Perth_AUS,e_Yandin_AUS,e_Merredin_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_029</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_016</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_014</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_021</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_011</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_041</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_066</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS,e_MountPiper_AUS,e_BulliCreek_AUS,e_Armidale_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_056</t>
-  </si>
-  <si>
-    <t>e_Armidale_AUS,e_BulliCreek_AUS,e_Tarong_AUS,e_Blackwall_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_053</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_042</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_001</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_005</t>
-  </si>
-  <si>
-    <t>e_Chalumbin_AUS,e_Strathmore_AUS,e_Nebo_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_059</t>
-  </si>
-  <si>
-    <t>e_Broadsound_AUS,e_Bouldercombe_AUS,e_GinGin_AUS,e_CalliopeRiver_AUS,e_Tarong_AUS,e_Blackwall_AUS</t>
-  </si>
-  <si>
     <t>elc_won_AUS_096</t>
   </si>
   <si>
@@ -3095,99 +3182,132 @@
     <t>elc_won_AUS_004</t>
   </si>
   <si>
-    <t>elc_won_AUS_094</t>
-  </si>
-  <si>
-    <t>e_TomPriceMine_AUS,e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_092</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_038</t>
-  </si>
-  <si>
-    <t>e_Para_AUS,e_Robertstown_AUS,e_Davenport_AUS,e_BrokenHill_AUS,e_Balranald_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_032</t>
-  </si>
-  <si>
-    <t>e_Sheffield_AUS,e_Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_054</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS,e_BulliCreek_AUS,e_Armidale_AUS,e_Tarong_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_078</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_090</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_020</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_045</t>
-  </si>
-  <si>
-    <t>e_w229759860-220_AUS,e_Davenport_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_012</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_034</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS,e_Para_AUS,e_Horsham_AUS,e_Balranald_AUS,e_Ballarat_AUS,e_SouthMorang_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_010</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_003</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_055</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS,e_BulliCreek_AUS,e_Armidale_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_062</t>
-  </si>
-  <si>
-    <t>e_Canberra_AUS,e_MountPiper_AUS,e_SydneyWest_AUS,e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_072</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_049</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_008</t>
-  </si>
-  <si>
-    <t>e_Broadsound_AUS,e_Nebo_AUS,e_Strathmore_AUS,e_Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_057</t>
-  </si>
-  <si>
-    <t>e_Armidale_AUS,e_Blackwall_AUS</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_AUS_021</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_AUS_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_049</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_047</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_045</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_046</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_AUS_012</t>
   </si>
   <si>
@@ -3212,6 +3332,48 @@
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_051</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 51</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_AUS_005</t>
   </si>
   <si>
@@ -3236,52 +3398,64 @@
     <t>connecting wind offshore to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_046</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
+    <t>distr_wofelc_wof_AUS_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
   </si>
   <si>
     <t>distr_wofelc_wof_AUS_017</t>
@@ -3320,186 +3494,90 @@
     <t>connecting wind offshore to buses in cluster 32</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_045</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_051</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_049</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_047</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 47</t>
-  </si>
-  <si>
     <t>elc_wof_AUS_021</t>
   </si>
   <si>
     <t>e_Kalgoorlie_AUS,e_Davenport_AUS</t>
   </si>
   <si>
+    <t>elc_wof_AUS_026</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_031</t>
+  </si>
+  <si>
+    <t>e_GinGin_AUS,e_Blackwall_AUS,e_Tarong_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_042</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_010</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_049</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_047</t>
+  </si>
+  <si>
+    <t>e_Nebo_AUS,e_Broadsound_AUS,e_CalliopeRiver_AUS,e_Bouldercombe_AUS,e_GinGin_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_045</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_006</t>
+  </si>
+  <si>
+    <t>e_Hazelwood_AUS,e_Murray_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_028</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_003</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_036</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_027</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_016</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS,e_Perth_AUS,e_Yandin_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_014</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_046</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_011</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS,e_Ballarat_AUS,e_SouthMorang_AUS,e_Rowville_AUS,e_Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_030</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_015</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_040</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_008</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_012</t>
   </si>
   <si>
@@ -3521,6 +3599,30 @@
     <t>e_Davenport_AUS,e_Robertstown_AUS</t>
   </si>
   <si>
+    <t>elc_wof_AUS_029</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_004</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_037</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_039</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_035</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_050</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_051</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS,e_Strathmore_AUS,e_CalliopeRiver_AUS</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_005</t>
   </si>
   <si>
@@ -3542,34 +3644,37 @@
     <t>e_Blackwall_AUS</t>
   </si>
   <si>
-    <t>elc_wof_AUS_028</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_003</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_036</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_027</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_016</t>
-  </si>
-  <si>
-    <t>e_Australind_AUS,e_Perth_AUS,e_Yandin_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_014</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_046</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_011</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS,e_Ballarat_AUS,e_SouthMorang_AUS,e_Rowville_AUS,e_Hazelwood_AUS</t>
+    <t>elc_wof_AUS_025</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_002</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_038</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS,e_w229759860-220_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_023</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_044</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_041</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_052</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_007</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_001</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_034</t>
   </si>
   <si>
     <t>elc_wof_AUS_017</t>
@@ -3591,111 +3696,6 @@
   </si>
   <si>
     <t>elc_wof_AUS_032</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_045</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_006</t>
-  </si>
-  <si>
-    <t>e_Hazelwood_AUS,e_Murray_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_025</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_002</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_038</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS,e_w229759860-220_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_023</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_044</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_041</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_030</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_015</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_040</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_008</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_029</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_004</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_037</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_039</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_035</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_050</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_051</t>
-  </si>
-  <si>
-    <t>e_Chalumbin_AUS,e_Strathmore_AUS,e_CalliopeRiver_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_052</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_007</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_001</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_034</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_026</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_031</t>
-  </si>
-  <si>
-    <t>e_GinGin_AUS,e_Blackwall_AUS,e_Tarong_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_042</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_010</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_049</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_047</t>
-  </si>
-  <si>
-    <t>e_Nebo_AUS,e_Broadsound_AUS,e_CalliopeRiver_AUS,e_Bouldercombe_AUS,e_GinGin_AUS</t>
   </si>
   <si>
     <t>e_won_AUS_001</t>
@@ -8321,7 +8321,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EDAC7D-BF48-4033-A8F1-324AD6D1A154}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2708B7-E097-4929-AF72-BCC0CAEFE8D1}">
   <dimension ref="B9:BD107"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8559,16 +8559,16 @@
         <v>446</v>
       </c>
       <c r="Y11" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="Z11" t="s">
         <v>644</v>
       </c>
       <c r="AA11">
-        <v>0.98466621786657815</v>
+        <v>0.97969590283269214</v>
       </c>
       <c r="AB11">
-        <v>281.11933911273309</v>
+        <v>372.24178140064373</v>
       </c>
       <c r="AD11" t="s">
         <v>445</v>
@@ -8598,13 +8598,13 @@
         <v>905</v>
       </c>
       <c r="AN11" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="AO11">
-        <v>0.98256179218990303</v>
+        <v>0.97620022609803814</v>
       </c>
       <c r="AP11">
-        <v>319.70047651844521</v>
+        <v>436.32918820263421</v>
       </c>
       <c r="AR11" t="s">
         <v>445</v>
@@ -8705,16 +8705,16 @@
         <v>450</v>
       </c>
       <c r="Y12" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="Z12" t="s">
         <v>645</v>
       </c>
       <c r="AA12">
-        <v>0.94191717639101813</v>
+        <v>0.98086220977655469</v>
       </c>
       <c r="AB12">
-        <v>1064.8517661646679</v>
+        <v>350.85948742983044</v>
       </c>
       <c r="AD12" t="s">
         <v>445</v>
@@ -8744,13 +8744,13 @@
         <v>906</v>
       </c>
       <c r="AN12" t="s">
-        <v>663</v>
+        <v>907</v>
       </c>
       <c r="AO12">
-        <v>0.97344873028830825</v>
+        <v>0.98607591956620455</v>
       </c>
       <c r="AP12">
-        <v>486.77327804768265</v>
+        <v>255.27480795291643</v>
       </c>
       <c r="AR12" t="s">
         <v>445</v>
@@ -8780,13 +8780,13 @@
         <v>1145</v>
       </c>
       <c r="BB12" t="s">
-        <v>1146</v>
+        <v>680</v>
       </c>
       <c r="BC12">
-        <v>0.99209673382744978</v>
+        <v>0.97261625181972589</v>
       </c>
       <c r="BD12">
-        <v>754.89395975118964</v>
+        <v>1078.2253319963402</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8851,16 +8851,16 @@
         <v>452</v>
       </c>
       <c r="Y13" t="s">
-        <v>439</v>
+        <v>390</v>
       </c>
       <c r="Z13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AA13">
-        <v>0.96994910016476243</v>
+        <v>0.99377506386421921</v>
       </c>
       <c r="AB13">
-        <v>550.93316364602254</v>
+        <v>114.12382915598114</v>
       </c>
       <c r="AD13" t="s">
         <v>445</v>
@@ -8887,16 +8887,16 @@
         <v>715</v>
       </c>
       <c r="AM13" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AN13" t="s">
-        <v>908</v>
+        <v>646</v>
       </c>
       <c r="AO13">
-        <v>0.94726945791757955</v>
+        <v>0.94516861039769784</v>
       </c>
       <c r="AP13">
-        <v>966.72660484437438</v>
+        <v>1005.2421427088731</v>
       </c>
       <c r="AR13" t="s">
         <v>445</v>
@@ -8923,16 +8923,16 @@
         <v>1043</v>
       </c>
       <c r="BA13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="BB13" t="s">
         <v>1147</v>
       </c>
-      <c r="BB13" t="s">
-        <v>649</v>
-      </c>
       <c r="BC13">
-        <v>0.9762650633688883</v>
+        <v>0.99257145555712289</v>
       </c>
       <c r="BD13">
-        <v>1033.7706446223781</v>
+        <v>724.76495397460064</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8997,16 +8997,16 @@
         <v>454</v>
       </c>
       <c r="Y14" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="Z14" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AA14">
-        <v>0.98507000954579316</v>
+        <v>0.95105540198711702</v>
       </c>
       <c r="AB14">
-        <v>273.71649166045961</v>
+        <v>897.31763023618794</v>
       </c>
       <c r="AD14" t="s">
         <v>445</v>
@@ -9039,10 +9039,10 @@
         <v>910</v>
       </c>
       <c r="AO14">
-        <v>0.99721814870334879</v>
+        <v>0.94231963623506931</v>
       </c>
       <c r="AP14">
-        <v>51.000607105273012</v>
+        <v>1057.4733356903953</v>
       </c>
       <c r="AR14" t="s">
         <v>445</v>
@@ -9072,13 +9072,13 @@
         <v>1148</v>
       </c>
       <c r="BB14" t="s">
-        <v>1149</v>
+        <v>648</v>
       </c>
       <c r="BC14">
-        <v>0.9859478284089821</v>
+        <v>0.96412973603590302</v>
       </c>
       <c r="BD14">
-        <v>915.80229055056782</v>
+        <v>1181.6193826292476</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9143,16 +9143,16 @@
         <v>456</v>
       </c>
       <c r="Y15" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="Z15" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AA15">
-        <v>0.95257490531108058</v>
+        <v>0.99131962187405476</v>
       </c>
       <c r="AB15">
-        <v>869.46006929685575</v>
+        <v>159.14026564233004</v>
       </c>
       <c r="AD15" t="s">
         <v>445</v>
@@ -9182,13 +9182,13 @@
         <v>911</v>
       </c>
       <c r="AN15" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="AO15">
-        <v>0.9965750017909164</v>
+        <v>0.97832027217029349</v>
       </c>
       <c r="AP15">
-        <v>62.791633833199988</v>
+        <v>397.46167687795332</v>
       </c>
       <c r="AR15" t="s">
         <v>445</v>
@@ -9215,16 +9215,16 @@
         <v>1047</v>
       </c>
       <c r="BA15" t="s">
+        <v>1149</v>
+      </c>
+      <c r="BB15" t="s">
         <v>1150</v>
       </c>
-      <c r="BB15" t="s">
-        <v>1151</v>
-      </c>
       <c r="BC15">
-        <v>0.99844627758702942</v>
+        <v>0.99566455794863251</v>
       </c>
       <c r="BD15">
-        <v>351.90958247653504</v>
+        <v>528.4560555267874</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9289,16 +9289,16 @@
         <v>458</v>
       </c>
       <c r="Y16" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="Z16" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AA16">
-        <v>0.9934232231965805</v>
+        <v>0.95110913617470227</v>
       </c>
       <c r="AB16">
-        <v>120.5742413960235</v>
+        <v>896.33250346379077</v>
       </c>
       <c r="AD16" t="s">
         <v>445</v>
@@ -9328,13 +9328,13 @@
         <v>912</v>
       </c>
       <c r="AN16" t="s">
-        <v>655</v>
+        <v>913</v>
       </c>
       <c r="AO16">
-        <v>0.98250131854428446</v>
+        <v>0.99484431329617862</v>
       </c>
       <c r="AP16">
-        <v>320.80916002145239</v>
+        <v>94.520922903391252</v>
       </c>
       <c r="AR16" t="s">
         <v>445</v>
@@ -9361,16 +9361,16 @@
         <v>1049</v>
       </c>
       <c r="BA16" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="BB16" t="s">
-        <v>973</v>
+        <v>651</v>
       </c>
       <c r="BC16">
-        <v>0.97654176188453468</v>
+        <v>0.9524344319526965</v>
       </c>
       <c r="BD16">
-        <v>1030.3995343734193</v>
+        <v>1324.1071707096473</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9435,16 +9435,16 @@
         <v>460</v>
       </c>
       <c r="Y17" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="Z17" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AA17">
-        <v>0.98371921732749934</v>
+        <v>0.96488357195289265</v>
       </c>
       <c r="AB17">
-        <v>298.48101566251137</v>
+        <v>643.80118086363541</v>
       </c>
       <c r="AD17" t="s">
         <v>445</v>
@@ -9471,16 +9471,16 @@
         <v>723</v>
       </c>
       <c r="AM17" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AN17" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="AO17">
-        <v>0.94941329297783439</v>
+        <v>0.97273741219297172</v>
       </c>
       <c r="AP17">
-        <v>927.42296207303548</v>
+        <v>499.8141097955185</v>
       </c>
       <c r="AR17" t="s">
         <v>445</v>
@@ -9507,16 +9507,16 @@
         <v>1051</v>
       </c>
       <c r="BA17" t="s">
+        <v>1152</v>
+      </c>
+      <c r="BB17" t="s">
         <v>1153</v>
       </c>
-      <c r="BB17" t="s">
-        <v>1154</v>
-      </c>
       <c r="BC17">
-        <v>0.99180629119732955</v>
+        <v>0.98797961821726321</v>
       </c>
       <c r="BD17">
-        <v>773.32738534281725</v>
+        <v>891.04831805300933</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9581,16 +9581,16 @@
         <v>462</v>
       </c>
       <c r="Y18" t="s">
-        <v>442</v>
+        <v>350</v>
       </c>
       <c r="Z18" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AA18">
-        <v>0.98946891329754838</v>
+        <v>0.99397024960358282</v>
       </c>
       <c r="AB18">
-        <v>193.0699228782787</v>
+        <v>110.54542393431565</v>
       </c>
       <c r="AD18" t="s">
         <v>445</v>
@@ -9617,16 +9617,16 @@
         <v>725</v>
       </c>
       <c r="AM18" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AN18" t="s">
-        <v>665</v>
+        <v>916</v>
       </c>
       <c r="AO18">
-        <v>0.94697941545710573</v>
+        <v>0.97984247759827614</v>
       </c>
       <c r="AP18">
-        <v>972.0440499530622</v>
+        <v>369.55457736493832</v>
       </c>
       <c r="AR18" t="s">
         <v>445</v>
@@ -9653,16 +9653,16 @@
         <v>1053</v>
       </c>
       <c r="BA18" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="BB18" t="s">
-        <v>1156</v>
+        <v>648</v>
       </c>
       <c r="BC18">
-        <v>0.9784511409772424</v>
+        <v>0.91754501241076647</v>
       </c>
       <c r="BD18">
-        <v>1007.136932427263</v>
+        <v>1749.1765987954952</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9727,16 +9727,16 @@
         <v>464</v>
       </c>
       <c r="Y19" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="Z19" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AA19">
-        <v>0.99515580458889907</v>
+        <v>0.98138635372944616</v>
       </c>
       <c r="AB19">
-        <v>88.81024920351615</v>
+        <v>341.25018162681971</v>
       </c>
       <c r="AD19" t="s">
         <v>445</v>
@@ -9763,16 +9763,16 @@
         <v>727</v>
       </c>
       <c r="AM19" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="AN19" t="s">
-        <v>665</v>
+        <v>679</v>
       </c>
       <c r="AO19">
-        <v>0.96335236529265011</v>
+        <v>0.99109308381957362</v>
       </c>
       <c r="AP19">
-        <v>671.87330296808034</v>
+        <v>163.29346330781715</v>
       </c>
       <c r="AR19" t="s">
         <v>445</v>
@@ -9799,16 +9799,16 @@
         <v>1055</v>
       </c>
       <c r="BA19" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="BB19" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="BC19">
-        <v>0.9955677970684097</v>
+        <v>0.98908658389363524</v>
       </c>
       <c r="BD19">
-        <v>534.59714605826571</v>
+        <v>877.56178622921061</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9873,16 +9873,16 @@
         <v>466</v>
       </c>
       <c r="Y20" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="Z20" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AA20">
-        <v>0.96473247588547761</v>
+        <v>0.99502756316390695</v>
       </c>
       <c r="AB20">
-        <v>646.57127543291119</v>
+        <v>91.161341995039152</v>
       </c>
       <c r="AD20" t="s">
         <v>445</v>
@@ -9909,16 +9909,16 @@
         <v>729</v>
       </c>
       <c r="AM20" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="AN20" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="AO20">
-        <v>0.97070223771032205</v>
+        <v>0.99573205734141002</v>
       </c>
       <c r="AP20">
-        <v>537.12564197742824</v>
+        <v>78.245615407483584</v>
       </c>
       <c r="AR20" t="s">
         <v>445</v>
@@ -9945,10 +9945,10 @@
         <v>1057</v>
       </c>
       <c r="BA20" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="BB20" t="s">
-        <v>924</v>
+        <v>955</v>
       </c>
       <c r="BC20">
         <v>0.97834276564858003</v>
@@ -10019,16 +10019,16 @@
         <v>468</v>
       </c>
       <c r="Y21" t="s">
-        <v>354</v>
+        <v>427</v>
       </c>
       <c r="Z21" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="AA21">
-        <v>0.9580334555499519</v>
+        <v>0.99219726142231079</v>
       </c>
       <c r="AB21">
-        <v>769.38664825088097</v>
+        <v>143.05020725763492</v>
       </c>
       <c r="AD21" t="s">
         <v>445</v>
@@ -10055,16 +10055,16 @@
         <v>731</v>
       </c>
       <c r="AM21" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="AN21" t="s">
-        <v>698</v>
+        <v>658</v>
       </c>
       <c r="AO21">
-        <v>0.98586375931635961</v>
+        <v>0.93728012376790604</v>
       </c>
       <c r="AP21">
-        <v>259.16441253340616</v>
+        <v>1149.8643975883897</v>
       </c>
       <c r="AR21" t="s">
         <v>445</v>
@@ -10091,10 +10091,10 @@
         <v>1059</v>
       </c>
       <c r="BA21" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="BB21" t="s">
-        <v>973</v>
+        <v>944</v>
       </c>
       <c r="BC21">
         <v>0.97810798081469907</v>
@@ -10165,16 +10165,16 @@
         <v>470</v>
       </c>
       <c r="Y22" t="s">
-        <v>441</v>
+        <v>402</v>
       </c>
       <c r="Z22" t="s">
         <v>654</v>
       </c>
       <c r="AA22">
-        <v>0.98447946182885371</v>
+        <v>0.99809443707900702</v>
       </c>
       <c r="AB22">
-        <v>284.54319980434889</v>
+        <v>34.93532021820478</v>
       </c>
       <c r="AD22" t="s">
         <v>445</v>
@@ -10201,16 +10201,16 @@
         <v>733</v>
       </c>
       <c r="AM22" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="AN22" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="AO22">
-        <v>0.98753047073573874</v>
+        <v>0.97740985609297437</v>
       </c>
       <c r="AP22">
-        <v>228.60803651145704</v>
+        <v>414.15263829547018</v>
       </c>
       <c r="AR22" t="s">
         <v>445</v>
@@ -10237,10 +10237,10 @@
         <v>1061</v>
       </c>
       <c r="BA22" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="BB22" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="BC22">
         <v>0.99215965418440455</v>
@@ -10311,16 +10311,16 @@
         <v>472</v>
       </c>
       <c r="Y23" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="Z23" t="s">
         <v>655</v>
       </c>
       <c r="AA23">
-        <v>0.98826693080891115</v>
+        <v>0.99741667924532684</v>
       </c>
       <c r="AB23">
-        <v>215.10626850329641</v>
+        <v>47.360880502342191</v>
       </c>
       <c r="AD23" t="s">
         <v>445</v>
@@ -10347,16 +10347,16 @@
         <v>735</v>
       </c>
       <c r="AM23" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="AN23" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="AO23">
-        <v>0.96497483135850137</v>
+        <v>0.97918864997471655</v>
       </c>
       <c r="AP23">
-        <v>642.12809176080782</v>
+        <v>381.5414171301972</v>
       </c>
       <c r="AR23" t="s">
         <v>445</v>
@@ -10383,10 +10383,10 @@
         <v>1063</v>
       </c>
       <c r="BA23" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="BB23" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="BC23">
         <v>0.96645436477691782</v>
@@ -10457,16 +10457,16 @@
         <v>474</v>
       </c>
       <c r="Y24" t="s">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="Z24" t="s">
         <v>656</v>
       </c>
       <c r="AA24">
-        <v>0.97618980314151516</v>
+        <v>0.99782027918606175</v>
       </c>
       <c r="AB24">
-        <v>436.52027573888904</v>
+        <v>39.961548255533756</v>
       </c>
       <c r="AD24" t="s">
         <v>445</v>
@@ -10493,16 +10493,16 @@
         <v>737</v>
       </c>
       <c r="AM24" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="AN24" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AO24">
-        <v>0.953110606460702</v>
+        <v>0.96550702044259584</v>
       </c>
       <c r="AP24">
-        <v>859.63888155379732</v>
+        <v>632.37129188574295</v>
       </c>
       <c r="AR24" t="s">
         <v>445</v>
@@ -10529,10 +10529,10 @@
         <v>1065</v>
       </c>
       <c r="BA24" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="BB24" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="BC24">
         <v>0.99312868008939148</v>
@@ -10603,16 +10603,16 @@
         <v>476</v>
       </c>
       <c r="Y25" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="Z25" t="s">
         <v>657</v>
       </c>
       <c r="AA25">
-        <v>0.99263667372558639</v>
+        <v>0.98466621786657815</v>
       </c>
       <c r="AB25">
-        <v>134.9943150309158</v>
+        <v>281.11933911273309</v>
       </c>
       <c r="AD25" t="s">
         <v>445</v>
@@ -10639,16 +10639,16 @@
         <v>739</v>
       </c>
       <c r="AM25" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="AN25" t="s">
-        <v>684</v>
+        <v>648</v>
       </c>
       <c r="AO25">
-        <v>0.95955011836243909</v>
+        <v>0.99191812933076651</v>
       </c>
       <c r="AP25">
-        <v>741.58116335528291</v>
+        <v>148.16762893594731</v>
       </c>
       <c r="AR25" t="s">
         <v>445</v>
@@ -10675,10 +10675,10 @@
         <v>1067</v>
       </c>
       <c r="BA25" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="BB25" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="BC25">
         <v>0.96520145465062446</v>
@@ -10749,16 +10749,16 @@
         <v>478</v>
       </c>
       <c r="Y26" t="s">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="Z26" t="s">
         <v>658</v>
       </c>
       <c r="AA26">
-        <v>0.98665714478881894</v>
+        <v>0.94191717639101813</v>
       </c>
       <c r="AB26">
-        <v>244.61901220498595</v>
+        <v>1064.8517661646679</v>
       </c>
       <c r="AD26" t="s">
         <v>445</v>
@@ -10785,16 +10785,16 @@
         <v>741</v>
       </c>
       <c r="AM26" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="AN26" t="s">
-        <v>924</v>
+        <v>710</v>
       </c>
       <c r="AO26">
-        <v>0.9966806183812299</v>
+        <v>0.97851296575183921</v>
       </c>
       <c r="AP26">
-        <v>60.855329677452332</v>
+        <v>393.92896121628166</v>
       </c>
       <c r="AR26" t="s">
         <v>445</v>
@@ -10821,10 +10821,10 @@
         <v>1069</v>
       </c>
       <c r="BA26" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="BB26" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="BC26">
         <v>0.92803055709901694</v>
@@ -10895,16 +10895,16 @@
         <v>480</v>
       </c>
       <c r="Y27" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="Z27" t="s">
         <v>659</v>
       </c>
       <c r="AA27">
-        <v>0.99671990332447369</v>
+        <v>0.96994910016476243</v>
       </c>
       <c r="AB27">
-        <v>60.135105717982277</v>
+        <v>550.93316364602254</v>
       </c>
       <c r="AD27" t="s">
         <v>445</v>
@@ -10931,16 +10931,16 @@
         <v>743</v>
       </c>
       <c r="AM27" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AN27" t="s">
-        <v>655</v>
+        <v>927</v>
       </c>
       <c r="AO27">
-        <v>0.99215245657219142</v>
+        <v>0.97693095508317673</v>
       </c>
       <c r="AP27">
-        <v>143.87162950982398</v>
+        <v>422.93249014176001</v>
       </c>
       <c r="AR27" t="s">
         <v>445</v>
@@ -10967,10 +10967,10 @@
         <v>1071</v>
       </c>
       <c r="BA27" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="BB27" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="BC27">
         <v>0.99716443001648403</v>
@@ -11077,16 +11077,16 @@
         <v>745</v>
       </c>
       <c r="AM28" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="AN28" t="s">
-        <v>653</v>
+        <v>929</v>
       </c>
       <c r="AO28">
-        <v>0.9485944422668402</v>
+        <v>0.9972902611932265</v>
       </c>
       <c r="AP28">
-        <v>942.43522510793025</v>
+        <v>49.678544790847084</v>
       </c>
       <c r="AR28" t="s">
         <v>445</v>
@@ -11113,16 +11113,16 @@
         <v>1073</v>
       </c>
       <c r="BA28" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="BB28" t="s">
-        <v>660</v>
+        <v>944</v>
       </c>
       <c r="BC28">
-        <v>0.98752340562932261</v>
+        <v>0.98610600453861563</v>
       </c>
       <c r="BD28">
-        <v>896.60650808275307</v>
+        <v>913.8751780378667</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11223,16 +11223,16 @@
         <v>747</v>
       </c>
       <c r="AM29" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="AN29" t="s">
-        <v>665</v>
+        <v>680</v>
       </c>
       <c r="AO29">
-        <v>0.97043152360247686</v>
+        <v>0.98586375931635961</v>
       </c>
       <c r="AP29">
-        <v>542.08873395459034</v>
+        <v>259.16441253340616</v>
       </c>
       <c r="AR29" t="s">
         <v>445</v>
@@ -11259,16 +11259,16 @@
         <v>1075</v>
       </c>
       <c r="BA29" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="BB29" t="s">
-        <v>1171</v>
+        <v>645</v>
       </c>
       <c r="BC29">
-        <v>0.98117820630330521</v>
+        <v>0.972593868603152</v>
       </c>
       <c r="BD29">
-        <v>973.9121865380647</v>
+        <v>1078.4980341849312</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11369,16 +11369,16 @@
         <v>749</v>
       </c>
       <c r="AM30" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="AN30" t="s">
-        <v>673</v>
+        <v>646</v>
       </c>
       <c r="AO30">
-        <v>0.9922676414012731</v>
+        <v>0.98753047073573874</v>
       </c>
       <c r="AP30">
-        <v>141.75990764332545</v>
+        <v>228.60803651145704</v>
       </c>
       <c r="AR30" t="s">
         <v>445</v>
@@ -11405,16 +11405,16 @@
         <v>1077</v>
       </c>
       <c r="BA30" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="BB30" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="BC30">
-        <v>0.96413043109717189</v>
+        <v>0.97474114937745526</v>
       </c>
       <c r="BD30">
-        <v>1181.6109144661225</v>
+        <v>1052.3369967513365</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11482,7 +11482,7 @@
         <v>347</v>
       </c>
       <c r="Z31" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="AA31">
         <v>0.96307923215762514</v>
@@ -11515,16 +11515,16 @@
         <v>751</v>
       </c>
       <c r="AM31" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="AN31" t="s">
-        <v>930</v>
+        <v>646</v>
       </c>
       <c r="AO31">
-        <v>0.97950961971620221</v>
+        <v>0.96497483135850137</v>
       </c>
       <c r="AP31">
-        <v>375.65697186962575</v>
+        <v>642.12809176080782</v>
       </c>
       <c r="AR31" t="s">
         <v>445</v>
@@ -11551,16 +11551,16 @@
         <v>1079</v>
       </c>
       <c r="BA31" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="BB31" t="s">
-        <v>665</v>
+        <v>689</v>
       </c>
       <c r="BC31">
-        <v>0.93824334088191808</v>
+        <v>0.99204121948401935</v>
       </c>
       <c r="BD31">
-        <v>1497.001963588631</v>
+        <v>758.41727008090197</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11628,7 +11628,7 @@
         <v>358</v>
       </c>
       <c r="Z32" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AA32">
         <v>0.94315950804663551</v>
@@ -11661,16 +11661,16 @@
         <v>753</v>
       </c>
       <c r="AM32" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="AN32" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AO32">
-        <v>0.94721908575810376</v>
+        <v>0.953110606460702</v>
       </c>
       <c r="AP32">
-        <v>967.65009443476538</v>
+        <v>859.63888155379732</v>
       </c>
       <c r="AR32" t="s">
         <v>445</v>
@@ -11697,16 +11697,16 @@
         <v>1081</v>
       </c>
       <c r="BA32" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="BB32" t="s">
-        <v>1016</v>
+        <v>1172</v>
       </c>
       <c r="BC32">
-        <v>0.99465492794345478</v>
+        <v>0.99209673382744978</v>
       </c>
       <c r="BD32">
-        <v>592.53390652206974</v>
+        <v>754.89395975118964</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11774,7 +11774,7 @@
         <v>366</v>
       </c>
       <c r="Z33" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AA33">
         <v>0.96140892845075643</v>
@@ -11807,16 +11807,16 @@
         <v>755</v>
       </c>
       <c r="AM33" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="AN33" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="AO33">
-        <v>0.98898335230625201</v>
+        <v>0.95955011836243909</v>
       </c>
       <c r="AP33">
-        <v>201.97187438538015</v>
+        <v>741.58116335528291</v>
       </c>
       <c r="AR33" t="s">
         <v>445</v>
@@ -11843,16 +11843,16 @@
         <v>1083</v>
       </c>
       <c r="BA33" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="BB33" t="s">
-        <v>1038</v>
+        <v>668</v>
       </c>
       <c r="BC33">
-        <v>0.9580046500205861</v>
+        <v>0.9762650633688883</v>
       </c>
       <c r="BD33">
-        <v>1256.2433472491919</v>
+        <v>1033.7706446223781</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11920,7 +11920,7 @@
         <v>369</v>
       </c>
       <c r="Z34" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AA34">
         <v>0.93763052839116845</v>
@@ -11953,16 +11953,16 @@
         <v>757</v>
       </c>
       <c r="AM34" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="AN34" t="s">
-        <v>934</v>
+        <v>668</v>
       </c>
       <c r="AO34">
-        <v>0.99506178999496608</v>
+        <v>0.97935848497620392</v>
       </c>
       <c r="AP34">
-        <v>90.533850092289356</v>
+        <v>378.42777543626062</v>
       </c>
       <c r="AR34" t="s">
         <v>445</v>
@@ -11989,16 +11989,16 @@
         <v>1085</v>
       </c>
       <c r="BA34" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="BB34" t="s">
-        <v>665</v>
+        <v>1175</v>
       </c>
       <c r="BC34">
-        <v>0.91754501241076647</v>
+        <v>0.9859478284089821</v>
       </c>
       <c r="BD34">
-        <v>1749.1765987954952</v>
+        <v>915.80229055056782</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -12066,7 +12066,7 @@
         <v>367</v>
       </c>
       <c r="Z35" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AA35">
         <v>0.96169171176041801</v>
@@ -12099,16 +12099,16 @@
         <v>759</v>
       </c>
       <c r="AM35" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="AN35" t="s">
-        <v>676</v>
+        <v>648</v>
       </c>
       <c r="AO35">
-        <v>0.99493880624410824</v>
+        <v>0.97738569554252064</v>
       </c>
       <c r="AP35">
-        <v>92.7885521913487</v>
+        <v>414.59558172045399</v>
       </c>
       <c r="AR35" t="s">
         <v>445</v>
@@ -12135,16 +12135,16 @@
         <v>1087</v>
       </c>
       <c r="BA35" t="s">
+        <v>1176</v>
+      </c>
+      <c r="BB35" t="s">
         <v>1177</v>
       </c>
-      <c r="BB35" t="s">
-        <v>1178</v>
-      </c>
       <c r="BC35">
-        <v>0.98908658389363524</v>
+        <v>0.99844627758702942</v>
       </c>
       <c r="BD35">
-        <v>877.56178622921061</v>
+        <v>351.90958247653504</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -12212,7 +12212,7 @@
         <v>348</v>
       </c>
       <c r="Z36" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="AA36">
         <v>0.99511617332099966</v>
@@ -12245,16 +12245,16 @@
         <v>761</v>
       </c>
       <c r="AM36" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AN36" t="s">
-        <v>685</v>
+        <v>651</v>
       </c>
       <c r="AO36">
-        <v>0.99160044224340704</v>
+        <v>0.98739702445646216</v>
       </c>
       <c r="AP36">
-        <v>153.99189220420479</v>
+        <v>231.05455163152675</v>
       </c>
       <c r="AR36" t="s">
         <v>445</v>
@@ -12281,16 +12281,16 @@
         <v>1089</v>
       </c>
       <c r="BA36" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="BB36" t="s">
-        <v>698</v>
+        <v>944</v>
       </c>
       <c r="BC36">
-        <v>0.98725104910668715</v>
+        <v>0.99059368543056114</v>
       </c>
       <c r="BD36">
-        <v>899.92471838352765</v>
+        <v>850.28743134038859</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12358,7 +12358,7 @@
         <v>374</v>
       </c>
       <c r="Z37" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AA37">
         <v>0.98218461904404952</v>
@@ -12391,16 +12391,16 @@
         <v>763</v>
       </c>
       <c r="AM37" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="AN37" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AO37">
-        <v>0.98943214953804659</v>
+        <v>0.99755801237420683</v>
       </c>
       <c r="AP37">
-        <v>193.7439251358123</v>
+        <v>44.769773139540511</v>
       </c>
       <c r="AR37" t="s">
         <v>445</v>
@@ -12427,16 +12427,16 @@
         <v>1091</v>
       </c>
       <c r="BA37" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="BB37" t="s">
-        <v>973</v>
+        <v>944</v>
       </c>
       <c r="BC37">
-        <v>0.98942049804970167</v>
+        <v>0.97057573829724286</v>
       </c>
       <c r="BD37">
-        <v>873.49359876113442</v>
+        <v>1103.0855884119239</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12504,7 +12504,7 @@
         <v>434</v>
       </c>
       <c r="Z38" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AA38">
         <v>0.99847910710774135</v>
@@ -12537,16 +12537,16 @@
         <v>765</v>
       </c>
       <c r="AM38" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="AN38" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="AO38">
-        <v>0.99751889144721539</v>
+        <v>0.99770486090207411</v>
       </c>
       <c r="AP38">
-        <v>45.486990134384541</v>
+        <v>42.077550128640524</v>
       </c>
       <c r="AR38" t="s">
         <v>445</v>
@@ -12573,16 +12573,16 @@
         <v>1093</v>
       </c>
       <c r="BA38" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="BB38" t="s">
-        <v>1182</v>
+        <v>944</v>
       </c>
       <c r="BC38">
-        <v>0.92540139052362402</v>
+        <v>0.93603050407099908</v>
       </c>
       <c r="BD38">
-        <v>1653.4597254538478</v>
+        <v>1523.9616920683277</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12647,16 +12647,16 @@
         <v>504</v>
       </c>
       <c r="Y39" t="s">
-        <v>368</v>
+        <v>418</v>
       </c>
       <c r="Z39" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AA39">
-        <v>0.94017535716671519</v>
+        <v>0.98777287103353073</v>
       </c>
       <c r="AB39">
-        <v>1096.7851186102214</v>
+        <v>224.16403105193586</v>
       </c>
       <c r="AD39" t="s">
         <v>445</v>
@@ -12683,16 +12683,16 @@
         <v>767</v>
       </c>
       <c r="AM39" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="AN39" t="s">
-        <v>942</v>
+        <v>686</v>
       </c>
       <c r="AO39">
-        <v>0.97572899399979196</v>
+        <v>0.97818029957439945</v>
       </c>
       <c r="AP39">
-        <v>444.96844333714796</v>
+        <v>400.02784113601069</v>
       </c>
       <c r="AR39" t="s">
         <v>445</v>
@@ -12719,16 +12719,16 @@
         <v>1095</v>
       </c>
       <c r="BA39" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="BB39" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="BC39">
-        <v>0.97283922785685117</v>
+        <v>0.96501627240771926</v>
       </c>
       <c r="BD39">
-        <v>1075.5087406106959</v>
+        <v>1170.8184144992874</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12793,16 +12793,16 @@
         <v>506</v>
       </c>
       <c r="Y40" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="Z40" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="AA40">
-        <v>0.98182986571182285</v>
+        <v>0.97754100001622091</v>
       </c>
       <c r="AB40">
-        <v>333.11912861658175</v>
+        <v>411.74833303595017</v>
       </c>
       <c r="AD40" t="s">
         <v>445</v>
@@ -12832,13 +12832,13 @@
         <v>943</v>
       </c>
       <c r="AN40" t="s">
-        <v>704</v>
+        <v>944</v>
       </c>
       <c r="AO40">
-        <v>0.97620022609803814</v>
+        <v>0.95946658042945154</v>
       </c>
       <c r="AP40">
-        <v>436.32918820263421</v>
+        <v>743.11269212672175</v>
       </c>
       <c r="AR40" t="s">
         <v>445</v>
@@ -12865,16 +12865,16 @@
         <v>1097</v>
       </c>
       <c r="BA40" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="BB40" t="s">
-        <v>665</v>
+        <v>972</v>
       </c>
       <c r="BC40">
-        <v>0.95074557504943547</v>
+        <v>0.99624960324149381</v>
       </c>
       <c r="BD40">
-        <v>1344.6830773143784</v>
+        <v>491.32518093986187</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12939,16 +12939,16 @@
         <v>508</v>
       </c>
       <c r="Y41" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="Z41" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="AA41">
-        <v>0.99024931522063975</v>
+        <v>0.95401962289287812</v>
       </c>
       <c r="AB41">
-        <v>178.76255428827085</v>
+        <v>842.97358029723534</v>
       </c>
       <c r="AD41" t="s">
         <v>445</v>
@@ -12975,16 +12975,16 @@
         <v>771</v>
       </c>
       <c r="AM41" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="AN41" t="s">
-        <v>945</v>
+        <v>657</v>
       </c>
       <c r="AO41">
-        <v>0.98607591956620455</v>
+        <v>0.96103827796400987</v>
       </c>
       <c r="AP41">
-        <v>255.27480795291643</v>
+        <v>714.29823732648526</v>
       </c>
       <c r="AR41" t="s">
         <v>445</v>
@@ -13011,16 +13011,16 @@
         <v>1099</v>
       </c>
       <c r="BA41" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="BB41" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="BC41">
-        <v>0.9534536251465805</v>
+        <v>0.96835427347694081</v>
       </c>
       <c r="BD41">
-        <v>1311.6900002974942</v>
+        <v>1130.1504348059382</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -13085,16 +13085,16 @@
         <v>510</v>
       </c>
       <c r="Y42" t="s">
-        <v>411</v>
+        <v>356</v>
       </c>
       <c r="Z42" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AA42">
-        <v>0.99501647162473339</v>
+        <v>0.98495178422440233</v>
       </c>
       <c r="AB42">
-        <v>91.364686879888396</v>
+        <v>275.88395588595779</v>
       </c>
       <c r="AD42" t="s">
         <v>445</v>
@@ -13124,13 +13124,13 @@
         <v>946</v>
       </c>
       <c r="AN42" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="AO42">
-        <v>0.94516861039769784</v>
+        <v>0.96185713019776531</v>
       </c>
       <c r="AP42">
-        <v>1005.2421427088731</v>
+        <v>699.28594637430331</v>
       </c>
       <c r="AR42" t="s">
         <v>445</v>
@@ -13157,16 +13157,16 @@
         <v>1101</v>
       </c>
       <c r="BA42" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="BB42" t="s">
-        <v>973</v>
+        <v>1185</v>
       </c>
       <c r="BC42">
-        <v>0.98610600453861563</v>
+        <v>0.97396073370136893</v>
       </c>
       <c r="BD42">
-        <v>913.8751780378667</v>
+        <v>1061.8450610716552</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -13231,16 +13231,16 @@
         <v>512</v>
       </c>
       <c r="Y43" t="s">
-        <v>437</v>
+        <v>378</v>
       </c>
       <c r="Z43" t="s">
-        <v>671</v>
+        <v>648</v>
       </c>
       <c r="AA43">
-        <v>0.99545036495775863</v>
+        <v>0.97886062539501351</v>
       </c>
       <c r="AB43">
-        <v>83.409975774425632</v>
+        <v>387.55520109141952</v>
       </c>
       <c r="AD43" t="s">
         <v>445</v>
@@ -13270,13 +13270,13 @@
         <v>947</v>
       </c>
       <c r="AN43" t="s">
-        <v>948</v>
+        <v>668</v>
       </c>
       <c r="AO43">
-        <v>0.94231963623506931</v>
+        <v>0.95931345925264233</v>
       </c>
       <c r="AP43">
-        <v>1057.4733356903953</v>
+        <v>745.91991370155699</v>
       </c>
       <c r="AR43" t="s">
         <v>445</v>
@@ -13303,16 +13303,16 @@
         <v>1103</v>
       </c>
       <c r="BA43" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="BB43" t="s">
-        <v>663</v>
+        <v>944</v>
       </c>
       <c r="BC43">
-        <v>0.972593868603152</v>
+        <v>0.97654176188453468</v>
       </c>
       <c r="BD43">
-        <v>1078.4980341849312</v>
+        <v>1030.3995343734193</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13377,16 +13377,16 @@
         <v>514</v>
       </c>
       <c r="Y44" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="Z44" t="s">
-        <v>672</v>
+        <v>648</v>
       </c>
       <c r="AA44">
-        <v>0.97969590283269214</v>
+        <v>0.99386727950885501</v>
       </c>
       <c r="AB44">
-        <v>372.24178140064373</v>
+        <v>112.43320900432452</v>
       </c>
       <c r="AD44" t="s">
         <v>445</v>
@@ -13413,16 +13413,16 @@
         <v>777</v>
       </c>
       <c r="AM44" t="s">
+        <v>948</v>
+      </c>
+      <c r="AN44" t="s">
         <v>949</v>
       </c>
-      <c r="AN44" t="s">
-        <v>649</v>
-      </c>
       <c r="AO44">
-        <v>0.97832027217029349</v>
+        <v>0.98333626289132436</v>
       </c>
       <c r="AP44">
-        <v>397.46167687795332</v>
+        <v>305.50184699238736</v>
       </c>
       <c r="AR44" t="s">
         <v>445</v>
@@ -13449,16 +13449,16 @@
         <v>1105</v>
       </c>
       <c r="BA44" t="s">
+        <v>1187</v>
+      </c>
+      <c r="BB44" t="s">
         <v>1188</v>
       </c>
-      <c r="BB44" t="s">
-        <v>665</v>
-      </c>
       <c r="BC44">
-        <v>0.97474114937745526</v>
+        <v>0.99180629119732955</v>
       </c>
       <c r="BD44">
-        <v>1052.3369967513365</v>
+        <v>773.32738534281725</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13523,16 +13523,16 @@
         <v>516</v>
       </c>
       <c r="Y45" t="s">
-        <v>415</v>
+        <v>371</v>
       </c>
       <c r="Z45" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="AA45">
-        <v>0.98086220977655469</v>
+        <v>0.96488803122020605</v>
       </c>
       <c r="AB45">
-        <v>350.85948742983044</v>
+        <v>643.71942762955541</v>
       </c>
       <c r="AD45" t="s">
         <v>445</v>
@@ -13565,10 +13565,10 @@
         <v>951</v>
       </c>
       <c r="AO45">
-        <v>0.99484431329617862</v>
+        <v>0.99580424242160948</v>
       </c>
       <c r="AP45">
-        <v>94.520922903391252</v>
+        <v>76.922222270493648</v>
       </c>
       <c r="AR45" t="s">
         <v>445</v>
@@ -13598,13 +13598,13 @@
         <v>1189</v>
       </c>
       <c r="BB45" t="s">
-        <v>659</v>
+        <v>1190</v>
       </c>
       <c r="BC45">
-        <v>0.99204121948401935</v>
+        <v>0.9784511409772424</v>
       </c>
       <c r="BD45">
-        <v>758.41727008090197</v>
+        <v>1007.136932427263</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13669,16 +13669,16 @@
         <v>518</v>
       </c>
       <c r="Y46" t="s">
-        <v>390</v>
+        <v>436</v>
       </c>
       <c r="Z46" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="AA46">
-        <v>0.99377506386421921</v>
+        <v>0.99588620223113744</v>
       </c>
       <c r="AB46">
-        <v>114.12382915598114</v>
+        <v>75.419625762480621</v>
       </c>
       <c r="AD46" t="s">
         <v>445</v>
@@ -13708,13 +13708,13 @@
         <v>952</v>
       </c>
       <c r="AN46" t="s">
-        <v>675</v>
+        <v>953</v>
       </c>
       <c r="AO46">
-        <v>0.97273741219297172</v>
+        <v>0.99143965884476559</v>
       </c>
       <c r="AP46">
-        <v>499.8141097955185</v>
+        <v>156.93958784596441</v>
       </c>
       <c r="AR46" t="s">
         <v>445</v>
@@ -13741,16 +13741,16 @@
         <v>1109</v>
       </c>
       <c r="BA46" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="BB46" t="s">
-        <v>973</v>
+        <v>1192</v>
       </c>
       <c r="BC46">
-        <v>0.99059368543056114</v>
+        <v>0.9955677970684097</v>
       </c>
       <c r="BD46">
-        <v>850.28743134038859</v>
+        <v>534.59714605826571</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13815,16 +13815,16 @@
         <v>520</v>
       </c>
       <c r="Y47" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="Z47" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="AA47">
-        <v>0.95105540198711702</v>
+        <v>0.99515580458889907</v>
       </c>
       <c r="AB47">
-        <v>897.31763023618794</v>
+        <v>88.81024920351615</v>
       </c>
       <c r="AD47" t="s">
         <v>445</v>
@@ -13851,16 +13851,16 @@
         <v>783</v>
       </c>
       <c r="AM47" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="AN47" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AO47">
-        <v>0.97984247759827614</v>
+        <v>0.9966806183812299</v>
       </c>
       <c r="AP47">
-        <v>369.55457736493832</v>
+        <v>60.855329677452332</v>
       </c>
       <c r="AR47" t="s">
         <v>445</v>
@@ -13887,16 +13887,16 @@
         <v>1111</v>
       </c>
       <c r="BA47" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="BB47" t="s">
-        <v>973</v>
+        <v>680</v>
       </c>
       <c r="BC47">
-        <v>0.97057573829724286</v>
+        <v>0.98725104910668715</v>
       </c>
       <c r="BD47">
-        <v>1103.0855884119239</v>
+        <v>899.92471838352765</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13961,16 +13961,16 @@
         <v>522</v>
       </c>
       <c r="Y48" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="Z48" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="AA48">
-        <v>0.99131962187405476</v>
+        <v>0.96473247588547761</v>
       </c>
       <c r="AB48">
-        <v>159.14026564233004</v>
+        <v>646.57127543291119</v>
       </c>
       <c r="AD48" t="s">
         <v>445</v>
@@ -13997,16 +13997,16 @@
         <v>785</v>
       </c>
       <c r="AM48" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="AN48" t="s">
-        <v>651</v>
+        <v>686</v>
       </c>
       <c r="AO48">
-        <v>0.99109308381957362</v>
+        <v>0.99215245657219142</v>
       </c>
       <c r="AP48">
-        <v>163.29346330781715</v>
+        <v>143.87162950982398</v>
       </c>
       <c r="AR48" t="s">
         <v>445</v>
@@ -14033,16 +14033,16 @@
         <v>1113</v>
       </c>
       <c r="BA48" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="BB48" t="s">
-        <v>973</v>
+        <v>944</v>
       </c>
       <c r="BC48">
-        <v>0.93603050407099908</v>
+        <v>0.98942049804970167</v>
       </c>
       <c r="BD48">
-        <v>1523.9616920683277</v>
+        <v>873.49359876113442</v>
       </c>
     </row>
     <row r="49" spans="2:56">
@@ -14107,16 +14107,16 @@
         <v>524</v>
       </c>
       <c r="Y49" t="s">
-        <v>418</v>
+        <v>354</v>
       </c>
       <c r="Z49" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="AA49">
-        <v>0.98777287103353073</v>
+        <v>0.9580334555499519</v>
       </c>
       <c r="AB49">
-        <v>224.16403105193586</v>
+        <v>769.38664825088097</v>
       </c>
       <c r="AD49" t="s">
         <v>445</v>
@@ -14143,16 +14143,16 @@
         <v>787</v>
       </c>
       <c r="AM49" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="AN49" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
       <c r="AO49">
-        <v>0.9937244183974584</v>
+        <v>0.9485944422668402</v>
       </c>
       <c r="AP49">
-        <v>115.0523293799298</v>
+        <v>942.43522510793025</v>
       </c>
       <c r="AR49" t="s">
         <v>445</v>
@@ -14179,16 +14179,16 @@
         <v>1115</v>
       </c>
       <c r="BA49" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="BB49" t="s">
-        <v>665</v>
+        <v>1196</v>
       </c>
       <c r="BC49">
-        <v>0.96501627240771926</v>
+        <v>0.92540139052362402</v>
       </c>
       <c r="BD49">
-        <v>1170.8184144992874</v>
+        <v>1653.4597254538478</v>
       </c>
     </row>
     <row r="50" spans="2:56">
@@ -14253,16 +14253,16 @@
         <v>526</v>
       </c>
       <c r="Y50" t="s">
-        <v>385</v>
+        <v>441</v>
       </c>
       <c r="Z50" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="AA50">
-        <v>0.97754100001622091</v>
+        <v>0.98447946182885371</v>
       </c>
       <c r="AB50">
-        <v>411.74833303595017</v>
+        <v>284.54319980434889</v>
       </c>
       <c r="AD50" t="s">
         <v>445</v>
@@ -14289,16 +14289,16 @@
         <v>789</v>
       </c>
       <c r="AM50" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AN50" t="s">
-        <v>958</v>
+        <v>648</v>
       </c>
       <c r="AO50">
-        <v>0.93186769579006068</v>
+        <v>0.97043152360247686</v>
       </c>
       <c r="AP50">
-        <v>1249.0922438488865</v>
+        <v>542.08873395459034</v>
       </c>
       <c r="AR50" t="s">
         <v>445</v>
@@ -14325,16 +14325,16 @@
         <v>1117</v>
       </c>
       <c r="BA50" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="BB50" t="s">
-        <v>1038</v>
+        <v>668</v>
       </c>
       <c r="BC50">
-        <v>0.99624960324149381</v>
+        <v>0.97283922785685117</v>
       </c>
       <c r="BD50">
-        <v>491.32518093986187</v>
+        <v>1075.5087406106959</v>
       </c>
     </row>
     <row r="51" spans="2:56">
@@ -14399,16 +14399,16 @@
         <v>528</v>
       </c>
       <c r="Y51" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="Z51" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="AA51">
-        <v>0.95401962289287812</v>
+        <v>0.94017535716671519</v>
       </c>
       <c r="AB51">
-        <v>842.97358029723534</v>
+        <v>1096.7851186102214</v>
       </c>
       <c r="AD51" t="s">
         <v>445</v>
@@ -14438,13 +14438,13 @@
         <v>959</v>
       </c>
       <c r="AN51" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="AO51">
-        <v>0.94664324606770156</v>
+        <v>0.9922676414012731</v>
       </c>
       <c r="AP51">
-        <v>978.20715542547146</v>
+        <v>141.75990764332545</v>
       </c>
       <c r="AR51" t="s">
         <v>445</v>
@@ -14471,16 +14471,16 @@
         <v>1119</v>
       </c>
       <c r="BA51" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="BB51" t="s">
-        <v>675</v>
+        <v>648</v>
       </c>
       <c r="BC51">
-        <v>0.96835427347694081</v>
+        <v>0.95074557504943547</v>
       </c>
       <c r="BD51">
-        <v>1130.1504348059382</v>
+        <v>1344.6830773143784</v>
       </c>
     </row>
     <row r="52" spans="2:56">
@@ -14545,16 +14545,16 @@
         <v>530</v>
       </c>
       <c r="Y52" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Z52" t="s">
-        <v>649</v>
+        <v>668</v>
       </c>
       <c r="AA52">
-        <v>0.98495178422440233</v>
+        <v>0.98182986571182285</v>
       </c>
       <c r="AB52">
-        <v>275.88395588595779</v>
+        <v>333.11912861658175</v>
       </c>
       <c r="AD52" t="s">
         <v>445</v>
@@ -14584,13 +14584,13 @@
         <v>960</v>
       </c>
       <c r="AN52" t="s">
-        <v>649</v>
+        <v>681</v>
       </c>
       <c r="AO52">
-        <v>0.96085367337953664</v>
+        <v>0.98256179218990303</v>
       </c>
       <c r="AP52">
-        <v>717.68265470849451</v>
+        <v>319.70047651844521</v>
       </c>
       <c r="AR52" t="s">
         <v>445</v>
@@ -14617,16 +14617,16 @@
         <v>1121</v>
       </c>
       <c r="BA52" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="BB52" t="s">
-        <v>1197</v>
+        <v>678</v>
       </c>
       <c r="BC52">
-        <v>0.97396073370136893</v>
+        <v>0.9534536251465805</v>
       </c>
       <c r="BD52">
-        <v>1061.8450610716552</v>
+        <v>1311.6900002974942</v>
       </c>
     </row>
     <row r="53" spans="2:56">
@@ -14691,16 +14691,16 @@
         <v>532</v>
       </c>
       <c r="Y53" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="Z53" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="AA53">
-        <v>0.97886062539501351</v>
+        <v>0.99024931522063975</v>
       </c>
       <c r="AB53">
-        <v>387.55520109141952</v>
+        <v>178.76255428827085</v>
       </c>
       <c r="AD53" t="s">
         <v>445</v>
@@ -14730,13 +14730,13 @@
         <v>961</v>
       </c>
       <c r="AN53" t="s">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="AO53">
-        <v>0.94667937507615152</v>
+        <v>0.97344873028830825</v>
       </c>
       <c r="AP53">
-        <v>977.54479027055595</v>
+        <v>486.77327804768265</v>
       </c>
       <c r="AR53" t="s">
         <v>445</v>
@@ -14763,10 +14763,10 @@
         <v>1123</v>
       </c>
       <c r="BA53" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="BB53" t="s">
-        <v>1001</v>
+        <v>939</v>
       </c>
       <c r="BC53">
         <v>0.98701879075230647</v>
@@ -14837,16 +14837,16 @@
         <v>534</v>
       </c>
       <c r="Y54" t="s">
-        <v>364</v>
+        <v>411</v>
       </c>
       <c r="Z54" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="AA54">
-        <v>0.99386727950885501</v>
+        <v>0.99501647162473339</v>
       </c>
       <c r="AB54">
-        <v>112.43320900432452</v>
+        <v>91.364686879888396</v>
       </c>
       <c r="AD54" t="s">
         <v>445</v>
@@ -14876,13 +14876,13 @@
         <v>962</v>
       </c>
       <c r="AN54" t="s">
-        <v>649</v>
+        <v>963</v>
       </c>
       <c r="AO54">
-        <v>0.99485429484434884</v>
+        <v>0.94726945791757955</v>
       </c>
       <c r="AP54">
-        <v>94.33792785360508</v>
+        <v>966.72660484437438</v>
       </c>
       <c r="AR54" t="s">
         <v>445</v>
@@ -14909,10 +14909,10 @@
         <v>1125</v>
       </c>
       <c r="BA54" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="BB54" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="BC54">
         <v>0.98556353666457686</v>
@@ -14983,16 +14983,16 @@
         <v>536</v>
       </c>
       <c r="Y55" t="s">
-        <v>371</v>
+        <v>437</v>
       </c>
       <c r="Z55" t="s">
         <v>675</v>
       </c>
       <c r="AA55">
-        <v>0.96488803122020605</v>
+        <v>0.99545036495775863</v>
       </c>
       <c r="AB55">
-        <v>643.71942762955541</v>
+        <v>83.409975774425632</v>
       </c>
       <c r="AD55" t="s">
         <v>445</v>
@@ -15019,16 +15019,16 @@
         <v>799</v>
       </c>
       <c r="AM55" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AN55" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AO55">
-        <v>0.99104002253663459</v>
+        <v>0.99721814870334879</v>
       </c>
       <c r="AP55">
-        <v>164.26625349503158</v>
+        <v>51.000607105273012</v>
       </c>
       <c r="AR55" t="s">
         <v>445</v>
@@ -15055,10 +15055,10 @@
         <v>1127</v>
       </c>
       <c r="BA55" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="BB55" t="s">
-        <v>973</v>
+        <v>944</v>
       </c>
       <c r="BC55">
         <v>0.98542037014322215</v>
@@ -15129,16 +15129,16 @@
         <v>538</v>
       </c>
       <c r="Y56" t="s">
-        <v>436</v>
+        <v>386</v>
       </c>
       <c r="Z56" t="s">
         <v>676</v>
       </c>
       <c r="AA56">
-        <v>0.99588620223113744</v>
+        <v>0.98507000954579316</v>
       </c>
       <c r="AB56">
-        <v>75.419625762480621</v>
+        <v>273.71649166045961</v>
       </c>
       <c r="AD56" t="s">
         <v>445</v>
@@ -15165,16 +15165,16 @@
         <v>801</v>
       </c>
       <c r="AM56" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AN56" t="s">
-        <v>966</v>
+        <v>669</v>
       </c>
       <c r="AO56">
-        <v>0.98218033156447682</v>
+        <v>0.9965750017909164</v>
       </c>
       <c r="AP56">
-        <v>326.69392131792426</v>
+        <v>62.791633833199988</v>
       </c>
       <c r="AR56" t="s">
         <v>445</v>
@@ -15201,10 +15201,10 @@
         <v>1129</v>
       </c>
       <c r="BA56" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="BB56" t="s">
-        <v>910</v>
+        <v>965</v>
       </c>
       <c r="BC56">
         <v>0.99613275225602693</v>
@@ -15275,16 +15275,16 @@
         <v>540</v>
       </c>
       <c r="Y57" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="Z57" t="s">
-        <v>644</v>
+        <v>677</v>
       </c>
       <c r="AA57">
-        <v>0.94904572806075094</v>
+        <v>0.95257490531108058</v>
       </c>
       <c r="AB57">
-        <v>934.16165221956703</v>
+        <v>869.46006929685575</v>
       </c>
       <c r="AD57" t="s">
         <v>445</v>
@@ -15314,13 +15314,13 @@
         <v>967</v>
       </c>
       <c r="AN57" t="s">
-        <v>968</v>
+        <v>645</v>
       </c>
       <c r="AO57">
-        <v>0.99585887269839302</v>
+        <v>0.95226889215734378</v>
       </c>
       <c r="AP57">
-        <v>75.920667196127695</v>
+        <v>875.07031044869723</v>
       </c>
       <c r="AR57" t="s">
         <v>445</v>
@@ -15347,16 +15347,16 @@
         <v>1131</v>
       </c>
       <c r="BA57" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="BB57" t="s">
-        <v>698</v>
+        <v>660</v>
       </c>
       <c r="BC57">
-        <v>0.97261625181972589</v>
+        <v>0.98752340562932261</v>
       </c>
       <c r="BD57">
-        <v>1078.2253319963402</v>
+        <v>896.60650808275307</v>
       </c>
     </row>
     <row r="58" spans="2:56">
@@ -15421,16 +15421,16 @@
         <v>542</v>
       </c>
       <c r="Y58" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="Z58" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AA58">
-        <v>0.94779673241739959</v>
+        <v>0.9934232231965805</v>
       </c>
       <c r="AB58">
-        <v>957.05990568100776</v>
+        <v>120.5742413960235</v>
       </c>
       <c r="AD58" t="s">
         <v>445</v>
@@ -15457,16 +15457,16 @@
         <v>805</v>
       </c>
       <c r="AM58" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="AN58" t="s">
-        <v>970</v>
+        <v>668</v>
       </c>
       <c r="AO58">
-        <v>0.99612820180322659</v>
+        <v>0.98244678792215867</v>
       </c>
       <c r="AP58">
-        <v>70.982966940846623</v>
+        <v>321.80888809375716</v>
       </c>
       <c r="AR58" t="s">
         <v>445</v>
@@ -15493,16 +15493,16 @@
         <v>1133</v>
       </c>
       <c r="BA58" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="BB58" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="BC58">
-        <v>0.99257145555712289</v>
+        <v>0.98117820630330521</v>
       </c>
       <c r="BD58">
-        <v>724.76495397460064</v>
+        <v>973.9121865380647</v>
       </c>
     </row>
     <row r="59" spans="2:56">
@@ -15567,16 +15567,16 @@
         <v>544</v>
       </c>
       <c r="Y59" t="s">
-        <v>440</v>
+        <v>372</v>
       </c>
       <c r="Z59" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AA59">
-        <v>0.96846296248311359</v>
+        <v>0.98371921732749934</v>
       </c>
       <c r="AB59">
-        <v>578.17902114291837</v>
+        <v>298.48101566251137</v>
       </c>
       <c r="AD59" t="s">
         <v>445</v>
@@ -15603,16 +15603,16 @@
         <v>807</v>
       </c>
       <c r="AM59" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="AN59" t="s">
-        <v>655</v>
+        <v>970</v>
       </c>
       <c r="AO59">
-        <v>0.97818029957439945</v>
+        <v>0.99244907456015963</v>
       </c>
       <c r="AP59">
-        <v>400.02784113601069</v>
+        <v>138.43363306374022</v>
       </c>
       <c r="AR59" t="s">
         <v>445</v>
@@ -15639,16 +15639,16 @@
         <v>1135</v>
       </c>
       <c r="BA59" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="BB59" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="BC59">
-        <v>0.96412973603590302</v>
+        <v>0.96413043109717189</v>
       </c>
       <c r="BD59">
-        <v>1181.6193826292476</v>
+        <v>1181.6109144661225</v>
       </c>
     </row>
     <row r="60" spans="2:56">
@@ -15713,16 +15713,16 @@
         <v>546</v>
       </c>
       <c r="Y60" t="s">
-        <v>400</v>
+        <v>442</v>
       </c>
       <c r="Z60" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AA60">
-        <v>0.99564253113732704</v>
+        <v>0.98946891329754838</v>
       </c>
       <c r="AB60">
-        <v>79.886929149003976</v>
+        <v>193.0699228782787</v>
       </c>
       <c r="AD60" t="s">
         <v>445</v>
@@ -15749,16 +15749,16 @@
         <v>809</v>
       </c>
       <c r="AM60" t="s">
+        <v>971</v>
+      </c>
+      <c r="AN60" t="s">
         <v>972</v>
       </c>
-      <c r="AN60" t="s">
-        <v>973</v>
-      </c>
       <c r="AO60">
-        <v>0.95946658042945154</v>
+        <v>0.99706791078062507</v>
       </c>
       <c r="AP60">
-        <v>743.11269212672175</v>
+        <v>53.754969021872945</v>
       </c>
       <c r="AR60" t="s">
         <v>445</v>
@@ -15785,16 +15785,16 @@
         <v>1137</v>
       </c>
       <c r="BA60" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="BB60" t="s">
-        <v>1207</v>
+        <v>648</v>
       </c>
       <c r="BC60">
-        <v>0.99566455794863251</v>
+        <v>0.93824334088191808</v>
       </c>
       <c r="BD60">
-        <v>528.4560555267874</v>
+        <v>1497.001963588631</v>
       </c>
     </row>
     <row r="61" spans="2:56">
@@ -15859,16 +15859,16 @@
         <v>548</v>
       </c>
       <c r="Y61" t="s">
-        <v>353</v>
+        <v>421</v>
       </c>
       <c r="Z61" t="s">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="AA61">
-        <v>0.95915670695527311</v>
+        <v>0.99042712787144371</v>
       </c>
       <c r="AB61">
-        <v>748.79370581999342</v>
+        <v>175.50265569019879</v>
       </c>
       <c r="AD61" t="s">
         <v>445</v>
@@ -15895,16 +15895,16 @@
         <v>811</v>
       </c>
       <c r="AM61" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="AN61" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="AO61">
-        <v>0.96103827796400987</v>
+        <v>0.99160044224340704</v>
       </c>
       <c r="AP61">
-        <v>714.29823732648526</v>
+        <v>153.99189220420479</v>
       </c>
       <c r="AR61" t="s">
         <v>445</v>
@@ -15931,16 +15931,16 @@
         <v>1139</v>
       </c>
       <c r="BA61" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="BB61" t="s">
-        <v>675</v>
+        <v>986</v>
       </c>
       <c r="BC61">
-        <v>0.9524344319526965</v>
+        <v>0.99465492794345478</v>
       </c>
       <c r="BD61">
-        <v>1324.1071707096473</v>
+        <v>592.53390652206974</v>
       </c>
     </row>
     <row r="62" spans="2:56">
@@ -16005,16 +16005,16 @@
         <v>550</v>
       </c>
       <c r="Y62" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="Z62" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AA62">
-        <v>0.98266638110143478</v>
+        <v>0.98458760722006711</v>
       </c>
       <c r="AB62">
-        <v>317.78301314036179</v>
+        <v>282.56053429877028</v>
       </c>
       <c r="AD62" t="s">
         <v>445</v>
@@ -16041,16 +16041,16 @@
         <v>813</v>
       </c>
       <c r="AM62" t="s">
+        <v>974</v>
+      </c>
+      <c r="AN62" t="s">
         <v>975</v>
       </c>
-      <c r="AN62" t="s">
-        <v>663</v>
-      </c>
       <c r="AO62">
-        <v>0.96185713019776531</v>
+        <v>0.98943214953804659</v>
       </c>
       <c r="AP62">
-        <v>699.28594637430331</v>
+        <v>193.7439251358123</v>
       </c>
       <c r="AR62" t="s">
         <v>445</v>
@@ -16077,16 +16077,16 @@
         <v>1141</v>
       </c>
       <c r="BA62" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="BB62" t="s">
-        <v>1210</v>
+        <v>972</v>
       </c>
       <c r="BC62">
-        <v>0.98797961821726321</v>
+        <v>0.9580046500205861</v>
       </c>
       <c r="BD62">
-        <v>891.04831805300933</v>
+        <v>1256.2433472491919</v>
       </c>
     </row>
     <row r="63" spans="2:56">
@@ -16151,16 +16151,16 @@
         <v>552</v>
       </c>
       <c r="Y63" t="s">
-        <v>422</v>
+        <v>388</v>
       </c>
       <c r="Z63" t="s">
-        <v>680</v>
+        <v>645</v>
       </c>
       <c r="AA63">
-        <v>0.99830013108627691</v>
+        <v>0.97454833391525864</v>
       </c>
       <c r="AB63">
-        <v>31.164263418257661</v>
+        <v>466.6138782202575</v>
       </c>
       <c r="AD63" t="s">
         <v>445</v>
@@ -16190,13 +16190,13 @@
         <v>976</v>
       </c>
       <c r="AN63" t="s">
-        <v>649</v>
+        <v>977</v>
       </c>
       <c r="AO63">
-        <v>0.95931345925264233</v>
+        <v>0.99751889144721539</v>
       </c>
       <c r="AP63">
-        <v>745.91991370155699</v>
+        <v>45.486990134384541</v>
       </c>
     </row>
     <row r="64" spans="2:56">
@@ -16261,16 +16261,16 @@
         <v>554</v>
       </c>
       <c r="Y64" t="s">
-        <v>424</v>
+        <v>351</v>
       </c>
       <c r="Z64" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="AA64">
-        <v>0.99408275357961784</v>
+        <v>0.95322333844045537</v>
       </c>
       <c r="AB64">
-        <v>108.48285104034026</v>
+        <v>857.57212859165099</v>
       </c>
       <c r="AD64" t="s">
         <v>445</v>
@@ -16297,16 +16297,16 @@
         <v>817</v>
       </c>
       <c r="AM64" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="AN64" t="s">
-        <v>964</v>
+        <v>979</v>
       </c>
       <c r="AO64">
-        <v>0.98333626289132436</v>
+        <v>0.97572899399979196</v>
       </c>
       <c r="AP64">
-        <v>305.50184699238736</v>
+        <v>444.96844333714796</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -16371,16 +16371,16 @@
         <v>556</v>
       </c>
       <c r="Y65" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="Z65" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="AA65">
-        <v>0.9719447908127189</v>
+        <v>0.97321507838078658</v>
       </c>
       <c r="AB65">
-        <v>514.34550176681955</v>
+        <v>491.05689635224547</v>
       </c>
       <c r="AD65" t="s">
         <v>445</v>
@@ -16407,16 +16407,16 @@
         <v>819</v>
       </c>
       <c r="AM65" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="AN65" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="AO65">
-        <v>0.99580424242160948</v>
+        <v>0.99423423237135644</v>
       </c>
       <c r="AP65">
-        <v>76.922222270493648</v>
+        <v>105.70573985846545</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -16481,16 +16481,16 @@
         <v>558</v>
       </c>
       <c r="Y66" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="Z66" t="s">
-        <v>683</v>
+        <v>648</v>
       </c>
       <c r="AA66">
-        <v>0.99655071603273171</v>
+        <v>0.98581703135158405</v>
       </c>
       <c r="AB66">
-        <v>63.236872733251452</v>
+        <v>260.02109188762591</v>
       </c>
       <c r="AD66" t="s">
         <v>445</v>
@@ -16517,16 +16517,16 @@
         <v>821</v>
       </c>
       <c r="AM66" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="AN66" t="s">
-        <v>981</v>
+        <v>671</v>
       </c>
       <c r="AO66">
-        <v>0.99143965884476559</v>
+        <v>0.96634981065643422</v>
       </c>
       <c r="AP66">
-        <v>156.93958784596441</v>
+        <v>616.9201379653731</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -16591,16 +16591,16 @@
         <v>560</v>
       </c>
       <c r="Y67" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="Z67" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AA67">
-        <v>0.95110913617470227</v>
+        <v>0.97542624087094398</v>
       </c>
       <c r="AB67">
-        <v>896.33250346379077</v>
+        <v>450.51891736602602</v>
       </c>
       <c r="AD67" t="s">
         <v>445</v>
@@ -16627,16 +16627,16 @@
         <v>823</v>
       </c>
       <c r="AM67" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AN67" t="s">
-        <v>656</v>
+        <v>984</v>
       </c>
       <c r="AO67">
-        <v>0.9643711256064017</v>
+        <v>0.99393164723700467</v>
       </c>
       <c r="AP67">
-        <v>653.19603054930235</v>
+        <v>111.25313398824829</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -16701,16 +16701,16 @@
         <v>562</v>
       </c>
       <c r="Y68" t="s">
-        <v>357</v>
+        <v>405</v>
       </c>
       <c r="Z68" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="AA68">
-        <v>0.96488357195289265</v>
+        <v>0.99745350130137034</v>
       </c>
       <c r="AB68">
-        <v>643.80118086363541</v>
+        <v>46.685809474876969</v>
       </c>
       <c r="AD68" t="s">
         <v>445</v>
@@ -16737,16 +16737,16 @@
         <v>825</v>
       </c>
       <c r="AM68" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="AN68" t="s">
-        <v>665</v>
+        <v>986</v>
       </c>
       <c r="AO68">
-        <v>0.99099266826252508</v>
+        <v>0.99746342019371192</v>
       </c>
       <c r="AP68">
-        <v>165.13441518704016</v>
+        <v>46.503963115281117</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -16811,16 +16811,16 @@
         <v>564</v>
       </c>
       <c r="Y69" t="s">
-        <v>350</v>
+        <v>443</v>
       </c>
       <c r="Z69" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AA69">
-        <v>0.99397024960358282</v>
+        <v>0.98101450166571025</v>
       </c>
       <c r="AB69">
-        <v>110.54542393431565</v>
+        <v>348.06746946197933</v>
       </c>
       <c r="AD69" t="s">
         <v>445</v>
@@ -16847,16 +16847,16 @@
         <v>827</v>
       </c>
       <c r="AM69" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="AN69" t="s">
-        <v>677</v>
+        <v>988</v>
       </c>
       <c r="AO69">
-        <v>0.96623363784081273</v>
+        <v>0.99690141662376341</v>
       </c>
       <c r="AP69">
-        <v>619.04997291843438</v>
+        <v>56.80736189767017</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -16921,16 +16921,16 @@
         <v>566</v>
       </c>
       <c r="Y70" t="s">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="Z70" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="AA70">
-        <v>0.98138635372944616</v>
+        <v>0.99489296223435719</v>
       </c>
       <c r="AB70">
-        <v>341.25018162681971</v>
+        <v>93.629025703450537</v>
       </c>
       <c r="AD70" t="s">
         <v>445</v>
@@ -16957,16 +16957,16 @@
         <v>829</v>
       </c>
       <c r="AM70" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="AN70" t="s">
-        <v>986</v>
+        <v>686</v>
       </c>
       <c r="AO70">
-        <v>0.99573205734141002</v>
+        <v>0.98250131854428446</v>
       </c>
       <c r="AP70">
-        <v>78.245615407483584</v>
+        <v>320.80916002145239</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17031,16 +17031,16 @@
         <v>568</v>
       </c>
       <c r="Y71" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="Z71" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AA71">
-        <v>0.99502756316390695</v>
+        <v>0.99705259621301434</v>
       </c>
       <c r="AB71">
-        <v>91.161341995039152</v>
+        <v>54.035736094736372</v>
       </c>
       <c r="AD71" t="s">
         <v>445</v>
@@ -17067,16 +17067,16 @@
         <v>831</v>
       </c>
       <c r="AM71" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="AN71" t="s">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="AO71">
-        <v>0.93728012376790604</v>
+        <v>0.94941329297783439</v>
       </c>
       <c r="AP71">
-        <v>1149.8643975883897</v>
+        <v>927.42296207303548</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17141,16 +17141,16 @@
         <v>570</v>
       </c>
       <c r="Y72" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="Z72" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AA72">
-        <v>0.99219726142231079</v>
+        <v>0.98826693080891115</v>
       </c>
       <c r="AB72">
-        <v>143.05020725763492</v>
+        <v>215.10626850329641</v>
       </c>
       <c r="AD72" t="s">
         <v>445</v>
@@ -17177,16 +17177,16 @@
         <v>833</v>
       </c>
       <c r="AM72" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="AN72" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AO72">
-        <v>0.97740985609297437</v>
+        <v>0.94697941545710573</v>
       </c>
       <c r="AP72">
-        <v>414.15263829547018</v>
+        <v>972.0440499530622</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -17251,16 +17251,16 @@
         <v>572</v>
       </c>
       <c r="Y73" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="Z73" t="s">
-        <v>688</v>
+        <v>646</v>
       </c>
       <c r="AA73">
-        <v>0.99809443707900702</v>
+        <v>0.97618980314151516</v>
       </c>
       <c r="AB73">
-        <v>34.93532021820478</v>
+        <v>436.52027573888904</v>
       </c>
       <c r="AD73" t="s">
         <v>445</v>
@@ -17287,16 +17287,16 @@
         <v>835</v>
       </c>
       <c r="AM73" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="AN73" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AO73">
-        <v>0.97918864997471655</v>
+        <v>0.96335236529265011</v>
       </c>
       <c r="AP73">
-        <v>381.5414171301972</v>
+        <v>671.87330296808034</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -17361,16 +17361,16 @@
         <v>574</v>
       </c>
       <c r="Y74" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="Z74" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="AA74">
-        <v>0.99741667924532684</v>
+        <v>0.99263667372558639</v>
       </c>
       <c r="AB74">
-        <v>47.360880502342191</v>
+        <v>134.9943150309158</v>
       </c>
       <c r="AD74" t="s">
         <v>445</v>
@@ -17397,16 +17397,16 @@
         <v>837</v>
       </c>
       <c r="AM74" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="AN74" t="s">
-        <v>665</v>
+        <v>994</v>
       </c>
       <c r="AO74">
-        <v>0.96550702044259584</v>
+        <v>0.97070223771032205</v>
       </c>
       <c r="AP74">
-        <v>632.37129188574295</v>
+        <v>537.12564197742824</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -17471,16 +17471,16 @@
         <v>576</v>
       </c>
       <c r="Y75" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="Z75" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="AA75">
-        <v>0.99782027918606175</v>
+        <v>0.98665714478881894</v>
       </c>
       <c r="AB75">
-        <v>39.961548255533756</v>
+        <v>244.61901220498595</v>
       </c>
       <c r="AD75" t="s">
         <v>445</v>
@@ -17507,16 +17507,16 @@
         <v>839</v>
       </c>
       <c r="AM75" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="AN75" t="s">
-        <v>665</v>
+        <v>996</v>
       </c>
       <c r="AO75">
-        <v>0.99191812933076651</v>
+        <v>0.97950961971620221</v>
       </c>
       <c r="AP75">
-        <v>148.16762893594731</v>
+        <v>375.65697186962575</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -17581,16 +17581,16 @@
         <v>578</v>
       </c>
       <c r="Y76" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="Z76" t="s">
-        <v>653</v>
+        <v>689</v>
       </c>
       <c r="AA76">
-        <v>0.98201413073603905</v>
+        <v>0.99671990332447369</v>
       </c>
       <c r="AB76">
-        <v>329.74093650595114</v>
+        <v>60.135105717982277</v>
       </c>
       <c r="AD76" t="s">
         <v>445</v>
@@ -17617,16 +17617,16 @@
         <v>841</v>
       </c>
       <c r="AM76" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="AN76" t="s">
-        <v>679</v>
+        <v>648</v>
       </c>
       <c r="AO76">
-        <v>0.97851296575183921</v>
+        <v>0.94721908575810376</v>
       </c>
       <c r="AP76">
-        <v>393.92896121628166</v>
+        <v>967.65009443476538</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -17691,16 +17691,16 @@
         <v>580</v>
       </c>
       <c r="Y77" t="s">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="Z77" t="s">
-        <v>663</v>
+        <v>690</v>
       </c>
       <c r="AA77">
-        <v>0.97808127216802332</v>
+        <v>0.99830013108627691</v>
       </c>
       <c r="AB77">
-        <v>401.84334358623994</v>
+        <v>31.164263418257661</v>
       </c>
       <c r="AD77" t="s">
         <v>445</v>
@@ -17727,16 +17727,16 @@
         <v>843</v>
       </c>
       <c r="AM77" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="AN77" t="s">
-        <v>994</v>
+        <v>648</v>
       </c>
       <c r="AO77">
-        <v>0.97693095508317673</v>
+        <v>0.98898335230625201</v>
       </c>
       <c r="AP77">
-        <v>422.93249014176001</v>
+        <v>201.97187438538015</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -17801,16 +17801,16 @@
         <v>582</v>
       </c>
       <c r="Y78" t="s">
-        <v>375</v>
+        <v>424</v>
       </c>
       <c r="Z78" t="s">
-        <v>665</v>
+        <v>691</v>
       </c>
       <c r="AA78">
-        <v>0.98589110095524246</v>
+        <v>0.99408275357961784</v>
       </c>
       <c r="AB78">
-        <v>258.66314915388926</v>
+        <v>108.48285104034026</v>
       </c>
       <c r="AD78" t="s">
         <v>445</v>
@@ -17837,16 +17837,16 @@
         <v>845</v>
       </c>
       <c r="AM78" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="AN78" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="AO78">
-        <v>0.9972902611932265</v>
+        <v>0.99506178999496608</v>
       </c>
       <c r="AP78">
-        <v>49.678544790847084</v>
+        <v>90.533850092289356</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -17911,16 +17911,16 @@
         <v>584</v>
       </c>
       <c r="Y79" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="Z79" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AA79">
-        <v>0.99646010176925304</v>
+        <v>0.9719447908127189</v>
       </c>
       <c r="AB79">
-        <v>64.89813423036172</v>
+        <v>514.34550176681955</v>
       </c>
       <c r="AD79" t="s">
         <v>445</v>
@@ -17947,16 +17947,16 @@
         <v>847</v>
       </c>
       <c r="AM79" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="AN79" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="AO79">
-        <v>0.97935848497620392</v>
+        <v>0.99493880624410824</v>
       </c>
       <c r="AP79">
-        <v>378.42777543626062</v>
+        <v>92.7885521913487</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18021,16 +18021,16 @@
         <v>586</v>
       </c>
       <c r="Y80" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Z80" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AA80">
-        <v>0.99487962039691491</v>
+        <v>0.99655071603273171</v>
       </c>
       <c r="AB80">
-        <v>93.8736260565599</v>
+        <v>63.236872733251452</v>
       </c>
       <c r="AD80" t="s">
         <v>445</v>
@@ -18057,16 +18057,16 @@
         <v>849</v>
       </c>
       <c r="AM80" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="AN80" t="s">
-        <v>665</v>
+        <v>646</v>
       </c>
       <c r="AO80">
-        <v>0.97738569554252064</v>
+        <v>0.9643711256064017</v>
       </c>
       <c r="AP80">
-        <v>414.59558172045399</v>
+        <v>653.19603054930235</v>
       </c>
     </row>
     <row r="81" spans="2:42">
@@ -18131,16 +18131,16 @@
         <v>588</v>
       </c>
       <c r="Y81" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="Z81" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AA81">
-        <v>0.97458216258452024</v>
+        <v>0.97971956708030139</v>
       </c>
       <c r="AB81">
-        <v>465.99368595046235</v>
+        <v>371.80793686114123</v>
       </c>
       <c r="AD81" t="s">
         <v>445</v>
@@ -18167,16 +18167,16 @@
         <v>851</v>
       </c>
       <c r="AM81" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="AN81" t="s">
-        <v>675</v>
+        <v>648</v>
       </c>
       <c r="AO81">
-        <v>0.98739702445646216</v>
+        <v>0.99099266826252508</v>
       </c>
       <c r="AP81">
-        <v>231.05455163152675</v>
+        <v>165.13441518704016</v>
       </c>
     </row>
     <row r="82" spans="2:42">
@@ -18241,16 +18241,16 @@
         <v>590</v>
       </c>
       <c r="Y82" t="s">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="Z82" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AA82">
-        <v>0.98303972846671772</v>
+        <v>0.98980411719589489</v>
       </c>
       <c r="AB82">
-        <v>310.93831144350901</v>
+        <v>186.92451807526095</v>
       </c>
       <c r="AD82" t="s">
         <v>445</v>
@@ -18277,16 +18277,16 @@
         <v>853</v>
       </c>
       <c r="AM82" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="AN82" t="s">
-        <v>1001</v>
+        <v>708</v>
       </c>
       <c r="AO82">
-        <v>0.99755801237420683</v>
+        <v>0.96623363784081273</v>
       </c>
       <c r="AP82">
-        <v>44.769773139540511</v>
+        <v>619.04997291843438</v>
       </c>
     </row>
     <row r="83" spans="2:42">
@@ -18351,16 +18351,16 @@
         <v>592</v>
       </c>
       <c r="Y83" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="Z83" t="s">
-        <v>695</v>
+        <v>645</v>
       </c>
       <c r="AA83">
-        <v>0.99273760630626895</v>
+        <v>0.95872760140098945</v>
       </c>
       <c r="AB83">
-        <v>133.14388438506904</v>
+        <v>756.66064098185961</v>
       </c>
       <c r="AD83" t="s">
         <v>445</v>
@@ -18387,16 +18387,16 @@
         <v>855</v>
       </c>
       <c r="AM83" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="AN83" t="s">
-        <v>1003</v>
+        <v>667</v>
       </c>
       <c r="AO83">
-        <v>0.99770486090207411</v>
+        <v>0.98900028996553313</v>
       </c>
       <c r="AP83">
-        <v>42.077550128640524</v>
+        <v>201.66135063189321</v>
       </c>
     </row>
     <row r="84" spans="2:42">
@@ -18461,16 +18461,16 @@
         <v>594</v>
       </c>
       <c r="Y84" t="s">
-        <v>431</v>
+        <v>379</v>
       </c>
       <c r="Z84" t="s">
         <v>696</v>
       </c>
       <c r="AA84">
-        <v>0.99564857688473862</v>
+        <v>0.93423394789967462</v>
       </c>
       <c r="AB84">
-        <v>79.77609044645817</v>
+        <v>1205.7109551726326</v>
       </c>
       <c r="AD84" t="s">
         <v>445</v>
@@ -18497,16 +18497,16 @@
         <v>857</v>
       </c>
       <c r="AM84" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="AN84" t="s">
-        <v>924</v>
+        <v>695</v>
       </c>
       <c r="AO84">
-        <v>0.98764154770136958</v>
+        <v>0.98539636691491217</v>
       </c>
       <c r="AP84">
-        <v>226.57162547489074</v>
+        <v>267.73327322661089</v>
       </c>
     </row>
     <row r="85" spans="2:42">
@@ -18571,16 +18571,16 @@
         <v>596</v>
       </c>
       <c r="Y85" t="s">
-        <v>429</v>
+        <v>349</v>
       </c>
       <c r="Z85" t="s">
-        <v>694</v>
+        <v>668</v>
       </c>
       <c r="AA85">
-        <v>0.99351242433990716</v>
+        <v>0.97861539621410798</v>
       </c>
       <c r="AB85">
-        <v>118.93888710170195</v>
+        <v>392.05106940802045</v>
       </c>
       <c r="AD85" t="s">
         <v>445</v>
@@ -18607,16 +18607,16 @@
         <v>859</v>
       </c>
       <c r="AM85" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="AN85" t="s">
-        <v>1006</v>
+        <v>648</v>
       </c>
       <c r="AO85">
-        <v>0.9977216312452537</v>
+        <v>0.95721921641733843</v>
       </c>
       <c r="AP85">
-        <v>41.77009383701548</v>
+        <v>784.31436568212814</v>
       </c>
     </row>
     <row r="86" spans="2:42">
@@ -18681,16 +18681,16 @@
         <v>598</v>
       </c>
       <c r="Y86" t="s">
-        <v>435</v>
+        <v>363</v>
       </c>
       <c r="Z86" t="s">
-        <v>697</v>
+        <v>648</v>
       </c>
       <c r="AA86">
-        <v>0.99821138151964162</v>
+        <v>0.97896212777707714</v>
       </c>
       <c r="AB86">
-        <v>32.791338806570671</v>
+        <v>385.69432408691944</v>
       </c>
       <c r="AD86" t="s">
         <v>445</v>
@@ -18717,16 +18717,16 @@
         <v>861</v>
       </c>
       <c r="AM86" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="AN86" t="s">
-        <v>663</v>
+        <v>1009</v>
       </c>
       <c r="AO86">
-        <v>0.97985884005408208</v>
+        <v>0.97128923400988465</v>
       </c>
       <c r="AP86">
-        <v>369.25459900849603</v>
+        <v>526.36404315211564</v>
       </c>
     </row>
     <row r="87" spans="2:42">
@@ -18791,16 +18791,16 @@
         <v>600</v>
       </c>
       <c r="Y87" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="Z87" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AA87">
-        <v>0.99042712787144371</v>
+        <v>0.99805781879500122</v>
       </c>
       <c r="AB87">
-        <v>175.50265569019879</v>
+        <v>35.60665542497717</v>
       </c>
       <c r="AD87" t="s">
         <v>445</v>
@@ -18827,16 +18827,16 @@
         <v>863</v>
       </c>
       <c r="AM87" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="AN87" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AO87">
-        <v>0.93800436607424875</v>
+        <v>0.98140230930972394</v>
       </c>
       <c r="AP87">
-        <v>1136.5866219721056</v>
+        <v>340.95766265506029</v>
       </c>
     </row>
     <row r="88" spans="2:42">
@@ -18901,16 +18901,16 @@
         <v>602</v>
       </c>
       <c r="Y88" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="Z88" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="AA88">
-        <v>0.98458760722006711</v>
+        <v>0.99892391441583261</v>
       </c>
       <c r="AB88">
-        <v>282.56053429877028</v>
+        <v>19.728235709736104</v>
       </c>
       <c r="AD88" t="s">
         <v>445</v>
@@ -18937,16 +18937,16 @@
         <v>865</v>
       </c>
       <c r="AM88" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="AN88" t="s">
-        <v>675</v>
+        <v>1012</v>
       </c>
       <c r="AO88">
-        <v>0.96962859242416655</v>
+        <v>0.99585787867207576</v>
       </c>
       <c r="AP88">
-        <v>556.80913889028056</v>
+        <v>75.938891011944406</v>
       </c>
     </row>
     <row r="89" spans="2:42">
@@ -19011,16 +19011,16 @@
         <v>604</v>
       </c>
       <c r="Y89" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="Z89" t="s">
-        <v>663</v>
+        <v>699</v>
       </c>
       <c r="AA89">
-        <v>0.97454833391525864</v>
+        <v>0.99646875354725362</v>
       </c>
       <c r="AB89">
-        <v>466.6138782202575</v>
+        <v>64.739518300349658</v>
       </c>
       <c r="AD89" t="s">
         <v>445</v>
@@ -19047,16 +19047,16 @@
         <v>867</v>
       </c>
       <c r="AM89" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="AN89" t="s">
-        <v>1011</v>
+        <v>678</v>
       </c>
       <c r="AO89">
-        <v>0.99423423237135644</v>
+        <v>0.98152722015516447</v>
       </c>
       <c r="AP89">
-        <v>105.70573985846545</v>
+        <v>338.66763048865067</v>
       </c>
     </row>
     <row r="90" spans="2:42">
@@ -19121,16 +19121,16 @@
         <v>606</v>
       </c>
       <c r="Y90" t="s">
-        <v>351</v>
+        <v>399</v>
       </c>
       <c r="Z90" t="s">
-        <v>649</v>
+        <v>700</v>
       </c>
       <c r="AA90">
-        <v>0.95322333844045537</v>
+        <v>0.9922209073807341</v>
       </c>
       <c r="AB90">
-        <v>857.57212859165099</v>
+        <v>142.61669801987438</v>
       </c>
       <c r="AD90" t="s">
         <v>445</v>
@@ -19157,16 +19157,16 @@
         <v>869</v>
       </c>
       <c r="AM90" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="AN90" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AO90">
-        <v>0.96634981065643422</v>
+        <v>0.98827869617428776</v>
       </c>
       <c r="AP90">
-        <v>616.9201379653731</v>
+        <v>214.89057013805822</v>
       </c>
     </row>
     <row r="91" spans="2:42">
@@ -19231,16 +19231,16 @@
         <v>608</v>
       </c>
       <c r="Y91" t="s">
-        <v>352</v>
+        <v>396</v>
       </c>
       <c r="Z91" t="s">
-        <v>649</v>
+        <v>671</v>
       </c>
       <c r="AA91">
-        <v>0.97321507838078658</v>
+        <v>0.98201413073603905</v>
       </c>
       <c r="AB91">
-        <v>491.05689635224547</v>
+        <v>329.74093650595114</v>
       </c>
       <c r="AD91" t="s">
         <v>445</v>
@@ -19267,16 +19267,16 @@
         <v>871</v>
       </c>
       <c r="AM91" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="AN91" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="AO91">
-        <v>0.99393164723700467</v>
+        <v>0.98732492064736277</v>
       </c>
       <c r="AP91">
-        <v>111.25313398824829</v>
+        <v>232.37645479834956</v>
       </c>
     </row>
     <row r="92" spans="2:42">
@@ -19341,16 +19341,16 @@
         <v>610</v>
       </c>
       <c r="Y92" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="Z92" t="s">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="AA92">
-        <v>0.98581703135158405</v>
+        <v>0.97808127216802332</v>
       </c>
       <c r="AB92">
-        <v>260.02109188762591</v>
+        <v>401.84334358623994</v>
       </c>
       <c r="AD92" t="s">
         <v>445</v>
@@ -19377,16 +19377,16 @@
         <v>873</v>
       </c>
       <c r="AM92" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="AN92" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="AO92">
-        <v>0.99746342019371192</v>
+        <v>0.99846088793014054</v>
       </c>
       <c r="AP92">
-        <v>46.503963115281117</v>
+        <v>28.217054614091012</v>
       </c>
     </row>
     <row r="93" spans="2:42">
@@ -19451,16 +19451,16 @@
         <v>612</v>
       </c>
       <c r="Y93" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z93" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AA93">
-        <v>0.97542624087094398</v>
+        <v>0.98589110095524246</v>
       </c>
       <c r="AB93">
-        <v>450.51891736602602</v>
+        <v>258.66314915388926</v>
       </c>
       <c r="AD93" t="s">
         <v>445</v>
@@ -19487,16 +19487,16 @@
         <v>875</v>
       </c>
       <c r="AM93" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="AN93" t="s">
-        <v>1018</v>
+        <v>686</v>
       </c>
       <c r="AO93">
-        <v>0.99690141662376341</v>
+        <v>0.9937244183974584</v>
       </c>
       <c r="AP93">
-        <v>56.80736189767017</v>
+        <v>115.0523293799298</v>
       </c>
     </row>
     <row r="94" spans="2:42">
@@ -19561,16 +19561,16 @@
         <v>614</v>
       </c>
       <c r="Y94" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Z94" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AA94">
-        <v>0.99745350130137034</v>
+        <v>0.99646010176925304</v>
       </c>
       <c r="AB94">
-        <v>46.685809474876969</v>
+        <v>64.89813423036172</v>
       </c>
       <c r="AD94" t="s">
         <v>445</v>
@@ -19597,16 +19597,16 @@
         <v>877</v>
       </c>
       <c r="AM94" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="AN94" t="s">
-        <v>674</v>
+        <v>1021</v>
       </c>
       <c r="AO94">
-        <v>0.98900028996553313</v>
+        <v>0.93186769579006068</v>
       </c>
       <c r="AP94">
-        <v>201.66135063189321</v>
+        <v>1249.0922438488865</v>
       </c>
     </row>
     <row r="95" spans="2:42">
@@ -19671,16 +19671,16 @@
         <v>616</v>
       </c>
       <c r="Y95" t="s">
-        <v>443</v>
+        <v>404</v>
       </c>
       <c r="Z95" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AA95">
-        <v>0.98101450166571025</v>
+        <v>0.99487962039691491</v>
       </c>
       <c r="AB95">
-        <v>348.06746946197933</v>
+        <v>93.8736260565599</v>
       </c>
       <c r="AD95" t="s">
         <v>445</v>
@@ -19707,16 +19707,16 @@
         <v>879</v>
       </c>
       <c r="AM95" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="AN95" t="s">
-        <v>705</v>
+        <v>646</v>
       </c>
       <c r="AO95">
-        <v>0.98539636691491217</v>
+        <v>0.94664324606770156</v>
       </c>
       <c r="AP95">
-        <v>267.73327322661089</v>
+        <v>978.20715542547146</v>
       </c>
     </row>
     <row r="96" spans="2:42">
@@ -19781,16 +19781,16 @@
         <v>618</v>
       </c>
       <c r="Y96" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="Z96" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AA96">
-        <v>0.99489296223435719</v>
+        <v>0.97458216258452024</v>
       </c>
       <c r="AB96">
-        <v>93.629025703450537</v>
+        <v>465.99368595046235</v>
       </c>
       <c r="AD96" t="s">
         <v>445</v>
@@ -19817,16 +19817,16 @@
         <v>881</v>
       </c>
       <c r="AM96" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="AN96" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AO96">
-        <v>0.95721921641733843</v>
+        <v>0.96085367337953664</v>
       </c>
       <c r="AP96">
-        <v>784.31436568212814</v>
+        <v>717.68265470849451</v>
       </c>
     </row>
     <row r="97" spans="2:42">
@@ -19891,16 +19891,16 @@
         <v>620</v>
       </c>
       <c r="Y97" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="Z97" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AA97">
-        <v>0.99705259621301434</v>
+        <v>0.98303972846671772</v>
       </c>
       <c r="AB97">
-        <v>54.035736094736372</v>
+        <v>310.93831144350901</v>
       </c>
       <c r="AD97" t="s">
         <v>445</v>
@@ -19927,16 +19927,16 @@
         <v>883</v>
       </c>
       <c r="AM97" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="AN97" t="s">
-        <v>1023</v>
+        <v>648</v>
       </c>
       <c r="AO97">
-        <v>0.97128923400988465</v>
+        <v>0.94667937507615152</v>
       </c>
       <c r="AP97">
-        <v>526.36404315211564</v>
+        <v>977.54479027055595</v>
       </c>
     </row>
     <row r="98" spans="2:42">
@@ -20001,16 +20001,16 @@
         <v>622</v>
       </c>
       <c r="Y98" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="Z98" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AA98">
-        <v>0.97971956708030139</v>
+        <v>0.99273760630626895</v>
       </c>
       <c r="AB98">
-        <v>371.80793686114123</v>
+        <v>133.14388438506904</v>
       </c>
       <c r="AD98" t="s">
         <v>445</v>
@@ -20037,16 +20037,16 @@
         <v>885</v>
       </c>
       <c r="AM98" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="AN98" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AO98">
-        <v>0.98140230930972394</v>
+        <v>0.99485429484434884</v>
       </c>
       <c r="AP98">
-        <v>340.95766265506029</v>
+        <v>94.33792785360508</v>
       </c>
     </row>
     <row r="99" spans="2:42">
@@ -20111,16 +20111,16 @@
         <v>624</v>
       </c>
       <c r="Y99" t="s">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="Z99" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AA99">
-        <v>0.98980411719589489</v>
+        <v>0.99564857688473862</v>
       </c>
       <c r="AB99">
-        <v>186.92451807526095</v>
+        <v>79.77609044645817</v>
       </c>
       <c r="AD99" t="s">
         <v>445</v>
@@ -20147,16 +20147,16 @@
         <v>887</v>
       </c>
       <c r="AM99" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="AN99" t="s">
-        <v>1026</v>
+        <v>949</v>
       </c>
       <c r="AO99">
-        <v>0.99585787867207576</v>
+        <v>0.99104002253663459</v>
       </c>
       <c r="AP99">
-        <v>75.938891011944406</v>
+        <v>164.26625349503158</v>
       </c>
     </row>
     <row r="100" spans="2:42">
@@ -20221,16 +20221,16 @@
         <v>626</v>
       </c>
       <c r="Y100" t="s">
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="Z100" t="s">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="AA100">
-        <v>0.95872760140098945</v>
+        <v>0.99351242433990716</v>
       </c>
       <c r="AB100">
-        <v>756.66064098185961</v>
+        <v>118.93888710170195</v>
       </c>
       <c r="AD100" t="s">
         <v>445</v>
@@ -20260,13 +20260,13 @@
         <v>1027</v>
       </c>
       <c r="AN100" t="s">
-        <v>650</v>
+        <v>1028</v>
       </c>
       <c r="AO100">
-        <v>0.98152722015516447</v>
+        <v>0.98218033156447682</v>
       </c>
       <c r="AP100">
-        <v>338.66763048865067</v>
+        <v>326.69392131792426</v>
       </c>
     </row>
     <row r="101" spans="2:42">
@@ -20331,16 +20331,16 @@
         <v>628</v>
       </c>
       <c r="Y101" t="s">
-        <v>379</v>
+        <v>435</v>
       </c>
       <c r="Z101" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AA101">
-        <v>0.93423394789967462</v>
+        <v>0.99821138151964162</v>
       </c>
       <c r="AB101">
-        <v>1205.7109551726326</v>
+        <v>32.791338806570671</v>
       </c>
       <c r="AD101" t="s">
         <v>445</v>
@@ -20367,16 +20367,16 @@
         <v>891</v>
       </c>
       <c r="AM101" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="AN101" t="s">
-        <v>675</v>
+        <v>1030</v>
       </c>
       <c r="AO101">
-        <v>0.98827869617428776</v>
+        <v>0.99585887269839302</v>
       </c>
       <c r="AP101">
-        <v>214.89057013805822</v>
+        <v>75.920667196127695</v>
       </c>
     </row>
     <row r="102" spans="2:42">
@@ -20441,16 +20441,16 @@
         <v>630</v>
       </c>
       <c r="Y102" t="s">
-        <v>349</v>
+        <v>393</v>
       </c>
       <c r="Z102" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="AA102">
-        <v>0.97861539621410798</v>
+        <v>0.94904572806075094</v>
       </c>
       <c r="AB102">
-        <v>392.05106940802045</v>
+        <v>934.16165221956703</v>
       </c>
       <c r="AD102" t="s">
         <v>445</v>
@@ -20477,16 +20477,16 @@
         <v>893</v>
       </c>
       <c r="AM102" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="AN102" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="AO102">
-        <v>0.98732492064736277</v>
+        <v>0.99612820180322659</v>
       </c>
       <c r="AP102">
-        <v>232.37645479834956</v>
+        <v>70.982966940846623</v>
       </c>
     </row>
     <row r="103" spans="2:42">
@@ -20551,16 +20551,16 @@
         <v>632</v>
       </c>
       <c r="Y103" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Z103" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AA103">
-        <v>0.97896212777707714</v>
+        <v>0.94779673241739959</v>
       </c>
       <c r="AB103">
-        <v>385.69432408691944</v>
+        <v>957.05990568100776</v>
       </c>
       <c r="AD103" t="s">
         <v>445</v>
@@ -20587,16 +20587,16 @@
         <v>895</v>
       </c>
       <c r="AM103" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="AN103" t="s">
-        <v>1032</v>
+        <v>955</v>
       </c>
       <c r="AO103">
-        <v>0.99846088793014054</v>
+        <v>0.98764154770136958</v>
       </c>
       <c r="AP103">
-        <v>28.217054614091012</v>
+        <v>226.57162547489074</v>
       </c>
     </row>
     <row r="104" spans="2:42">
@@ -20661,16 +20661,16 @@
         <v>634</v>
       </c>
       <c r="Y104" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="Z104" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AA104">
-        <v>0.99805781879500122</v>
+        <v>0.96846296248311359</v>
       </c>
       <c r="AB104">
-        <v>35.60665542497717</v>
+        <v>578.17902114291837</v>
       </c>
       <c r="AD104" t="s">
         <v>445</v>
@@ -20697,16 +20697,16 @@
         <v>897</v>
       </c>
       <c r="AM104" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="AN104" t="s">
-        <v>663</v>
+        <v>1035</v>
       </c>
       <c r="AO104">
-        <v>0.95226889215734378</v>
+        <v>0.9977216312452537</v>
       </c>
       <c r="AP104">
-        <v>875.07031044869723</v>
+        <v>41.77009383701548</v>
       </c>
     </row>
     <row r="105" spans="2:42">
@@ -20771,16 +20771,16 @@
         <v>636</v>
       </c>
       <c r="Y105" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="Z105" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AA105">
-        <v>0.99892391441583261</v>
+        <v>0.99564253113732704</v>
       </c>
       <c r="AB105">
-        <v>19.728235709736104</v>
+        <v>79.886929149003976</v>
       </c>
       <c r="AD105" t="s">
         <v>445</v>
@@ -20807,16 +20807,16 @@
         <v>899</v>
       </c>
       <c r="AM105" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="AN105" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="AO105">
-        <v>0.98244678792215867</v>
+        <v>0.97985884005408208</v>
       </c>
       <c r="AP105">
-        <v>321.80888809375716</v>
+        <v>369.25459900849603</v>
       </c>
     </row>
     <row r="106" spans="2:42">
@@ -20881,16 +20881,16 @@
         <v>638</v>
       </c>
       <c r="Y106" t="s">
-        <v>401</v>
+        <v>353</v>
       </c>
       <c r="Z106" t="s">
-        <v>709</v>
+        <v>668</v>
       </c>
       <c r="AA106">
-        <v>0.99646875354725362</v>
+        <v>0.95915670695527311</v>
       </c>
       <c r="AB106">
-        <v>64.739518300349658</v>
+        <v>748.79370581999342</v>
       </c>
       <c r="AD106" t="s">
         <v>445</v>
@@ -20917,16 +20917,16 @@
         <v>901</v>
       </c>
       <c r="AM106" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="AN106" t="s">
-        <v>1036</v>
+        <v>648</v>
       </c>
       <c r="AO106">
-        <v>0.99244907456015963</v>
+        <v>0.93800436607424875</v>
       </c>
       <c r="AP106">
-        <v>138.43363306374022</v>
+        <v>1136.5866219721056</v>
       </c>
     </row>
     <row r="107" spans="2:42">
@@ -20991,16 +20991,16 @@
         <v>640</v>
       </c>
       <c r="Y107" t="s">
-        <v>399</v>
+        <v>433</v>
       </c>
       <c r="Z107" t="s">
         <v>710</v>
       </c>
       <c r="AA107">
-        <v>0.9922209073807341</v>
+        <v>0.98266638110143478</v>
       </c>
       <c r="AB107">
-        <v>142.61669801987438</v>
+        <v>317.78301314036179</v>
       </c>
       <c r="AD107" t="s">
         <v>445</v>
@@ -21027,16 +21027,16 @@
         <v>903</v>
       </c>
       <c r="AM107" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AN107" t="s">
-        <v>1038</v>
+        <v>651</v>
       </c>
       <c r="AO107">
-        <v>0.99706791078062507</v>
+        <v>0.96962859242416655</v>
       </c>
       <c r="AP107">
-        <v>53.754969021872945</v>
+        <v>556.80913889028056</v>
       </c>
     </row>
   </sheetData>
@@ -21045,7 +21045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11434451-9B4C-4445-81C9-DD25AC8C18EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14294B30-8F37-40A7-B26F-087D095741EF}">
   <dimension ref="B9:Z107"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -21157,7 +21157,7 @@
         <v>1211</v>
       </c>
       <c r="K11" t="s">
-        <v>999</v>
+        <v>937</v>
       </c>
       <c r="L11">
         <v>0.17596388835381646</v>
@@ -21190,7 +21190,7 @@
         <v>1405</v>
       </c>
       <c r="X11" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="Y11">
         <v>45.567749999999997</v>
@@ -21225,7 +21225,7 @@
         <v>1213</v>
       </c>
       <c r="K12" t="s">
-        <v>952</v>
+        <v>914</v>
       </c>
       <c r="L12">
         <v>0.5998563972685973</v>
@@ -21258,7 +21258,7 @@
         <v>1407</v>
       </c>
       <c r="X12" t="s">
-        <v>1180</v>
+        <v>1194</v>
       </c>
       <c r="Y12">
         <v>102.99525</v>
@@ -21293,7 +21293,7 @@
         <v>1215</v>
       </c>
       <c r="K13" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="L13">
         <v>4.2823239792782193</v>
@@ -21326,7 +21326,7 @@
         <v>1409</v>
       </c>
       <c r="X13" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="Y13">
         <v>77.929500000000004</v>
@@ -21361,7 +21361,7 @@
         <v>1217</v>
       </c>
       <c r="K14" t="s">
-        <v>1009</v>
+        <v>1038</v>
       </c>
       <c r="L14">
         <v>9.5215803844936261E-2</v>
@@ -21394,7 +21394,7 @@
         <v>1411</v>
       </c>
       <c r="X14" t="s">
-        <v>1191</v>
+        <v>1179</v>
       </c>
       <c r="Y14">
         <v>34.414499999999997</v>
@@ -21429,7 +21429,7 @@
         <v>1219</v>
       </c>
       <c r="K15" t="s">
-        <v>1000</v>
+        <v>938</v>
       </c>
       <c r="L15">
         <v>3.6287474003893196</v>
@@ -21462,7 +21462,7 @@
         <v>1413</v>
       </c>
       <c r="X15" t="s">
-        <v>1152</v>
+        <v>1186</v>
       </c>
       <c r="Y15">
         <v>48.263249999999999</v>
@@ -21497,7 +21497,7 @@
         <v>1221</v>
       </c>
       <c r="K16" t="s">
-        <v>953</v>
+        <v>915</v>
       </c>
       <c r="L16">
         <v>43.604071708920948</v>
@@ -21530,7 +21530,7 @@
         <v>1415</v>
       </c>
       <c r="X16" t="s">
-        <v>1177</v>
+        <v>1155</v>
       </c>
       <c r="Y16">
         <v>27.429749999999999</v>
@@ -21565,7 +21565,7 @@
         <v>1223</v>
       </c>
       <c r="K17" t="s">
-        <v>928</v>
+        <v>959</v>
       </c>
       <c r="L17">
         <v>9.6809271032388455</v>
@@ -21598,7 +21598,7 @@
         <v>1417</v>
       </c>
       <c r="X17" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="Y17">
         <v>29.697749999999999</v>
@@ -21633,7 +21633,7 @@
         <v>1225</v>
       </c>
       <c r="K18" t="s">
-        <v>1035</v>
+        <v>969</v>
       </c>
       <c r="L18">
         <v>19.57643322237125</v>
@@ -21666,7 +21666,7 @@
         <v>1419</v>
       </c>
       <c r="X18" t="s">
-        <v>1189</v>
+        <v>1170</v>
       </c>
       <c r="Y18">
         <v>39.247500000000002</v>
@@ -21701,7 +21701,7 @@
         <v>1227</v>
       </c>
       <c r="K19" t="s">
-        <v>932</v>
+        <v>998</v>
       </c>
       <c r="L19">
         <v>55.638210824668811</v>
@@ -21734,7 +21734,7 @@
         <v>1421</v>
       </c>
       <c r="X19" t="s">
-        <v>1174</v>
+        <v>1209</v>
       </c>
       <c r="Y19">
         <v>54.114750000000001</v>
@@ -21769,7 +21769,7 @@
         <v>1229</v>
       </c>
       <c r="K20" t="s">
-        <v>1027</v>
+        <v>1013</v>
       </c>
       <c r="L20">
         <v>4.3112694152725819</v>
@@ -21802,7 +21802,7 @@
         <v>1423</v>
       </c>
       <c r="X20" t="s">
-        <v>1206</v>
+        <v>1149</v>
       </c>
       <c r="Y20">
         <v>46.38</v>
@@ -21837,7 +21837,7 @@
         <v>1231</v>
       </c>
       <c r="K21" t="s">
-        <v>991</v>
+        <v>924</v>
       </c>
       <c r="L21">
         <v>11.295459465941514</v>
@@ -21870,7 +21870,7 @@
         <v>1425</v>
       </c>
       <c r="X21" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="Y21">
         <v>11.891999999999999</v>
@@ -21905,7 +21905,7 @@
         <v>1233</v>
       </c>
       <c r="K22" t="s">
-        <v>1024</v>
+        <v>1010</v>
       </c>
       <c r="L22">
         <v>3.350731358569373</v>
@@ -21938,7 +21938,7 @@
         <v>1427</v>
       </c>
       <c r="X22" t="s">
-        <v>1145</v>
+        <v>1171</v>
       </c>
       <c r="Y22">
         <v>163.69575</v>
@@ -21973,7 +21973,7 @@
         <v>1235</v>
       </c>
       <c r="K23" t="s">
-        <v>983</v>
+        <v>1003</v>
       </c>
       <c r="L23">
         <v>89.260194648908481</v>
@@ -22006,7 +22006,7 @@
         <v>1429</v>
       </c>
       <c r="X23" t="s">
-        <v>1153</v>
+        <v>1187</v>
       </c>
       <c r="Y23">
         <v>98.379000000000005</v>
@@ -22041,7 +22041,7 @@
         <v>1237</v>
       </c>
       <c r="K24" t="s">
-        <v>989</v>
+        <v>922</v>
       </c>
       <c r="L24">
         <v>54.288016768663745</v>
@@ -22074,7 +22074,7 @@
         <v>1431</v>
       </c>
       <c r="X24" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="Y24">
         <v>89.855999999999995</v>
@@ -22109,7 +22109,7 @@
         <v>1239</v>
       </c>
       <c r="K25" t="s">
-        <v>927</v>
+        <v>958</v>
       </c>
       <c r="L25">
         <v>76.46332597527315</v>
@@ -22142,7 +22142,7 @@
         <v>1433</v>
       </c>
       <c r="X25" t="s">
-        <v>1187</v>
+        <v>1168</v>
       </c>
       <c r="Y25">
         <v>46.682250000000003</v>
@@ -22177,7 +22177,7 @@
         <v>1241</v>
       </c>
       <c r="K26" t="s">
-        <v>988</v>
+        <v>921</v>
       </c>
       <c r="L26">
         <v>127.51605886676012</v>
@@ -22210,7 +22210,7 @@
         <v>1435</v>
       </c>
       <c r="X26" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="Y26">
         <v>54.84825</v>
@@ -22245,7 +22245,7 @@
         <v>1243</v>
       </c>
       <c r="K27" t="s">
-        <v>946</v>
+        <v>908</v>
       </c>
       <c r="L27">
         <v>46.793063320317437</v>
@@ -22278,7 +22278,7 @@
         <v>1437</v>
       </c>
       <c r="X27" t="s">
-        <v>1169</v>
+        <v>1204</v>
       </c>
       <c r="Y27">
         <v>44.145000000000003</v>
@@ -22313,7 +22313,7 @@
         <v>1245</v>
       </c>
       <c r="K28" t="s">
-        <v>913</v>
+        <v>990</v>
       </c>
       <c r="L28">
         <v>82.443327158392236</v>
@@ -22346,7 +22346,7 @@
         <v>1439</v>
       </c>
       <c r="X28" t="s">
-        <v>1170</v>
+        <v>1205</v>
       </c>
       <c r="Y28">
         <v>62.381250000000001</v>
@@ -22381,7 +22381,7 @@
         <v>1247</v>
       </c>
       <c r="K29" t="s">
-        <v>961</v>
+        <v>1024</v>
       </c>
       <c r="L29">
         <v>97.980091042432477</v>
@@ -22414,7 +22414,7 @@
         <v>1441</v>
       </c>
       <c r="X29" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="Y29">
         <v>8.1000000000000003E-2</v>
@@ -22449,7 +22449,7 @@
         <v>1249</v>
       </c>
       <c r="K30" t="s">
-        <v>1021</v>
+        <v>1007</v>
       </c>
       <c r="L30">
         <v>110.94074818055437</v>
@@ -22482,7 +22482,7 @@
         <v>1443</v>
       </c>
       <c r="X30" t="s">
-        <v>1148</v>
+        <v>1174</v>
       </c>
       <c r="Y30">
         <v>133.70025000000001</v>
@@ -22517,7 +22517,7 @@
         <v>1251</v>
       </c>
       <c r="K31" t="s">
-        <v>990</v>
+        <v>923</v>
       </c>
       <c r="L31">
         <v>2.4273016266691929</v>
@@ -22585,7 +22585,7 @@
         <v>1253</v>
       </c>
       <c r="K32" t="s">
-        <v>931</v>
+        <v>997</v>
       </c>
       <c r="L32">
         <v>0.49128575065453367</v>
@@ -22618,7 +22618,7 @@
         <v>1447</v>
       </c>
       <c r="X32" t="s">
-        <v>1172</v>
+        <v>1207</v>
       </c>
       <c r="Y32">
         <v>170.13075000000001</v>
@@ -22653,7 +22653,7 @@
         <v>1255</v>
       </c>
       <c r="K33" t="s">
-        <v>915</v>
+        <v>992</v>
       </c>
       <c r="L33">
         <v>1.2848345469829228</v>
@@ -22686,7 +22686,7 @@
         <v>1449</v>
       </c>
       <c r="X33" t="s">
-        <v>1183</v>
+        <v>1197</v>
       </c>
       <c r="Y33">
         <v>65.342250000000007</v>
@@ -22721,7 +22721,7 @@
         <v>1257</v>
       </c>
       <c r="K34" t="s">
-        <v>1008</v>
+        <v>1037</v>
       </c>
       <c r="L34">
         <v>0.18935486724764602</v>
@@ -22754,7 +22754,7 @@
         <v>1451</v>
       </c>
       <c r="X34" t="s">
-        <v>1147</v>
+        <v>1173</v>
       </c>
       <c r="Y34">
         <v>53.101500000000001</v>
@@ -22789,7 +22789,7 @@
         <v>1259</v>
       </c>
       <c r="K35" t="s">
-        <v>914</v>
+        <v>991</v>
       </c>
       <c r="L35">
         <v>0.58118601062718378</v>
@@ -22822,7 +22822,7 @@
         <v>1453</v>
       </c>
       <c r="X35" t="s">
-        <v>1179</v>
+        <v>1193</v>
       </c>
       <c r="Y35">
         <v>49.923749999999998</v>
@@ -22857,7 +22857,7 @@
         <v>1261</v>
       </c>
       <c r="K36" t="s">
-        <v>926</v>
+        <v>957</v>
       </c>
       <c r="L36">
         <v>3.6717551314203591</v>
@@ -22890,7 +22890,7 @@
         <v>1455</v>
       </c>
       <c r="X36" t="s">
-        <v>1202</v>
+        <v>1145</v>
       </c>
       <c r="Y36">
         <v>98.321250000000006</v>
@@ -22925,7 +22925,7 @@
         <v>1263</v>
       </c>
       <c r="K37" t="s">
-        <v>957</v>
+        <v>1020</v>
       </c>
       <c r="L37">
         <v>0.9445236469650512</v>
@@ -22958,7 +22958,7 @@
         <v>1457</v>
       </c>
       <c r="X37" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="Y37">
         <v>99.285749999999993</v>
@@ -22993,7 +22993,7 @@
         <v>1265</v>
       </c>
       <c r="K38" t="s">
-        <v>921</v>
+        <v>933</v>
       </c>
       <c r="L38">
         <v>5.8689650080792175</v>
@@ -23026,7 +23026,7 @@
         <v>1459</v>
       </c>
       <c r="X38" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="Y38">
         <v>35.836500000000001</v>
@@ -23061,7 +23061,7 @@
         <v>1267</v>
       </c>
       <c r="K39" t="s">
-        <v>987</v>
+        <v>920</v>
       </c>
       <c r="L39">
         <v>2.928657185415191</v>
@@ -23094,7 +23094,7 @@
         <v>1461</v>
       </c>
       <c r="X39" t="s">
-        <v>1190</v>
+        <v>1178</v>
       </c>
       <c r="Y39">
         <v>62.210999999999999</v>
@@ -23129,7 +23129,7 @@
         <v>1269</v>
       </c>
       <c r="K40" t="s">
-        <v>978</v>
+        <v>950</v>
       </c>
       <c r="L40">
         <v>1.2558278274148955</v>
@@ -23162,7 +23162,7 @@
         <v>1463</v>
       </c>
       <c r="X40" t="s">
-        <v>1186</v>
+        <v>1167</v>
       </c>
       <c r="Y40">
         <v>31.096499999999999</v>
@@ -23197,7 +23197,7 @@
         <v>1271</v>
       </c>
       <c r="K41" t="s">
-        <v>967</v>
+        <v>1029</v>
       </c>
       <c r="L41">
         <v>2.2433982976323423</v>
@@ -23230,7 +23230,7 @@
         <v>1465</v>
       </c>
       <c r="X41" t="s">
-        <v>1203</v>
+        <v>1146</v>
       </c>
       <c r="Y41">
         <v>34.518749999999997</v>
@@ -23265,7 +23265,7 @@
         <v>1273</v>
       </c>
       <c r="K42" t="s">
-        <v>1015</v>
+        <v>985</v>
       </c>
       <c r="L42">
         <v>1.4423728327070269</v>
@@ -23298,7 +23298,7 @@
         <v>1467</v>
       </c>
       <c r="X42" t="s">
-        <v>1175</v>
+        <v>1210</v>
       </c>
       <c r="Y42">
         <v>2.74125</v>
@@ -23333,7 +23333,7 @@
         <v>1275</v>
       </c>
       <c r="K43" t="s">
-        <v>939</v>
+        <v>976</v>
       </c>
       <c r="L43">
         <v>8.0555754971063411</v>
@@ -23366,7 +23366,7 @@
         <v>1469</v>
       </c>
       <c r="X43" t="s">
-        <v>1157</v>
+        <v>1191</v>
       </c>
       <c r="Y43">
         <v>24.691500000000001</v>
@@ -23401,7 +23401,7 @@
         <v>1277</v>
       </c>
       <c r="K44" t="s">
-        <v>1025</v>
+        <v>1011</v>
       </c>
       <c r="L44">
         <v>20.016919488105035</v>
@@ -23434,7 +23434,7 @@
         <v>1471</v>
       </c>
       <c r="X44" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="Y44">
         <v>47.016750000000002</v>
@@ -23469,7 +23469,7 @@
         <v>1279</v>
       </c>
       <c r="K45" t="s">
-        <v>936</v>
+        <v>973</v>
       </c>
       <c r="L45">
         <v>20.987410272533506</v>
@@ -23502,7 +23502,7 @@
         <v>1473</v>
       </c>
       <c r="X45" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
       <c r="Y45">
         <v>19.535250000000001</v>
@@ -23537,7 +23537,7 @@
         <v>1281</v>
       </c>
       <c r="K46" t="s">
-        <v>937</v>
+        <v>974</v>
       </c>
       <c r="L46">
         <v>55.435583296031403</v>
@@ -23570,7 +23570,7 @@
         <v>1475</v>
       </c>
       <c r="X46" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="Y46">
         <v>25.143000000000001</v>
@@ -23605,7 +23605,7 @@
         <v>1283</v>
       </c>
       <c r="K47" t="s">
-        <v>950</v>
+        <v>912</v>
       </c>
       <c r="L47">
         <v>32.999903868338116</v>
@@ -23638,7 +23638,7 @@
         <v>1477</v>
       </c>
       <c r="X47" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="Y47">
         <v>67.352999999999994</v>
@@ -23673,7 +23673,7 @@
         <v>1285</v>
       </c>
       <c r="K48" t="s">
-        <v>1013</v>
+        <v>983</v>
       </c>
       <c r="L48">
         <v>49.696797018491381</v>
@@ -23706,7 +23706,7 @@
         <v>1479</v>
       </c>
       <c r="X48" t="s">
-        <v>1181</v>
+        <v>1195</v>
       </c>
       <c r="Y48">
         <v>34.546500000000002</v>
@@ -23741,7 +23741,7 @@
         <v>1287</v>
       </c>
       <c r="K49" t="s">
-        <v>963</v>
+        <v>1026</v>
       </c>
       <c r="L49">
         <v>32.640247665750501</v>
@@ -23774,7 +23774,7 @@
         <v>1481</v>
       </c>
       <c r="X49" t="s">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="Y49">
         <v>77.410499999999999</v>
@@ -23809,7 +23809,7 @@
         <v>1289</v>
       </c>
       <c r="K50" t="s">
-        <v>962</v>
+        <v>1025</v>
       </c>
       <c r="L50">
         <v>65.219358423551554</v>
@@ -23842,7 +23842,7 @@
         <v>1483</v>
       </c>
       <c r="X50" t="s">
-        <v>1188</v>
+        <v>1169</v>
       </c>
       <c r="Y50">
         <v>63.802500000000002</v>
@@ -23877,7 +23877,7 @@
         <v>1291</v>
       </c>
       <c r="K51" t="s">
-        <v>992</v>
+        <v>925</v>
       </c>
       <c r="L51">
         <v>52.726851063159351</v>
@@ -23910,7 +23910,7 @@
         <v>1485</v>
       </c>
       <c r="X51" t="s">
-        <v>1185</v>
+        <v>1199</v>
       </c>
       <c r="Y51">
         <v>53.966999999999999</v>
@@ -23945,7 +23945,7 @@
         <v>1293</v>
       </c>
       <c r="K52" t="s">
-        <v>998</v>
+        <v>936</v>
       </c>
       <c r="L52">
         <v>48.062334008658908</v>
@@ -23978,7 +23978,7 @@
         <v>1487</v>
       </c>
       <c r="X52" t="s">
-        <v>1205</v>
+        <v>1148</v>
       </c>
       <c r="Y52">
         <v>83.250749999999996</v>
@@ -24013,7 +24013,7 @@
         <v>1295</v>
       </c>
       <c r="K53" t="s">
-        <v>965</v>
+        <v>1027</v>
       </c>
       <c r="L53">
         <v>115.35264042679813</v>
@@ -24046,7 +24046,7 @@
         <v>1489</v>
       </c>
       <c r="X53" t="s">
-        <v>1173</v>
+        <v>1208</v>
       </c>
       <c r="Y53">
         <v>188.35499999999999</v>
@@ -24081,7 +24081,7 @@
         <v>1297</v>
       </c>
       <c r="K54" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
       <c r="L54">
         <v>66.906827934341507</v>
@@ -24114,7 +24114,7 @@
         <v>1491</v>
       </c>
       <c r="X54" t="s">
-        <v>1184</v>
+        <v>1198</v>
       </c>
       <c r="Y54">
         <v>114.67274999999999</v>
@@ -24149,7 +24149,7 @@
         <v>1299</v>
       </c>
       <c r="K55" t="s">
-        <v>1022</v>
+        <v>1008</v>
       </c>
       <c r="L55">
         <v>134.24925626793836</v>
@@ -24182,7 +24182,7 @@
         <v>1493</v>
       </c>
       <c r="X55" t="s">
-        <v>1176</v>
+        <v>1154</v>
       </c>
       <c r="Y55">
         <v>53.234250000000003</v>
@@ -24217,7 +24217,7 @@
         <v>1301</v>
       </c>
       <c r="K56" t="s">
-        <v>984</v>
+        <v>1004</v>
       </c>
       <c r="L56">
         <v>93.313759881118116</v>
@@ -24250,7 +24250,7 @@
         <v>1495</v>
       </c>
       <c r="X56" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="Y56">
         <v>159.49875</v>
@@ -24285,7 +24285,7 @@
         <v>1303</v>
       </c>
       <c r="K57" t="s">
-        <v>916</v>
+        <v>993</v>
       </c>
       <c r="L57">
         <v>145.76340565827428</v>
@@ -24318,7 +24318,7 @@
         <v>1497</v>
       </c>
       <c r="X57" t="s">
-        <v>1209</v>
+        <v>1152</v>
       </c>
       <c r="Y57">
         <v>134.5095</v>
@@ -24353,7 +24353,7 @@
         <v>1305</v>
       </c>
       <c r="K58" t="s">
-        <v>960</v>
+        <v>1023</v>
       </c>
       <c r="L58">
         <v>148.48080229460197</v>
@@ -24386,7 +24386,7 @@
         <v>1499</v>
       </c>
       <c r="X58" t="s">
-        <v>1155</v>
+        <v>1189</v>
       </c>
       <c r="Y58">
         <v>183.47624999999999</v>
@@ -24421,7 +24421,7 @@
         <v>1307</v>
       </c>
       <c r="K59" t="s">
-        <v>1034</v>
+        <v>968</v>
       </c>
       <c r="L59">
         <v>71.838937782979016</v>
@@ -24454,7 +24454,7 @@
         <v>1501</v>
       </c>
       <c r="X59" t="s">
-        <v>1208</v>
+        <v>1151</v>
       </c>
       <c r="Y59">
         <v>27.345749999999999</v>
@@ -24489,7 +24489,7 @@
         <v>1309</v>
       </c>
       <c r="K60" t="s">
-        <v>976</v>
+        <v>947</v>
       </c>
       <c r="L60">
         <v>80.257558228094155</v>
@@ -24522,7 +24522,7 @@
         <v>1503</v>
       </c>
       <c r="X60" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="Y60">
         <v>11.7315</v>
@@ -24557,7 +24557,7 @@
         <v>1311</v>
       </c>
       <c r="K61" t="s">
-        <v>977</v>
+        <v>948</v>
       </c>
       <c r="L61">
         <v>146.07778098481995</v>
@@ -24590,7 +24590,7 @@
         <v>1505</v>
       </c>
       <c r="X61" t="s">
-        <v>1196</v>
+        <v>1184</v>
       </c>
       <c r="Y61">
         <v>195.03299999999999</v>
@@ -24625,7 +24625,7 @@
         <v>1313</v>
       </c>
       <c r="K62" t="s">
-        <v>949</v>
+        <v>911</v>
       </c>
       <c r="L62">
         <v>106.1298736355218</v>
@@ -24658,7 +24658,7 @@
         <v>1507</v>
       </c>
       <c r="X62" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="Y62">
         <v>154.16175000000001</v>
@@ -24693,7 +24693,7 @@
         <v>1315</v>
       </c>
       <c r="K63" t="s">
-        <v>997</v>
+        <v>935</v>
       </c>
       <c r="L63">
         <v>124.94443081089416</v>
@@ -24728,7 +24728,7 @@
         <v>1317</v>
       </c>
       <c r="K64" t="s">
-        <v>1017</v>
+        <v>987</v>
       </c>
       <c r="L64">
         <v>12.652627740935781</v>
@@ -24763,7 +24763,7 @@
         <v>1319</v>
       </c>
       <c r="K65" t="s">
-        <v>1029</v>
+        <v>1015</v>
       </c>
       <c r="L65">
         <v>22.889688294443275</v>
@@ -24798,7 +24798,7 @@
         <v>1321</v>
       </c>
       <c r="K66" t="s">
-        <v>995</v>
+        <v>928</v>
       </c>
       <c r="L66">
         <v>1.5318794868726651</v>
@@ -24833,7 +24833,7 @@
         <v>1323</v>
       </c>
       <c r="K67" t="s">
-        <v>1037</v>
+        <v>971</v>
       </c>
       <c r="L67">
         <v>0.59942290733321824</v>
@@ -24868,7 +24868,7 @@
         <v>1325</v>
       </c>
       <c r="K68" t="s">
-        <v>933</v>
+        <v>999</v>
       </c>
       <c r="L68">
         <v>11.453222815679586</v>
@@ -24903,7 +24903,7 @@
         <v>1327</v>
       </c>
       <c r="K69" t="s">
-        <v>1002</v>
+        <v>940</v>
       </c>
       <c r="L69">
         <v>2.2803547354553286</v>
@@ -24938,7 +24938,7 @@
         <v>1329</v>
       </c>
       <c r="K70" t="s">
-        <v>911</v>
+        <v>966</v>
       </c>
       <c r="L70">
         <v>1.6411981852360265</v>
@@ -24973,7 +24973,7 @@
         <v>1331</v>
       </c>
       <c r="K71" t="s">
-        <v>969</v>
+        <v>1031</v>
       </c>
       <c r="L71">
         <v>3.6294095116605649</v>
@@ -25008,7 +25008,7 @@
         <v>1333</v>
       </c>
       <c r="K72" t="s">
-        <v>1031</v>
+        <v>1017</v>
       </c>
       <c r="L72">
         <v>4.463691536387925</v>
@@ -25043,7 +25043,7 @@
         <v>1335</v>
       </c>
       <c r="K73" t="s">
-        <v>935</v>
+        <v>1001</v>
       </c>
       <c r="L73">
         <v>0.15904812550112069</v>
@@ -25078,7 +25078,7 @@
         <v>1337</v>
       </c>
       <c r="K74" t="s">
-        <v>909</v>
+        <v>964</v>
       </c>
       <c r="L74">
         <v>0.38231455598608644</v>
@@ -25113,7 +25113,7 @@
         <v>1339</v>
       </c>
       <c r="K75" t="s">
-        <v>941</v>
+        <v>978</v>
       </c>
       <c r="L75">
         <v>48.459263659244627</v>
@@ -25148,7 +25148,7 @@
         <v>1341</v>
       </c>
       <c r="K76" t="s">
-        <v>993</v>
+        <v>926</v>
       </c>
       <c r="L76">
         <v>31.18047373096908</v>
@@ -25183,7 +25183,7 @@
         <v>1343</v>
       </c>
       <c r="K77" t="s">
-        <v>955</v>
+        <v>917</v>
       </c>
       <c r="L77">
         <v>21.737639110123883</v>
@@ -25218,7 +25218,7 @@
         <v>1345</v>
       </c>
       <c r="K78" t="s">
-        <v>980</v>
+        <v>952</v>
       </c>
       <c r="L78">
         <v>7.7564715726947338</v>
@@ -25253,7 +25253,7 @@
         <v>1347</v>
       </c>
       <c r="K79" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="L79">
         <v>59.663991486822887</v>
@@ -25288,7 +25288,7 @@
         <v>1349</v>
       </c>
       <c r="K80" t="s">
-        <v>944</v>
+        <v>906</v>
       </c>
       <c r="L80">
         <v>67.484986191080594</v>
@@ -25323,7 +25323,7 @@
         <v>1351</v>
       </c>
       <c r="K81" t="s">
-        <v>985</v>
+        <v>918</v>
       </c>
       <c r="L81">
         <v>8.9831631319223497</v>
@@ -25358,7 +25358,7 @@
         <v>1353</v>
       </c>
       <c r="K82" t="s">
-        <v>1033</v>
+        <v>967</v>
       </c>
       <c r="L82">
         <v>74.407838302658988</v>
@@ -25393,7 +25393,7 @@
         <v>1355</v>
       </c>
       <c r="K83" t="s">
-        <v>906</v>
+        <v>961</v>
       </c>
       <c r="L83">
         <v>66.237243466162568</v>
@@ -25428,7 +25428,7 @@
         <v>1357</v>
       </c>
       <c r="K84" t="s">
-        <v>912</v>
+        <v>989</v>
       </c>
       <c r="L84">
         <v>87.803826101842702</v>
@@ -25463,7 +25463,7 @@
         <v>1359</v>
       </c>
       <c r="K85" t="s">
-        <v>971</v>
+        <v>942</v>
       </c>
       <c r="L85">
         <v>13.111660750581855</v>
@@ -25498,7 +25498,7 @@
         <v>1361</v>
       </c>
       <c r="K86" t="s">
-        <v>1007</v>
+        <v>1036</v>
       </c>
       <c r="L86">
         <v>28.441848841140754</v>
@@ -25533,7 +25533,7 @@
         <v>1363</v>
       </c>
       <c r="K87" t="s">
-        <v>975</v>
+        <v>946</v>
       </c>
       <c r="L87">
         <v>143.86519004409737</v>
@@ -25568,7 +25568,7 @@
         <v>1365</v>
       </c>
       <c r="K88" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
       <c r="L88">
         <v>2.4247911368184991</v>
@@ -25603,7 +25603,7 @@
         <v>1367</v>
       </c>
       <c r="K89" t="s">
-        <v>1005</v>
+        <v>1034</v>
       </c>
       <c r="L89">
         <v>1.2775502846450904</v>
@@ -25638,7 +25638,7 @@
         <v>1369</v>
       </c>
       <c r="K90" t="s">
-        <v>956</v>
+        <v>1019</v>
       </c>
       <c r="L90">
         <v>13.425882161067216</v>
@@ -25673,7 +25673,7 @@
         <v>1371</v>
       </c>
       <c r="K91" t="s">
-        <v>925</v>
+        <v>956</v>
       </c>
       <c r="L91">
         <v>2.4640928691199862</v>
@@ -25708,7 +25708,7 @@
         <v>1373</v>
       </c>
       <c r="K92" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="L92">
         <v>121.00853795417976</v>
@@ -25743,7 +25743,7 @@
         <v>1375</v>
       </c>
       <c r="K93" t="s">
-        <v>929</v>
+        <v>995</v>
       </c>
       <c r="L93">
         <v>124.790495670129</v>
@@ -25778,7 +25778,7 @@
         <v>1377</v>
       </c>
       <c r="K94" t="s">
-        <v>982</v>
+        <v>1002</v>
       </c>
       <c r="L94">
         <v>76.573281453558408</v>
@@ -25813,7 +25813,7 @@
         <v>1379</v>
       </c>
       <c r="K95" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="L95">
         <v>83.622813239085914</v>
@@ -25848,7 +25848,7 @@
         <v>1381</v>
       </c>
       <c r="K96" t="s">
-        <v>959</v>
+        <v>1022</v>
       </c>
       <c r="L96">
         <v>98.771916583186524</v>
@@ -25883,7 +25883,7 @@
         <v>1383</v>
       </c>
       <c r="K97" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="L97">
         <v>113.7602367199374</v>
@@ -25918,7 +25918,7 @@
         <v>1385</v>
       </c>
       <c r="K98" t="s">
-        <v>947</v>
+        <v>909</v>
       </c>
       <c r="L98">
         <v>106.58940043603886</v>
@@ -25953,7 +25953,7 @@
         <v>1387</v>
       </c>
       <c r="K99" t="s">
-        <v>907</v>
+        <v>962</v>
       </c>
       <c r="L99">
         <v>82.155437931771587</v>
@@ -25988,7 +25988,7 @@
         <v>1389</v>
       </c>
       <c r="K100" t="s">
-        <v>1020</v>
+        <v>1006</v>
       </c>
       <c r="L100">
         <v>129.44215482043572</v>
@@ -26023,7 +26023,7 @@
         <v>1391</v>
       </c>
       <c r="K101" t="s">
-        <v>972</v>
+        <v>943</v>
       </c>
       <c r="L101">
         <v>0.89144958684441589</v>
@@ -26058,7 +26058,7 @@
         <v>1393</v>
       </c>
       <c r="K102" t="s">
-        <v>1012</v>
+        <v>982</v>
       </c>
       <c r="L102">
         <v>75.325753274416684</v>
@@ -26093,7 +26093,7 @@
         <v>1395</v>
       </c>
       <c r="K103" t="s">
-        <v>923</v>
+        <v>954</v>
       </c>
       <c r="L103">
         <v>22.126012715065421</v>
@@ -26128,7 +26128,7 @@
         <v>1397</v>
       </c>
       <c r="K104" t="s">
-        <v>1010</v>
+        <v>980</v>
       </c>
       <c r="L104">
         <v>65.153596720209478</v>
@@ -26163,7 +26163,7 @@
         <v>1399</v>
       </c>
       <c r="K105" t="s">
-        <v>905</v>
+        <v>960</v>
       </c>
       <c r="L105">
         <v>111.2273781855134</v>
@@ -26198,7 +26198,7 @@
         <v>1401</v>
       </c>
       <c r="K106" t="s">
-        <v>1004</v>
+        <v>1033</v>
       </c>
       <c r="L106">
         <v>16.632205399674447</v>
@@ -26233,7 +26233,7 @@
         <v>1403</v>
       </c>
       <c r="K107" t="s">
-        <v>943</v>
+        <v>905</v>
       </c>
       <c r="L107">
         <v>47.109387092480588</v>
@@ -26248,7 +26248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{516A802A-7610-4CB6-80F7-D7944111E1A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1966218-81A4-4F32-B71F-27264B226C8D}">
   <dimension ref="B9:Y136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CD6397-0FCC-429B-B287-BD93F9E5D9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F99A06A-E1CF-47B5-9F07-5B966712EBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,18 +1403,456 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_AUS_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_AUS_040</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 40</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_AUS_037</t>
   </si>
   <si>
@@ -1505,180 +1943,6 @@
     <t>connecting solar to buses in cluster 79</t>
   </si>
   <si>
-    <t>distr_solelc_spv_AUS_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_AUS_072</t>
   </si>
   <si>
@@ -1727,288 +1991,180 @@
     <t>connecting solar to buses in cluster 90</t>
   </si>
   <si>
-    <t>distr_solelc_spv_AUS_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Karratha_AUS,e_TomPriceMine_AUS,e_AUS22p9S118p7E_AUS,e_PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>e_PortHedland_AUS,e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS</t>
+  </si>
+  <si>
+    <t>e_MountPiper_AUS,e_Armidale_AUS</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_Robertstown_AUS,e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS,e_Para_AUS</t>
+  </si>
+  <si>
+    <t>e_MountPiper_AUS,e_Armidale_AUS,e_BulliCreek_AUS,e_CentralCoast_AUS</t>
+  </si>
+  <si>
+    <t>e_Broadsound_AUS,e_WandoanSouth_AUS</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS</t>
+  </si>
+  <si>
+    <t>e_Morawa_AUS,e_Merredin_AUS,e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_Kalgoorlie_AUS,e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_AUS22p9S118p7E_AUS,e_Chalumbin_AUS,e_Davenport_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_Robertstown_AUS,e_Para_AUS,e_Balranald_AUS,e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS,e_Broadsound_AUS,e_Strathmore_AUS</t>
+  </si>
+  <si>
+    <t>e_SydneyWest_AUS,e_MountPiper_AUS,e_CentralCoast_AUS</t>
+  </si>
+  <si>
+    <t>e_Perth_AUS,e_Yandin_AUS,e_Australind_AUS</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS,e_Merredin_AUS,e_Morawa_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_Chalumbin_AUS,e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>e_Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>e_Merredin_AUS,e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>e_Para_AUS</t>
+  </si>
+  <si>
+    <t>e_Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>e_Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>e_TomPriceMine_AUS,e_Morawa_AUS,e_AUS22p9S118p7E_AUS,e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_Strathmore_AUS,e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS,e_Horsham_AUS,e_Ballarat_AUS</t>
+  </si>
+  <si>
+    <t>e_Balranald_AUS,e_SouthMorang_AUS,e_DarlingtonPoint_AUS</t>
+  </si>
+  <si>
+    <t>e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS,e_BulliCreek_AUS</t>
+  </si>
+  <si>
+    <t>e_Morawa_AUS,e_TomPriceMine_AUS,e_Karratha_AUS</t>
+  </si>
+  <si>
+    <t>e_TomPriceMine_AUS,e_Karratha_AUS,e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>e_AUS22p9S118p7E_AUS,e_PortHedland_AUS,e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS,e_Ballarat_AUS,e_SouthMorang_AUS</t>
+  </si>
+  <si>
+    <t>e_Ballarat_AUS,e_Rowville_AUS,e_SouthMorang_AUS,e_Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>e_SouthMorang_AUS,e_DarlingtonPoint_AUS,e_Wagga_AUS</t>
+  </si>
+  <si>
+    <t>e_Murray_AUS,e_Canberra_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_Robertstown_AUS,e_Para_AUS</t>
+  </si>
+  <si>
+    <t>e_SouthMorang_AUS,e_Sheffield_AUS,e_Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>e_Strathmore_AUS,e_Nebo_AUS,e_Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>e_Murray_AUS,e_Wagga_AUS,e_UpperTumut_AUS</t>
+  </si>
+  <si>
+    <t>e_Strathmore_AUS,e_Nebo_AUS,e_Broadsound_AUS,e_Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>e_BulliCreek_AUS,e_Tarong_AUS,e_Armidale_AUS,e_Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>e_Balranald_AUS,e_BrokenHill_AUS,e_DarlingtonPoint_AUS</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS,e_Broadsound_AUS,e_Calvale_AUS,e_Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>e_Canberra_AUS,e_MountPiper_AUS,e_SydneyWest_AUS</t>
+  </si>
+  <si>
+    <t>e_AUS22p9S118p7E_AUS,e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_AUS22p9S118p7E_AUS,e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>e_BrokenHill_AUS,e_WandoanSouth_AUS,e_MountPiper_AUS</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS,e_BrokenHill_AUS,e_Broadsound_AUS,e_WandoanSouth_AUS</t>
+  </si>
+  <si>
+    <t>e_Wagga_AUS,e_UpperTumut_AUS,e_Canberra_AUS,e_MountPiper_AUS</t>
+  </si>
+  <si>
     <t>e_Morawa_AUS,e_Kalgoorlie_AUS</t>
   </si>
   <si>
     <t>e_PortHedland_AUS,e_AUS22p9S118p7E_AUS,e_Chalumbin_AUS</t>
   </si>
   <si>
-    <t>e_Davenport_AUS</t>
-  </si>
-  <si>
-    <t>e_Chalumbin_AUS</t>
-  </si>
-  <si>
     <t>e_DarlingtonPoint_AUS,e_Wagga_AUS,e_MountPiper_AUS</t>
   </si>
   <si>
@@ -2018,9 +2174,6 @@
     <t>e_Morawa_AUS,e_TomPriceMine_AUS</t>
   </si>
   <si>
-    <t>e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
     <t>e_Horsham_AUS,e_Balranald_AUS,e_Ballarat_AUS,e_Rowville_AUS,e_SouthMorang_AUS,e_Hazelwood_AUS</t>
   </si>
   <si>
@@ -2033,163 +2186,316 @@
     <t>e_Broadsound_AUS,e_Calvale_AUS,e_Bouldercombe_AUS,e_Tarong_AUS,e_GinGin_AUS,e_CalliopeRiver_AUS,e_Brisbane_AUS</t>
   </si>
   <si>
-    <t>e_Perth_AUS,e_Yandin_AUS,e_Australind_AUS</t>
-  </si>
-  <si>
-    <t>e_Australind_AUS,e_Merredin_AUS,e_Morawa_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_Chalumbin_AUS,e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>e_Hazelwood_AUS</t>
-  </si>
-  <si>
-    <t>e_AUS22p9S118p7E_AUS,e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>e_AUS22p9S118p7E_AUS,e_Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>e_BrokenHill_AUS,e_WandoanSouth_AUS,e_MountPiper_AUS</t>
-  </si>
-  <si>
-    <t>e_Broadsound_AUS,e_WandoanSouth_AUS</t>
-  </si>
-  <si>
-    <t>e_Balranald_AUS,e_BrokenHill_AUS,e_DarlingtonPoint_AUS</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS,e_Broadsound_AUS,e_Calvale_AUS,e_Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS,e_BulliCreek_AUS</t>
-  </si>
-  <si>
-    <t>e_Canberra_AUS,e_MountPiper_AUS,e_SydneyWest_AUS</t>
-  </si>
-  <si>
-    <t>e_PortHedland_AUS,e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS,e_Horsham_AUS,e_Ballarat_AUS</t>
-  </si>
-  <si>
-    <t>e_Balranald_AUS,e_SouthMorang_AUS,e_DarlingtonPoint_AUS</t>
-  </si>
-  <si>
-    <t>e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_Robertstown_AUS,e_Para_AUS</t>
-  </si>
-  <si>
-    <t>e_SouthMorang_AUS,e_Sheffield_AUS,e_Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>e_Strathmore_AUS,e_Nebo_AUS,e_Broadsound_AUS</t>
-  </si>
-  <si>
-    <t>e_Murray_AUS,e_Wagga_AUS,e_UpperTumut_AUS</t>
-  </si>
-  <si>
-    <t>e_Strathmore_AUS,e_Nebo_AUS,e_Broadsound_AUS,e_Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>e_BulliCreek_AUS,e_Tarong_AUS,e_Armidale_AUS,e_Brisbane_AUS</t>
-  </si>
-  <si>
     <t>e_Australind_AUS,e_Merredin_AUS</t>
   </si>
   <si>
-    <t>e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
     <t>e_CentralCoast_AUS,e_Armidale_AUS</t>
   </si>
   <si>
-    <t>e_Australind_AUS</t>
-  </si>
-  <si>
-    <t>e_Morawa_AUS,e_Merredin_AUS,e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>e_Kalgoorlie_AUS,e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>e_AUS22p9S118p7E_AUS,e_Chalumbin_AUS,e_Davenport_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_Robertstown_AUS,e_Para_AUS,e_Balranald_AUS,e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>e_Chalumbin_AUS,e_Broadsound_AUS,e_Strathmore_AUS</t>
-  </si>
-  <si>
-    <t>e_SydneyWest_AUS,e_MountPiper_AUS,e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>e_TomPriceMine_AUS,e_Morawa_AUS,e_AUS22p9S118p7E_AUS,e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>e_Strathmore_AUS,e_Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>e_Chalumbin_AUS,e_BrokenHill_AUS,e_Broadsound_AUS,e_WandoanSouth_AUS</t>
-  </si>
-  <si>
-    <t>e_Wagga_AUS,e_UpperTumut_AUS,e_Canberra_AUS,e_MountPiper_AUS</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS,e_TomPriceMine_AUS,e_AUS22p9S118p7E_AUS,e_PortHedland_AUS</t>
-  </si>
-  <si>
-    <t>e_MountPiper_AUS,e_Armidale_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_Robertstown_AUS,e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS,e_Para_AUS</t>
-  </si>
-  <si>
-    <t>e_MountPiper_AUS,e_Armidale_AUS,e_BulliCreek_AUS,e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>e_Merredin_AUS,e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>e_Para_AUS</t>
-  </si>
-  <si>
-    <t>e_Broadsound_AUS</t>
-  </si>
-  <si>
-    <t>e_Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>e_Morawa_AUS,e_TomPriceMine_AUS,e_Karratha_AUS</t>
-  </si>
-  <si>
-    <t>e_TomPriceMine_AUS,e_Karratha_AUS,e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>e_AUS22p9S118p7E_AUS,e_PortHedland_AUS,e_Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS,e_Ballarat_AUS,e_SouthMorang_AUS</t>
-  </si>
-  <si>
-    <t>e_Ballarat_AUS,e_Rowville_AUS,e_SouthMorang_AUS,e_Hazelwood_AUS</t>
-  </si>
-  <si>
-    <t>e_SouthMorang_AUS,e_DarlingtonPoint_AUS,e_Wagga_AUS</t>
-  </si>
-  <si>
-    <t>e_Murray_AUS,e_Canberra_AUS</t>
+    <t>distr_wonelc_won_AUS_071</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_095</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_073</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_089</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_078</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_090</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_084</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_093</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_081</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_096</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_079</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_076</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_097</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_070</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_088</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_082</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_087</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
   </si>
   <si>
     <t>distr_wonelc_won_AUS_094</t>
@@ -2222,6 +2528,162 @@
     <t>connecting wind onshore to buses in cluster 54</t>
   </si>
   <si>
+    <t>distr_wonelc_won_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_072</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_075</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_091</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_085</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_077</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_080</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_086</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_AUS_053</t>
   </si>
   <si>
@@ -2252,252 +2714,6 @@
     <t>connecting wind onshore to buses in cluster 59</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_072</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_071</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_095</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_073</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_089</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_078</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_090</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_096</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_079</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_076</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_075</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_091</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_085</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_077</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_AUS_083</t>
   </si>
   <si>
@@ -2528,162 +2744,6 @@
     <t>connecting wind onshore to buses in cluster 63</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_084</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_080</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_086</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_097</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_070</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_088</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_AUS_074</t>
   </si>
   <si>
@@ -2714,64 +2774,208 @@
     <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_082</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_087</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_093</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_081</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>elc_won_AUS_071</t>
+  </si>
+  <si>
+    <t>e_Perth_AUS,e_Yandin_AUS,e_Morawa_AUS,e_Merredin_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_029</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_016</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_014</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_021</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_011</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_041</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_066</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS,e_MountPiper_AUS,e_BulliCreek_AUS,e_Armidale_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_056</t>
+  </si>
+  <si>
+    <t>e_Armidale_AUS,e_BulliCreek_AUS,e_Tarong_AUS,e_Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_095</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_073</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_089</t>
+  </si>
+  <si>
+    <t>e_Kalgoorlie_AUS,e_AUS22p9S118p7E_AUS,e_Davenport_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_064</t>
+  </si>
+  <si>
+    <t>e_Canberra_AUS,e_SydneyWest_AUS,e_CentralCoast_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_060</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_078</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_090</t>
+  </si>
+  <si>
+    <t>e_TomPriceMine_AUS,e_PortHedland_AUS,e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_020</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_045</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS,e_Davenport_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_012</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_034</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS,e_Para_AUS,e_Horsham_AUS,e_Balranald_AUS,e_Ballarat_AUS,e_SouthMorang_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_010</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_003</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_055</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS,e_BulliCreek_AUS,e_Armidale_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_062</t>
+  </si>
+  <si>
+    <t>e_Canberra_AUS,e_MountPiper_AUS,e_SydneyWest_AUS,e_CentralCoast_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_084</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_013</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_046</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_093</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS,e_TomPriceMine_AUS,e_PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_081</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_026</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_015</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_007</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_096</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS,e_TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_079</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS,e_Perth_AUS,e_Yandin_AUS,e_Merredin_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_076</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_024</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_004</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_097</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_070</t>
+  </si>
+  <si>
+    <t>e_Morawa_AUS,e_Merredin_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_017</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_088</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_AUS22p9S118p7E_AUS,e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_052</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_037</t>
+  </si>
+  <si>
+    <t>e_Balranald_AUS,e_Horsham_AUS,e_Ballarat_AUS,e_SouthMorang_AUS,e_DarlingtonPoint_AUS,e_Wagga_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_002</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_006</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS,e_Strathmore_AUS,e_Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_067</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_069</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_082</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_087</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_028</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_044</t>
   </si>
   <si>
     <t>elc_won_AUS_094</t>
@@ -2801,6 +3005,120 @@
     <t>e_WandoanSouth_AUS,e_BulliCreek_AUS,e_Armidale_AUS,e_Tarong_AUS</t>
   </si>
   <si>
+    <t>elc_won_AUS_035</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_036</t>
+  </si>
+  <si>
+    <t>e_BrokenHill_AUS,e_Balranald_AUS,e_DarlingtonPoint_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_033</t>
+  </si>
+  <si>
+    <t>e_SouthMorang_AUS,e_Sheffield_AUS,e_Rowville_AUS,e_Hazelwood_AUS,e_Palmerston_AUS,e_Murray_AUS,e_Canberra_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_065</t>
+  </si>
+  <si>
+    <t>e_BrokenHill_AUS,e_DarlingtonPoint_AUS,e_MountPiper_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_072</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_049</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_008</t>
+  </si>
+  <si>
+    <t>e_Broadsound_AUS,e_Nebo_AUS,e_Strathmore_AUS,e_Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_057</t>
+  </si>
+  <si>
+    <t>e_Armidale_AUS,e_Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_075</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_091</t>
+  </si>
+  <si>
+    <t>e_PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_085</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_077</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_050</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_051</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS,e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_030</t>
+  </si>
+  <si>
+    <t>e_Rowville_AUS,e_Hazelwood_AUS,e_SouthMorang_AUS,e_Murray_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_068</t>
+  </si>
+  <si>
+    <t>e_MountPiper_AUS,e_UpperTumut_AUS,e_Wagga_AUS,e_Canberra_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_080</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_027</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_086</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_048</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_019</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_040</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_039</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_043</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS,e_Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_031</t>
+  </si>
+  <si>
+    <t>e_Murray_AUS,e_Wagga_AUS,e_UpperTumut_AUS,e_Canberra_AUS</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_061</t>
+  </si>
+  <si>
+    <t>e_MountPiper_AUS,e_Armidale_AUS,e_CentralCoast_AUS</t>
+  </si>
+  <si>
     <t>elc_won_AUS_053</t>
   </si>
   <si>
@@ -2822,183 +3140,6 @@
     <t>e_Broadsound_AUS,e_Bouldercombe_AUS,e_GinGin_AUS,e_CalliopeRiver_AUS,e_Tarong_AUS,e_Brisbane_AUS</t>
   </si>
   <si>
-    <t>elc_won_AUS_072</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_049</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_008</t>
-  </si>
-  <si>
-    <t>e_Broadsound_AUS,e_Nebo_AUS,e_Strathmore_AUS,e_Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_057</t>
-  </si>
-  <si>
-    <t>e_Armidale_AUS,e_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_071</t>
-  </si>
-  <si>
-    <t>e_Perth_AUS,e_Yandin_AUS,e_Morawa_AUS,e_Merredin_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_029</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_016</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_014</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_021</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_011</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_041</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_066</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS,e_MountPiper_AUS,e_BulliCreek_AUS,e_Armidale_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_056</t>
-  </si>
-  <si>
-    <t>e_Armidale_AUS,e_BulliCreek_AUS,e_Tarong_AUS,e_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_095</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_073</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_089</t>
-  </si>
-  <si>
-    <t>e_Kalgoorlie_AUS,e_AUS22p9S118p7E_AUS,e_Davenport_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_064</t>
-  </si>
-  <si>
-    <t>e_Canberra_AUS,e_SydneyWest_AUS,e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_060</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_078</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_090</t>
-  </si>
-  <si>
-    <t>e_TomPriceMine_AUS,e_PortHedland_AUS,e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_020</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_045</t>
-  </si>
-  <si>
-    <t>e_Chalumbin_AUS,e_Davenport_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_012</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_034</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS,e_Para_AUS,e_Horsham_AUS,e_Balranald_AUS,e_Ballarat_AUS,e_SouthMorang_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_010</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_003</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_055</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS,e_BulliCreek_AUS,e_Armidale_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_062</t>
-  </si>
-  <si>
-    <t>e_Canberra_AUS,e_MountPiper_AUS,e_SydneyWest_AUS,e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_096</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS,e_TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_079</t>
-  </si>
-  <si>
-    <t>e_Australind_AUS,e_Perth_AUS,e_Yandin_AUS,e_Merredin_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_076</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_024</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_004</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_075</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_091</t>
-  </si>
-  <si>
-    <t>e_PortHedland_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_085</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_077</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_050</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_051</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_030</t>
-  </si>
-  <si>
-    <t>e_Rowville_AUS,e_Hazelwood_AUS,e_SouthMorang_AUS,e_Murray_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_068</t>
-  </si>
-  <si>
-    <t>e_MountPiper_AUS,e_UpperTumut_AUS,e_Wagga_AUS,e_Canberra_AUS</t>
-  </si>
-  <si>
     <t>elc_won_AUS_083</t>
   </si>
   <si>
@@ -3020,114 +3161,6 @@
     <t>elc_won_AUS_063</t>
   </si>
   <si>
-    <t>elc_won_AUS_084</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_013</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_046</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_080</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_027</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_086</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_048</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_019</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_040</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_039</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_043</t>
-  </si>
-  <si>
-    <t>e_Chalumbin_AUS,e_Broadsound_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_031</t>
-  </si>
-  <si>
-    <t>e_Murray_AUS,e_Wagga_AUS,e_UpperTumut_AUS,e_Canberra_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_061</t>
-  </si>
-  <si>
-    <t>e_MountPiper_AUS,e_Armidale_AUS,e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_035</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_036</t>
-  </si>
-  <si>
-    <t>e_BrokenHill_AUS,e_Balranald_AUS,e_DarlingtonPoint_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_033</t>
-  </si>
-  <si>
-    <t>e_SouthMorang_AUS,e_Sheffield_AUS,e_Rowville_AUS,e_Hazelwood_AUS,e_Palmerston_AUS,e_Murray_AUS,e_Canberra_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_065</t>
-  </si>
-  <si>
-    <t>e_BrokenHill_AUS,e_DarlingtonPoint_AUS,e_MountPiper_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_097</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_070</t>
-  </si>
-  <si>
-    <t>e_Morawa_AUS,e_Merredin_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_017</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_088</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS,e_AUS22p9S118p7E_AUS,e_Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_052</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_037</t>
-  </si>
-  <si>
-    <t>e_Balranald_AUS,e_Horsham_AUS,e_Ballarat_AUS,e_SouthMorang_AUS,e_DarlingtonPoint_AUS,e_Wagga_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_002</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_006</t>
-  </si>
-  <si>
-    <t>e_Chalumbin_AUS,e_Strathmore_AUS,e_Broadsound_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_067</t>
-  </si>
-  <si>
     <t>elc_won_AUS_074</t>
   </si>
   <si>
@@ -3146,37 +3179,106 @@
     <t>e_Chalumbin_AUS,e_Davenport_AUS,e_BrokenHill_AUS</t>
   </si>
   <si>
-    <t>elc_won_AUS_069</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_082</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_087</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_028</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_044</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_093</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS,e_TomPriceMine_AUS,e_PortHedland_AUS</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_081</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_026</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_015</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_007</t>
+    <t>distr_wofelc_wof_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_046</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
   </si>
   <si>
     <t>distr_wofelc_wof_AUS_025</t>
@@ -3215,88 +3317,106 @@
     <t>connecting wind offshore to buses in cluster 41</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_046</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
+    <t>distr_wofelc_wof_AUS_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_048</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_045</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_AUS_012</t>
@@ -3317,10 +3437,16 @@
     <t>connecting wind offshore to buses in cluster 51</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
+    <t>distr_wofelc_wof_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wofelc_wof_AUS_024</t>
@@ -3341,132 +3467,6 @@
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_048</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_045</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_AUS_042</t>
   </si>
   <si>
@@ -3491,6 +3491,66 @@
     <t>connecting wind offshore to buses in cluster 47</t>
   </si>
   <si>
+    <t>elc_wof_AUS_029</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_004</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_037</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_039</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_035</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_027</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_016</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS,e_Perth_AUS,e_Yandin_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_014</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_046</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_011</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS,e_Ballarat_AUS,e_SouthMorang_AUS,e_Rowville_AUS,e_Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_030</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_015</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_040</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_008</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_028</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_003</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_036</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_025</t>
   </si>
   <si>
@@ -3518,55 +3578,76 @@
     <t>elc_wof_AUS_041</t>
   </si>
   <si>
-    <t>elc_wof_AUS_029</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_004</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_037</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_039</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_035</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_030</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_015</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_040</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_008</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_027</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_016</t>
-  </si>
-  <si>
-    <t>e_Australind_AUS,e_Perth_AUS,e_Yandin_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_014</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_046</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_011</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS,e_Ballarat_AUS,e_SouthMorang_AUS,e_Rowville_AUS,e_Hazelwood_AUS</t>
+    <t>elc_wof_AUS_017</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_018</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS,e_Merredin_AUS,e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_022</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_043</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_009</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_032</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_001</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_034</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_026</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_031</t>
+  </si>
+  <si>
+    <t>e_GinGin_AUS,e_Brisbane_AUS,e_Tarong_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_005</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_013</t>
+  </si>
+  <si>
+    <t>e_Sheffield_AUS,e_Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_048</t>
+  </si>
+  <si>
+    <t>e_Nebo_AUS,e_Bouldercombe_AUS,e_Broadsound_AUS,e_CalliopeRiver_AUS,e_GinGin_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_033</t>
+  </si>
+  <si>
+    <t>e_Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_021</t>
+  </si>
+  <si>
+    <t>e_Kalgoorlie_AUS,e_Davenport_AUS</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_045</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_006</t>
+  </si>
+  <si>
+    <t>e_Hazelwood_AUS,e_Murray_AUS</t>
   </si>
   <si>
     <t>elc_wof_AUS_012</t>
@@ -3584,10 +3665,10 @@
     <t>e_Chalumbin_AUS,e_Strathmore_AUS,e_CalliopeRiver_AUS</t>
   </si>
   <si>
-    <t>elc_wof_AUS_021</t>
-  </si>
-  <si>
-    <t>e_Kalgoorlie_AUS,e_Davenport_AUS</t>
+    <t>elc_wof_AUS_052</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_007</t>
   </si>
   <si>
     <t>elc_wof_AUS_024</t>
@@ -3603,87 +3684,6 @@
   </si>
   <si>
     <t>e_Davenport_AUS,e_Robertstown_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_005</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_013</t>
-  </si>
-  <si>
-    <t>e_Sheffield_AUS,e_Hazelwood_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_048</t>
-  </si>
-  <si>
-    <t>e_Nebo_AUS,e_Bouldercombe_AUS,e_Broadsound_AUS,e_CalliopeRiver_AUS,e_GinGin_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_033</t>
-  </si>
-  <si>
-    <t>e_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_028</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_003</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_036</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_052</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_007</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_026</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_031</t>
-  </si>
-  <si>
-    <t>e_GinGin_AUS,e_Brisbane_AUS,e_Tarong_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_017</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_018</t>
-  </si>
-  <si>
-    <t>e_Australind_AUS,e_Merredin_AUS,e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_022</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_043</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_009</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_032</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_045</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_006</t>
-  </si>
-  <si>
-    <t>e_Hazelwood_AUS,e_Murray_AUS</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_001</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_034</t>
   </si>
   <si>
     <t>elc_wof_AUS_042</t>
@@ -8327,7 +8327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DAC219-AA72-4122-94F0-C0BD43DFC404}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B0176A7-5531-4320-B9D7-75C83C755B9E}">
   <dimension ref="B9:BD107"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8565,16 +8565,16 @@
         <v>446</v>
       </c>
       <c r="Y11" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="Z11" t="s">
         <v>644</v>
       </c>
       <c r="AA11">
-        <v>0.98507000954579316</v>
+        <v>0.99515580458889907</v>
       </c>
       <c r="AB11">
-        <v>273.71649166045961</v>
+        <v>88.81024920351615</v>
       </c>
       <c r="AD11" t="s">
         <v>445</v>
@@ -8607,10 +8607,10 @@
         <v>904</v>
       </c>
       <c r="AO11">
-        <v>0.99423423237135644</v>
+        <v>0.99573205734141002</v>
       </c>
       <c r="AP11">
-        <v>105.70573985846545</v>
+        <v>78.245615407483584</v>
       </c>
       <c r="AR11" t="s">
         <v>445</v>
@@ -8643,10 +8643,10 @@
         <v>1143</v>
       </c>
       <c r="BC11">
-        <v>0.98725104910668715</v>
+        <v>0.99059368543056114</v>
       </c>
       <c r="BD11">
-        <v>899.92471838352765</v>
+        <v>850.28743134038859</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8711,16 +8711,16 @@
         <v>450</v>
       </c>
       <c r="Y12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Z12" t="s">
         <v>645</v>
       </c>
       <c r="AA12">
-        <v>0.95257490531108058</v>
+        <v>0.96473247588547761</v>
       </c>
       <c r="AB12">
-        <v>869.46006929685575</v>
+        <v>646.57127543291119</v>
       </c>
       <c r="AD12" t="s">
         <v>445</v>
@@ -8750,13 +8750,13 @@
         <v>905</v>
       </c>
       <c r="AN12" t="s">
-        <v>668</v>
+        <v>694</v>
       </c>
       <c r="AO12">
-        <v>0.96634981065643422</v>
+        <v>0.93728012376790604</v>
       </c>
       <c r="AP12">
-        <v>616.9201379653731</v>
+        <v>1149.8643975883897</v>
       </c>
       <c r="AR12" t="s">
         <v>445</v>
@@ -8786,13 +8786,13 @@
         <v>1144</v>
       </c>
       <c r="BB12" t="s">
-        <v>1145</v>
+        <v>995</v>
       </c>
       <c r="BC12">
-        <v>0.98942049804970167</v>
+        <v>0.97057573829724286</v>
       </c>
       <c r="BD12">
-        <v>873.49359876113442</v>
+        <v>1103.0855884119239</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8857,16 +8857,16 @@
         <v>452</v>
       </c>
       <c r="Y13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Z13" t="s">
         <v>646</v>
       </c>
       <c r="AA13">
-        <v>0.9934232231965805</v>
+        <v>0.9580334555499519</v>
       </c>
       <c r="AB13">
-        <v>120.5742413960235</v>
+        <v>769.38664825088097</v>
       </c>
       <c r="AD13" t="s">
         <v>445</v>
@@ -8896,13 +8896,13 @@
         <v>906</v>
       </c>
       <c r="AN13" t="s">
-        <v>907</v>
+        <v>648</v>
       </c>
       <c r="AO13">
-        <v>0.99393164723700467</v>
+        <v>0.97740985609297437</v>
       </c>
       <c r="AP13">
-        <v>111.25313398824829</v>
+        <v>414.15263829547018</v>
       </c>
       <c r="AR13" t="s">
         <v>445</v>
@@ -8929,16 +8929,16 @@
         <v>1042</v>
       </c>
       <c r="BA13" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="BB13" t="s">
-        <v>1147</v>
+        <v>995</v>
       </c>
       <c r="BC13">
-        <v>0.92540139052362402</v>
+        <v>0.93603050407099908</v>
       </c>
       <c r="BD13">
-        <v>1653.4597254538478</v>
+        <v>1523.9616920683277</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -9003,16 +9003,16 @@
         <v>454</v>
       </c>
       <c r="Y14" t="s">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="Z14" t="s">
         <v>647</v>
       </c>
       <c r="AA14">
-        <v>0.98371921732749934</v>
+        <v>0.98447946182885371</v>
       </c>
       <c r="AB14">
-        <v>298.48101566251137</v>
+        <v>284.54319980434889</v>
       </c>
       <c r="AD14" t="s">
         <v>445</v>
@@ -9039,16 +9039,16 @@
         <v>715</v>
       </c>
       <c r="AM14" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AN14" t="s">
-        <v>909</v>
+        <v>648</v>
       </c>
       <c r="AO14">
-        <v>0.99746342019371192</v>
+        <v>0.97918864997471655</v>
       </c>
       <c r="AP14">
-        <v>46.503963115281117</v>
+        <v>381.5414171301972</v>
       </c>
       <c r="AR14" t="s">
         <v>445</v>
@@ -9075,16 +9075,16 @@
         <v>1044</v>
       </c>
       <c r="BA14" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="BB14" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="BC14">
-        <v>0.97283922785685117</v>
+        <v>0.96501627240771926</v>
       </c>
       <c r="BD14">
-        <v>1075.5087406106959</v>
+        <v>1170.8184144992874</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9149,16 +9149,16 @@
         <v>456</v>
       </c>
       <c r="Y15" t="s">
-        <v>442</v>
+        <v>368</v>
       </c>
       <c r="Z15" t="s">
         <v>648</v>
       </c>
       <c r="AA15">
-        <v>0.98946891329754838</v>
+        <v>0.94017535716671519</v>
       </c>
       <c r="AB15">
-        <v>193.0699228782787</v>
+        <v>1096.7851186102214</v>
       </c>
       <c r="AD15" t="s">
         <v>445</v>
@@ -9185,16 +9185,16 @@
         <v>717</v>
       </c>
       <c r="AM15" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="AN15" t="s">
-        <v>911</v>
+        <v>648</v>
       </c>
       <c r="AO15">
-        <v>0.99690141662376341</v>
+        <v>0.96550702044259584</v>
       </c>
       <c r="AP15">
-        <v>56.80736189767017</v>
+        <v>632.37129188574295</v>
       </c>
       <c r="AR15" t="s">
         <v>445</v>
@@ -9221,16 +9221,16 @@
         <v>1046</v>
       </c>
       <c r="BA15" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="BB15" t="s">
-        <v>647</v>
+        <v>992</v>
       </c>
       <c r="BC15">
-        <v>0.95074557504943547</v>
+        <v>0.99624960324149381</v>
       </c>
       <c r="BD15">
-        <v>1344.6830773143784</v>
+        <v>491.32518093986187</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9295,16 +9295,16 @@
         <v>458</v>
       </c>
       <c r="Y16" t="s">
-        <v>421</v>
+        <v>360</v>
       </c>
       <c r="Z16" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="AA16">
-        <v>0.99042712787144371</v>
+        <v>0.98182986571182285</v>
       </c>
       <c r="AB16">
-        <v>175.50265569019879</v>
+        <v>333.11912861658175</v>
       </c>
       <c r="AD16" t="s">
         <v>445</v>
@@ -9331,16 +9331,16 @@
         <v>719</v>
       </c>
       <c r="AM16" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="AN16" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AO16">
-        <v>0.97935848497620392</v>
+        <v>0.99191812933076651</v>
       </c>
       <c r="AP16">
-        <v>378.42777543626062</v>
+        <v>148.16762893594731</v>
       </c>
       <c r="AR16" t="s">
         <v>445</v>
@@ -9367,16 +9367,16 @@
         <v>1048</v>
       </c>
       <c r="BA16" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="BB16" t="s">
-        <v>647</v>
+        <v>702</v>
       </c>
       <c r="BC16">
-        <v>0.9534536251465805</v>
+        <v>0.96645436477691782</v>
       </c>
       <c r="BD16">
-        <v>1311.6900002974942</v>
+        <v>1153.2976558012185</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9441,16 +9441,16 @@
         <v>460</v>
       </c>
       <c r="Y17" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
       <c r="Z17" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AA17">
-        <v>0.98458760722006711</v>
+        <v>0.99024931522063975</v>
       </c>
       <c r="AB17">
-        <v>282.56053429877028</v>
+        <v>178.76255428827085</v>
       </c>
       <c r="AD17" t="s">
         <v>445</v>
@@ -9477,16 +9477,16 @@
         <v>721</v>
       </c>
       <c r="AM17" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="AN17" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="AO17">
-        <v>0.97738569554252064</v>
+        <v>0.97851296575183921</v>
       </c>
       <c r="AP17">
-        <v>414.59558172045399</v>
+        <v>393.92896121628166</v>
       </c>
       <c r="AR17" t="s">
         <v>445</v>
@@ -9513,16 +9513,16 @@
         <v>1050</v>
       </c>
       <c r="BA17" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="BB17" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="BC17">
-        <v>0.99059368543056114</v>
+        <v>0.99312868008939148</v>
       </c>
       <c r="BD17">
-        <v>850.28743134038859</v>
+        <v>689.39977032661727</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9587,16 +9587,16 @@
         <v>462</v>
       </c>
       <c r="Y18" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="Z18" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AA18">
-        <v>0.97454833391525864</v>
+        <v>0.99501647162473339</v>
       </c>
       <c r="AB18">
-        <v>466.6138782202575</v>
+        <v>91.364686879888396</v>
       </c>
       <c r="AD18" t="s">
         <v>445</v>
@@ -9623,16 +9623,16 @@
         <v>723</v>
       </c>
       <c r="AM18" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="AN18" t="s">
-        <v>647</v>
+        <v>912</v>
       </c>
       <c r="AO18">
-        <v>0.98739702445646216</v>
+        <v>0.97693095508317673</v>
       </c>
       <c r="AP18">
-        <v>231.05455163152675</v>
+        <v>422.93249014176001</v>
       </c>
       <c r="AR18" t="s">
         <v>445</v>
@@ -9659,16 +9659,16 @@
         <v>1052</v>
       </c>
       <c r="BA18" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="BB18" t="s">
-        <v>968</v>
+        <v>656</v>
       </c>
       <c r="BC18">
-        <v>0.97057573829724286</v>
+        <v>0.96520145465062446</v>
       </c>
       <c r="BD18">
-        <v>1103.0855884119239</v>
+        <v>1168.5622775065585</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9733,16 +9733,16 @@
         <v>464</v>
       </c>
       <c r="Y19" t="s">
-        <v>351</v>
+        <v>437</v>
       </c>
       <c r="Z19" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="AA19">
-        <v>0.95322333844045537</v>
+        <v>0.99545036495775863</v>
       </c>
       <c r="AB19">
-        <v>857.57212859165099</v>
+        <v>83.409975774425632</v>
       </c>
       <c r="AD19" t="s">
         <v>445</v>
@@ -9769,16 +9769,16 @@
         <v>725</v>
       </c>
       <c r="AM19" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="AN19" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="AO19">
-        <v>0.99755801237420683</v>
+        <v>0.9972902611932265</v>
       </c>
       <c r="AP19">
-        <v>44.769773139540511</v>
+        <v>49.678544790847084</v>
       </c>
       <c r="AR19" t="s">
         <v>445</v>
@@ -9805,16 +9805,16 @@
         <v>1054</v>
       </c>
       <c r="BA19" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="BB19" t="s">
-        <v>968</v>
+        <v>648</v>
       </c>
       <c r="BC19">
-        <v>0.93603050407099908</v>
+        <v>0.92803055709901694</v>
       </c>
       <c r="BD19">
-        <v>1523.9616920683277</v>
+        <v>1621.4277126769766</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9879,16 +9879,16 @@
         <v>466</v>
       </c>
       <c r="Y20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Z20" t="s">
         <v>646</v>
       </c>
       <c r="AA20">
-        <v>0.97321507838078658</v>
+        <v>0.95915670695527311</v>
       </c>
       <c r="AB20">
-        <v>491.05689635224547</v>
+        <v>748.79370581999342</v>
       </c>
       <c r="AD20" t="s">
         <v>445</v>
@@ -9915,16 +9915,16 @@
         <v>727</v>
       </c>
       <c r="AM20" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AN20" t="s">
-        <v>918</v>
+        <v>702</v>
       </c>
       <c r="AO20">
-        <v>0.99770486090207411</v>
+        <v>0.98256179218990303</v>
       </c>
       <c r="AP20">
-        <v>42.077550128640524</v>
+        <v>319.70047651844521</v>
       </c>
       <c r="AR20" t="s">
         <v>445</v>
@@ -9951,16 +9951,16 @@
         <v>1056</v>
       </c>
       <c r="BA20" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="BB20" t="s">
-        <v>647</v>
+        <v>1154</v>
       </c>
       <c r="BC20">
-        <v>0.96501627240771926</v>
+        <v>0.99716443001648403</v>
       </c>
       <c r="BD20">
-        <v>1170.8184144992874</v>
+        <v>433.2641749538127</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -10025,16 +10025,16 @@
         <v>468</v>
       </c>
       <c r="Y21" t="s">
-        <v>377</v>
+        <v>433</v>
       </c>
       <c r="Z21" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="AA21">
-        <v>0.98581703135158405</v>
+        <v>0.98266638110143478</v>
       </c>
       <c r="AB21">
-        <v>260.02109188762591</v>
+        <v>317.78301314036179</v>
       </c>
       <c r="AD21" t="s">
         <v>445</v>
@@ -10061,16 +10061,16 @@
         <v>729</v>
       </c>
       <c r="AM21" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="AN21" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="AO21">
-        <v>0.95226889215734378</v>
+        <v>0.97344873028830825</v>
       </c>
       <c r="AP21">
-        <v>875.07031044869723</v>
+        <v>486.77327804768265</v>
       </c>
       <c r="AR21" t="s">
         <v>445</v>
@@ -10097,16 +10097,16 @@
         <v>1058</v>
       </c>
       <c r="BA21" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="BB21" t="s">
-        <v>924</v>
+        <v>1143</v>
       </c>
       <c r="BC21">
-        <v>0.99624960324149381</v>
+        <v>0.98610600453861563</v>
       </c>
       <c r="BD21">
-        <v>491.32518093986187</v>
+        <v>913.8751780378667</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10171,16 +10171,16 @@
         <v>470</v>
       </c>
       <c r="Y22" t="s">
-        <v>376</v>
+        <v>417</v>
       </c>
       <c r="Z22" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="AA22">
-        <v>0.97542624087094398</v>
+        <v>0.99406720218050904</v>
       </c>
       <c r="AB22">
-        <v>450.51891736602602</v>
+        <v>108.76796002400131</v>
       </c>
       <c r="AD22" t="s">
         <v>445</v>
@@ -10207,16 +10207,16 @@
         <v>731</v>
       </c>
       <c r="AM22" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="AN22" t="s">
-        <v>646</v>
+        <v>918</v>
       </c>
       <c r="AO22">
-        <v>0.98244678792215867</v>
+        <v>0.94726945791757955</v>
       </c>
       <c r="AP22">
-        <v>321.80888809375716</v>
+        <v>966.72660484437438</v>
       </c>
       <c r="AR22" t="s">
         <v>445</v>
@@ -10243,16 +10243,16 @@
         <v>1060</v>
       </c>
       <c r="BA22" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="BB22" t="s">
-        <v>1152</v>
+        <v>656</v>
       </c>
       <c r="BC22">
-        <v>0.98610600453861563</v>
+        <v>0.972593868603152</v>
       </c>
       <c r="BD22">
-        <v>913.8751780378667</v>
+        <v>1078.4980341849312</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10317,16 +10317,16 @@
         <v>472</v>
       </c>
       <c r="Y23" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="Z23" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AA23">
-        <v>0.99745350130137034</v>
+        <v>0.99132119972938326</v>
       </c>
       <c r="AB23">
-        <v>46.685809474876969</v>
+        <v>159.11133829463989</v>
       </c>
       <c r="AD23" t="s">
         <v>445</v>
@@ -10353,16 +10353,16 @@
         <v>733</v>
       </c>
       <c r="AM23" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="AN23" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AO23">
-        <v>0.99244907456015963</v>
+        <v>0.99721814870334879</v>
       </c>
       <c r="AP23">
-        <v>138.43363306374022</v>
+        <v>51.000607105273012</v>
       </c>
       <c r="AR23" t="s">
         <v>445</v>
@@ -10389,16 +10389,16 @@
         <v>1062</v>
       </c>
       <c r="BA23" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="BB23" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="BC23">
-        <v>0.972593868603152</v>
+        <v>0.97474114937745526</v>
       </c>
       <c r="BD23">
-        <v>1078.4980341849312</v>
+        <v>1052.3369967513365</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10463,16 +10463,16 @@
         <v>474</v>
       </c>
       <c r="Y24" t="s">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="Z24" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AA24">
-        <v>0.98101450166571025</v>
+        <v>0.9643190988261251</v>
       </c>
       <c r="AB24">
-        <v>348.06746946197933</v>
+        <v>654.14985485437251</v>
       </c>
       <c r="AD24" t="s">
         <v>445</v>
@@ -10499,16 +10499,16 @@
         <v>735</v>
       </c>
       <c r="AM24" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="AN24" t="s">
-        <v>924</v>
+        <v>708</v>
       </c>
       <c r="AO24">
-        <v>0.99706791078062507</v>
+        <v>0.9965750017909164</v>
       </c>
       <c r="AP24">
-        <v>53.754969021872945</v>
+        <v>62.791633833199988</v>
       </c>
       <c r="AR24" t="s">
         <v>445</v>
@@ -10535,16 +10535,16 @@
         <v>1064</v>
       </c>
       <c r="BA24" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="BB24" t="s">
-        <v>647</v>
+        <v>669</v>
       </c>
       <c r="BC24">
-        <v>0.97474114937745526</v>
+        <v>0.99204121948401935</v>
       </c>
       <c r="BD24">
-        <v>1052.3369967513365</v>
+        <v>758.41727008090197</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10609,16 +10609,16 @@
         <v>476</v>
       </c>
       <c r="Y25" t="s">
-        <v>413</v>
+        <v>347</v>
       </c>
       <c r="Z25" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AA25">
-        <v>0.99489296223435719</v>
+        <v>0.96307923215762514</v>
       </c>
       <c r="AB25">
-        <v>93.629025703450537</v>
+        <v>676.88074377687337</v>
       </c>
       <c r="AD25" t="s">
         <v>445</v>
@@ -10645,16 +10645,16 @@
         <v>737</v>
       </c>
       <c r="AM25" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="AN25" t="s">
-        <v>926</v>
+        <v>707</v>
       </c>
       <c r="AO25">
-        <v>0.99573205734141002</v>
+        <v>0.98900028996553313</v>
       </c>
       <c r="AP25">
-        <v>78.245615407483584</v>
+        <v>201.66135063189321</v>
       </c>
       <c r="AR25" t="s">
         <v>445</v>
@@ -10681,16 +10681,16 @@
         <v>1066</v>
       </c>
       <c r="BA25" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="BB25" t="s">
-        <v>701</v>
+        <v>947</v>
       </c>
       <c r="BC25">
-        <v>0.99204121948401935</v>
+        <v>0.97834276564858003</v>
       </c>
       <c r="BD25">
-        <v>758.41727008090197</v>
+        <v>1008.4573051814666</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10755,16 +10755,16 @@
         <v>478</v>
       </c>
       <c r="Y26" t="s">
-        <v>425</v>
+        <v>358</v>
       </c>
       <c r="Z26" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AA26">
-        <v>0.99705259621301434</v>
+        <v>0.94315950804663551</v>
       </c>
       <c r="AB26">
-        <v>54.035736094736372</v>
+        <v>1042.0756858116829</v>
       </c>
       <c r="AD26" t="s">
         <v>445</v>
@@ -10791,16 +10791,16 @@
         <v>739</v>
       </c>
       <c r="AM26" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="AN26" t="s">
-        <v>661</v>
+        <v>924</v>
       </c>
       <c r="AO26">
-        <v>0.93728012376790604</v>
+        <v>0.98539636691491217</v>
       </c>
       <c r="AP26">
-        <v>1149.8643975883897</v>
+        <v>267.73327322661089</v>
       </c>
       <c r="AR26" t="s">
         <v>445</v>
@@ -10827,16 +10827,16 @@
         <v>1068</v>
       </c>
       <c r="BA26" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="BB26" t="s">
-        <v>650</v>
+        <v>995</v>
       </c>
       <c r="BC26">
-        <v>0.96645436477691782</v>
+        <v>0.97810798081469907</v>
       </c>
       <c r="BD26">
-        <v>1153.2976558012185</v>
+        <v>1011.3177670742492</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10901,16 +10901,16 @@
         <v>480</v>
       </c>
       <c r="Y27" t="s">
-        <v>422</v>
+        <v>366</v>
       </c>
       <c r="Z27" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="AA27">
-        <v>0.99830013108627691</v>
+        <v>0.96140892845075643</v>
       </c>
       <c r="AB27">
-        <v>31.164263418257661</v>
+        <v>707.50297840279961</v>
       </c>
       <c r="AD27" t="s">
         <v>445</v>
@@ -10937,16 +10937,16 @@
         <v>741</v>
       </c>
       <c r="AM27" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="AN27" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO27">
-        <v>0.97740985609297437</v>
+        <v>0.95721921641733843</v>
       </c>
       <c r="AP27">
-        <v>414.15263829547018</v>
+        <v>784.31436568212814</v>
       </c>
       <c r="AR27" t="s">
         <v>445</v>
@@ -10973,16 +10973,16 @@
         <v>1070</v>
       </c>
       <c r="BA27" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="BB27" t="s">
-        <v>1163</v>
+        <v>708</v>
       </c>
       <c r="BC27">
-        <v>0.99312868008939148</v>
+        <v>0.99215965418440455</v>
       </c>
       <c r="BD27">
-        <v>689.39977032661727</v>
+        <v>750.90061442978902</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -11047,16 +11047,16 @@
         <v>482</v>
       </c>
       <c r="Y28" t="s">
-        <v>424</v>
+        <v>369</v>
       </c>
       <c r="Z28" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="AA28">
-        <v>0.99408275357961784</v>
+        <v>0.93763052839116845</v>
       </c>
       <c r="AB28">
-        <v>108.48285104034026</v>
+        <v>1143.4403128285794</v>
       </c>
       <c r="AD28" t="s">
         <v>445</v>
@@ -11083,16 +11083,16 @@
         <v>743</v>
       </c>
       <c r="AM28" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="AN28" t="s">
-        <v>647</v>
+        <v>927</v>
       </c>
       <c r="AO28">
-        <v>0.97918864997471655</v>
+        <v>0.97128923400988465</v>
       </c>
       <c r="AP28">
-        <v>381.5414171301972</v>
+        <v>526.36404315211564</v>
       </c>
       <c r="AR28" t="s">
         <v>445</v>
@@ -11119,16 +11119,16 @@
         <v>1072</v>
       </c>
       <c r="BA28" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="BB28" t="s">
-        <v>651</v>
+        <v>1163</v>
       </c>
       <c r="BC28">
-        <v>0.96520145465062446</v>
+        <v>0.98725104910668715</v>
       </c>
       <c r="BD28">
-        <v>1168.5622775065585</v>
+        <v>899.92471838352765</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11193,16 +11193,16 @@
         <v>484</v>
       </c>
       <c r="Y29" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="Z29" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="AA29">
-        <v>0.9719447908127189</v>
+        <v>0.96169171176041801</v>
       </c>
       <c r="AB29">
-        <v>514.34550176681955</v>
+        <v>702.3186177256697</v>
       </c>
       <c r="AD29" t="s">
         <v>445</v>
@@ -11229,16 +11229,16 @@
         <v>745</v>
       </c>
       <c r="AM29" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="AN29" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO29">
-        <v>0.96550702044259584</v>
+        <v>0.98140230930972394</v>
       </c>
       <c r="AP29">
-        <v>632.37129188574295</v>
+        <v>340.95766265506029</v>
       </c>
       <c r="AR29" t="s">
         <v>445</v>
@@ -11265,16 +11265,16 @@
         <v>1074</v>
       </c>
       <c r="BA29" t="s">
+        <v>1164</v>
+      </c>
+      <c r="BB29" t="s">
         <v>1165</v>
       </c>
-      <c r="BB29" t="s">
-        <v>647</v>
-      </c>
       <c r="BC29">
-        <v>0.92803055709901694</v>
+        <v>0.98942049804970167</v>
       </c>
       <c r="BD29">
-        <v>1621.4277126769766</v>
+        <v>873.49359876113442</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11339,16 +11339,16 @@
         <v>486</v>
       </c>
       <c r="Y30" t="s">
-        <v>406</v>
+        <v>348</v>
       </c>
       <c r="Z30" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AA30">
-        <v>0.99655071603273171</v>
+        <v>0.99511617332099966</v>
       </c>
       <c r="AB30">
-        <v>63.236872733251452</v>
+        <v>89.536822448339535</v>
       </c>
       <c r="AD30" t="s">
         <v>445</v>
@@ -11375,16 +11375,16 @@
         <v>747</v>
       </c>
       <c r="AM30" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="AN30" t="s">
-        <v>647</v>
+        <v>930</v>
       </c>
       <c r="AO30">
-        <v>0.99191812933076651</v>
+        <v>0.99585787867207576</v>
       </c>
       <c r="AP30">
-        <v>148.16762893594731</v>
+        <v>75.938891011944406</v>
       </c>
       <c r="AR30" t="s">
         <v>445</v>
@@ -11417,10 +11417,10 @@
         <v>1167</v>
       </c>
       <c r="BC30">
-        <v>0.99716443001648403</v>
+        <v>0.92540139052362402</v>
       </c>
       <c r="BD30">
-        <v>433.2641749538127</v>
+        <v>1653.4597254538478</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11485,16 +11485,16 @@
         <v>488</v>
       </c>
       <c r="Y31" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="Z31" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AA31">
-        <v>0.98466621786657815</v>
+        <v>0.98218461904404952</v>
       </c>
       <c r="AB31">
-        <v>281.11933911273309</v>
+        <v>326.61531752575877</v>
       </c>
       <c r="AD31" t="s">
         <v>445</v>
@@ -11521,16 +11521,16 @@
         <v>749</v>
       </c>
       <c r="AM31" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="AN31" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="AO31">
-        <v>0.97851296575183921</v>
+        <v>0.98152722015516447</v>
       </c>
       <c r="AP31">
-        <v>393.92896121628166</v>
+        <v>338.66763048865067</v>
       </c>
       <c r="AR31" t="s">
         <v>445</v>
@@ -11560,13 +11560,13 @@
         <v>1168</v>
       </c>
       <c r="BB31" t="s">
-        <v>1169</v>
+        <v>646</v>
       </c>
       <c r="BC31">
-        <v>0.99209673382744978</v>
+        <v>0.97283922785685117</v>
       </c>
       <c r="BD31">
-        <v>754.89395975118964</v>
+        <v>1075.5087406106959</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11631,16 +11631,16 @@
         <v>490</v>
       </c>
       <c r="Y32" t="s">
-        <v>381</v>
+        <v>434</v>
       </c>
       <c r="Z32" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AA32">
-        <v>0.94191717639101813</v>
+        <v>0.99847910710774135</v>
       </c>
       <c r="AB32">
-        <v>1064.8517661646679</v>
+        <v>27.883036358075909</v>
       </c>
       <c r="AD32" t="s">
         <v>445</v>
@@ -11667,16 +11667,16 @@
         <v>751</v>
       </c>
       <c r="AM32" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AN32" t="s">
-        <v>934</v>
+        <v>648</v>
       </c>
       <c r="AO32">
-        <v>0.97693095508317673</v>
+        <v>0.98827869617428776</v>
       </c>
       <c r="AP32">
-        <v>422.93249014176001</v>
+        <v>214.89057013805822</v>
       </c>
       <c r="AR32" t="s">
         <v>445</v>
@@ -11703,16 +11703,16 @@
         <v>1080</v>
       </c>
       <c r="BA32" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="BB32" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="BC32">
-        <v>0.96835427347694081</v>
+        <v>0.95074557504943547</v>
       </c>
       <c r="BD32">
-        <v>1130.1504348059382</v>
+        <v>1344.6830773143784</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11777,16 +11777,16 @@
         <v>492</v>
       </c>
       <c r="Y33" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="Z33" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AA33">
-        <v>0.96994910016476243</v>
+        <v>0.99830013108627691</v>
       </c>
       <c r="AB33">
-        <v>550.93316364602254</v>
+        <v>31.164263418257661</v>
       </c>
       <c r="AD33" t="s">
         <v>445</v>
@@ -11813,16 +11813,16 @@
         <v>753</v>
       </c>
       <c r="AM33" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="AN33" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="AO33">
-        <v>0.9972902611932265</v>
+        <v>0.98732492064736277</v>
       </c>
       <c r="AP33">
-        <v>49.678544790847084</v>
+        <v>232.37645479834956</v>
       </c>
       <c r="AR33" t="s">
         <v>445</v>
@@ -11849,16 +11849,16 @@
         <v>1082</v>
       </c>
       <c r="BA33" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="BB33" t="s">
-        <v>1172</v>
+        <v>648</v>
       </c>
       <c r="BC33">
-        <v>0.97396073370136893</v>
+        <v>0.9534536251465805</v>
       </c>
       <c r="BD33">
-        <v>1061.8450610716552</v>
+        <v>1311.6900002974942</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11923,16 +11923,16 @@
         <v>494</v>
       </c>
       <c r="Y34" t="s">
-        <v>353</v>
+        <v>424</v>
       </c>
       <c r="Z34" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="AA34">
-        <v>0.95915670695527311</v>
+        <v>0.99408275357961784</v>
       </c>
       <c r="AB34">
-        <v>748.79370581999342</v>
+        <v>108.48285104034026</v>
       </c>
       <c r="AD34" t="s">
         <v>445</v>
@@ -11959,16 +11959,16 @@
         <v>755</v>
       </c>
       <c r="AM34" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="AN34" t="s">
-        <v>650</v>
+        <v>936</v>
       </c>
       <c r="AO34">
-        <v>0.98256179218990303</v>
+        <v>0.99846088793014054</v>
       </c>
       <c r="AP34">
-        <v>319.70047651844521</v>
+        <v>28.217054614091012</v>
       </c>
       <c r="AR34" t="s">
         <v>445</v>
@@ -11995,16 +11995,16 @@
         <v>1084</v>
       </c>
       <c r="BA34" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="BB34" t="s">
-        <v>1174</v>
+        <v>653</v>
       </c>
       <c r="BC34">
-        <v>0.95124834316022966</v>
+        <v>0.98752340562932261</v>
       </c>
       <c r="BD34">
-        <v>1338.5576858312013</v>
+        <v>896.60650808275307</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -12069,16 +12069,16 @@
         <v>496</v>
       </c>
       <c r="Y35" t="s">
-        <v>433</v>
+        <v>361</v>
       </c>
       <c r="Z35" t="s">
         <v>663</v>
       </c>
       <c r="AA35">
-        <v>0.98266638110143478</v>
+        <v>0.9719447908127189</v>
       </c>
       <c r="AB35">
-        <v>317.78301314036179</v>
+        <v>514.34550176681955</v>
       </c>
       <c r="AD35" t="s">
         <v>445</v>
@@ -12105,16 +12105,16 @@
         <v>757</v>
       </c>
       <c r="AM35" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AN35" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="AO35">
-        <v>0.97344873028830825</v>
+        <v>0.9643711256064017</v>
       </c>
       <c r="AP35">
-        <v>486.77327804768265</v>
+        <v>653.19603054930235</v>
       </c>
       <c r="AR35" t="s">
         <v>445</v>
@@ -12141,16 +12141,16 @@
         <v>1086</v>
       </c>
       <c r="BA35" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="BB35" t="s">
-        <v>646</v>
+        <v>1173</v>
       </c>
       <c r="BC35">
-        <v>0.9762650633688883</v>
+        <v>0.98117820630330521</v>
       </c>
       <c r="BD35">
-        <v>1033.7706446223781</v>
+        <v>973.9121865380647</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -12215,16 +12215,16 @@
         <v>498</v>
       </c>
       <c r="Y36" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Z36" t="s">
         <v>664</v>
       </c>
       <c r="AA36">
-        <v>0.99273760630626895</v>
+        <v>0.99655071603273171</v>
       </c>
       <c r="AB36">
-        <v>133.14388438506904</v>
+        <v>63.236872733251452</v>
       </c>
       <c r="AD36" t="s">
         <v>445</v>
@@ -12251,16 +12251,16 @@
         <v>759</v>
       </c>
       <c r="AM36" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="AN36" t="s">
-        <v>940</v>
+        <v>648</v>
       </c>
       <c r="AO36">
-        <v>0.94726945791757955</v>
+        <v>0.99099266826252508</v>
       </c>
       <c r="AP36">
-        <v>966.72660484437438</v>
+        <v>165.13441518704016</v>
       </c>
       <c r="AR36" t="s">
         <v>445</v>
@@ -12287,16 +12287,16 @@
         <v>1088</v>
       </c>
       <c r="BA36" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="BB36" t="s">
-        <v>1177</v>
+        <v>646</v>
       </c>
       <c r="BC36">
-        <v>0.9859478284089821</v>
+        <v>0.96413043109717189</v>
       </c>
       <c r="BD36">
-        <v>915.80229055056782</v>
+        <v>1181.6109144661225</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12361,16 +12361,16 @@
         <v>500</v>
       </c>
       <c r="Y37" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="Z37" t="s">
         <v>665</v>
       </c>
       <c r="AA37">
-        <v>0.99564857688473862</v>
+        <v>0.98826693080891115</v>
       </c>
       <c r="AB37">
-        <v>79.77609044645817</v>
+        <v>215.10626850329641</v>
       </c>
       <c r="AD37" t="s">
         <v>445</v>
@@ -12397,16 +12397,16 @@
         <v>761</v>
       </c>
       <c r="AM37" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="AN37" t="s">
-        <v>942</v>
+        <v>696</v>
       </c>
       <c r="AO37">
-        <v>0.99721814870334879</v>
+        <v>0.96623363784081273</v>
       </c>
       <c r="AP37">
-        <v>51.000607105273012</v>
+        <v>619.04997291843438</v>
       </c>
       <c r="AR37" t="s">
         <v>445</v>
@@ -12433,16 +12433,16 @@
         <v>1090</v>
       </c>
       <c r="BA37" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="BB37" t="s">
-        <v>1179</v>
+        <v>648</v>
       </c>
       <c r="BC37">
-        <v>0.99844627758702942</v>
+        <v>0.93824334088191808</v>
       </c>
       <c r="BD37">
-        <v>351.90958247653504</v>
+        <v>1497.001963588631</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12507,16 +12507,16 @@
         <v>502</v>
       </c>
       <c r="Y38" t="s">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="Z38" t="s">
         <v>666</v>
       </c>
       <c r="AA38">
-        <v>0.99351242433990716</v>
+        <v>0.97618980314151516</v>
       </c>
       <c r="AB38">
-        <v>118.93888710170195</v>
+        <v>436.52027573888904</v>
       </c>
       <c r="AD38" t="s">
         <v>445</v>
@@ -12543,16 +12543,16 @@
         <v>763</v>
       </c>
       <c r="AM38" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="AN38" t="s">
-        <v>681</v>
+        <v>941</v>
       </c>
       <c r="AO38">
-        <v>0.9965750017909164</v>
+        <v>0.9966806183812299</v>
       </c>
       <c r="AP38">
-        <v>62.791633833199988</v>
+        <v>60.855329677452332</v>
       </c>
       <c r="AR38" t="s">
         <v>445</v>
@@ -12579,16 +12579,16 @@
         <v>1092</v>
       </c>
       <c r="BA38" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="BB38" t="s">
-        <v>968</v>
+        <v>977</v>
       </c>
       <c r="BC38">
-        <v>0.97654176188453468</v>
+        <v>0.99465492794345478</v>
       </c>
       <c r="BD38">
-        <v>1030.3995343734193</v>
+        <v>592.53390652206974</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12653,16 +12653,16 @@
         <v>504</v>
       </c>
       <c r="Y39" t="s">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="Z39" t="s">
         <v>667</v>
       </c>
       <c r="AA39">
-        <v>0.99821138151964162</v>
+        <v>0.99263667372558639</v>
       </c>
       <c r="AB39">
-        <v>32.791338806570671</v>
+        <v>134.9943150309158</v>
       </c>
       <c r="AD39" t="s">
         <v>445</v>
@@ -12689,16 +12689,16 @@
         <v>765</v>
       </c>
       <c r="AM39" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="AN39" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="AO39">
-        <v>0.98900028996553313</v>
+        <v>0.99215245657219142</v>
       </c>
       <c r="AP39">
-        <v>201.66135063189321</v>
+        <v>143.87162950982398</v>
       </c>
       <c r="AR39" t="s">
         <v>445</v>
@@ -12725,16 +12725,16 @@
         <v>1094</v>
       </c>
       <c r="BA39" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="BB39" t="s">
-        <v>1182</v>
+        <v>992</v>
       </c>
       <c r="BC39">
-        <v>0.99180629119732955</v>
+        <v>0.9580046500205861</v>
       </c>
       <c r="BD39">
-        <v>773.32738534281725</v>
+        <v>1256.2433472491919</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12799,16 +12799,16 @@
         <v>506</v>
       </c>
       <c r="Y40" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="Z40" t="s">
         <v>668</v>
       </c>
       <c r="AA40">
-        <v>0.98201413073603905</v>
+        <v>0.98665714478881894</v>
       </c>
       <c r="AB40">
-        <v>329.74093650595114</v>
+        <v>244.61901220498595</v>
       </c>
       <c r="AD40" t="s">
         <v>445</v>
@@ -12835,16 +12835,16 @@
         <v>767</v>
       </c>
       <c r="AM40" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="AN40" t="s">
-        <v>946</v>
+        <v>645</v>
       </c>
       <c r="AO40">
-        <v>0.98539636691491217</v>
+        <v>0.9485944422668402</v>
       </c>
       <c r="AP40">
-        <v>267.73327322661089</v>
+        <v>942.43522510793025</v>
       </c>
       <c r="AR40" t="s">
         <v>445</v>
@@ -12871,16 +12871,16 @@
         <v>1096</v>
       </c>
       <c r="BA40" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="BB40" t="s">
-        <v>1184</v>
+        <v>995</v>
       </c>
       <c r="BC40">
-        <v>0.9784511409772424</v>
+        <v>0.98542037014322215</v>
       </c>
       <c r="BD40">
-        <v>1007.136932427263</v>
+        <v>922.22849042174391</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12945,16 +12945,16 @@
         <v>508</v>
       </c>
       <c r="Y41" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="Z41" t="s">
-        <v>651</v>
+        <v>669</v>
       </c>
       <c r="AA41">
-        <v>0.97808127216802332</v>
+        <v>0.99671990332447369</v>
       </c>
       <c r="AB41">
-        <v>401.84334358623994</v>
+        <v>60.135105717982277</v>
       </c>
       <c r="AD41" t="s">
         <v>445</v>
@@ -12981,16 +12981,16 @@
         <v>769</v>
       </c>
       <c r="AM41" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="AN41" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO41">
-        <v>0.95721921641733843</v>
+        <v>0.97043152360247686</v>
       </c>
       <c r="AP41">
-        <v>784.31436568212814</v>
+        <v>542.08873395459034</v>
       </c>
       <c r="AR41" t="s">
         <v>445</v>
@@ -13017,16 +13017,16 @@
         <v>1098</v>
       </c>
       <c r="BA41" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="BB41" t="s">
-        <v>1186</v>
+        <v>920</v>
       </c>
       <c r="BC41">
-        <v>0.9955677970684097</v>
+        <v>0.99613275225602693</v>
       </c>
       <c r="BD41">
-        <v>534.59714605826571</v>
+        <v>498.74132348416083</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -13091,16 +13091,16 @@
         <v>510</v>
       </c>
       <c r="Y42" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="Z42" t="s">
-        <v>647</v>
+        <v>670</v>
       </c>
       <c r="AA42">
-        <v>0.98589110095524246</v>
+        <v>0.97969590283269214</v>
       </c>
       <c r="AB42">
-        <v>258.66314915388926</v>
+        <v>372.24178140064373</v>
       </c>
       <c r="AD42" t="s">
         <v>445</v>
@@ -13127,16 +13127,16 @@
         <v>771</v>
       </c>
       <c r="AM42" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="AN42" t="s">
-        <v>949</v>
+        <v>671</v>
       </c>
       <c r="AO42">
-        <v>0.97128923400988465</v>
+        <v>0.9922676414012731</v>
       </c>
       <c r="AP42">
-        <v>526.36404315211564</v>
+        <v>141.75990764332545</v>
       </c>
       <c r="AR42" t="s">
         <v>445</v>
@@ -13163,16 +13163,16 @@
         <v>1100</v>
       </c>
       <c r="BA42" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="BB42" t="s">
-        <v>960</v>
+        <v>701</v>
       </c>
       <c r="BC42">
-        <v>0.97834276564858003</v>
+        <v>0.97261625181972589</v>
       </c>
       <c r="BD42">
-        <v>1008.4573051814666</v>
+        <v>1078.2253319963402</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -13237,16 +13237,16 @@
         <v>512</v>
       </c>
       <c r="Y43" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="Z43" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="AA43">
-        <v>0.99646010176925304</v>
+        <v>0.98086220977655469</v>
       </c>
       <c r="AB43">
-        <v>64.89813423036172</v>
+        <v>350.85948742983044</v>
       </c>
       <c r="AD43" t="s">
         <v>445</v>
@@ -13273,16 +13273,16 @@
         <v>773</v>
       </c>
       <c r="AM43" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="AN43" t="s">
-        <v>647</v>
+        <v>947</v>
       </c>
       <c r="AO43">
-        <v>0.98140230930972394</v>
+        <v>0.98764154770136958</v>
       </c>
       <c r="AP43">
-        <v>340.95766265506029</v>
+        <v>226.57162547489074</v>
       </c>
       <c r="AR43" t="s">
         <v>445</v>
@@ -13309,16 +13309,16 @@
         <v>1102</v>
       </c>
       <c r="BA43" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
       <c r="BB43" t="s">
-        <v>968</v>
+        <v>1182</v>
       </c>
       <c r="BC43">
-        <v>0.97810798081469907</v>
+        <v>0.99257145555712289</v>
       </c>
       <c r="BD43">
-        <v>1011.3177670742492</v>
+        <v>724.76495397460064</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13383,16 +13383,16 @@
         <v>514</v>
       </c>
       <c r="Y44" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="Z44" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="AA44">
-        <v>0.99487962039691491</v>
+        <v>0.99377506386421921</v>
       </c>
       <c r="AB44">
-        <v>93.8736260565599</v>
+        <v>114.12382915598114</v>
       </c>
       <c r="AD44" t="s">
         <v>445</v>
@@ -13419,16 +13419,16 @@
         <v>775</v>
       </c>
       <c r="AM44" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="AN44" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="AO44">
-        <v>0.99585787867207576</v>
+        <v>0.9977216312452537</v>
       </c>
       <c r="AP44">
-        <v>75.938891011944406</v>
+        <v>41.77009383701548</v>
       </c>
       <c r="AR44" t="s">
         <v>445</v>
@@ -13455,16 +13455,16 @@
         <v>1104</v>
       </c>
       <c r="BA44" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="BB44" t="s">
-        <v>681</v>
+        <v>995</v>
       </c>
       <c r="BC44">
-        <v>0.99215965418440455</v>
+        <v>0.97654176188453468</v>
       </c>
       <c r="BD44">
-        <v>750.90061442978902</v>
+        <v>1030.3995343734193</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13529,16 +13529,16 @@
         <v>516</v>
       </c>
       <c r="Y45" t="s">
-        <v>438</v>
+        <v>380</v>
       </c>
       <c r="Z45" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="AA45">
-        <v>0.97458216258452024</v>
+        <v>0.95105540198711702</v>
       </c>
       <c r="AB45">
-        <v>465.99368595046235</v>
+        <v>897.31763023618794</v>
       </c>
       <c r="AD45" t="s">
         <v>445</v>
@@ -13565,16 +13565,16 @@
         <v>777</v>
       </c>
       <c r="AM45" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="AN45" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="AO45">
-        <v>0.98152722015516447</v>
+        <v>0.97985884005408208</v>
       </c>
       <c r="AP45">
-        <v>338.66763048865067</v>
+        <v>369.25459900849603</v>
       </c>
       <c r="AR45" t="s">
         <v>445</v>
@@ -13601,16 +13601,16 @@
         <v>1106</v>
       </c>
       <c r="BA45" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="BB45" t="s">
-        <v>916</v>
+        <v>1185</v>
       </c>
       <c r="BC45">
-        <v>0.98701879075230647</v>
+        <v>0.99180629119732955</v>
       </c>
       <c r="BD45">
-        <v>902.75439933439907</v>
+        <v>773.32738534281725</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13675,16 +13675,16 @@
         <v>518</v>
       </c>
       <c r="Y46" t="s">
-        <v>430</v>
+        <v>373</v>
       </c>
       <c r="Z46" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="AA46">
-        <v>0.98303972846671772</v>
+        <v>0.99131962187405476</v>
       </c>
       <c r="AB46">
-        <v>310.93831144350901</v>
+        <v>159.14026564233004</v>
       </c>
       <c r="AD46" t="s">
         <v>445</v>
@@ -13711,16 +13711,16 @@
         <v>779</v>
       </c>
       <c r="AM46" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="AN46" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO46">
-        <v>0.98827869617428776</v>
+        <v>0.93800436607424875</v>
       </c>
       <c r="AP46">
-        <v>214.89057013805822</v>
+        <v>1136.5866219721056</v>
       </c>
       <c r="AR46" t="s">
         <v>445</v>
@@ -13747,16 +13747,16 @@
         <v>1108</v>
       </c>
       <c r="BA46" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="BB46" t="s">
-        <v>708</v>
+        <v>1187</v>
       </c>
       <c r="BC46">
-        <v>0.98556353666457686</v>
+        <v>0.9784511409772424</v>
       </c>
       <c r="BD46">
-        <v>920.4842449699056</v>
+        <v>1007.136932427263</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13821,16 +13821,16 @@
         <v>520</v>
       </c>
       <c r="Y47" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="Z47" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AA47">
-        <v>0.95110913617470227</v>
+        <v>0.98201413073603905</v>
       </c>
       <c r="AB47">
-        <v>896.33250346379077</v>
+        <v>329.74093650595114</v>
       </c>
       <c r="AD47" t="s">
         <v>445</v>
@@ -13857,16 +13857,16 @@
         <v>781</v>
       </c>
       <c r="AM47" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="AN47" t="s">
-        <v>956</v>
+        <v>648</v>
       </c>
       <c r="AO47">
-        <v>0.98732492064736277</v>
+        <v>0.96962859242416655</v>
       </c>
       <c r="AP47">
-        <v>232.37645479834956</v>
+        <v>556.80913889028056</v>
       </c>
       <c r="AR47" t="s">
         <v>445</v>
@@ -13893,16 +13893,16 @@
         <v>1110</v>
       </c>
       <c r="BA47" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="BB47" t="s">
-        <v>649</v>
+        <v>1189</v>
       </c>
       <c r="BC47">
-        <v>0.97261625181972589</v>
+        <v>0.9955677970684097</v>
       </c>
       <c r="BD47">
-        <v>1078.2253319963402</v>
+        <v>534.59714605826571</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13967,16 +13967,16 @@
         <v>522</v>
       </c>
       <c r="Y48" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="Z48" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="AA48">
-        <v>0.96488357195289265</v>
+        <v>0.97808127216802332</v>
       </c>
       <c r="AB48">
-        <v>643.80118086363541</v>
+        <v>401.84334358623994</v>
       </c>
       <c r="AD48" t="s">
         <v>445</v>
@@ -14003,16 +14003,16 @@
         <v>783</v>
       </c>
       <c r="AM48" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="AN48" t="s">
-        <v>958</v>
+        <v>676</v>
       </c>
       <c r="AO48">
-        <v>0.99846088793014054</v>
+        <v>0.97620022609803814</v>
       </c>
       <c r="AP48">
-        <v>28.217054614091012</v>
+        <v>436.32918820263421</v>
       </c>
       <c r="AR48" t="s">
         <v>445</v>
@@ -14039,16 +14039,16 @@
         <v>1112</v>
       </c>
       <c r="BA48" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="BB48" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="BC48">
-        <v>0.99257145555712289</v>
+        <v>0.95124834316022966</v>
       </c>
       <c r="BD48">
-        <v>724.76495397460064</v>
+        <v>1338.5576858312013</v>
       </c>
     </row>
     <row r="49" spans="2:56">
@@ -14113,16 +14113,16 @@
         <v>524</v>
       </c>
       <c r="Y49" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="Z49" t="s">
-        <v>673</v>
+        <v>648</v>
       </c>
       <c r="AA49">
-        <v>0.99397024960358282</v>
+        <v>0.98589110095524246</v>
       </c>
       <c r="AB49">
-        <v>110.54542393431565</v>
+        <v>258.66314915388926</v>
       </c>
       <c r="AD49" t="s">
         <v>445</v>
@@ -14149,16 +14149,16 @@
         <v>785</v>
       </c>
       <c r="AM49" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="AN49" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="AO49">
-        <v>0.98764154770136958</v>
+        <v>0.98607591956620455</v>
       </c>
       <c r="AP49">
-        <v>226.57162547489074</v>
+        <v>255.27480795291643</v>
       </c>
       <c r="AR49" t="s">
         <v>445</v>
@@ -14185,16 +14185,16 @@
         <v>1114</v>
       </c>
       <c r="BA49" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="BB49" t="s">
-        <v>682</v>
+        <v>648</v>
       </c>
       <c r="BC49">
-        <v>0.98752340562932261</v>
+        <v>0.91754501241076647</v>
       </c>
       <c r="BD49">
-        <v>896.60650808275307</v>
+        <v>1749.1765987954952</v>
       </c>
     </row>
     <row r="50" spans="2:56">
@@ -14259,16 +14259,16 @@
         <v>526</v>
       </c>
       <c r="Y50" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="Z50" t="s">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="AA50">
-        <v>0.98138635372944616</v>
+        <v>0.99646010176925304</v>
       </c>
       <c r="AB50">
-        <v>341.25018162681971</v>
+        <v>64.89813423036172</v>
       </c>
       <c r="AD50" t="s">
         <v>445</v>
@@ -14295,16 +14295,16 @@
         <v>787</v>
       </c>
       <c r="AM50" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="AN50" t="s">
-        <v>962</v>
+        <v>666</v>
       </c>
       <c r="AO50">
-        <v>0.9977216312452537</v>
+        <v>0.94516861039769784</v>
       </c>
       <c r="AP50">
-        <v>41.77009383701548</v>
+        <v>1005.2421427088731</v>
       </c>
       <c r="AR50" t="s">
         <v>445</v>
@@ -14331,16 +14331,16 @@
         <v>1116</v>
       </c>
       <c r="BA50" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="BB50" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="BC50">
-        <v>0.98117820630330521</v>
+        <v>0.98908658389363524</v>
       </c>
       <c r="BD50">
-        <v>973.9121865380647</v>
+        <v>877.56178622921061</v>
       </c>
     </row>
     <row r="51" spans="2:56">
@@ -14405,16 +14405,16 @@
         <v>528</v>
       </c>
       <c r="Y51" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="Z51" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AA51">
-        <v>0.99502756316390695</v>
+        <v>0.99487962039691491</v>
       </c>
       <c r="AB51">
-        <v>91.161341995039152</v>
+        <v>93.8736260565599</v>
       </c>
       <c r="AD51" t="s">
         <v>445</v>
@@ -14441,16 +14441,16 @@
         <v>789</v>
       </c>
       <c r="AM51" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="AN51" t="s">
-        <v>651</v>
+        <v>958</v>
       </c>
       <c r="AO51">
-        <v>0.97985884005408208</v>
+        <v>0.94231963623506931</v>
       </c>
       <c r="AP51">
-        <v>369.25459900849603</v>
+        <v>1057.4733356903953</v>
       </c>
       <c r="AR51" t="s">
         <v>445</v>
@@ -14477,16 +14477,16 @@
         <v>1118</v>
       </c>
       <c r="BA51" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="BB51" t="s">
-        <v>646</v>
+        <v>1196</v>
       </c>
       <c r="BC51">
-        <v>0.96413043109717189</v>
+        <v>0.99209673382744978</v>
       </c>
       <c r="BD51">
-        <v>1181.6109144661225</v>
+        <v>754.89395975118964</v>
       </c>
     </row>
     <row r="52" spans="2:56">
@@ -14551,16 +14551,16 @@
         <v>530</v>
       </c>
       <c r="Y52" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="Z52" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AA52">
-        <v>0.99219726142231079</v>
+        <v>0.97458216258452024</v>
       </c>
       <c r="AB52">
-        <v>143.05020725763492</v>
+        <v>465.99368595046235</v>
       </c>
       <c r="AD52" t="s">
         <v>445</v>
@@ -14587,16 +14587,16 @@
         <v>791</v>
       </c>
       <c r="AM52" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="AN52" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AO52">
-        <v>0.93800436607424875</v>
+        <v>0.97832027217029349</v>
       </c>
       <c r="AP52">
-        <v>1136.5866219721056</v>
+        <v>397.46167687795332</v>
       </c>
       <c r="AR52" t="s">
         <v>445</v>
@@ -14623,16 +14623,16 @@
         <v>1120</v>
       </c>
       <c r="BA52" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="BB52" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="BC52">
-        <v>0.93824334088191808</v>
+        <v>0.96835427347694081</v>
       </c>
       <c r="BD52">
-        <v>1497.001963588631</v>
+        <v>1130.1504348059382</v>
       </c>
     </row>
     <row r="53" spans="2:56">
@@ -14697,16 +14697,16 @@
         <v>532</v>
       </c>
       <c r="Y53" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="Z53" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AA53">
-        <v>0.99809443707900702</v>
+        <v>0.98303972846671772</v>
       </c>
       <c r="AB53">
-        <v>34.93532021820478</v>
+        <v>310.93831144350901</v>
       </c>
       <c r="AD53" t="s">
         <v>445</v>
@@ -14733,16 +14733,16 @@
         <v>793</v>
       </c>
       <c r="AM53" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="AN53" t="s">
-        <v>647</v>
+        <v>961</v>
       </c>
       <c r="AO53">
-        <v>0.96962859242416655</v>
+        <v>0.99484431329617862</v>
       </c>
       <c r="AP53">
-        <v>556.80913889028056</v>
+        <v>94.520922903391252</v>
       </c>
       <c r="AR53" t="s">
         <v>445</v>
@@ -14769,16 +14769,16 @@
         <v>1122</v>
       </c>
       <c r="BA53" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="BB53" t="s">
-        <v>909</v>
+        <v>1199</v>
       </c>
       <c r="BC53">
-        <v>0.99465492794345478</v>
+        <v>0.97396073370136893</v>
       </c>
       <c r="BD53">
-        <v>592.53390652206974</v>
+        <v>1061.8450610716552</v>
       </c>
     </row>
     <row r="54" spans="2:56">
@@ -14843,16 +14843,16 @@
         <v>534</v>
       </c>
       <c r="Y54" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="Z54" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AA54">
-        <v>0.99741667924532684</v>
+        <v>0.97971956708030139</v>
       </c>
       <c r="AB54">
-        <v>47.360880502342191</v>
+        <v>371.80793686114123</v>
       </c>
       <c r="AD54" t="s">
         <v>445</v>
@@ -14879,16 +14879,16 @@
         <v>795</v>
       </c>
       <c r="AM54" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="AN54" t="s">
-        <v>698</v>
+        <v>648</v>
       </c>
       <c r="AO54">
-        <v>0.97818029957439945</v>
+        <v>0.97273741219297172</v>
       </c>
       <c r="AP54">
-        <v>400.02784113601069</v>
+        <v>499.8141097955185</v>
       </c>
       <c r="AR54" t="s">
         <v>445</v>
@@ -14915,16 +14915,16 @@
         <v>1124</v>
       </c>
       <c r="BA54" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="BB54" t="s">
-        <v>924</v>
+        <v>1022</v>
       </c>
       <c r="BC54">
-        <v>0.9580046500205861</v>
+        <v>0.98701879075230647</v>
       </c>
       <c r="BD54">
-        <v>1256.2433472491919</v>
+        <v>902.75439933439907</v>
       </c>
     </row>
     <row r="55" spans="2:56">
@@ -14989,16 +14989,16 @@
         <v>536</v>
       </c>
       <c r="Y55" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="Z55" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AA55">
-        <v>0.99782027918606175</v>
+        <v>0.98980411719589489</v>
       </c>
       <c r="AB55">
-        <v>39.961548255533756</v>
+        <v>186.92451807526095</v>
       </c>
       <c r="AD55" t="s">
         <v>445</v>
@@ -15025,16 +15025,16 @@
         <v>797</v>
       </c>
       <c r="AM55" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="AN55" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="AO55">
-        <v>0.95946658042945154</v>
+        <v>0.97984247759827614</v>
       </c>
       <c r="AP55">
-        <v>743.11269212672175</v>
+        <v>369.55457736493832</v>
       </c>
       <c r="AR55" t="s">
         <v>445</v>
@@ -15061,16 +15061,16 @@
         <v>1126</v>
       </c>
       <c r="BA55" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="BB55" t="s">
-        <v>647</v>
+        <v>682</v>
       </c>
       <c r="BC55">
-        <v>0.91754501241076647</v>
+        <v>0.98556353666457686</v>
       </c>
       <c r="BD55">
-        <v>1749.1765987954952</v>
+        <v>920.4842449699056</v>
       </c>
     </row>
     <row r="56" spans="2:56">
@@ -15135,16 +15135,16 @@
         <v>538</v>
       </c>
       <c r="Y56" t="s">
-        <v>418</v>
+        <v>387</v>
       </c>
       <c r="Z56" t="s">
-        <v>679</v>
+        <v>656</v>
       </c>
       <c r="AA56">
-        <v>0.98777287103353073</v>
+        <v>0.95872760140098945</v>
       </c>
       <c r="AB56">
-        <v>224.16403105193586</v>
+        <v>756.66064098185961</v>
       </c>
       <c r="AD56" t="s">
         <v>445</v>
@@ -15171,16 +15171,16 @@
         <v>799</v>
       </c>
       <c r="AM56" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="AN56" t="s">
-        <v>660</v>
+        <v>700</v>
       </c>
       <c r="AO56">
-        <v>0.96103827796400987</v>
+        <v>0.99109308381957362</v>
       </c>
       <c r="AP56">
-        <v>714.29823732648526</v>
+        <v>163.29346330781715</v>
       </c>
       <c r="AR56" t="s">
         <v>445</v>
@@ -15207,16 +15207,16 @@
         <v>1128</v>
       </c>
       <c r="BA56" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="BB56" t="s">
-        <v>1204</v>
+        <v>646</v>
       </c>
       <c r="BC56">
-        <v>0.98908658389363524</v>
+        <v>0.9762650633688883</v>
       </c>
       <c r="BD56">
-        <v>877.56178622921061</v>
+        <v>1033.7706446223781</v>
       </c>
     </row>
     <row r="57" spans="2:56">
@@ -15281,16 +15281,16 @@
         <v>540</v>
       </c>
       <c r="Y57" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="Z57" t="s">
-        <v>651</v>
+        <v>678</v>
       </c>
       <c r="AA57">
-        <v>0.97754100001622091</v>
+        <v>0.93423394789967462</v>
       </c>
       <c r="AB57">
-        <v>411.74833303595017</v>
+        <v>1205.7109551726326</v>
       </c>
       <c r="AD57" t="s">
         <v>445</v>
@@ -15317,16 +15317,16 @@
         <v>801</v>
       </c>
       <c r="AM57" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="AN57" t="s">
-        <v>651</v>
+        <v>701</v>
       </c>
       <c r="AO57">
-        <v>0.96185713019776531</v>
+        <v>0.98586375931635961</v>
       </c>
       <c r="AP57">
-        <v>699.28594637430331</v>
+        <v>259.16441253340616</v>
       </c>
       <c r="AR57" t="s">
         <v>445</v>
@@ -15353,16 +15353,16 @@
         <v>1130</v>
       </c>
       <c r="BA57" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="BB57" t="s">
-        <v>968</v>
+        <v>1204</v>
       </c>
       <c r="BC57">
-        <v>0.98542037014322215</v>
+        <v>0.9859478284089821</v>
       </c>
       <c r="BD57">
-        <v>922.22849042174391</v>
+        <v>915.80229055056782</v>
       </c>
     </row>
     <row r="58" spans="2:56">
@@ -15427,16 +15427,16 @@
         <v>542</v>
       </c>
       <c r="Y58" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="Z58" t="s">
-        <v>680</v>
+        <v>646</v>
       </c>
       <c r="AA58">
-        <v>0.95401962289287812</v>
+        <v>0.97861539621410798</v>
       </c>
       <c r="AB58">
-        <v>842.97358029723534</v>
+        <v>392.05106940802045</v>
       </c>
       <c r="AD58" t="s">
         <v>445</v>
@@ -15463,16 +15463,16 @@
         <v>803</v>
       </c>
       <c r="AM58" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="AN58" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="AO58">
-        <v>0.95931345925264233</v>
+        <v>0.98753047073573874</v>
       </c>
       <c r="AP58">
-        <v>745.91991370155699</v>
+        <v>228.60803651145704</v>
       </c>
       <c r="AR58" t="s">
         <v>445</v>
@@ -15499,16 +15499,16 @@
         <v>1132</v>
       </c>
       <c r="BA58" t="s">
+        <v>1205</v>
+      </c>
+      <c r="BB58" t="s">
         <v>1206</v>
       </c>
-      <c r="BB58" t="s">
-        <v>942</v>
-      </c>
       <c r="BC58">
-        <v>0.99613275225602693</v>
+        <v>0.99844627758702942</v>
       </c>
       <c r="BD58">
-        <v>498.74132348416083</v>
+        <v>351.90958247653504</v>
       </c>
     </row>
     <row r="59" spans="2:56">
@@ -15573,16 +15573,16 @@
         <v>544</v>
       </c>
       <c r="Y59" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="Z59" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AA59">
-        <v>0.98495178422440233</v>
+        <v>0.97896212777707714</v>
       </c>
       <c r="AB59">
-        <v>275.88395588595779</v>
+        <v>385.69432408691944</v>
       </c>
       <c r="AD59" t="s">
         <v>445</v>
@@ -15609,16 +15609,16 @@
         <v>805</v>
       </c>
       <c r="AM59" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="AN59" t="s">
-        <v>973</v>
+        <v>666</v>
       </c>
       <c r="AO59">
-        <v>0.98333626289132436</v>
+        <v>0.96497483135850137</v>
       </c>
       <c r="AP59">
-        <v>305.50184699238736</v>
+        <v>642.12809176080782</v>
       </c>
       <c r="AR59" t="s">
         <v>445</v>
@@ -15648,7 +15648,7 @@
         <v>1207</v>
       </c>
       <c r="BB59" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="BC59">
         <v>0.96412973603590302</v>
@@ -15719,16 +15719,16 @@
         <v>546</v>
       </c>
       <c r="Y60" t="s">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="Z60" t="s">
-        <v>647</v>
+        <v>679</v>
       </c>
       <c r="AA60">
-        <v>0.97886062539501351</v>
+        <v>0.99805781879500122</v>
       </c>
       <c r="AB60">
-        <v>387.55520109141952</v>
+        <v>35.60665542497717</v>
       </c>
       <c r="AD60" t="s">
         <v>445</v>
@@ -15755,16 +15755,16 @@
         <v>807</v>
       </c>
       <c r="AM60" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="AN60" t="s">
-        <v>975</v>
+        <v>648</v>
       </c>
       <c r="AO60">
-        <v>0.99580424242160948</v>
+        <v>0.953110606460702</v>
       </c>
       <c r="AP60">
-        <v>76.922222270493648</v>
+        <v>859.63888155379732</v>
       </c>
       <c r="AR60" t="s">
         <v>445</v>
@@ -15865,16 +15865,16 @@
         <v>548</v>
       </c>
       <c r="Y61" t="s">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="Z61" t="s">
-        <v>647</v>
+        <v>680</v>
       </c>
       <c r="AA61">
-        <v>0.99386727950885501</v>
+        <v>0.99892391441583261</v>
       </c>
       <c r="AB61">
-        <v>112.43320900432452</v>
+        <v>19.728235709736104</v>
       </c>
       <c r="AD61" t="s">
         <v>445</v>
@@ -15901,16 +15901,16 @@
         <v>809</v>
       </c>
       <c r="AM61" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="AN61" t="s">
-        <v>977</v>
+        <v>683</v>
       </c>
       <c r="AO61">
-        <v>0.99143965884476559</v>
+        <v>0.95955011836243909</v>
       </c>
       <c r="AP61">
-        <v>156.93958784596441</v>
+        <v>741.58116335528291</v>
       </c>
       <c r="AR61" t="s">
         <v>445</v>
@@ -15940,7 +15940,7 @@
         <v>1210</v>
       </c>
       <c r="BB61" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="BC61">
         <v>0.9524344319526965</v>
@@ -16011,16 +16011,16 @@
         <v>550</v>
       </c>
       <c r="Y62" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="Z62" t="s">
-        <v>647</v>
+        <v>681</v>
       </c>
       <c r="AA62">
-        <v>0.96488803122020605</v>
+        <v>0.99646875354725362</v>
       </c>
       <c r="AB62">
-        <v>643.71942762955541</v>
+        <v>64.739518300349658</v>
       </c>
       <c r="AD62" t="s">
         <v>445</v>
@@ -16047,16 +16047,16 @@
         <v>811</v>
       </c>
       <c r="AM62" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="AN62" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="AO62">
-        <v>0.97950961971620221</v>
+        <v>0.99423423237135644</v>
       </c>
       <c r="AP62">
-        <v>375.65697186962575</v>
+        <v>105.70573985846545</v>
       </c>
       <c r="AR62" t="s">
         <v>445</v>
@@ -16157,16 +16157,16 @@
         <v>552</v>
       </c>
       <c r="Y63" t="s">
-        <v>436</v>
+        <v>399</v>
       </c>
       <c r="Z63" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AA63">
-        <v>0.99588620223113744</v>
+        <v>0.9922209073807341</v>
       </c>
       <c r="AB63">
-        <v>75.419625762480621</v>
+        <v>142.61669801987438</v>
       </c>
       <c r="AD63" t="s">
         <v>445</v>
@@ -16193,16 +16193,16 @@
         <v>813</v>
       </c>
       <c r="AM63" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="AN63" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AO63">
-        <v>0.94721908575810376</v>
+        <v>0.96634981065643422</v>
       </c>
       <c r="AP63">
-        <v>967.65009443476538</v>
+        <v>616.9201379653731</v>
       </c>
     </row>
     <row r="64" spans="2:56">
@@ -16267,16 +16267,16 @@
         <v>554</v>
       </c>
       <c r="Y64" t="s">
-        <v>417</v>
+        <v>362</v>
       </c>
       <c r="Z64" t="s">
-        <v>682</v>
+        <v>648</v>
       </c>
       <c r="AA64">
-        <v>0.99406720218050904</v>
+        <v>0.95110913617470227</v>
       </c>
       <c r="AB64">
-        <v>108.76796002400131</v>
+        <v>896.33250346379077</v>
       </c>
       <c r="AD64" t="s">
         <v>445</v>
@@ -16303,16 +16303,16 @@
         <v>815</v>
       </c>
       <c r="AM64" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="AN64" t="s">
-        <v>647</v>
+        <v>975</v>
       </c>
       <c r="AO64">
-        <v>0.98898335230625201</v>
+        <v>0.99393164723700467</v>
       </c>
       <c r="AP64">
-        <v>201.97187438538015</v>
+        <v>111.25313398824829</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -16377,16 +16377,16 @@
         <v>556</v>
       </c>
       <c r="Y65" t="s">
-        <v>423</v>
+        <v>357</v>
       </c>
       <c r="Z65" t="s">
         <v>683</v>
       </c>
       <c r="AA65">
-        <v>0.99132119972938326</v>
+        <v>0.96488357195289265</v>
       </c>
       <c r="AB65">
-        <v>159.11133829463989</v>
+        <v>643.80118086363541</v>
       </c>
       <c r="AD65" t="s">
         <v>445</v>
@@ -16413,16 +16413,16 @@
         <v>817</v>
       </c>
       <c r="AM65" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="AN65" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="AO65">
-        <v>0.99506178999496608</v>
+        <v>0.99746342019371192</v>
       </c>
       <c r="AP65">
-        <v>90.533850092289356</v>
+        <v>46.503963115281117</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -16487,16 +16487,16 @@
         <v>558</v>
       </c>
       <c r="Y66" t="s">
-        <v>392</v>
+        <v>350</v>
       </c>
       <c r="Z66" t="s">
         <v>684</v>
       </c>
       <c r="AA66">
-        <v>0.9643190988261251</v>
+        <v>0.99397024960358282</v>
       </c>
       <c r="AB66">
-        <v>654.14985485437251</v>
+        <v>110.54542393431565</v>
       </c>
       <c r="AD66" t="s">
         <v>445</v>
@@ -16523,16 +16523,16 @@
         <v>819</v>
       </c>
       <c r="AM66" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="AN66" t="s">
-        <v>681</v>
+        <v>979</v>
       </c>
       <c r="AO66">
-        <v>0.99493880624410824</v>
+        <v>0.99690141662376341</v>
       </c>
       <c r="AP66">
-        <v>92.7885521913487</v>
+        <v>56.80736189767017</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -16597,16 +16597,16 @@
         <v>560</v>
       </c>
       <c r="Y67" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="Z67" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="AA67">
-        <v>0.96307923215762514</v>
+        <v>0.98138635372944616</v>
       </c>
       <c r="AB67">
-        <v>676.88074377687337</v>
+        <v>341.25018162681971</v>
       </c>
       <c r="AD67" t="s">
         <v>445</v>
@@ -16633,16 +16633,16 @@
         <v>821</v>
       </c>
       <c r="AM67" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="AN67" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="AO67">
-        <v>0.9643711256064017</v>
+        <v>0.99160044224340704</v>
       </c>
       <c r="AP67">
-        <v>653.19603054930235</v>
+        <v>153.99189220420479</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -16707,16 +16707,16 @@
         <v>562</v>
       </c>
       <c r="Y68" t="s">
-        <v>358</v>
+        <v>412</v>
       </c>
       <c r="Z68" t="s">
         <v>685</v>
       </c>
       <c r="AA68">
-        <v>0.94315950804663551</v>
+        <v>0.99502756316390695</v>
       </c>
       <c r="AB68">
-        <v>1042.0756858116829</v>
+        <v>91.161341995039152</v>
       </c>
       <c r="AD68" t="s">
         <v>445</v>
@@ -16743,16 +16743,16 @@
         <v>823</v>
       </c>
       <c r="AM68" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="AN68" t="s">
-        <v>647</v>
+        <v>982</v>
       </c>
       <c r="AO68">
-        <v>0.99099266826252508</v>
+        <v>0.98943214953804659</v>
       </c>
       <c r="AP68">
-        <v>165.13441518704016</v>
+        <v>193.7439251358123</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -16817,16 +16817,16 @@
         <v>564</v>
       </c>
       <c r="Y69" t="s">
-        <v>366</v>
+        <v>427</v>
       </c>
       <c r="Z69" t="s">
-        <v>647</v>
+        <v>686</v>
       </c>
       <c r="AA69">
-        <v>0.96140892845075643</v>
+        <v>0.99219726142231079</v>
       </c>
       <c r="AB69">
-        <v>707.50297840279961</v>
+        <v>143.05020725763492</v>
       </c>
       <c r="AD69" t="s">
         <v>445</v>
@@ -16853,16 +16853,16 @@
         <v>825</v>
       </c>
       <c r="AM69" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="AN69" t="s">
-        <v>691</v>
+        <v>984</v>
       </c>
       <c r="AO69">
-        <v>0.96623363784081273</v>
+        <v>0.99751889144721539</v>
       </c>
       <c r="AP69">
-        <v>619.04997291843438</v>
+        <v>45.486990134384541</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -16927,16 +16927,16 @@
         <v>566</v>
       </c>
       <c r="Y70" t="s">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="Z70" t="s">
-        <v>647</v>
+        <v>687</v>
       </c>
       <c r="AA70">
-        <v>0.93763052839116845</v>
+        <v>0.99809443707900702</v>
       </c>
       <c r="AB70">
-        <v>1143.4403128285794</v>
+        <v>34.93532021820478</v>
       </c>
       <c r="AD70" t="s">
         <v>445</v>
@@ -16963,16 +16963,16 @@
         <v>827</v>
       </c>
       <c r="AM70" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="AN70" t="s">
-        <v>698</v>
+        <v>986</v>
       </c>
       <c r="AO70">
-        <v>0.9937244183974584</v>
+        <v>0.97572899399979196</v>
       </c>
       <c r="AP70">
-        <v>115.0523293799298</v>
+        <v>444.96844333714796</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17037,16 +17037,16 @@
         <v>568</v>
       </c>
       <c r="Y71" t="s">
-        <v>367</v>
+        <v>426</v>
       </c>
       <c r="Z71" t="s">
-        <v>647</v>
+        <v>688</v>
       </c>
       <c r="AA71">
-        <v>0.96169171176041801</v>
+        <v>0.99741667924532684</v>
       </c>
       <c r="AB71">
-        <v>702.3186177256697</v>
+        <v>47.360880502342191</v>
       </c>
       <c r="AD71" t="s">
         <v>445</v>
@@ -17073,16 +17073,16 @@
         <v>829</v>
       </c>
       <c r="AM71" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="AN71" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="AO71">
-        <v>0.93186769579006068</v>
+        <v>0.95226889215734378</v>
       </c>
       <c r="AP71">
-        <v>1249.0922438488865</v>
+        <v>875.07031044869723</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17147,16 +17147,16 @@
         <v>570</v>
       </c>
       <c r="Y72" t="s">
-        <v>348</v>
+        <v>428</v>
       </c>
       <c r="Z72" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="AA72">
-        <v>0.99511617332099966</v>
+        <v>0.99782027918606175</v>
       </c>
       <c r="AB72">
-        <v>89.536822448339535</v>
+        <v>39.961548255533756</v>
       </c>
       <c r="AD72" t="s">
         <v>445</v>
@@ -17183,16 +17183,16 @@
         <v>831</v>
       </c>
       <c r="AM72" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="AN72" t="s">
-        <v>680</v>
+        <v>646</v>
       </c>
       <c r="AO72">
-        <v>0.94664324606770156</v>
+        <v>0.98244678792215867</v>
       </c>
       <c r="AP72">
-        <v>978.20715542547146</v>
+        <v>321.80888809375716</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -17257,16 +17257,16 @@
         <v>572</v>
       </c>
       <c r="Y73" t="s">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="Z73" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="AA73">
-        <v>0.98218461904404952</v>
+        <v>0.99273760630626895</v>
       </c>
       <c r="AB73">
-        <v>326.61531752575877</v>
+        <v>133.14388438506904</v>
       </c>
       <c r="AD73" t="s">
         <v>445</v>
@@ -17293,16 +17293,16 @@
         <v>833</v>
       </c>
       <c r="AM73" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="AN73" t="s">
-        <v>646</v>
+        <v>990</v>
       </c>
       <c r="AO73">
-        <v>0.96085367337953664</v>
+        <v>0.99244907456015963</v>
       </c>
       <c r="AP73">
-        <v>717.68265470849451</v>
+        <v>138.43363306374022</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -17367,16 +17367,16 @@
         <v>574</v>
       </c>
       <c r="Y74" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="Z74" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="AA74">
-        <v>0.99847910710774135</v>
+        <v>0.99564857688473862</v>
       </c>
       <c r="AB74">
-        <v>27.883036358075909</v>
+        <v>79.77609044645817</v>
       </c>
       <c r="AD74" t="s">
         <v>445</v>
@@ -17403,16 +17403,16 @@
         <v>835</v>
       </c>
       <c r="AM74" t="s">
+        <v>991</v>
+      </c>
+      <c r="AN74" t="s">
         <v>992</v>
       </c>
-      <c r="AN74" t="s">
-        <v>647</v>
-      </c>
       <c r="AO74">
-        <v>0.94667937507615152</v>
+        <v>0.99706791078062507</v>
       </c>
       <c r="AP74">
-        <v>977.54479027055595</v>
+        <v>53.754969021872945</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -17477,16 +17477,16 @@
         <v>576</v>
       </c>
       <c r="Y75" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
       <c r="Z75" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="AA75">
-        <v>0.97969590283269214</v>
+        <v>0.99351242433990716</v>
       </c>
       <c r="AB75">
-        <v>372.24178140064373</v>
+        <v>118.93888710170195</v>
       </c>
       <c r="AD75" t="s">
         <v>445</v>
@@ -17516,13 +17516,13 @@
         <v>993</v>
       </c>
       <c r="AN75" t="s">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="AO75">
-        <v>0.99485429484434884</v>
+        <v>0.97818029957439945</v>
       </c>
       <c r="AP75">
-        <v>94.33792785360508</v>
+        <v>400.02784113601069</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -17587,16 +17587,16 @@
         <v>578</v>
       </c>
       <c r="Y76" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="Z76" t="s">
-        <v>651</v>
+        <v>692</v>
       </c>
       <c r="AA76">
-        <v>0.98086220977655469</v>
+        <v>0.99821138151964162</v>
       </c>
       <c r="AB76">
-        <v>350.85948742983044</v>
+        <v>32.791338806570671</v>
       </c>
       <c r="AD76" t="s">
         <v>445</v>
@@ -17626,13 +17626,13 @@
         <v>994</v>
       </c>
       <c r="AN76" t="s">
-        <v>973</v>
+        <v>995</v>
       </c>
       <c r="AO76">
-        <v>0.99104002253663459</v>
+        <v>0.95946658042945154</v>
       </c>
       <c r="AP76">
-        <v>164.26625349503158</v>
+        <v>743.11269212672175</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -17697,16 +17697,16 @@
         <v>580</v>
       </c>
       <c r="Y77" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Z77" t="s">
-        <v>651</v>
+        <v>693</v>
       </c>
       <c r="AA77">
-        <v>0.99377506386421921</v>
+        <v>0.98466621786657815</v>
       </c>
       <c r="AB77">
-        <v>114.12382915598114</v>
+        <v>281.11933911273309</v>
       </c>
       <c r="AD77" t="s">
         <v>445</v>
@@ -17733,16 +17733,16 @@
         <v>841</v>
       </c>
       <c r="AM77" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="AN77" t="s">
-        <v>996</v>
+        <v>693</v>
       </c>
       <c r="AO77">
-        <v>0.98218033156447682</v>
+        <v>0.96103827796400987</v>
       </c>
       <c r="AP77">
-        <v>326.69392131792426</v>
+        <v>714.29823732648526</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -17807,16 +17807,16 @@
         <v>582</v>
       </c>
       <c r="Y78" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Z78" t="s">
-        <v>680</v>
+        <v>694</v>
       </c>
       <c r="AA78">
-        <v>0.95105540198711702</v>
+        <v>0.94191717639101813</v>
       </c>
       <c r="AB78">
-        <v>897.31763023618794</v>
+        <v>1064.8517661646679</v>
       </c>
       <c r="AD78" t="s">
         <v>445</v>
@@ -17846,13 +17846,13 @@
         <v>997</v>
       </c>
       <c r="AN78" t="s">
-        <v>998</v>
+        <v>656</v>
       </c>
       <c r="AO78">
-        <v>0.99585887269839302</v>
+        <v>0.96185713019776531</v>
       </c>
       <c r="AP78">
-        <v>75.920667196127695</v>
+        <v>699.28594637430331</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -17917,16 +17917,16 @@
         <v>584</v>
       </c>
       <c r="Y79" t="s">
-        <v>373</v>
+        <v>439</v>
       </c>
       <c r="Z79" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="AA79">
-        <v>0.99131962187405476</v>
+        <v>0.96994910016476243</v>
       </c>
       <c r="AB79">
-        <v>159.14026564233004</v>
+        <v>550.93316364602254</v>
       </c>
       <c r="AD79" t="s">
         <v>445</v>
@@ -17953,16 +17953,16 @@
         <v>845</v>
       </c>
       <c r="AM79" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="AN79" t="s">
-        <v>1000</v>
+        <v>646</v>
       </c>
       <c r="AO79">
-        <v>0.99612820180322659</v>
+        <v>0.95931345925264233</v>
       </c>
       <c r="AP79">
-        <v>70.982966940846623</v>
+        <v>745.91991370155699</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18030,7 +18030,7 @@
         <v>393</v>
       </c>
       <c r="Z80" t="s">
-        <v>660</v>
+        <v>693</v>
       </c>
       <c r="AA80">
         <v>0.94904572806075094</v>
@@ -18063,16 +18063,16 @@
         <v>847</v>
       </c>
       <c r="AM80" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="AN80" t="s">
-        <v>673</v>
+        <v>1000</v>
       </c>
       <c r="AO80">
-        <v>0.99160044224340704</v>
+        <v>0.98333626289132436</v>
       </c>
       <c r="AP80">
-        <v>153.99189220420479</v>
+        <v>305.50184699238736</v>
       </c>
     </row>
     <row r="81" spans="2:42">
@@ -18140,7 +18140,7 @@
         <v>365</v>
       </c>
       <c r="Z81" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AA81">
         <v>0.94779673241739959</v>
@@ -18173,16 +18173,16 @@
         <v>849</v>
       </c>
       <c r="AM81" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AN81" t="s">
         <v>1002</v>
       </c>
-      <c r="AN81" t="s">
-        <v>1003</v>
-      </c>
       <c r="AO81">
-        <v>0.98943214953804659</v>
+        <v>0.99580424242160948</v>
       </c>
       <c r="AP81">
-        <v>193.7439251358123</v>
+        <v>76.922222270493648</v>
       </c>
     </row>
     <row r="82" spans="2:42">
@@ -18250,7 +18250,7 @@
         <v>440</v>
       </c>
       <c r="Z82" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="AA82">
         <v>0.96846296248311359</v>
@@ -18283,16 +18283,16 @@
         <v>851</v>
       </c>
       <c r="AM82" t="s">
+        <v>1003</v>
+      </c>
+      <c r="AN82" t="s">
         <v>1004</v>
       </c>
-      <c r="AN82" t="s">
-        <v>1005</v>
-      </c>
       <c r="AO82">
-        <v>0.99751889144721539</v>
+        <v>0.99143965884476559</v>
       </c>
       <c r="AP82">
-        <v>45.486990134384541</v>
+        <v>156.93958784596441</v>
       </c>
     </row>
     <row r="83" spans="2:42">
@@ -18360,7 +18360,7 @@
         <v>400</v>
       </c>
       <c r="Z83" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="AA83">
         <v>0.99564253113732704</v>
@@ -18393,16 +18393,16 @@
         <v>853</v>
       </c>
       <c r="AM83" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AN83" t="s">
-        <v>1007</v>
+        <v>665</v>
       </c>
       <c r="AO83">
-        <v>0.97572899399979196</v>
+        <v>0.9937244183974584</v>
       </c>
       <c r="AP83">
-        <v>444.96844333714796</v>
+        <v>115.0523293799298</v>
       </c>
     </row>
     <row r="84" spans="2:42">
@@ -18467,16 +18467,16 @@
         <v>594</v>
       </c>
       <c r="Y84" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="Z84" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="AA84">
-        <v>0.99515580458889907</v>
+        <v>0.98507000954579316</v>
       </c>
       <c r="AB84">
-        <v>88.81024920351615</v>
+        <v>273.71649166045961</v>
       </c>
       <c r="AD84" t="s">
         <v>445</v>
@@ -18503,16 +18503,16 @@
         <v>855</v>
       </c>
       <c r="AM84" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="AN84" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="AO84">
-        <v>0.97620022609803814</v>
+        <v>0.93186769579006068</v>
       </c>
       <c r="AP84">
-        <v>436.32918820263421</v>
+        <v>1249.0922438488865</v>
       </c>
     </row>
     <row r="85" spans="2:42">
@@ -18577,16 +18577,16 @@
         <v>596</v>
       </c>
       <c r="Y85" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z85" t="s">
-        <v>668</v>
+        <v>699</v>
       </c>
       <c r="AA85">
-        <v>0.96473247588547761</v>
+        <v>0.95257490531108058</v>
       </c>
       <c r="AB85">
-        <v>646.57127543291119</v>
+        <v>869.46006929685575</v>
       </c>
       <c r="AD85" t="s">
         <v>445</v>
@@ -18613,16 +18613,16 @@
         <v>857</v>
       </c>
       <c r="AM85" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="AN85" t="s">
-        <v>1010</v>
+        <v>666</v>
       </c>
       <c r="AO85">
-        <v>0.98607591956620455</v>
+        <v>0.94664324606770156</v>
       </c>
       <c r="AP85">
-        <v>255.27480795291643</v>
+        <v>978.20715542547146</v>
       </c>
     </row>
     <row r="86" spans="2:42">
@@ -18687,16 +18687,16 @@
         <v>598</v>
       </c>
       <c r="Y86" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z86" t="s">
         <v>646</v>
       </c>
       <c r="AA86">
-        <v>0.9580334555499519</v>
+        <v>0.9934232231965805</v>
       </c>
       <c r="AB86">
-        <v>769.38664825088097</v>
+        <v>120.5742413960235</v>
       </c>
       <c r="AD86" t="s">
         <v>445</v>
@@ -18723,16 +18723,16 @@
         <v>859</v>
       </c>
       <c r="AM86" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="AN86" t="s">
-        <v>680</v>
+        <v>646</v>
       </c>
       <c r="AO86">
-        <v>0.94516861039769784</v>
+        <v>0.96085367337953664</v>
       </c>
       <c r="AP86">
-        <v>1005.2421427088731</v>
+        <v>717.68265470849451</v>
       </c>
     </row>
     <row r="87" spans="2:42">
@@ -18797,16 +18797,16 @@
         <v>600</v>
       </c>
       <c r="Y87" t="s">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="Z87" t="s">
-        <v>694</v>
+        <v>648</v>
       </c>
       <c r="AA87">
-        <v>0.98447946182885371</v>
+        <v>0.98371921732749934</v>
       </c>
       <c r="AB87">
-        <v>284.54319980434889</v>
+        <v>298.48101566251137</v>
       </c>
       <c r="AD87" t="s">
         <v>445</v>
@@ -18833,16 +18833,16 @@
         <v>861</v>
       </c>
       <c r="AM87" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="AN87" t="s">
-        <v>1013</v>
+        <v>648</v>
       </c>
       <c r="AO87">
-        <v>0.94231963623506931</v>
+        <v>0.94667937507615152</v>
       </c>
       <c r="AP87">
-        <v>1057.4733356903953</v>
+        <v>977.54479027055595</v>
       </c>
     </row>
     <row r="88" spans="2:42">
@@ -18907,16 +18907,16 @@
         <v>602</v>
       </c>
       <c r="Y88" t="s">
-        <v>368</v>
+        <v>442</v>
       </c>
       <c r="Z88" t="s">
-        <v>647</v>
+        <v>700</v>
       </c>
       <c r="AA88">
-        <v>0.94017535716671519</v>
+        <v>0.98946891329754838</v>
       </c>
       <c r="AB88">
-        <v>1096.7851186102214</v>
+        <v>193.0699228782787</v>
       </c>
       <c r="AD88" t="s">
         <v>445</v>
@@ -18943,16 +18943,16 @@
         <v>863</v>
       </c>
       <c r="AM88" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="AN88" t="s">
         <v>646</v>
       </c>
       <c r="AO88">
-        <v>0.97832027217029349</v>
+        <v>0.99485429484434884</v>
       </c>
       <c r="AP88">
-        <v>397.46167687795332</v>
+        <v>94.33792785360508</v>
       </c>
     </row>
     <row r="89" spans="2:42">
@@ -19017,16 +19017,16 @@
         <v>604</v>
       </c>
       <c r="Y89" t="s">
-        <v>360</v>
+        <v>421</v>
       </c>
       <c r="Z89" t="s">
-        <v>646</v>
+        <v>701</v>
       </c>
       <c r="AA89">
-        <v>0.98182986571182285</v>
+        <v>0.99042712787144371</v>
       </c>
       <c r="AB89">
-        <v>333.11912861658175</v>
+        <v>175.50265569019879</v>
       </c>
       <c r="AD89" t="s">
         <v>445</v>
@@ -19053,16 +19053,16 @@
         <v>865</v>
       </c>
       <c r="AM89" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="AN89" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="AO89">
-        <v>0.99484431329617862</v>
+        <v>0.99104002253663459</v>
       </c>
       <c r="AP89">
-        <v>94.520922903391252</v>
+        <v>164.26625349503158</v>
       </c>
     </row>
     <row r="90" spans="2:42">
@@ -19127,16 +19127,16 @@
         <v>606</v>
       </c>
       <c r="Y90" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="Z90" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AA90">
-        <v>0.99024931522063975</v>
+        <v>0.98458760722006711</v>
       </c>
       <c r="AB90">
-        <v>178.76255428827085</v>
+        <v>282.56053429877028</v>
       </c>
       <c r="AD90" t="s">
         <v>445</v>
@@ -19163,16 +19163,16 @@
         <v>867</v>
       </c>
       <c r="AM90" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="AN90" t="s">
-        <v>647</v>
+        <v>1013</v>
       </c>
       <c r="AO90">
-        <v>0.97273741219297172</v>
+        <v>0.98218033156447682</v>
       </c>
       <c r="AP90">
-        <v>499.8141097955185</v>
+        <v>326.69392131792426</v>
       </c>
     </row>
     <row r="91" spans="2:42">
@@ -19237,16 +19237,16 @@
         <v>608</v>
       </c>
       <c r="Y91" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="Z91" t="s">
-        <v>696</v>
+        <v>656</v>
       </c>
       <c r="AA91">
-        <v>0.99501647162473339</v>
+        <v>0.97454833391525864</v>
       </c>
       <c r="AB91">
-        <v>91.364686879888396</v>
+        <v>466.6138782202575</v>
       </c>
       <c r="AD91" t="s">
         <v>445</v>
@@ -19273,16 +19273,16 @@
         <v>869</v>
       </c>
       <c r="AM91" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="AN91" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="AO91">
-        <v>0.97984247759827614</v>
+        <v>0.99585887269839302</v>
       </c>
       <c r="AP91">
-        <v>369.55457736493832</v>
+        <v>75.920667196127695</v>
       </c>
     </row>
     <row r="92" spans="2:42">
@@ -19347,16 +19347,16 @@
         <v>610</v>
       </c>
       <c r="Y92" t="s">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="Z92" t="s">
-        <v>697</v>
+        <v>646</v>
       </c>
       <c r="AA92">
-        <v>0.99545036495775863</v>
+        <v>0.95322333844045537</v>
       </c>
       <c r="AB92">
-        <v>83.409975774425632</v>
+        <v>857.57212859165099</v>
       </c>
       <c r="AD92" t="s">
         <v>445</v>
@@ -19383,16 +19383,16 @@
         <v>871</v>
       </c>
       <c r="AM92" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="AN92" t="s">
-        <v>648</v>
+        <v>1017</v>
       </c>
       <c r="AO92">
-        <v>0.99109308381957362</v>
+        <v>0.99612820180322659</v>
       </c>
       <c r="AP92">
-        <v>163.29346330781715</v>
+        <v>70.982966940846623</v>
       </c>
     </row>
     <row r="93" spans="2:42">
@@ -19457,16 +19457,16 @@
         <v>612</v>
       </c>
       <c r="Y93" t="s">
-        <v>416</v>
+        <v>352</v>
       </c>
       <c r="Z93" t="s">
-        <v>698</v>
+        <v>646</v>
       </c>
       <c r="AA93">
-        <v>0.98826693080891115</v>
+        <v>0.97321507838078658</v>
       </c>
       <c r="AB93">
-        <v>215.10626850329641</v>
+        <v>491.05689635224547</v>
       </c>
       <c r="AD93" t="s">
         <v>445</v>
@@ -19493,16 +19493,16 @@
         <v>873</v>
       </c>
       <c r="AM93" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="AN93" t="s">
-        <v>698</v>
+        <v>646</v>
       </c>
       <c r="AO93">
-        <v>0.98250131854428446</v>
+        <v>0.97935848497620392</v>
       </c>
       <c r="AP93">
-        <v>320.80916002145239</v>
+        <v>378.42777543626062</v>
       </c>
     </row>
     <row r="94" spans="2:42">
@@ -19567,16 +19567,16 @@
         <v>614</v>
       </c>
       <c r="Y94" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="Z94" t="s">
-        <v>680</v>
+        <v>648</v>
       </c>
       <c r="AA94">
-        <v>0.97618980314151516</v>
+        <v>0.98581703135158405</v>
       </c>
       <c r="AB94">
-        <v>436.52027573888904</v>
+        <v>260.02109188762591</v>
       </c>
       <c r="AD94" t="s">
         <v>445</v>
@@ -19603,16 +19603,16 @@
         <v>875</v>
       </c>
       <c r="AM94" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="AN94" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="AO94">
-        <v>0.94941329297783439</v>
+        <v>0.97738569554252064</v>
       </c>
       <c r="AP94">
-        <v>927.42296207303548</v>
+        <v>414.59558172045399</v>
       </c>
     </row>
     <row r="95" spans="2:42">
@@ -19677,16 +19677,16 @@
         <v>616</v>
       </c>
       <c r="Y95" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="Z95" t="s">
-        <v>699</v>
+        <v>648</v>
       </c>
       <c r="AA95">
-        <v>0.99263667372558639</v>
+        <v>0.97542624087094398</v>
       </c>
       <c r="AB95">
-        <v>134.9943150309158</v>
+        <v>450.51891736602602</v>
       </c>
       <c r="AD95" t="s">
         <v>445</v>
@@ -19713,16 +19713,16 @@
         <v>877</v>
       </c>
       <c r="AM95" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="AN95" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO95">
-        <v>0.94697941545710573</v>
+        <v>0.98739702445646216</v>
       </c>
       <c r="AP95">
-        <v>972.0440499530622</v>
+        <v>231.05455163152675</v>
       </c>
     </row>
     <row r="96" spans="2:42">
@@ -19787,16 +19787,16 @@
         <v>618</v>
       </c>
       <c r="Y96" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
       <c r="Z96" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="AA96">
-        <v>0.98665714478881894</v>
+        <v>0.99745350130137034</v>
       </c>
       <c r="AB96">
-        <v>244.61901220498595</v>
+        <v>46.685809474876969</v>
       </c>
       <c r="AD96" t="s">
         <v>445</v>
@@ -19823,16 +19823,16 @@
         <v>879</v>
       </c>
       <c r="AM96" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="AN96" t="s">
-        <v>647</v>
+        <v>1022</v>
       </c>
       <c r="AO96">
-        <v>0.96335236529265011</v>
+        <v>0.99755801237420683</v>
       </c>
       <c r="AP96">
-        <v>671.87330296808034</v>
+        <v>44.769773139540511</v>
       </c>
     </row>
     <row r="97" spans="2:42">
@@ -19897,16 +19897,16 @@
         <v>620</v>
       </c>
       <c r="Y97" t="s">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="Z97" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="AA97">
-        <v>0.99671990332447369</v>
+        <v>0.98101450166571025</v>
       </c>
       <c r="AB97">
-        <v>60.135105717982277</v>
+        <v>348.06746946197933</v>
       </c>
       <c r="AD97" t="s">
         <v>445</v>
@@ -19933,16 +19933,16 @@
         <v>881</v>
       </c>
       <c r="AM97" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="AN97" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="AO97">
-        <v>0.97070223771032205</v>
+        <v>0.99770486090207411</v>
       </c>
       <c r="AP97">
-        <v>537.12564197742824</v>
+        <v>42.077550128640524</v>
       </c>
     </row>
     <row r="98" spans="2:42">
@@ -20007,16 +20007,16 @@
         <v>622</v>
       </c>
       <c r="Y98" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="Z98" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="AA98">
-        <v>0.97971956708030139</v>
+        <v>0.99489296223435719</v>
       </c>
       <c r="AB98">
-        <v>371.80793686114123</v>
+        <v>93.629025703450537</v>
       </c>
       <c r="AD98" t="s">
         <v>445</v>
@@ -20043,16 +20043,16 @@
         <v>883</v>
       </c>
       <c r="AM98" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="AN98" t="s">
-        <v>649</v>
+        <v>1026</v>
       </c>
       <c r="AO98">
-        <v>0.98586375931635961</v>
+        <v>0.97950961971620221</v>
       </c>
       <c r="AP98">
-        <v>259.16441253340616</v>
+        <v>375.65697186962575</v>
       </c>
     </row>
     <row r="99" spans="2:42">
@@ -20117,16 +20117,16 @@
         <v>624</v>
       </c>
       <c r="Y99" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="Z99" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="AA99">
-        <v>0.98980411719589489</v>
+        <v>0.99705259621301434</v>
       </c>
       <c r="AB99">
-        <v>186.92451807526095</v>
+        <v>54.035736094736372</v>
       </c>
       <c r="AD99" t="s">
         <v>445</v>
@@ -20153,16 +20153,16 @@
         <v>885</v>
       </c>
       <c r="AM99" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AN99" t="s">
-        <v>680</v>
+        <v>648</v>
       </c>
       <c r="AO99">
-        <v>0.98753047073573874</v>
+        <v>0.94721908575810376</v>
       </c>
       <c r="AP99">
-        <v>228.60803651145704</v>
+        <v>967.65009443476538</v>
       </c>
     </row>
     <row r="100" spans="2:42">
@@ -20227,16 +20227,16 @@
         <v>626</v>
       </c>
       <c r="Y100" t="s">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="Z100" t="s">
-        <v>651</v>
+        <v>707</v>
       </c>
       <c r="AA100">
-        <v>0.95872760140098945</v>
+        <v>0.98777287103353073</v>
       </c>
       <c r="AB100">
-        <v>756.66064098185961</v>
+        <v>224.16403105193586</v>
       </c>
       <c r="AD100" t="s">
         <v>445</v>
@@ -20263,16 +20263,16 @@
         <v>887</v>
       </c>
       <c r="AM100" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="AN100" t="s">
-        <v>680</v>
+        <v>648</v>
       </c>
       <c r="AO100">
-        <v>0.96497483135850137</v>
+        <v>0.98898335230625201</v>
       </c>
       <c r="AP100">
-        <v>642.12809176080782</v>
+        <v>201.97187438538015</v>
       </c>
     </row>
     <row r="101" spans="2:42">
@@ -20337,16 +20337,16 @@
         <v>628</v>
       </c>
       <c r="Y101" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="Z101" t="s">
-        <v>704</v>
+        <v>656</v>
       </c>
       <c r="AA101">
-        <v>0.93423394789967462</v>
+        <v>0.97754100001622091</v>
       </c>
       <c r="AB101">
-        <v>1205.7109551726326</v>
+        <v>411.74833303595017</v>
       </c>
       <c r="AD101" t="s">
         <v>445</v>
@@ -20373,16 +20373,16 @@
         <v>889</v>
       </c>
       <c r="AM101" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AN101" t="s">
         <v>1030</v>
       </c>
-      <c r="AN101" t="s">
-        <v>647</v>
-      </c>
       <c r="AO101">
-        <v>0.953110606460702</v>
+        <v>0.99506178999496608</v>
       </c>
       <c r="AP101">
-        <v>859.63888155379732</v>
+        <v>90.533850092289356</v>
       </c>
     </row>
     <row r="102" spans="2:42">
@@ -20447,16 +20447,16 @@
         <v>630</v>
       </c>
       <c r="Y102" t="s">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="Z102" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="AA102">
-        <v>0.97861539621410798</v>
+        <v>0.95401962289287812</v>
       </c>
       <c r="AB102">
-        <v>392.05106940802045</v>
+        <v>842.97358029723534</v>
       </c>
       <c r="AD102" t="s">
         <v>445</v>
@@ -20486,13 +20486,13 @@
         <v>1031</v>
       </c>
       <c r="AN102" t="s">
-        <v>672</v>
+        <v>708</v>
       </c>
       <c r="AO102">
-        <v>0.95955011836243909</v>
+        <v>0.99493880624410824</v>
       </c>
       <c r="AP102">
-        <v>741.58116335528291</v>
+        <v>92.7885521913487</v>
       </c>
     </row>
     <row r="103" spans="2:42">
@@ -20557,16 +20557,16 @@
         <v>632</v>
       </c>
       <c r="Y103" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="Z103" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AA103">
-        <v>0.97896212777707714</v>
+        <v>0.98495178422440233</v>
       </c>
       <c r="AB103">
-        <v>385.69432408691944</v>
+        <v>275.88395588595779</v>
       </c>
       <c r="AD103" t="s">
         <v>445</v>
@@ -20596,13 +20596,13 @@
         <v>1032</v>
       </c>
       <c r="AN103" t="s">
-        <v>1033</v>
+        <v>665</v>
       </c>
       <c r="AO103">
-        <v>0.9966806183812299</v>
+        <v>0.98250131854428446</v>
       </c>
       <c r="AP103">
-        <v>60.855329677452332</v>
+        <v>320.80916002145239</v>
       </c>
     </row>
     <row r="104" spans="2:42">
@@ -20667,16 +20667,16 @@
         <v>634</v>
       </c>
       <c r="Y104" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="Z104" t="s">
-        <v>705</v>
+        <v>648</v>
       </c>
       <c r="AA104">
-        <v>0.99805781879500122</v>
+        <v>0.97886062539501351</v>
       </c>
       <c r="AB104">
-        <v>35.60665542497717</v>
+        <v>387.55520109141952</v>
       </c>
       <c r="AD104" t="s">
         <v>445</v>
@@ -20703,16 +20703,16 @@
         <v>895</v>
       </c>
       <c r="AM104" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="AN104" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="AO104">
-        <v>0.99215245657219142</v>
+        <v>0.94941329297783439</v>
       </c>
       <c r="AP104">
-        <v>143.87162950982398</v>
+        <v>927.42296207303548</v>
       </c>
     </row>
     <row r="105" spans="2:42">
@@ -20777,16 +20777,16 @@
         <v>636</v>
       </c>
       <c r="Y105" t="s">
-        <v>407</v>
+        <v>364</v>
       </c>
       <c r="Z105" t="s">
-        <v>706</v>
+        <v>648</v>
       </c>
       <c r="AA105">
-        <v>0.99892391441583261</v>
+        <v>0.99386727950885501</v>
       </c>
       <c r="AB105">
-        <v>19.728235709736104</v>
+        <v>112.43320900432452</v>
       </c>
       <c r="AD105" t="s">
         <v>445</v>
@@ -20813,16 +20813,16 @@
         <v>897</v>
       </c>
       <c r="AM105" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="AN105" t="s">
-        <v>668</v>
+        <v>648</v>
       </c>
       <c r="AO105">
-        <v>0.9485944422668402</v>
+        <v>0.94697941545710573</v>
       </c>
       <c r="AP105">
-        <v>942.43522510793025</v>
+        <v>972.0440499530622</v>
       </c>
     </row>
     <row r="106" spans="2:42">
@@ -20887,16 +20887,16 @@
         <v>638</v>
       </c>
       <c r="Y106" t="s">
-        <v>401</v>
+        <v>371</v>
       </c>
       <c r="Z106" t="s">
-        <v>707</v>
+        <v>648</v>
       </c>
       <c r="AA106">
-        <v>0.99646875354725362</v>
+        <v>0.96488803122020605</v>
       </c>
       <c r="AB106">
-        <v>64.739518300349658</v>
+        <v>643.71942762955541</v>
       </c>
       <c r="AD106" t="s">
         <v>445</v>
@@ -20923,16 +20923,16 @@
         <v>899</v>
       </c>
       <c r="AM106" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="AN106" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO106">
-        <v>0.97043152360247686</v>
+        <v>0.96335236529265011</v>
       </c>
       <c r="AP106">
-        <v>542.08873395459034</v>
+        <v>671.87330296808034</v>
       </c>
     </row>
     <row r="107" spans="2:42">
@@ -20997,16 +20997,16 @@
         <v>640</v>
       </c>
       <c r="Y107" t="s">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="Z107" t="s">
         <v>708</v>
       </c>
       <c r="AA107">
-        <v>0.9922209073807341</v>
+        <v>0.99588620223113744</v>
       </c>
       <c r="AB107">
-        <v>142.61669801987438</v>
+        <v>75.419625762480621</v>
       </c>
       <c r="AD107" t="s">
         <v>445</v>
@@ -21033,16 +21033,16 @@
         <v>901</v>
       </c>
       <c r="AM107" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AN107" t="s">
         <v>1037</v>
       </c>
-      <c r="AN107" t="s">
-        <v>690</v>
-      </c>
       <c r="AO107">
-        <v>0.9922676414012731</v>
+        <v>0.97070223771032205</v>
       </c>
       <c r="AP107">
-        <v>141.75990764332545</v>
+        <v>537.12564197742824</v>
       </c>
     </row>
   </sheetData>
@@ -21051,7 +21051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60927AD7-0A9A-42E7-AB0F-D2F324041C63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615F3A40-975D-408D-8314-A5404FC3BBD8}">
   <dimension ref="B9:Z107"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -21163,7 +21163,7 @@
         <v>1213</v>
       </c>
       <c r="K11" t="s">
-        <v>914</v>
+        <v>1020</v>
       </c>
       <c r="L11">
         <v>0.17596388835381646</v>
@@ -21196,7 +21196,7 @@
         <v>1407</v>
       </c>
       <c r="X11" t="s">
-        <v>1205</v>
+        <v>1178</v>
       </c>
       <c r="Y11">
         <v>45.567749999999997</v>
@@ -21231,7 +21231,7 @@
         <v>1215</v>
       </c>
       <c r="K12" t="s">
-        <v>1017</v>
+        <v>962</v>
       </c>
       <c r="L12">
         <v>0.5998563972685973</v>
@@ -21264,7 +21264,7 @@
         <v>1409</v>
       </c>
       <c r="X12" t="s">
-        <v>1144</v>
+        <v>1164</v>
       </c>
       <c r="Y12">
         <v>102.99525</v>
@@ -21299,7 +21299,7 @@
         <v>1217</v>
       </c>
       <c r="K13" t="s">
-        <v>954</v>
+        <v>932</v>
       </c>
       <c r="L13">
         <v>4.2823239792782193</v>
@@ -21332,7 +21332,7 @@
         <v>1411</v>
       </c>
       <c r="X13" t="s">
-        <v>1188</v>
+        <v>1160</v>
       </c>
       <c r="Y13">
         <v>77.929500000000004</v>
@@ -21367,7 +21367,7 @@
         <v>1219</v>
       </c>
       <c r="K14" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
       <c r="L14">
         <v>9.5215803844936261E-2</v>
@@ -21400,7 +21400,7 @@
         <v>1413</v>
       </c>
       <c r="X14" t="s">
-        <v>1153</v>
+        <v>1144</v>
       </c>
       <c r="Y14">
         <v>34.414499999999997</v>
@@ -21435,7 +21435,7 @@
         <v>1221</v>
       </c>
       <c r="K15" t="s">
-        <v>915</v>
+        <v>1021</v>
       </c>
       <c r="L15">
         <v>3.6287474003893196</v>
@@ -21468,7 +21468,7 @@
         <v>1415</v>
       </c>
       <c r="X15" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="Y15">
         <v>48.263249999999999</v>
@@ -21503,7 +21503,7 @@
         <v>1223</v>
       </c>
       <c r="K16" t="s">
-        <v>1018</v>
+        <v>963</v>
       </c>
       <c r="L16">
         <v>43.604071708920948</v>
@@ -21536,7 +21536,7 @@
         <v>1417</v>
       </c>
       <c r="X16" t="s">
-        <v>1203</v>
+        <v>1193</v>
       </c>
       <c r="Y16">
         <v>27.429749999999999</v>
@@ -21571,7 +21571,7 @@
         <v>1225</v>
       </c>
       <c r="K17" t="s">
-        <v>1037</v>
+        <v>945</v>
       </c>
       <c r="L17">
         <v>9.6809271032388455</v>
@@ -21604,7 +21604,7 @@
         <v>1419</v>
       </c>
       <c r="X17" t="s">
-        <v>1191</v>
+        <v>1201</v>
       </c>
       <c r="Y17">
         <v>29.697749999999999</v>
@@ -21639,7 +21639,7 @@
         <v>1227</v>
       </c>
       <c r="K18" t="s">
-        <v>921</v>
+        <v>989</v>
       </c>
       <c r="L18">
         <v>19.57643322237125</v>
@@ -21672,7 +21672,7 @@
         <v>1421</v>
       </c>
       <c r="X18" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="Y18">
         <v>39.247500000000002</v>
@@ -21707,7 +21707,7 @@
         <v>1229</v>
       </c>
       <c r="K19" t="s">
-        <v>981</v>
+        <v>1028</v>
       </c>
       <c r="L19">
         <v>55.638210824668811</v>
@@ -21740,7 +21740,7 @@
         <v>1423</v>
       </c>
       <c r="X19" t="s">
-        <v>1200</v>
+        <v>1176</v>
       </c>
       <c r="Y19">
         <v>54.114750000000001</v>
@@ -21775,7 +21775,7 @@
         <v>1231</v>
       </c>
       <c r="K20" t="s">
-        <v>953</v>
+        <v>931</v>
       </c>
       <c r="L20">
         <v>4.3112694152725819</v>
@@ -21843,7 +21843,7 @@
         <v>1233</v>
       </c>
       <c r="K21" t="s">
-        <v>931</v>
+        <v>909</v>
       </c>
       <c r="L21">
         <v>11.295459465941514</v>
@@ -21876,7 +21876,7 @@
         <v>1427</v>
       </c>
       <c r="X21" t="s">
-        <v>1166</v>
+        <v>1153</v>
       </c>
       <c r="Y21">
         <v>11.891999999999999</v>
@@ -21911,7 +21911,7 @@
         <v>1235</v>
       </c>
       <c r="K22" t="s">
-        <v>950</v>
+        <v>928</v>
       </c>
       <c r="L22">
         <v>3.350731358569373</v>
@@ -21944,7 +21944,7 @@
         <v>1429</v>
       </c>
       <c r="X22" t="s">
-        <v>1168</v>
+        <v>1195</v>
       </c>
       <c r="Y22">
         <v>163.69575</v>
@@ -21979,7 +21979,7 @@
         <v>1237</v>
       </c>
       <c r="K23" t="s">
-        <v>986</v>
+        <v>938</v>
       </c>
       <c r="L23">
         <v>89.260194648908481</v>
@@ -22012,7 +22012,7 @@
         <v>1431</v>
       </c>
       <c r="X23" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="Y23">
         <v>98.379000000000005</v>
@@ -22047,7 +22047,7 @@
         <v>1239</v>
       </c>
       <c r="K24" t="s">
-        <v>929</v>
+        <v>907</v>
       </c>
       <c r="L24">
         <v>54.288016768663745</v>
@@ -22080,7 +22080,7 @@
         <v>1433</v>
       </c>
       <c r="X24" t="s">
-        <v>1164</v>
+        <v>1151</v>
       </c>
       <c r="Y24">
         <v>89.855999999999995</v>
@@ -22115,7 +22115,7 @@
         <v>1241</v>
       </c>
       <c r="K25" t="s">
-        <v>1036</v>
+        <v>944</v>
       </c>
       <c r="L25">
         <v>76.46332597527315</v>
@@ -22148,7 +22148,7 @@
         <v>1435</v>
       </c>
       <c r="X25" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="Y25">
         <v>46.682250000000003</v>
@@ -22183,7 +22183,7 @@
         <v>1243</v>
       </c>
       <c r="K26" t="s">
-        <v>928</v>
+        <v>906</v>
       </c>
       <c r="L26">
         <v>127.51605886676012</v>
@@ -22216,7 +22216,7 @@
         <v>1437</v>
       </c>
       <c r="X26" t="s">
-        <v>1162</v>
+        <v>1149</v>
       </c>
       <c r="Y26">
         <v>54.84825</v>
@@ -22251,7 +22251,7 @@
         <v>1245</v>
       </c>
       <c r="K27" t="s">
-        <v>1011</v>
+        <v>956</v>
       </c>
       <c r="L27">
         <v>46.793063320317437</v>
@@ -22284,7 +22284,7 @@
         <v>1439</v>
       </c>
       <c r="X27" t="s">
-        <v>1195</v>
+        <v>1171</v>
       </c>
       <c r="Y27">
         <v>44.145000000000003</v>
@@ -22319,7 +22319,7 @@
         <v>1247</v>
       </c>
       <c r="K28" t="s">
-        <v>1022</v>
+        <v>1033</v>
       </c>
       <c r="L28">
         <v>82.443327158392236</v>
@@ -22352,7 +22352,7 @@
         <v>1441</v>
       </c>
       <c r="X28" t="s">
-        <v>1196</v>
+        <v>1172</v>
       </c>
       <c r="Y28">
         <v>62.381250000000001</v>
@@ -22387,7 +22387,7 @@
         <v>1249</v>
       </c>
       <c r="K29" t="s">
-        <v>992</v>
+        <v>1009</v>
       </c>
       <c r="L29">
         <v>97.980091042432477</v>
@@ -22420,7 +22420,7 @@
         <v>1443</v>
       </c>
       <c r="X29" t="s">
-        <v>1178</v>
+        <v>1205</v>
       </c>
       <c r="Y29">
         <v>8.1000000000000003E-2</v>
@@ -22455,7 +22455,7 @@
         <v>1251</v>
       </c>
       <c r="K30" t="s">
-        <v>947</v>
+        <v>925</v>
       </c>
       <c r="L30">
         <v>110.94074818055437</v>
@@ -22488,7 +22488,7 @@
         <v>1445</v>
       </c>
       <c r="X30" t="s">
-        <v>1176</v>
+        <v>1203</v>
       </c>
       <c r="Y30">
         <v>133.70025000000001</v>
@@ -22523,7 +22523,7 @@
         <v>1253</v>
       </c>
       <c r="K31" t="s">
-        <v>930</v>
+        <v>908</v>
       </c>
       <c r="L31">
         <v>2.4273016266691929</v>
@@ -22556,7 +22556,7 @@
         <v>1447</v>
       </c>
       <c r="X31" t="s">
-        <v>1173</v>
+        <v>1190</v>
       </c>
       <c r="Y31">
         <v>102.82425000000001</v>
@@ -22591,7 +22591,7 @@
         <v>1255</v>
       </c>
       <c r="K32" t="s">
-        <v>980</v>
+        <v>1027</v>
       </c>
       <c r="L32">
         <v>0.49128575065453367</v>
@@ -22624,7 +22624,7 @@
         <v>1449</v>
       </c>
       <c r="X32" t="s">
-        <v>1198</v>
+        <v>1174</v>
       </c>
       <c r="Y32">
         <v>170.13075000000001</v>
@@ -22659,7 +22659,7 @@
         <v>1257</v>
       </c>
       <c r="K33" t="s">
-        <v>1024</v>
+        <v>1035</v>
       </c>
       <c r="L33">
         <v>1.2848345469829228</v>
@@ -22692,7 +22692,7 @@
         <v>1451</v>
       </c>
       <c r="X33" t="s">
-        <v>1148</v>
+        <v>1168</v>
       </c>
       <c r="Y33">
         <v>65.342250000000007</v>
@@ -22727,7 +22727,7 @@
         <v>1259</v>
       </c>
       <c r="K34" t="s">
-        <v>964</v>
+        <v>951</v>
       </c>
       <c r="L34">
         <v>0.18935486724764602</v>
@@ -22760,7 +22760,7 @@
         <v>1453</v>
       </c>
       <c r="X34" t="s">
-        <v>1175</v>
+        <v>1202</v>
       </c>
       <c r="Y34">
         <v>53.101500000000001</v>
@@ -22795,7 +22795,7 @@
         <v>1261</v>
       </c>
       <c r="K35" t="s">
-        <v>1023</v>
+        <v>1034</v>
       </c>
       <c r="L35">
         <v>0.58118601062718378</v>
@@ -22828,7 +22828,7 @@
         <v>1455</v>
       </c>
       <c r="X35" t="s">
-        <v>1142</v>
+        <v>1162</v>
       </c>
       <c r="Y35">
         <v>49.923749999999998</v>
@@ -22863,7 +22863,7 @@
         <v>1263</v>
       </c>
       <c r="K36" t="s">
-        <v>1035</v>
+        <v>943</v>
       </c>
       <c r="L36">
         <v>3.6717551314203591</v>
@@ -22896,7 +22896,7 @@
         <v>1457</v>
       </c>
       <c r="X36" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="Y36">
         <v>98.321250000000006</v>
@@ -22931,7 +22931,7 @@
         <v>1265</v>
       </c>
       <c r="K37" t="s">
-        <v>989</v>
+        <v>1006</v>
       </c>
       <c r="L37">
         <v>0.9445236469650512</v>
@@ -22964,7 +22964,7 @@
         <v>1459</v>
       </c>
       <c r="X37" t="s">
-        <v>1161</v>
+        <v>1148</v>
       </c>
       <c r="Y37">
         <v>99.285749999999993</v>
@@ -22999,7 +22999,7 @@
         <v>1267</v>
       </c>
       <c r="K38" t="s">
-        <v>1030</v>
+        <v>969</v>
       </c>
       <c r="L38">
         <v>5.8689650080792175</v>
@@ -23032,7 +23032,7 @@
         <v>1461</v>
       </c>
       <c r="X38" t="s">
-        <v>1187</v>
+        <v>1159</v>
       </c>
       <c r="Y38">
         <v>35.836500000000001</v>
@@ -23067,7 +23067,7 @@
         <v>1269</v>
       </c>
       <c r="K39" t="s">
-        <v>927</v>
+        <v>905</v>
       </c>
       <c r="L39">
         <v>2.928657185415191</v>
@@ -23100,7 +23100,7 @@
         <v>1463</v>
       </c>
       <c r="X39" t="s">
-        <v>1151</v>
+        <v>1142</v>
       </c>
       <c r="Y39">
         <v>62.210999999999999</v>
@@ -23135,7 +23135,7 @@
         <v>1271</v>
       </c>
       <c r="K40" t="s">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="L40">
         <v>1.2558278274148955</v>
@@ -23168,7 +23168,7 @@
         <v>1465</v>
       </c>
       <c r="X40" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="Y40">
         <v>31.096499999999999</v>
@@ -23203,7 +23203,7 @@
         <v>1273</v>
       </c>
       <c r="K41" t="s">
-        <v>997</v>
+        <v>1014</v>
       </c>
       <c r="L41">
         <v>2.2433982976323423</v>
@@ -23236,7 +23236,7 @@
         <v>1467</v>
       </c>
       <c r="X41" t="s">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="Y41">
         <v>34.518749999999997</v>
@@ -23271,7 +23271,7 @@
         <v>1275</v>
       </c>
       <c r="K42" t="s">
-        <v>908</v>
+        <v>976</v>
       </c>
       <c r="L42">
         <v>1.4423728327070269</v>
@@ -23304,7 +23304,7 @@
         <v>1469</v>
       </c>
       <c r="X42" t="s">
-        <v>1201</v>
+        <v>1177</v>
       </c>
       <c r="Y42">
         <v>2.74125</v>
@@ -23339,7 +23339,7 @@
         <v>1277</v>
       </c>
       <c r="K43" t="s">
-        <v>1004</v>
+        <v>983</v>
       </c>
       <c r="L43">
         <v>8.0555754971063411</v>
@@ -23372,7 +23372,7 @@
         <v>1471</v>
       </c>
       <c r="X43" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="Y43">
         <v>24.691500000000001</v>
@@ -23407,7 +23407,7 @@
         <v>1279</v>
       </c>
       <c r="K44" t="s">
-        <v>951</v>
+        <v>929</v>
       </c>
       <c r="L44">
         <v>20.016919488105035</v>
@@ -23440,7 +23440,7 @@
         <v>1473</v>
       </c>
       <c r="X44" t="s">
-        <v>1206</v>
+        <v>1179</v>
       </c>
       <c r="Y44">
         <v>47.016750000000002</v>
@@ -23475,7 +23475,7 @@
         <v>1281</v>
       </c>
       <c r="K45" t="s">
-        <v>1001</v>
+        <v>980</v>
       </c>
       <c r="L45">
         <v>20.987410272533506</v>
@@ -23508,7 +23508,7 @@
         <v>1475</v>
       </c>
       <c r="X45" t="s">
-        <v>1156</v>
+        <v>1147</v>
       </c>
       <c r="Y45">
         <v>19.535250000000001</v>
@@ -23543,7 +23543,7 @@
         <v>1283</v>
       </c>
       <c r="K46" t="s">
-        <v>1002</v>
+        <v>981</v>
       </c>
       <c r="L46">
         <v>55.435583296031403</v>
@@ -23576,7 +23576,7 @@
         <v>1477</v>
       </c>
       <c r="X46" t="s">
-        <v>1189</v>
+        <v>1161</v>
       </c>
       <c r="Y46">
         <v>25.143000000000001</v>
@@ -23611,7 +23611,7 @@
         <v>1285</v>
       </c>
       <c r="K47" t="s">
-        <v>1015</v>
+        <v>960</v>
       </c>
       <c r="L47">
         <v>32.999903868338116</v>
@@ -23644,7 +23644,7 @@
         <v>1479</v>
       </c>
       <c r="X47" t="s">
-        <v>1154</v>
+        <v>1145</v>
       </c>
       <c r="Y47">
         <v>67.352999999999994</v>
@@ -23679,7 +23679,7 @@
         <v>1287</v>
       </c>
       <c r="K48" t="s">
-        <v>906</v>
+        <v>974</v>
       </c>
       <c r="L48">
         <v>49.696797018491381</v>
@@ -23712,7 +23712,7 @@
         <v>1481</v>
       </c>
       <c r="X48" t="s">
-        <v>1146</v>
+        <v>1166</v>
       </c>
       <c r="Y48">
         <v>34.546500000000002</v>
@@ -23747,7 +23747,7 @@
         <v>1289</v>
       </c>
       <c r="K49" t="s">
-        <v>994</v>
+        <v>1011</v>
       </c>
       <c r="L49">
         <v>32.640247665750501</v>
@@ -23780,7 +23780,7 @@
         <v>1483</v>
       </c>
       <c r="X49" t="s">
-        <v>1155</v>
+        <v>1146</v>
       </c>
       <c r="Y49">
         <v>77.410499999999999</v>
@@ -23815,7 +23815,7 @@
         <v>1291</v>
       </c>
       <c r="K50" t="s">
-        <v>993</v>
+        <v>1010</v>
       </c>
       <c r="L50">
         <v>65.219358423551554</v>
@@ -23848,7 +23848,7 @@
         <v>1485</v>
       </c>
       <c r="X50" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="Y50">
         <v>63.802500000000002</v>
@@ -23883,7 +23883,7 @@
         <v>1293</v>
       </c>
       <c r="K51" t="s">
-        <v>932</v>
+        <v>910</v>
       </c>
       <c r="L51">
         <v>52.726851063159351</v>
@@ -23916,7 +23916,7 @@
         <v>1487</v>
       </c>
       <c r="X51" t="s">
-        <v>1150</v>
+        <v>1170</v>
       </c>
       <c r="Y51">
         <v>53.966999999999999</v>
@@ -23951,7 +23951,7 @@
         <v>1295</v>
       </c>
       <c r="K52" t="s">
-        <v>913</v>
+        <v>1019</v>
       </c>
       <c r="L52">
         <v>48.062334008658908</v>
@@ -24019,7 +24019,7 @@
         <v>1297</v>
       </c>
       <c r="K53" t="s">
-        <v>995</v>
+        <v>1012</v>
       </c>
       <c r="L53">
         <v>115.35264042679813</v>
@@ -24052,7 +24052,7 @@
         <v>1491</v>
       </c>
       <c r="X53" t="s">
-        <v>1199</v>
+        <v>1175</v>
       </c>
       <c r="Y53">
         <v>188.35499999999999</v>
@@ -24087,7 +24087,7 @@
         <v>1299</v>
       </c>
       <c r="K54" t="s">
-        <v>1031</v>
+        <v>970</v>
       </c>
       <c r="L54">
         <v>66.906827934341507</v>
@@ -24120,7 +24120,7 @@
         <v>1493</v>
       </c>
       <c r="X54" t="s">
-        <v>1149</v>
+        <v>1169</v>
       </c>
       <c r="Y54">
         <v>114.67274999999999</v>
@@ -24155,7 +24155,7 @@
         <v>1301</v>
       </c>
       <c r="K55" t="s">
-        <v>948</v>
+        <v>926</v>
       </c>
       <c r="L55">
         <v>134.24925626793836</v>
@@ -24188,7 +24188,7 @@
         <v>1495</v>
       </c>
       <c r="X55" t="s">
-        <v>1202</v>
+        <v>1192</v>
       </c>
       <c r="Y55">
         <v>53.234250000000003</v>
@@ -24223,7 +24223,7 @@
         <v>1303</v>
       </c>
       <c r="K56" t="s">
-        <v>987</v>
+        <v>939</v>
       </c>
       <c r="L56">
         <v>93.313759881118116</v>
@@ -24256,7 +24256,7 @@
         <v>1497</v>
       </c>
       <c r="X56" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="Y56">
         <v>159.49875</v>
@@ -24291,7 +24291,7 @@
         <v>1305</v>
       </c>
       <c r="K57" t="s">
-        <v>1025</v>
+        <v>1036</v>
       </c>
       <c r="L57">
         <v>145.76340565827428</v>
@@ -24359,7 +24359,7 @@
         <v>1307</v>
       </c>
       <c r="K58" t="s">
-        <v>991</v>
+        <v>1008</v>
       </c>
       <c r="L58">
         <v>148.48080229460197</v>
@@ -24392,7 +24392,7 @@
         <v>1501</v>
       </c>
       <c r="X58" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="Y58">
         <v>183.47624999999999</v>
@@ -24427,7 +24427,7 @@
         <v>1309</v>
       </c>
       <c r="K59" t="s">
-        <v>920</v>
+        <v>988</v>
       </c>
       <c r="L59">
         <v>71.838937782979016</v>
@@ -24495,7 +24495,7 @@
         <v>1311</v>
       </c>
       <c r="K60" t="s">
-        <v>971</v>
+        <v>998</v>
       </c>
       <c r="L60">
         <v>80.257558228094155</v>
@@ -24528,7 +24528,7 @@
         <v>1505</v>
       </c>
       <c r="X60" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="Y60">
         <v>11.7315</v>
@@ -24563,7 +24563,7 @@
         <v>1313</v>
       </c>
       <c r="K61" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
       <c r="L61">
         <v>146.07778098481995</v>
@@ -24596,7 +24596,7 @@
         <v>1507</v>
       </c>
       <c r="X61" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="Y61">
         <v>195.03299999999999</v>
@@ -24631,7 +24631,7 @@
         <v>1315</v>
       </c>
       <c r="K62" t="s">
-        <v>1014</v>
+        <v>959</v>
       </c>
       <c r="L62">
         <v>106.1298736355218</v>
@@ -24664,7 +24664,7 @@
         <v>1509</v>
       </c>
       <c r="X62" t="s">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="Y62">
         <v>154.16175000000001</v>
@@ -24699,7 +24699,7 @@
         <v>1317</v>
       </c>
       <c r="K63" t="s">
-        <v>912</v>
+        <v>1018</v>
       </c>
       <c r="L63">
         <v>124.94443081089416</v>
@@ -24734,7 +24734,7 @@
         <v>1319</v>
       </c>
       <c r="K64" t="s">
-        <v>910</v>
+        <v>978</v>
       </c>
       <c r="L64">
         <v>12.652627740935781</v>
@@ -24769,7 +24769,7 @@
         <v>1321</v>
       </c>
       <c r="K65" t="s">
-        <v>955</v>
+        <v>933</v>
       </c>
       <c r="L65">
         <v>22.889688294443275</v>
@@ -24804,7 +24804,7 @@
         <v>1323</v>
       </c>
       <c r="K66" t="s">
-        <v>935</v>
+        <v>913</v>
       </c>
       <c r="L66">
         <v>1.5318794868726651</v>
@@ -24839,7 +24839,7 @@
         <v>1325</v>
       </c>
       <c r="K67" t="s">
-        <v>923</v>
+        <v>991</v>
       </c>
       <c r="L67">
         <v>0.59942290733321824</v>
@@ -24874,7 +24874,7 @@
         <v>1327</v>
       </c>
       <c r="K68" t="s">
-        <v>982</v>
+        <v>1029</v>
       </c>
       <c r="L68">
         <v>11.453222815679586</v>
@@ -24909,7 +24909,7 @@
         <v>1329</v>
       </c>
       <c r="K69" t="s">
-        <v>917</v>
+        <v>1023</v>
       </c>
       <c r="L69">
         <v>2.2803547354553286</v>
@@ -24944,7 +24944,7 @@
         <v>1331</v>
       </c>
       <c r="K70" t="s">
-        <v>943</v>
+        <v>921</v>
       </c>
       <c r="L70">
         <v>1.6411981852360265</v>
@@ -24979,7 +24979,7 @@
         <v>1333</v>
       </c>
       <c r="K71" t="s">
-        <v>999</v>
+        <v>1016</v>
       </c>
       <c r="L71">
         <v>3.6294095116605649</v>
@@ -25014,7 +25014,7 @@
         <v>1335</v>
       </c>
       <c r="K72" t="s">
-        <v>957</v>
+        <v>935</v>
       </c>
       <c r="L72">
         <v>4.463691536387925</v>
@@ -25049,7 +25049,7 @@
         <v>1337</v>
       </c>
       <c r="K73" t="s">
-        <v>984</v>
+        <v>1031</v>
       </c>
       <c r="L73">
         <v>0.15904812550112069</v>
@@ -25084,7 +25084,7 @@
         <v>1339</v>
       </c>
       <c r="K74" t="s">
-        <v>941</v>
+        <v>919</v>
       </c>
       <c r="L74">
         <v>0.38231455598608644</v>
@@ -25119,7 +25119,7 @@
         <v>1341</v>
       </c>
       <c r="K75" t="s">
-        <v>1006</v>
+        <v>985</v>
       </c>
       <c r="L75">
         <v>48.459263659244627</v>
@@ -25154,7 +25154,7 @@
         <v>1343</v>
       </c>
       <c r="K76" t="s">
-        <v>933</v>
+        <v>911</v>
       </c>
       <c r="L76">
         <v>31.18047373096908</v>
@@ -25189,7 +25189,7 @@
         <v>1345</v>
       </c>
       <c r="K77" t="s">
-        <v>1020</v>
+        <v>965</v>
       </c>
       <c r="L77">
         <v>21.737639110123883</v>
@@ -25224,7 +25224,7 @@
         <v>1347</v>
       </c>
       <c r="K78" t="s">
-        <v>976</v>
+        <v>1003</v>
       </c>
       <c r="L78">
         <v>7.7564715726947338</v>
@@ -25259,7 +25259,7 @@
         <v>1349</v>
       </c>
       <c r="K79" t="s">
-        <v>1027</v>
+        <v>966</v>
       </c>
       <c r="L79">
         <v>59.663991486822887</v>
@@ -25294,7 +25294,7 @@
         <v>1351</v>
       </c>
       <c r="K80" t="s">
-        <v>1009</v>
+        <v>954</v>
       </c>
       <c r="L80">
         <v>67.484986191080594</v>
@@ -25329,7 +25329,7 @@
         <v>1353</v>
       </c>
       <c r="K81" t="s">
-        <v>925</v>
+        <v>903</v>
       </c>
       <c r="L81">
         <v>8.9831631319223497</v>
@@ -25364,7 +25364,7 @@
         <v>1355</v>
       </c>
       <c r="K82" t="s">
-        <v>919</v>
+        <v>987</v>
       </c>
       <c r="L82">
         <v>74.407838302658988</v>
@@ -25399,7 +25399,7 @@
         <v>1357</v>
       </c>
       <c r="K83" t="s">
-        <v>938</v>
+        <v>916</v>
       </c>
       <c r="L83">
         <v>66.237243466162568</v>
@@ -25434,7 +25434,7 @@
         <v>1359</v>
       </c>
       <c r="K84" t="s">
-        <v>1021</v>
+        <v>1032</v>
       </c>
       <c r="L84">
         <v>87.803826101842702</v>
@@ -25469,7 +25469,7 @@
         <v>1361</v>
       </c>
       <c r="K85" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
       <c r="L85">
         <v>13.111660750581855</v>
@@ -25504,7 +25504,7 @@
         <v>1363</v>
       </c>
       <c r="K86" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="L86">
         <v>28.441848841140754</v>
@@ -25539,7 +25539,7 @@
         <v>1365</v>
       </c>
       <c r="K87" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="L87">
         <v>143.86519004409737</v>
@@ -25574,7 +25574,7 @@
         <v>1367</v>
       </c>
       <c r="K88" t="s">
-        <v>944</v>
+        <v>922</v>
       </c>
       <c r="L88">
         <v>2.4247911368184991</v>
@@ -25609,7 +25609,7 @@
         <v>1369</v>
       </c>
       <c r="K89" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
       <c r="L89">
         <v>1.2775502846450904</v>
@@ -25644,7 +25644,7 @@
         <v>1371</v>
       </c>
       <c r="K90" t="s">
-        <v>988</v>
+        <v>1005</v>
       </c>
       <c r="L90">
         <v>13.425882161067216</v>
@@ -25679,7 +25679,7 @@
         <v>1373</v>
       </c>
       <c r="K91" t="s">
-        <v>1034</v>
+        <v>942</v>
       </c>
       <c r="L91">
         <v>2.4640928691199862</v>
@@ -25714,7 +25714,7 @@
         <v>1375</v>
       </c>
       <c r="K92" t="s">
-        <v>1028</v>
+        <v>967</v>
       </c>
       <c r="L92">
         <v>121.00853795417976</v>
@@ -25749,7 +25749,7 @@
         <v>1377</v>
       </c>
       <c r="K93" t="s">
-        <v>978</v>
+        <v>1025</v>
       </c>
       <c r="L93">
         <v>124.790495670129</v>
@@ -25784,7 +25784,7 @@
         <v>1379</v>
       </c>
       <c r="K94" t="s">
-        <v>985</v>
+        <v>937</v>
       </c>
       <c r="L94">
         <v>76.573281453558408</v>
@@ -25819,7 +25819,7 @@
         <v>1381</v>
       </c>
       <c r="K95" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
       <c r="L95">
         <v>83.622813239085914</v>
@@ -25854,7 +25854,7 @@
         <v>1383</v>
       </c>
       <c r="K96" t="s">
-        <v>990</v>
+        <v>1007</v>
       </c>
       <c r="L96">
         <v>98.771916583186524</v>
@@ -25889,7 +25889,7 @@
         <v>1385</v>
       </c>
       <c r="K97" t="s">
-        <v>1029</v>
+        <v>968</v>
       </c>
       <c r="L97">
         <v>113.7602367199374</v>
@@ -25924,7 +25924,7 @@
         <v>1387</v>
       </c>
       <c r="K98" t="s">
-        <v>1012</v>
+        <v>957</v>
       </c>
       <c r="L98">
         <v>106.58940043603886</v>
@@ -25959,7 +25959,7 @@
         <v>1389</v>
       </c>
       <c r="K99" t="s">
-        <v>939</v>
+        <v>917</v>
       </c>
       <c r="L99">
         <v>82.155437931771587</v>
@@ -25994,7 +25994,7 @@
         <v>1391</v>
       </c>
       <c r="K100" t="s">
-        <v>945</v>
+        <v>923</v>
       </c>
       <c r="L100">
         <v>129.44215482043572</v>
@@ -26029,7 +26029,7 @@
         <v>1393</v>
       </c>
       <c r="K101" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="L101">
         <v>0.89144958684441589</v>
@@ -26064,7 +26064,7 @@
         <v>1395</v>
       </c>
       <c r="K102" t="s">
-        <v>905</v>
+        <v>973</v>
       </c>
       <c r="L102">
         <v>75.325753274416684</v>
@@ -26099,7 +26099,7 @@
         <v>1397</v>
       </c>
       <c r="K103" t="s">
-        <v>1032</v>
+        <v>940</v>
       </c>
       <c r="L103">
         <v>22.126012715065421</v>
@@ -26134,7 +26134,7 @@
         <v>1399</v>
       </c>
       <c r="K104" t="s">
-        <v>903</v>
+        <v>971</v>
       </c>
       <c r="L104">
         <v>65.153596720209478</v>
@@ -26169,7 +26169,7 @@
         <v>1401</v>
       </c>
       <c r="K105" t="s">
-        <v>937</v>
+        <v>915</v>
       </c>
       <c r="L105">
         <v>111.2273781855134</v>
@@ -26204,7 +26204,7 @@
         <v>1403</v>
       </c>
       <c r="K106" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="L106">
         <v>16.632205399674447</v>
@@ -26239,7 +26239,7 @@
         <v>1405</v>
       </c>
       <c r="K107" t="s">
-        <v>1008</v>
+        <v>953</v>
       </c>
       <c r="L107">
         <v>47.109387092480588</v>
@@ -26254,7 +26254,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9E1D6D-B468-432D-902E-A9B8D59E8796}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15792D1-F6B5-4AA1-BC33-DEDB84C13BD5}">
   <dimension ref="B9:Y136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78699F2F-7A11-40C0-876C-A15A071012F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEFCEAA-A050-4982-8663-5C52D3F15BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,18 +1403,36 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_AUS_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_AUS_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_AUS_014</t>
   </si>
   <si>
@@ -1433,6 +1451,216 @@
     <t>connecting solar to buses in cluster 97</t>
   </si>
   <si>
+    <t>distr_solelc_spv_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_AUS_009</t>
   </si>
   <si>
@@ -1463,34 +1691,190 @@
     <t>connecting solar to buses in cluster 62</t>
   </si>
   <si>
-    <t>distr_solelc_spv_AUS_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
+    <t>distr_solelc_spv_AUS_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
     <t>distr_solelc_spv_AUS_006</t>
@@ -1529,160 +1913,40 @@
     <t>connecting solar to buses in cluster 77</t>
   </si>
   <si>
-    <t>distr_solelc_spv_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
+    <t>distr_solelc_spv_AUS_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
   </si>
   <si>
     <t>distr_solelc_spv_AUS_022</t>
@@ -1727,276 +1991,21 @@
     <t>connecting solar to buses in cluster 91</t>
   </si>
   <si>
-    <t>distr_solelc_spv_AUS_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Robertstown_AUS</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>e_BrokenHill_AUS</t>
+  </si>
+  <si>
     <t>e_Nebo_AUS</t>
   </si>
   <si>
@@ -2006,22 +2015,106 @@
     <t>e_Kalgoorlie_AUS</t>
   </si>
   <si>
+    <t>e_Armidale_AUS</t>
+  </si>
+  <si>
+    <t>e_Merredin_AUS</t>
+  </si>
+  <si>
+    <t>e_Morawa_AUS</t>
+  </si>
+  <si>
+    <t>e_Horsham_AUS</t>
+  </si>
+  <si>
+    <t>e_SydneyWest_AUS</t>
+  </si>
+  <si>
     <t>e_Davenport_AUS</t>
   </si>
   <si>
+    <t>e_Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>e_Para_AUS</t>
+  </si>
+  <si>
+    <t>e_OlympicDamWest_AUS</t>
+  </si>
+  <si>
+    <t>e_CalliopeRiver_AUS</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS</t>
+  </si>
+  <si>
+    <t>e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
+    <t>e_SouthMorang_AUS</t>
+  </si>
+  <si>
+    <t>e_Ballarat_AUS</t>
+  </si>
+  <si>
+    <t>e_Strathmore_AUS</t>
+  </si>
+  <si>
+    <t>e_TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>e_Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS</t>
+  </si>
+  <si>
+    <t>e_Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>e_Canberra_AUS</t>
+  </si>
+  <si>
+    <t>e_PortHedland_AUS</t>
+  </si>
+  <si>
     <t>e_Balranald_AUS</t>
   </si>
   <si>
-    <t>e_OlympicDamWest_AUS</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS</t>
-  </si>
-  <si>
-    <t>e_Broadsound_AUS</t>
+    <t>e_Wagga_AUS</t>
+  </si>
+  <si>
+    <t>e_Rowville_AUS</t>
+  </si>
+  <si>
+    <t>e_Yandin_AUS</t>
+  </si>
+  <si>
+    <t>e_CentralCoast_AUS</t>
+  </si>
+  <si>
+    <t>e_Perth_AUS</t>
+  </si>
+  <si>
+    <t>e_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS</t>
+  </si>
+  <si>
+    <t>e_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>e_Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarong_AUS</t>
+  </si>
+  <si>
+    <t>e_GinGin_AUS</t>
+  </si>
+  <si>
+    <t>e_Sheffield_AUS</t>
   </si>
   <si>
     <t>e_Calvale_AUS</t>
@@ -2030,52 +2123,10 @@
     <t>e_BulliCreek_AUS</t>
   </si>
   <si>
-    <t>e_Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>e_Australind_AUS</t>
-  </si>
-  <si>
-    <t>e_Ipswich_AUS</t>
-  </si>
-  <si>
-    <t>e_Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>e_TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>e_Morawa_AUS</t>
-  </si>
-  <si>
-    <t>e_Kingston_AUS</t>
-  </si>
-  <si>
-    <t>e_Sheffield_AUS</t>
-  </si>
-  <si>
-    <t>e_Canberra_AUS</t>
-  </si>
-  <si>
-    <t>e_PortHedland_AUS</t>
-  </si>
-  <si>
-    <t>e_Armidale_AUS</t>
-  </si>
-  <si>
-    <t>e_Merredin_AUS</t>
-  </si>
-  <si>
-    <t>e_Horsham_AUS</t>
-  </si>
-  <si>
-    <t>e_Strathmore_AUS</t>
+    <t>e_MountPiper_AUS</t>
+  </si>
+  <si>
+    <t>e_Murray_AUS</t>
   </si>
   <si>
     <t>e_UpperTumut_AUS</t>
@@ -2084,55 +2135,190 @@
     <t>e_Tarrone_AUS</t>
   </si>
   <si>
-    <t>e_Tarong_AUS</t>
-  </si>
-  <si>
-    <t>e_GinGin_AUS</t>
-  </si>
-  <si>
-    <t>e_MountPiper_AUS</t>
-  </si>
-  <si>
-    <t>e_Murray_AUS</t>
-  </si>
-  <si>
-    <t>e_Robertstown_AUS</t>
-  </si>
-  <si>
-    <t>e_SydneyWest_AUS</t>
-  </si>
-  <si>
-    <t>e_Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>e_Para_AUS</t>
-  </si>
-  <si>
-    <t>e_CalliopeRiver_AUS</t>
-  </si>
-  <si>
-    <t>e_Wagga_AUS</t>
-  </si>
-  <si>
-    <t>e_Rowville_AUS</t>
-  </si>
-  <si>
-    <t>e_Yandin_AUS</t>
-  </si>
-  <si>
-    <t>e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>e_Perth_AUS</t>
-  </si>
-  <si>
-    <t>e_SouthMorang_AUS</t>
-  </si>
-  <si>
-    <t>e_Ballarat_AUS</t>
-  </si>
-  <si>
-    <t>e_Hazelwood_AUS</t>
+    <t>distr_wonelc_won_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_083</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_074</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_087</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_096</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_097</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_073</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_080</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_082</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_084</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_092</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 92</t>
   </si>
   <si>
     <t>distr_wonelc_won_AUS_025</t>
@@ -2165,22 +2351,130 @@
     <t>connecting wind onshore to buses in cluster 88</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
+    <t>distr_wonelc_won_AUS_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_095</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_089</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_075</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_085</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 85</t>
   </si>
   <si>
     <t>distr_wonelc_won_AUS_021</t>
@@ -2267,78 +2561,6 @@
     <t>connecting wind onshore to buses in cluster 93</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_074</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_075</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_085</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 85</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_AUS_001</t>
   </si>
   <si>
@@ -2405,6 +2627,30 @@
     <t>connecting wind onshore to buses in cluster 91</t>
   </si>
   <si>
+    <t>distr_wonelc_won_AUS_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_077</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 77</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_AUS_028</t>
   </si>
   <si>
@@ -2441,90 +2687,6 @@
     <t>connecting wind onshore to buses in cluster 86</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_089</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_095</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 95</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_AUS_039</t>
   </si>
   <si>
@@ -2555,166 +2717,97 @@
     <t>connecting wind onshore to buses in cluster 94</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_083</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_077</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_073</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_080</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_082</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_084</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_092</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_087</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_096</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_097</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 97</t>
+    <t>elc_won_AUS_003</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_054</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_063</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_083</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_020</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_031</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_055</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_066</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_074</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_011</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_036</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_087</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_096</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_097</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_023</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_042</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_045</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_047</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_061</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_064</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_002</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_005</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_015</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_043</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_052</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_065</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_073</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_080</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_082</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_084</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_092</t>
   </si>
   <si>
     <t>elc_won_AUS_025</t>
@@ -2732,13 +2825,67 @@
     <t>elc_won_AUS_088</t>
   </si>
   <si>
-    <t>elc_won_AUS_023</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_042</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_045</t>
+    <t>elc_won_AUS_004</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_007</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_009</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_017</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_019</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_040</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_095</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_013</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_032</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_037</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_049</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_050</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_060</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_089</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_008</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_012</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_018</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_026</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_030</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_075</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_085</t>
   </si>
   <si>
     <t>elc_won_AUS_021</t>
@@ -2783,42 +2930,6 @@
     <t>elc_won_AUS_093</t>
   </si>
   <si>
-    <t>elc_won_AUS_020</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_031</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_055</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_066</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_074</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_008</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_012</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_018</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_026</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_030</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_075</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_085</t>
-  </si>
-  <si>
     <t>elc_won_AUS_001</t>
   </si>
   <si>
@@ -2852,6 +2963,18 @@
     <t>elc_won_AUS_091</t>
   </si>
   <si>
+    <t>elc_won_AUS_010</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_035</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_069</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_077</t>
+  </si>
+  <si>
     <t>elc_won_AUS_028</t>
   </si>
   <si>
@@ -2870,48 +2993,6 @@
     <t>elc_won_AUS_086</t>
   </si>
   <si>
-    <t>elc_won_AUS_013</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_032</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_037</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_049</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_050</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_060</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_089</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_004</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_007</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_009</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_017</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_019</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_040</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_095</t>
-  </si>
-  <si>
     <t>elc_won_AUS_039</t>
   </si>
   <si>
@@ -2927,85 +3008,190 @@
     <t>elc_won_AUS_094</t>
   </si>
   <si>
-    <t>elc_won_AUS_003</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_054</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_063</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_083</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_047</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_061</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_064</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_010</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_035</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_069</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_077</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_002</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_005</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_015</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_043</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_052</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_065</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_073</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_080</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_082</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_084</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_092</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_011</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_036</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_087</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_096</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_097</t>
+    <t>distr_wofelc_wof_AUS_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_046</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_049</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 50</t>
   </si>
   <si>
     <t>distr_wofelc_wof_AUS_014</t>
@@ -3032,18 +3218,6 @@
     <t>connecting wind offshore to buses in cluster 51</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_AUS_026</t>
   </si>
   <si>
@@ -3068,90 +3242,6 @@
     <t>connecting wind offshore to buses in cluster 47</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_049</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 49</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_AUS_010</t>
   </si>
   <si>
@@ -3182,30 +3272,6 @@
     <t>connecting wind offshore to buses in cluster 52</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 50</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_AUS_004</t>
   </si>
   <si>
@@ -3224,24 +3290,6 @@
     <t>connecting wind offshore to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_046</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 46</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_AUS_002</t>
   </si>
   <si>
@@ -3272,52 +3320,97 @@
     <t>connecting wind offshore to buses in cluster 45</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
+    <t>elc_wof_AUS_017</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_018</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_019</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_015</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_023</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_003</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_043</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_008</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_009</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_016</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_035</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_037</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_041</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_005</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_022</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_029</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_032</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_036</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_039</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_001</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_034</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_046</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_006</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_020</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_028</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_040</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_049</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_024</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_030</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_038</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_050</t>
   </si>
   <si>
     <t>elc_wof_AUS_014</t>
@@ -3332,12 +3425,6 @@
     <t>elc_wof_AUS_051</t>
   </si>
   <si>
-    <t>elc_wof_AUS_006</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_020</t>
-  </si>
-  <si>
     <t>elc_wof_AUS_026</t>
   </si>
   <si>
@@ -3350,48 +3437,6 @@
     <t>elc_wof_AUS_047</t>
   </si>
   <si>
-    <t>elc_wof_AUS_005</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_022</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_029</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_032</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_036</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_039</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_017</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_018</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_019</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_003</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_043</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_028</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_040</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_049</t>
-  </si>
-  <si>
     <t>elc_wof_AUS_010</t>
   </si>
   <si>
@@ -3407,18 +3452,6 @@
     <t>elc_wof_AUS_052</t>
   </si>
   <si>
-    <t>elc_wof_AUS_015</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_023</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_038</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_050</t>
-  </si>
-  <si>
     <t>elc_wof_AUS_004</t>
   </si>
   <si>
@@ -3428,15 +3461,6 @@
     <t>elc_wof_AUS_025</t>
   </si>
   <si>
-    <t>elc_wof_AUS_001</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_034</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_046</t>
-  </si>
-  <si>
     <t>elc_wof_AUS_002</t>
   </si>
   <si>
@@ -3450,30 +3474,6 @@
   </si>
   <si>
     <t>elc_wof_AUS_045</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_008</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_009</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_016</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_035</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_037</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_041</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_024</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_030</t>
   </si>
   <si>
     <t>e_won_AUS_001</t>
@@ -8099,7 +8099,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB85DA0E-0BA9-4D7D-B50F-63561FAC4DE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD2FB4D-97D0-4314-BA2E-908BF61EC8BC}">
   <dimension ref="B9:BD107"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8307,7 +8307,7 @@
         <v>0.62315477680692222</v>
       </c>
       <c r="M11">
-        <v>0.18254179932444109</v>
+        <v>0.129108240861808</v>
       </c>
       <c r="O11" t="s">
         <v>445</v>
@@ -8337,16 +8337,16 @@
         <v>446</v>
       </c>
       <c r="Y11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Z11" t="s">
         <v>644</v>
       </c>
       <c r="AA11">
-        <v>0.97630367280108865</v>
+        <v>0.99240501837238893</v>
       </c>
       <c r="AB11">
-        <v>434.43266531337389</v>
+        <v>139.24132983953538</v>
       </c>
       <c r="AD11" t="s">
         <v>445</v>
@@ -8376,13 +8376,13 @@
         <v>884</v>
       </c>
       <c r="AN11" t="s">
-        <v>654</v>
+        <v>678</v>
       </c>
       <c r="AO11">
-        <v>0.98155612527850788</v>
+        <v>0.98822008409109219</v>
       </c>
       <c r="AP11">
-        <v>338.13770322735616</v>
+        <v>215.96512499664277</v>
       </c>
       <c r="AR11" t="s">
         <v>445</v>
@@ -8412,13 +8412,13 @@
         <v>1085</v>
       </c>
       <c r="BB11" t="s">
-        <v>679</v>
+        <v>664</v>
       </c>
       <c r="BC11">
-        <v>0.98514006154561162</v>
+        <v>0.98425930791162897</v>
       </c>
       <c r="BD11">
-        <v>925.6435835026324</v>
+        <v>936.37409860998696</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8453,7 +8453,7 @@
         <v>4.5871569647254073</v>
       </c>
       <c r="M12">
-        <v>0.17419579548853559</v>
+        <v>0.16949075539584732</v>
       </c>
       <c r="O12" t="s">
         <v>445</v>
@@ -8483,16 +8483,16 @@
         <v>450</v>
       </c>
       <c r="Y12" t="s">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="Z12" t="s">
         <v>645</v>
       </c>
       <c r="AA12">
-        <v>0.978447054607678</v>
+        <v>0.9365516394102017</v>
       </c>
       <c r="AB12">
-        <v>395.13733219256937</v>
+        <v>1163.2199441463022</v>
       </c>
       <c r="AD12" t="s">
         <v>445</v>
@@ -8522,13 +8522,13 @@
         <v>885</v>
       </c>
       <c r="AN12" t="s">
-        <v>649</v>
+        <v>689</v>
       </c>
       <c r="AO12">
-        <v>0.92201529031984186</v>
+        <v>0.99332113976407466</v>
       </c>
       <c r="AP12">
-        <v>1429.719677469566</v>
+        <v>122.44577099196496</v>
       </c>
       <c r="AR12" t="s">
         <v>445</v>
@@ -8558,13 +8558,13 @@
         <v>1086</v>
       </c>
       <c r="BB12" t="s">
-        <v>676</v>
+        <v>657</v>
       </c>
       <c r="BC12">
-        <v>0.9852903703395921</v>
+        <v>0.97983022896434013</v>
       </c>
       <c r="BD12">
-        <v>923.81232136263634</v>
+        <v>990.33504378445582</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8599,7 +8599,7 @@
         <v>1.1750156806043059</v>
       </c>
       <c r="M13">
-        <v>0.16662752662198499</v>
+        <v>0.16457070870590459</v>
       </c>
       <c r="O13" t="s">
         <v>445</v>
@@ -8629,16 +8629,16 @@
         <v>452</v>
       </c>
       <c r="Y13" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="Z13" t="s">
         <v>646</v>
       </c>
       <c r="AA13">
-        <v>0.96307923215762514</v>
+        <v>0.97527660765685298</v>
       </c>
       <c r="AB13">
-        <v>676.88074377687337</v>
+        <v>453.26219295769499</v>
       </c>
       <c r="AD13" t="s">
         <v>445</v>
@@ -8668,13 +8668,13 @@
         <v>886</v>
       </c>
       <c r="AN13" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="AO13">
-        <v>0.98335963574413709</v>
+        <v>0.99451359177835219</v>
       </c>
       <c r="AP13">
-        <v>305.07334469081934</v>
+        <v>100.58415073020944</v>
       </c>
       <c r="AR13" t="s">
         <v>445</v>
@@ -8704,13 +8704,13 @@
         <v>1087</v>
       </c>
       <c r="BB13" t="s">
-        <v>685</v>
+        <v>657</v>
       </c>
       <c r="BC13">
-        <v>0.99350055753404454</v>
+        <v>0.98532695715711582</v>
       </c>
       <c r="BD13">
-        <v>665.79794850597443</v>
+        <v>923.36657196913927</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8745,7 +8745,7 @@
         <v>0.36780463939705538</v>
       </c>
       <c r="M14">
-        <v>0.15509196316414611</v>
+        <v>0.10856437421490227</v>
       </c>
       <c r="O14" t="s">
         <v>445</v>
@@ -8775,16 +8775,16 @@
         <v>454</v>
       </c>
       <c r="Y14" t="s">
-        <v>443</v>
+        <v>358</v>
       </c>
       <c r="Z14" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AA14">
-        <v>0.9793351210469925</v>
+        <v>0.97630367280108865</v>
       </c>
       <c r="AB14">
-        <v>378.85611413846999</v>
+        <v>434.43266531337389</v>
       </c>
       <c r="AD14" t="s">
         <v>445</v>
@@ -8814,13 +8814,13 @@
         <v>887</v>
       </c>
       <c r="AN14" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="AO14">
-        <v>0.98001801309124148</v>
+        <v>0.9909682810714957</v>
       </c>
       <c r="AP14">
-        <v>366.33642666057369</v>
+        <v>165.58151368924484</v>
       </c>
       <c r="AR14" t="s">
         <v>445</v>
@@ -8850,13 +8850,13 @@
         <v>1088</v>
       </c>
       <c r="BB14" t="s">
-        <v>646</v>
+        <v>682</v>
       </c>
       <c r="BC14">
-        <v>0.9737385233335023</v>
+        <v>0.9827191942014929</v>
       </c>
       <c r="BD14">
-        <v>1064.5523240534972</v>
+        <v>955.13781731181223</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8891,7 +8891,7 @@
         <v>2.0139334917395968</v>
       </c>
       <c r="M15">
-        <v>0.1658878296531022</v>
+        <v>0.14501481951056702</v>
       </c>
       <c r="O15" t="s">
         <v>445</v>
@@ -8921,16 +8921,16 @@
         <v>456</v>
       </c>
       <c r="Y15" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Z15" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AA15">
-        <v>0.98418645978522035</v>
+        <v>0.978447054607678</v>
       </c>
       <c r="AB15">
-        <v>289.91490393762615</v>
+        <v>395.13733219256937</v>
       </c>
       <c r="AD15" t="s">
         <v>445</v>
@@ -8960,13 +8960,13 @@
         <v>888</v>
       </c>
       <c r="AN15" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="AO15">
-        <v>0.91475976979271756</v>
+        <v>0.99537175847221593</v>
       </c>
       <c r="AP15">
-        <v>1562.7375538001788</v>
+        <v>84.85109467604083</v>
       </c>
       <c r="AR15" t="s">
         <v>445</v>
@@ -8996,13 +8996,13 @@
         <v>1089</v>
       </c>
       <c r="BB15" t="s">
-        <v>688</v>
+        <v>658</v>
       </c>
       <c r="BC15">
-        <v>0.98870653772658501</v>
+        <v>0.95475709315784774</v>
       </c>
       <c r="BD15">
-        <v>882.19201536443973</v>
+        <v>1295.8094150268885</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9037,7 +9037,7 @@
         <v>4.567467906283377</v>
       </c>
       <c r="M16">
-        <v>0.1890644419668592</v>
+        <v>0.18892535432905502</v>
       </c>
       <c r="O16" t="s">
         <v>445</v>
@@ -9067,16 +9067,16 @@
         <v>458</v>
       </c>
       <c r="Y16" t="s">
-        <v>362</v>
+        <v>442</v>
       </c>
       <c r="Z16" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AA16">
-        <v>0.9906346744759631</v>
+        <v>0.96307923215762514</v>
       </c>
       <c r="AB16">
-        <v>171.69763460734316</v>
+        <v>676.88074377687337</v>
       </c>
       <c r="AD16" t="s">
         <v>445</v>
@@ -9106,13 +9106,13 @@
         <v>889</v>
       </c>
       <c r="AN16" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="AO16">
-        <v>0.99339062123477628</v>
+        <v>0.95891375083366426</v>
       </c>
       <c r="AP16">
-        <v>121.17194402910137</v>
+        <v>753.24790138282128</v>
       </c>
       <c r="AR16" t="s">
         <v>445</v>
@@ -9142,13 +9142,13 @@
         <v>1090</v>
       </c>
       <c r="BB16" t="s">
-        <v>660</v>
+        <v>678</v>
       </c>
       <c r="BC16">
-        <v>0.9861533644012247</v>
+        <v>0.98683737688914319</v>
       </c>
       <c r="BD16">
-        <v>913.29817704507911</v>
+        <v>904.96462490060583</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9183,7 +9183,7 @@
         <v>21.201348678928575</v>
       </c>
       <c r="M17">
-        <v>0.19468311301410679</v>
+        <v>0.19364518490898483</v>
       </c>
       <c r="O17" t="s">
         <v>445</v>
@@ -9213,16 +9213,16 @@
         <v>460</v>
       </c>
       <c r="Y17" t="s">
-        <v>377</v>
+        <v>443</v>
       </c>
       <c r="Z17" t="s">
         <v>649</v>
       </c>
       <c r="AA17">
-        <v>0.95915670695527311</v>
+        <v>0.9793351210469925</v>
       </c>
       <c r="AB17">
-        <v>748.79370581999342</v>
+        <v>378.85611413846999</v>
       </c>
       <c r="AD17" t="s">
         <v>445</v>
@@ -9252,13 +9252,13 @@
         <v>890</v>
       </c>
       <c r="AN17" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="AO17">
-        <v>0.9495926116188812</v>
+        <v>0.97364425413724487</v>
       </c>
       <c r="AP17">
-        <v>924.13545365384425</v>
+        <v>483.18867415051142</v>
       </c>
       <c r="AR17" t="s">
         <v>445</v>
@@ -9288,13 +9288,13 @@
         <v>1091</v>
       </c>
       <c r="BB17" t="s">
-        <v>655</v>
+        <v>674</v>
       </c>
       <c r="BC17">
-        <v>0.946000484445496</v>
+        <v>0.98183502015800017</v>
       </c>
       <c r="BD17">
-        <v>1402.4940978390403</v>
+        <v>965.91000440836387</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9329,7 +9329,7 @@
         <v>6.4480607359441047</v>
       </c>
       <c r="M18">
-        <v>0.1938378451211078</v>
+        <v>0.19317803521340254</v>
       </c>
       <c r="O18" t="s">
         <v>445</v>
@@ -9359,16 +9359,16 @@
         <v>462</v>
       </c>
       <c r="Y18" t="s">
-        <v>407</v>
+        <v>354</v>
       </c>
       <c r="Z18" t="s">
         <v>650</v>
       </c>
       <c r="AA18">
-        <v>0.98927829835282999</v>
+        <v>0.99059066767492976</v>
       </c>
       <c r="AB18">
-        <v>196.56453019811752</v>
+        <v>172.50442595962087</v>
       </c>
       <c r="AD18" t="s">
         <v>445</v>
@@ -9398,13 +9398,13 @@
         <v>891</v>
       </c>
       <c r="AN18" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="AO18">
-        <v>0.95120262528231503</v>
+        <v>0.95472325192752561</v>
       </c>
       <c r="AP18">
-        <v>894.61853649089164</v>
+        <v>830.07371466203085</v>
       </c>
       <c r="AR18" t="s">
         <v>445</v>
@@ -9434,13 +9434,13 @@
         <v>1092</v>
       </c>
       <c r="BB18" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="BC18">
-        <v>0.96304008712262701</v>
+        <v>0.98460725799374227</v>
       </c>
       <c r="BD18">
-        <v>1194.8949385559945</v>
+        <v>932.13490677623929</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9475,7 +9475,7 @@
         <v>1.3432633560097478</v>
       </c>
       <c r="M19">
-        <v>0.18136651093221071</v>
+        <v>0.18041783498245925</v>
       </c>
       <c r="O19" t="s">
         <v>445</v>
@@ -9505,16 +9505,16 @@
         <v>464</v>
       </c>
       <c r="Y19" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="Z19" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="AA19">
-        <v>0.97846149456848719</v>
+        <v>0.95570380597210192</v>
       </c>
       <c r="AB19">
-        <v>394.87259957773409</v>
+        <v>812.09689051146574</v>
       </c>
       <c r="AD19" t="s">
         <v>445</v>
@@ -9544,13 +9544,13 @@
         <v>892</v>
       </c>
       <c r="AN19" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AO19">
-        <v>0.96378142476218853</v>
+        <v>0.99476921667660834</v>
       </c>
       <c r="AP19">
-        <v>664.00721269321059</v>
+        <v>95.897694262180153</v>
       </c>
       <c r="AR19" t="s">
         <v>445</v>
@@ -9580,13 +9580,13 @@
         <v>1093</v>
       </c>
       <c r="BB19" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="BC19">
-        <v>0.98902339847455312</v>
+        <v>0.99676099935070339</v>
       </c>
       <c r="BD19">
-        <v>878.33159525169435</v>
+        <v>458.86857454202811</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9621,7 +9621,7 @@
         <v>37.91472233272016</v>
       </c>
       <c r="M20">
-        <v>0.19495339263173581</v>
+        <v>0.1941466361615807</v>
       </c>
       <c r="O20" t="s">
         <v>445</v>
@@ -9651,16 +9651,16 @@
         <v>466</v>
       </c>
       <c r="Y20" t="s">
-        <v>353</v>
+        <v>398</v>
       </c>
       <c r="Z20" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AA20">
-        <v>0.98522854207859256</v>
+        <v>0.98883273909819114</v>
       </c>
       <c r="AB20">
-        <v>270.81006189247</v>
+        <v>204.7331165331625</v>
       </c>
       <c r="AD20" t="s">
         <v>445</v>
@@ -9690,13 +9690,13 @@
         <v>893</v>
       </c>
       <c r="AN20" t="s">
-        <v>670</v>
+        <v>644</v>
       </c>
       <c r="AO20">
-        <v>0.97998268051544435</v>
+        <v>0.99223838421520194</v>
       </c>
       <c r="AP20">
-        <v>366.9841905501878</v>
+        <v>142.29628938796495</v>
       </c>
       <c r="AR20" t="s">
         <v>445</v>
@@ -9726,13 +9726,13 @@
         <v>1094</v>
       </c>
       <c r="BB20" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="BC20">
-        <v>0.99181397642123026</v>
+        <v>0.96948890259934162</v>
       </c>
       <c r="BD20">
-        <v>772.83962979925604</v>
+        <v>1116.3268699980208</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9767,7 +9767,7 @@
         <v>14.905025922100801</v>
       </c>
       <c r="M21">
-        <v>0.191685294431162</v>
+        <v>0.19148308989241797</v>
       </c>
       <c r="O21" t="s">
         <v>445</v>
@@ -9797,16 +9797,16 @@
         <v>468</v>
       </c>
       <c r="Y21" t="s">
-        <v>361</v>
+        <v>419</v>
       </c>
       <c r="Z21" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="AA21">
-        <v>0.99185644171670617</v>
+        <v>0.98262913774151028</v>
       </c>
       <c r="AB21">
-        <v>149.29856852705402</v>
+        <v>318.46580807231078</v>
       </c>
       <c r="AD21" t="s">
         <v>445</v>
@@ -9836,13 +9836,13 @@
         <v>894</v>
       </c>
       <c r="AN21" t="s">
-        <v>676</v>
+        <v>658</v>
       </c>
       <c r="AO21">
-        <v>0.99273887587992471</v>
+        <v>0.93136449657406906</v>
       </c>
       <c r="AP21">
-        <v>133.12060886804619</v>
+        <v>1258.3175628087345</v>
       </c>
       <c r="AR21" t="s">
         <v>445</v>
@@ -9872,13 +9872,13 @@
         <v>1095</v>
       </c>
       <c r="BB21" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="BC21">
-        <v>0.98624400907289522</v>
+        <v>0.97338301712868025</v>
       </c>
       <c r="BD21">
-        <v>912.19382279522597</v>
+        <v>1068.8835746489126</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9913,7 +9913,7 @@
         <v>28.062880038419888</v>
       </c>
       <c r="M22">
-        <v>0.1992634187419042</v>
+        <v>0.19897541486325493</v>
       </c>
       <c r="O22" t="s">
         <v>445</v>
@@ -9943,16 +9943,16 @@
         <v>470</v>
       </c>
       <c r="Y22" t="s">
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="Z22" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="AA22">
-        <v>0.94189846566095958</v>
+        <v>0.99090558233812054</v>
       </c>
       <c r="AB22">
-        <v>1065.1947962157406</v>
+        <v>166.73099046779075</v>
       </c>
       <c r="AD22" t="s">
         <v>445</v>
@@ -9982,13 +9982,13 @@
         <v>895</v>
       </c>
       <c r="AN22" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="AO22">
-        <v>0.95931345925264233</v>
+        <v>0.9340182520227388</v>
       </c>
       <c r="AP22">
-        <v>745.91991370155699</v>
+        <v>1209.6653795831226</v>
       </c>
       <c r="AR22" t="s">
         <v>445</v>
@@ -10018,13 +10018,13 @@
         <v>1096</v>
       </c>
       <c r="BB22" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
       <c r="BC22">
-        <v>0.96572704859346925</v>
+        <v>0.98973750247525893</v>
       </c>
       <c r="BD22">
-        <v>1162.1587913028991</v>
+        <v>869.63142817642859</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10059,7 +10059,7 @@
         <v>9.5669187778416713</v>
       </c>
       <c r="M23">
-        <v>0.1981543299061847</v>
+        <v>0.19761666490755192</v>
       </c>
       <c r="O23" t="s">
         <v>445</v>
@@ -10089,16 +10089,16 @@
         <v>472</v>
       </c>
       <c r="Y23" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z23" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AA23">
-        <v>0.95001627981732095</v>
+        <v>0.99144634427862732</v>
       </c>
       <c r="AB23">
-        <v>916.36820334911533</v>
+        <v>156.81702155849862</v>
       </c>
       <c r="AD23" t="s">
         <v>445</v>
@@ -10128,13 +10128,13 @@
         <v>896</v>
       </c>
       <c r="AN23" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="AO23">
-        <v>0.99411928823407203</v>
+        <v>0.9922959111510915</v>
       </c>
       <c r="AP23">
-        <v>107.81304904201184</v>
+        <v>141.24162889665487</v>
       </c>
       <c r="AR23" t="s">
         <v>445</v>
@@ -10164,13 +10164,13 @@
         <v>1097</v>
       </c>
       <c r="BB23" t="s">
-        <v>671</v>
+        <v>652</v>
       </c>
       <c r="BC23">
-        <v>0.98481153677494815</v>
+        <v>0.96515942387218789</v>
       </c>
       <c r="BD23">
-        <v>929.64611029188166</v>
+        <v>1169.0743524905106</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10235,16 +10235,16 @@
         <v>474</v>
       </c>
       <c r="Y24" t="s">
-        <v>441</v>
+        <v>347</v>
       </c>
       <c r="Z24" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="AA24">
-        <v>0.98042178820377779</v>
+        <v>0.99571254852817692</v>
       </c>
       <c r="AB24">
-        <v>358.93388293074008</v>
+        <v>78.60327698342283</v>
       </c>
       <c r="AD24" t="s">
         <v>445</v>
@@ -10274,13 +10274,13 @@
         <v>897</v>
       </c>
       <c r="AN24" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="AO24">
-        <v>0.9790694594776973</v>
+        <v>0.97817316280665345</v>
       </c>
       <c r="AP24">
-        <v>383.72657624221517</v>
+        <v>400.1586818780205</v>
       </c>
       <c r="AR24" t="s">
         <v>445</v>
@@ -10310,13 +10310,13 @@
         <v>1098</v>
       </c>
       <c r="BB24" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="BC24">
-        <v>0.99067149991228087</v>
+        <v>0.98624400907289522</v>
       </c>
       <c r="BD24">
-        <v>845.34880556723965</v>
+        <v>912.19382279522597</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10351,7 +10351,7 @@
         <v>22.160141399950017</v>
       </c>
       <c r="M25">
-        <v>0.19388483095769571</v>
+        <v>0.19344088149831118</v>
       </c>
       <c r="O25" t="s">
         <v>445</v>
@@ -10381,16 +10381,16 @@
         <v>476</v>
       </c>
       <c r="Y25" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Z25" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AA25">
-        <v>0.99521113523741833</v>
+        <v>0.99165895214194211</v>
       </c>
       <c r="AB25">
-        <v>87.795853980664262</v>
+        <v>152.91921073106212</v>
       </c>
       <c r="AD25" t="s">
         <v>445</v>
@@ -10420,13 +10420,13 @@
         <v>898</v>
       </c>
       <c r="AN25" t="s">
-        <v>653</v>
+        <v>672</v>
       </c>
       <c r="AO25">
-        <v>0.99570788786991582</v>
+        <v>0.99339062123477628</v>
       </c>
       <c r="AP25">
-        <v>78.688722384876669</v>
+        <v>121.17194402910137</v>
       </c>
       <c r="AR25" t="s">
         <v>445</v>
@@ -10456,13 +10456,13 @@
         <v>1099</v>
       </c>
       <c r="BB25" t="s">
-        <v>689</v>
+        <v>658</v>
       </c>
       <c r="BC25">
-        <v>0.99113893512004347</v>
+        <v>0.96572704859346925</v>
       </c>
       <c r="BD25">
-        <v>815.68225104790747</v>
+        <v>1162.1587913028991</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10497,7 +10497,7 @@
         <v>22.155826313547117</v>
       </c>
       <c r="M26">
-        <v>0.19525350260916621</v>
+        <v>0.19441937605650672</v>
       </c>
       <c r="O26" t="s">
         <v>445</v>
@@ -10527,16 +10527,16 @@
         <v>478</v>
       </c>
       <c r="Y26" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="Z26" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AA26">
-        <v>0.98246197339983365</v>
+        <v>0.99664889239239962</v>
       </c>
       <c r="AB26">
-        <v>321.53048766971619</v>
+        <v>61.436972806007184</v>
       </c>
       <c r="AD26" t="s">
         <v>445</v>
@@ -10566,13 +10566,13 @@
         <v>899</v>
       </c>
       <c r="AN26" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="AO26">
-        <v>0.98562252349041679</v>
+        <v>0.9495926116188812</v>
       </c>
       <c r="AP26">
-        <v>263.58706934235943</v>
+        <v>924.13545365384425</v>
       </c>
       <c r="AR26" t="s">
         <v>445</v>
@@ -10602,13 +10602,13 @@
         <v>1100</v>
       </c>
       <c r="BB26" t="s">
-        <v>651</v>
+        <v>688</v>
       </c>
       <c r="BC26">
-        <v>0.97513993579453706</v>
+        <v>0.98481153677494815</v>
       </c>
       <c r="BD26">
-        <v>1047.478448903224</v>
+        <v>929.64611029188166</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10643,7 +10643,7 @@
         <v>1.8430906098772319</v>
       </c>
       <c r="M27">
-        <v>0.1833442230297955</v>
+        <v>0.17442766650275371</v>
       </c>
       <c r="O27" t="s">
         <v>445</v>
@@ -10673,16 +10673,16 @@
         <v>480</v>
       </c>
       <c r="Y27" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="Z27" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="AA27">
-        <v>0.98352964899150075</v>
+        <v>0.99092130604056927</v>
       </c>
       <c r="AB27">
-        <v>301.95643515581952</v>
+        <v>166.44272258956366</v>
       </c>
       <c r="AD27" t="s">
         <v>445</v>
@@ -10712,13 +10712,13 @@
         <v>900</v>
       </c>
       <c r="AN27" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="AO27">
-        <v>0.94920173100235461</v>
+        <v>0.95120262528231503</v>
       </c>
       <c r="AP27">
-        <v>931.3015982901652</v>
+        <v>894.61853649089164</v>
       </c>
       <c r="AR27" t="s">
         <v>445</v>
@@ -10748,13 +10748,13 @@
         <v>1101</v>
       </c>
       <c r="BB27" t="s">
-        <v>670</v>
+        <v>689</v>
       </c>
       <c r="BC27">
-        <v>0.98425930791162897</v>
+        <v>0.99067149991228087</v>
       </c>
       <c r="BD27">
-        <v>936.37409860998696</v>
+        <v>845.34880556723965</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10789,7 +10789,7 @@
         <v>2.3172069250944403</v>
       </c>
       <c r="M28">
-        <v>0.17732897583641141</v>
+        <v>0.13320125053753509</v>
       </c>
       <c r="O28" t="s">
         <v>445</v>
@@ -10819,16 +10819,16 @@
         <v>482</v>
       </c>
       <c r="Y28" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="Z28" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AA28">
-        <v>0.91847114692356346</v>
+        <v>0.95611998680969301</v>
       </c>
       <c r="AB28">
-        <v>1494.6956397346703</v>
+        <v>804.46690848896196</v>
       </c>
       <c r="AD28" t="s">
         <v>445</v>
@@ -10858,13 +10858,13 @@
         <v>901</v>
       </c>
       <c r="AN28" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="AO28">
-        <v>0.94099051948143053</v>
+        <v>0.97689731236523503</v>
       </c>
       <c r="AP28">
-        <v>1081.8404761737738</v>
+        <v>423.54927330402518</v>
       </c>
       <c r="AR28" t="s">
         <v>445</v>
@@ -10894,13 +10894,13 @@
         <v>1102</v>
       </c>
       <c r="BB28" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="BC28">
-        <v>0.97983022896434013</v>
+        <v>0.99113893512004347</v>
       </c>
       <c r="BD28">
-        <v>990.33504378445582</v>
+        <v>815.68225104790747</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10935,7 +10935,7 @@
         <v>1.5005532638340171</v>
       </c>
       <c r="M29">
-        <v>0.18534809154875229</v>
+        <v>0.17296974176372637</v>
       </c>
       <c r="O29" t="s">
         <v>445</v>
@@ -10965,16 +10965,16 @@
         <v>484</v>
       </c>
       <c r="Y29" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="Z29" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="AA29">
-        <v>0.92680423740224549</v>
+        <v>0.99055684074965455</v>
       </c>
       <c r="AB29">
-        <v>1341.9223142921653</v>
+        <v>173.12458625633352</v>
       </c>
       <c r="AD29" t="s">
         <v>445</v>
@@ -11004,13 +11004,13 @@
         <v>902</v>
       </c>
       <c r="AN29" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="AO29">
-        <v>0.97163156886146174</v>
+        <v>0.96933352809933682</v>
       </c>
       <c r="AP29">
-        <v>520.0879042065344</v>
+        <v>562.21865151215866</v>
       </c>
       <c r="AR29" t="s">
         <v>445</v>
@@ -11040,13 +11040,13 @@
         <v>1103</v>
       </c>
       <c r="BB29" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="BC29">
-        <v>0.98532695715711582</v>
+        <v>0.97513993579453706</v>
       </c>
       <c r="BD29">
-        <v>923.36657196913927</v>
+        <v>1047.478448903224</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11081,7 +11081,7 @@
         <v>2.8390605236233233</v>
       </c>
       <c r="M30">
-        <v>0.18202090697765119</v>
+        <v>0.17067923305632671</v>
       </c>
       <c r="O30" t="s">
         <v>445</v>
@@ -11111,16 +11111,16 @@
         <v>486</v>
       </c>
       <c r="Y30" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="Z30" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AA30">
-        <v>0.96447115506861258</v>
+        <v>0.99723631056718209</v>
       </c>
       <c r="AB30">
-        <v>651.36215707543533</v>
+        <v>50.667639601661186</v>
       </c>
       <c r="AD30" t="s">
         <v>445</v>
@@ -11150,13 +11150,13 @@
         <v>903</v>
       </c>
       <c r="AN30" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="AO30">
-        <v>0.99407790982046917</v>
+        <v>0.94508652322363806</v>
       </c>
       <c r="AP30">
-        <v>108.57165329139941</v>
+        <v>1006.7470742333013</v>
       </c>
       <c r="AR30" t="s">
         <v>445</v>
@@ -11186,13 +11186,13 @@
         <v>1104</v>
       </c>
       <c r="BB30" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="BC30">
-        <v>0.98683737688914319</v>
+        <v>0.99416549953505795</v>
       </c>
       <c r="BD30">
-        <v>904.96462490060583</v>
+        <v>623.59629617498683</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11227,7 +11227,7 @@
         <v>19.742609342426579</v>
       </c>
       <c r="M31">
-        <v>0.1930446371854751</v>
+        <v>0.19235566912313079</v>
       </c>
       <c r="O31" t="s">
         <v>445</v>
@@ -11257,16 +11257,16 @@
         <v>488</v>
       </c>
       <c r="Y31" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="Z31" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AA31">
-        <v>0.98828003950132159</v>
+        <v>0.96929197405517931</v>
       </c>
       <c r="AB31">
-        <v>214.8659424757702</v>
+        <v>562.98047565504703</v>
       </c>
       <c r="AD31" t="s">
         <v>445</v>
@@ -11296,13 +11296,13 @@
         <v>904</v>
       </c>
       <c r="AN31" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="AO31">
-        <v>0.97471651986393804</v>
+        <v>0.99347025982523174</v>
       </c>
       <c r="AP31">
-        <v>463.53046916113516</v>
+        <v>119.71190320408562</v>
       </c>
       <c r="AR31" t="s">
         <v>445</v>
@@ -11332,13 +11332,13 @@
         <v>1105</v>
       </c>
       <c r="BB31" t="s">
-        <v>684</v>
+        <v>659</v>
       </c>
       <c r="BC31">
-        <v>0.98183502015800017</v>
+        <v>0.98458868956887557</v>
       </c>
       <c r="BD31">
-        <v>965.91000440836387</v>
+        <v>932.36113208586551</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11403,16 +11403,16 @@
         <v>490</v>
       </c>
       <c r="Y32" t="s">
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="Z32" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AA32">
-        <v>0.99382591612551541</v>
+        <v>0.98417563223370064</v>
       </c>
       <c r="AB32">
-        <v>113.1915376988852</v>
+        <v>290.11340904882155</v>
       </c>
       <c r="AD32" t="s">
         <v>445</v>
@@ -11442,13 +11442,13 @@
         <v>905</v>
       </c>
       <c r="AN32" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
       <c r="AO32">
-        <v>0.95301935344113697</v>
+        <v>0.99424478665673766</v>
       </c>
       <c r="AP32">
-        <v>861.31185357915479</v>
+        <v>105.51224462647731</v>
       </c>
       <c r="AR32" t="s">
         <v>445</v>
@@ -11478,13 +11478,13 @@
         <v>1106</v>
       </c>
       <c r="BB32" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="BC32">
-        <v>0.95190272587812108</v>
+        <v>0.98345026231369026</v>
       </c>
       <c r="BD32">
-        <v>1330.585123051558</v>
+        <v>946.23097081154037</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11519,7 +11519,7 @@
         <v>49.344521286550219</v>
       </c>
       <c r="M33">
-        <v>0.2061234003164942</v>
+        <v>0.20490009163907266</v>
       </c>
       <c r="O33" t="s">
         <v>445</v>
@@ -11549,16 +11549,16 @@
         <v>492</v>
       </c>
       <c r="Y33" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="Z33" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AA33">
-        <v>0.99482528705797657</v>
+        <v>0.99385704522942342</v>
       </c>
       <c r="AB33">
-        <v>94.869737270428971</v>
+        <v>112.62083746056986</v>
       </c>
       <c r="AD33" t="s">
         <v>445</v>
@@ -11588,13 +11588,13 @@
         <v>906</v>
       </c>
       <c r="AN33" t="s">
-        <v>674</v>
+        <v>648</v>
       </c>
       <c r="AO33">
-        <v>0.99537175847221593</v>
+        <v>0.97867478517995188</v>
       </c>
       <c r="AP33">
-        <v>84.85109467604083</v>
+        <v>390.96227170088139</v>
       </c>
       <c r="AR33" t="s">
         <v>445</v>
@@ -11624,13 +11624,13 @@
         <v>1107</v>
       </c>
       <c r="BB33" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="BC33">
-        <v>0.97560382464771223</v>
+        <v>0.98870653772658501</v>
       </c>
       <c r="BD33">
-        <v>1041.8267363753732</v>
+        <v>882.19201536443973</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11665,7 +11665,7 @@
         <v>2.7184906996602578</v>
       </c>
       <c r="M34">
-        <v>0.1819708991648061</v>
+        <v>0.18036080878987584</v>
       </c>
       <c r="O34" t="s">
         <v>445</v>
@@ -11695,16 +11695,16 @@
         <v>494</v>
       </c>
       <c r="Y34" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="Z34" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="AA34">
-        <v>0.97321507838078658</v>
+        <v>0.99512174530146036</v>
       </c>
       <c r="AB34">
-        <v>491.05689635224547</v>
+        <v>89.434669473226961</v>
       </c>
       <c r="AD34" t="s">
         <v>445</v>
@@ -11734,13 +11734,13 @@
         <v>907</v>
       </c>
       <c r="AN34" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="AO34">
-        <v>0.95891375083366426</v>
+        <v>0.95781637101189843</v>
       </c>
       <c r="AP34">
-        <v>753.24790138282128</v>
+        <v>773.36653144852835</v>
       </c>
       <c r="AR34" t="s">
         <v>445</v>
@@ -11770,13 +11770,13 @@
         <v>1108</v>
       </c>
       <c r="BB34" t="s">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="BC34">
-        <v>0.89604746025791282</v>
+        <v>0.9861533644012247</v>
       </c>
       <c r="BD34">
-        <v>2011.088442524429</v>
+        <v>913.29817704507911</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11811,7 +11811,7 @@
         <v>4.4965976901270084</v>
       </c>
       <c r="M35">
-        <v>0.17521994198797591</v>
+        <v>0.1623267369784053</v>
       </c>
       <c r="O35" t="s">
         <v>445</v>
@@ -11841,16 +11841,16 @@
         <v>496</v>
       </c>
       <c r="Y35" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="Z35" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="AA35">
-        <v>0.97866893212504957</v>
+        <v>0.97275257137901638</v>
       </c>
       <c r="AB35">
-        <v>391.06957770742463</v>
+        <v>499.53619138470009</v>
       </c>
       <c r="AD35" t="s">
         <v>445</v>
@@ -11880,13 +11880,13 @@
         <v>908</v>
       </c>
       <c r="AN35" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="AO35">
-        <v>0.97364425413724487</v>
+        <v>0.98886553660707677</v>
       </c>
       <c r="AP35">
-        <v>483.18867415051142</v>
+        <v>204.13182887025886</v>
       </c>
       <c r="AR35" t="s">
         <v>445</v>
@@ -11916,13 +11916,13 @@
         <v>1109</v>
       </c>
       <c r="BB35" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="BC35">
-        <v>0.97093554889152922</v>
+        <v>0.95190272587812108</v>
       </c>
       <c r="BD35">
-        <v>1098.7018960048697</v>
+        <v>1330.585123051558</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11957,7 +11957,7 @@
         <v>20.443718045322946</v>
       </c>
       <c r="M36">
-        <v>0.2000619605160506</v>
+        <v>0.19987868500931139</v>
       </c>
       <c r="O36" t="s">
         <v>445</v>
@@ -11987,16 +11987,16 @@
         <v>498</v>
       </c>
       <c r="Y36" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="Z36" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="AA36">
-        <v>0.9933008323747714</v>
+        <v>0.95322333844045537</v>
       </c>
       <c r="AB36">
-        <v>122.81807312919075</v>
+        <v>857.57212859165099</v>
       </c>
       <c r="AD36" t="s">
         <v>445</v>
@@ -12026,13 +12026,13 @@
         <v>909</v>
       </c>
       <c r="AN36" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="AO36">
-        <v>0.95472325192752561</v>
+        <v>0.93811411999108418</v>
       </c>
       <c r="AP36">
-        <v>830.07371466203085</v>
+        <v>1134.5744668301231</v>
       </c>
       <c r="AR36" t="s">
         <v>445</v>
@@ -12062,13 +12062,13 @@
         <v>1110</v>
       </c>
       <c r="BB36" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="BC36">
-        <v>0.98986511819476719</v>
+        <v>0.97560382464771223</v>
       </c>
       <c r="BD36">
-        <v>868.07664332708646</v>
+        <v>1041.8267363753732</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12103,7 +12103,7 @@
         <v>0.67217440269328321</v>
       </c>
       <c r="M37">
-        <v>0.16310358366687311</v>
+        <v>0.15651398690283896</v>
       </c>
       <c r="O37" t="s">
         <v>445</v>
@@ -12133,16 +12133,16 @@
         <v>500</v>
       </c>
       <c r="Y37" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="Z37" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="AA37">
-        <v>0.9771403150431911</v>
+        <v>0.93792673193465337</v>
       </c>
       <c r="AB37">
-        <v>419.09422420816315</v>
+        <v>1138.0099145313559</v>
       </c>
       <c r="AD37" t="s">
         <v>445</v>
@@ -12172,13 +12172,13 @@
         <v>910</v>
       </c>
       <c r="AN37" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="AO37">
-        <v>0.99476921667660834</v>
+        <v>0.9832447093861123</v>
       </c>
       <c r="AP37">
-        <v>95.897694262180153</v>
+        <v>307.18032792127502</v>
       </c>
       <c r="AR37" t="s">
         <v>445</v>
@@ -12208,13 +12208,13 @@
         <v>1111</v>
       </c>
       <c r="BB37" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="BC37">
-        <v>0.99159294969939915</v>
+        <v>0.89604746025791282</v>
       </c>
       <c r="BD37">
-        <v>786.86745907813679</v>
+        <v>2011.088442524429</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12279,16 +12279,16 @@
         <v>502</v>
       </c>
       <c r="Y38" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="Z38" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="AA38">
-        <v>0.96576017716725859</v>
+        <v>0.99238887682283938</v>
       </c>
       <c r="AB38">
-        <v>627.73008526692502</v>
+        <v>139.53725824794503</v>
       </c>
       <c r="AD38" t="s">
         <v>445</v>
@@ -12318,13 +12318,13 @@
         <v>911</v>
       </c>
       <c r="AN38" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="AO38">
-        <v>0.99146900514737779</v>
+        <v>0.99401394460386272</v>
       </c>
       <c r="AP38">
-        <v>156.40157229807483</v>
+        <v>109.74434892918245</v>
       </c>
       <c r="AR38" t="s">
         <v>445</v>
@@ -12354,13 +12354,13 @@
         <v>1112</v>
       </c>
       <c r="BB38" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="BC38">
-        <v>0.98080906590233208</v>
+        <v>0.95200980188478979</v>
       </c>
       <c r="BD38">
-        <v>978.40954708992126</v>
+        <v>1329.2805803703113</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12395,7 +12395,7 @@
         <v>100.23792680097552</v>
       </c>
       <c r="M39">
-        <v>0.2016402967110828</v>
+        <v>0.18116632231530605</v>
       </c>
       <c r="O39" t="s">
         <v>445</v>
@@ -12425,16 +12425,16 @@
         <v>504</v>
       </c>
       <c r="Y39" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="Z39" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="AA39">
-        <v>0.99320659129827649</v>
+        <v>0.99511596204556785</v>
       </c>
       <c r="AB39">
-        <v>124.54582619826394</v>
+        <v>89.54069583125569</v>
       </c>
       <c r="AD39" t="s">
         <v>445</v>
@@ -12464,13 +12464,13 @@
         <v>912</v>
       </c>
       <c r="AN39" t="s">
-        <v>644</v>
+        <v>676</v>
       </c>
       <c r="AO39">
-        <v>0.97494022509165501</v>
+        <v>0.99712495361968201</v>
       </c>
       <c r="AP39">
-        <v>459.42920665299067</v>
+        <v>52.709183639163186</v>
       </c>
       <c r="AR39" t="s">
         <v>445</v>
@@ -12500,13 +12500,13 @@
         <v>1113</v>
       </c>
       <c r="BB39" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="BC39">
-        <v>0.9611655354348162</v>
+        <v>0.97707982144598671</v>
       </c>
       <c r="BD39">
-        <v>1217.7332266191565</v>
+        <v>1023.8441753830622</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12571,16 +12571,16 @@
         <v>506</v>
       </c>
       <c r="Y40" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="Z40" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="AA40">
-        <v>0.97901340677155257</v>
+        <v>0.9916566373699115</v>
       </c>
       <c r="AB40">
-        <v>384.75420918820265</v>
+        <v>152.96164821828896</v>
       </c>
       <c r="AD40" t="s">
         <v>445</v>
@@ -12610,13 +12610,13 @@
         <v>913</v>
       </c>
       <c r="AN40" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="AO40">
-        <v>0.99342004180524168</v>
+        <v>0.99728565567097416</v>
       </c>
       <c r="AP40">
-        <v>120.63256690390332</v>
+        <v>49.762979365472916</v>
       </c>
       <c r="AR40" t="s">
         <v>445</v>
@@ -12646,13 +12646,13 @@
         <v>1114</v>
       </c>
       <c r="BB40" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="BC40">
-        <v>0.9827191942014929</v>
+        <v>0.98962892741174779</v>
       </c>
       <c r="BD40">
-        <v>955.13781731181223</v>
+        <v>870.9542343668727</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12717,16 +12717,16 @@
         <v>508</v>
       </c>
       <c r="Y41" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="Z41" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="AA41">
-        <v>0.95936298088609862</v>
+        <v>0.98522037572241172</v>
       </c>
       <c r="AB41">
-        <v>745.01201708819133</v>
+        <v>270.9597784224527</v>
       </c>
       <c r="AD41" t="s">
         <v>445</v>
@@ -12756,13 +12756,13 @@
         <v>914</v>
       </c>
       <c r="AN41" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="AO41">
-        <v>0.99501310191160197</v>
+        <v>0.95358024529553875</v>
       </c>
       <c r="AP41">
-        <v>91.426464953964114</v>
+        <v>851.0288362484556</v>
       </c>
       <c r="AR41" t="s">
         <v>445</v>
@@ -12792,13 +12792,13 @@
         <v>1115</v>
       </c>
       <c r="BB41" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="BC41">
-        <v>0.95475709315784774</v>
+        <v>0.93242166156261008</v>
       </c>
       <c r="BD41">
-        <v>1295.8094150268885</v>
+        <v>1567.9294232955338</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12863,16 +12863,16 @@
         <v>510</v>
       </c>
       <c r="Y42" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="Z42" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
       <c r="AA42">
-        <v>0.9970088962341721</v>
+        <v>0.98831913038449382</v>
       </c>
       <c r="AB42">
-        <v>54.836902373510455</v>
+        <v>214.14927628428001</v>
       </c>
       <c r="AD42" t="s">
         <v>445</v>
@@ -12902,13 +12902,13 @@
         <v>915</v>
       </c>
       <c r="AN42" t="s">
-        <v>649</v>
+        <v>685</v>
       </c>
       <c r="AO42">
-        <v>0.9633630443304535</v>
+        <v>0.98155612527850788</v>
       </c>
       <c r="AP42">
-        <v>671.67752060835289</v>
+        <v>338.13770322735616</v>
       </c>
       <c r="AR42" t="s">
         <v>445</v>
@@ -12938,13 +12938,13 @@
         <v>1116</v>
       </c>
       <c r="BB42" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="BC42">
-        <v>0.98962892741174779</v>
+        <v>0.98514006154561162</v>
       </c>
       <c r="BD42">
-        <v>870.9542343668727</v>
+        <v>925.6435835026324</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -13009,16 +13009,16 @@
         <v>512</v>
       </c>
       <c r="Y43" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Z43" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="AA43">
-        <v>0.99480818130085191</v>
+        <v>0.98522854207859256</v>
       </c>
       <c r="AB43">
-        <v>95.183342817714731</v>
+        <v>270.81006189247</v>
       </c>
       <c r="AD43" t="s">
         <v>445</v>
@@ -13048,13 +13048,13 @@
         <v>916</v>
       </c>
       <c r="AN43" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AO43">
-        <v>0.98994878939511521</v>
+        <v>0.92201529031984186</v>
       </c>
       <c r="AP43">
-        <v>184.27219442288737</v>
+        <v>1429.719677469566</v>
       </c>
       <c r="AR43" t="s">
         <v>445</v>
@@ -13084,13 +13084,13 @@
         <v>1117</v>
       </c>
       <c r="BB43" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="BC43">
-        <v>0.93242166156261008</v>
+        <v>0.9852903703395921</v>
       </c>
       <c r="BD43">
-        <v>1567.9294232955338</v>
+        <v>923.81232136263634</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13125,7 +13125,7 @@
         <v>17.455188698838782</v>
       </c>
       <c r="M44">
-        <v>0.18659723410857121</v>
+        <v>0.1609687803389015</v>
       </c>
       <c r="O44" t="s">
         <v>445</v>
@@ -13155,16 +13155,16 @@
         <v>514</v>
       </c>
       <c r="Y44" t="s">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="Z44" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AA44">
-        <v>0.92426797711114228</v>
+        <v>0.99185644171670617</v>
       </c>
       <c r="AB44">
-        <v>1388.420419629058</v>
+        <v>149.29856852705402</v>
       </c>
       <c r="AD44" t="s">
         <v>445</v>
@@ -13194,13 +13194,13 @@
         <v>917</v>
       </c>
       <c r="AN44" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AO44">
-        <v>0.96684854231168849</v>
+        <v>0.98335963574413709</v>
       </c>
       <c r="AP44">
-        <v>607.77672428571168</v>
+        <v>305.07334469081934</v>
       </c>
       <c r="AR44" t="s">
         <v>445</v>
@@ -13230,13 +13230,13 @@
         <v>1118</v>
       </c>
       <c r="BB44" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="BC44">
-        <v>0.99167399400086409</v>
+        <v>0.99350055753404454</v>
       </c>
       <c r="BD44">
-        <v>781.72384741182896</v>
+        <v>665.79794850597443</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13271,7 +13271,7 @@
         <v>37.0118256629992</v>
       </c>
       <c r="M45">
-        <v>0.1990685230369556</v>
+        <v>0.19874837763123138</v>
       </c>
       <c r="O45" t="s">
         <v>445</v>
@@ -13301,16 +13301,16 @@
         <v>516</v>
       </c>
       <c r="Y45" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Z45" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="AA45">
-        <v>0.92861598426622882</v>
+        <v>0.94189846566095958</v>
       </c>
       <c r="AB45">
-        <v>1308.7069551191387</v>
+        <v>1065.1947962157406</v>
       </c>
       <c r="AD45" t="s">
         <v>445</v>
@@ -13340,13 +13340,13 @@
         <v>918</v>
       </c>
       <c r="AN45" t="s">
-        <v>678</v>
+        <v>652</v>
       </c>
       <c r="AO45">
-        <v>0.99443080330687583</v>
+        <v>0.98001801309124148</v>
       </c>
       <c r="AP45">
-        <v>102.10193937394267</v>
+        <v>366.33642666057369</v>
       </c>
       <c r="AR45" t="s">
         <v>445</v>
@@ -13376,13 +13376,13 @@
         <v>1119</v>
       </c>
       <c r="BB45" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="BC45">
-        <v>0.98870750020933817</v>
+        <v>0.9737385233335023</v>
       </c>
       <c r="BD45">
-        <v>882.18028911622969</v>
+        <v>1064.5523240534972</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13417,7 +13417,7 @@
         <v>57.04947416201933</v>
       </c>
       <c r="M46">
-        <v>0.19294251355833419</v>
+        <v>0.13505975949083393</v>
       </c>
       <c r="O46" t="s">
         <v>445</v>
@@ -13447,16 +13447,16 @@
         <v>518</v>
       </c>
       <c r="Y46" t="s">
-        <v>386</v>
+        <v>439</v>
       </c>
       <c r="Z46" t="s">
         <v>649</v>
       </c>
       <c r="AA46">
-        <v>0.95808092951199286</v>
+        <v>0.95001627981732095</v>
       </c>
       <c r="AB46">
-        <v>768.51629228013144</v>
+        <v>916.36820334911533</v>
       </c>
       <c r="AD46" t="s">
         <v>445</v>
@@ -13486,13 +13486,13 @@
         <v>919</v>
       </c>
       <c r="AN46" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="AO46">
-        <v>0.99161135964647729</v>
+        <v>0.91475976979271756</v>
       </c>
       <c r="AP46">
-        <v>153.79173981458226</v>
+        <v>1562.7375538001788</v>
       </c>
       <c r="AR46" t="s">
         <v>445</v>
@@ -13522,13 +13522,13 @@
         <v>1120</v>
       </c>
       <c r="BB46" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="BC46">
-        <v>0.97890667967973555</v>
+        <v>0.946000484445496</v>
       </c>
       <c r="BD46">
-        <v>1001.5869525685553</v>
+        <v>1402.4940978390403</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13563,7 +13563,7 @@
         <v>73.263486534558155</v>
       </c>
       <c r="M47">
-        <v>0.2089486720520416</v>
+        <v>0.14626407043642911</v>
       </c>
       <c r="O47" t="s">
         <v>445</v>
@@ -13593,16 +13593,16 @@
         <v>520</v>
       </c>
       <c r="Y47" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="Z47" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="AA47">
-        <v>0.98362353815347903</v>
+        <v>0.98042178820377779</v>
       </c>
       <c r="AB47">
-        <v>300.23513385288544</v>
+        <v>358.93388293074008</v>
       </c>
       <c r="AD47" t="s">
         <v>445</v>
@@ -13632,13 +13632,13 @@
         <v>920</v>
       </c>
       <c r="AN47" t="s">
-        <v>648</v>
+        <v>683</v>
       </c>
       <c r="AO47">
-        <v>0.99096791212626811</v>
+        <v>0.9937640046384969</v>
       </c>
       <c r="AP47">
-        <v>165.5882776850855</v>
+        <v>114.32658162755614</v>
       </c>
       <c r="AR47" t="s">
         <v>445</v>
@@ -13668,13 +13668,13 @@
         <v>1121</v>
       </c>
       <c r="BB47" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="BC47">
-        <v>0.99416549953505795</v>
+        <v>0.96304008712262701</v>
       </c>
       <c r="BD47">
-        <v>623.59629617498683</v>
+        <v>1194.8949385559945</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13739,16 +13739,16 @@
         <v>522</v>
       </c>
       <c r="Y48" t="s">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="Z48" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="AA48">
-        <v>0.99495707351657814</v>
+        <v>0.95808092951199286</v>
       </c>
       <c r="AB48">
-        <v>92.453652196066486</v>
+        <v>768.51629228013144</v>
       </c>
       <c r="AD48" t="s">
         <v>445</v>
@@ -13778,13 +13778,13 @@
         <v>921</v>
       </c>
       <c r="AN48" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="AO48">
-        <v>0.99153287968327641</v>
+        <v>0.98434157772378295</v>
       </c>
       <c r="AP48">
-        <v>155.23053913993309</v>
+        <v>287.07107506397949</v>
       </c>
       <c r="AR48" t="s">
         <v>445</v>
@@ -13814,13 +13814,13 @@
         <v>1122</v>
       </c>
       <c r="BB48" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="BC48">
-        <v>0.98458868956887557</v>
+        <v>0.98902339847455312</v>
       </c>
       <c r="BD48">
-        <v>932.36113208586551</v>
+        <v>878.33159525169435</v>
       </c>
     </row>
     <row r="49" spans="2:56">
@@ -13855,7 +13855,7 @@
         <v>87.23926107037741</v>
       </c>
       <c r="M49">
-        <v>0.21021204789718159</v>
+        <v>0.14714843352802712</v>
       </c>
       <c r="O49" t="s">
         <v>445</v>
@@ -13885,16 +13885,16 @@
         <v>524</v>
       </c>
       <c r="Y49" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="Z49" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="AA49">
-        <v>0.969236873889878</v>
+        <v>0.98362353815347903</v>
       </c>
       <c r="AB49">
-        <v>563.9906453522367</v>
+        <v>300.23513385288544</v>
       </c>
       <c r="AD49" t="s">
         <v>445</v>
@@ -13924,13 +13924,13 @@
         <v>922</v>
       </c>
       <c r="AN49" t="s">
-        <v>689</v>
+        <v>655</v>
       </c>
       <c r="AO49">
-        <v>0.99568711277871247</v>
+        <v>0.98724240938456542</v>
       </c>
       <c r="AP49">
-        <v>79.069599056938102</v>
+        <v>233.88916128296634</v>
       </c>
       <c r="AR49" t="s">
         <v>445</v>
@@ -13960,13 +13960,13 @@
         <v>1123</v>
       </c>
       <c r="BB49" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="BC49">
-        <v>0.98345026231369026</v>
+        <v>0.99181397642123026</v>
       </c>
       <c r="BD49">
-        <v>946.23097081154037</v>
+        <v>772.83962979925604</v>
       </c>
     </row>
     <row r="50" spans="2:56">
@@ -14001,7 +14001,7 @@
         <v>174.30633413429078</v>
       </c>
       <c r="M50">
-        <v>0.2078093509571235</v>
+        <v>0.15412160122752708</v>
       </c>
       <c r="O50" t="s">
         <v>445</v>
@@ -14031,16 +14031,16 @@
         <v>526</v>
       </c>
       <c r="Y50" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="Z50" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="AA50">
-        <v>0.93773368388956246</v>
+        <v>0.99495707351657814</v>
       </c>
       <c r="AB50">
-        <v>1141.5491286913555</v>
+        <v>92.453652196066486</v>
       </c>
       <c r="AD50" t="s">
         <v>445</v>
@@ -14070,13 +14070,13 @@
         <v>923</v>
       </c>
       <c r="AN50" t="s">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="AO50">
-        <v>0.98225029258055574</v>
+        <v>0.99486897494175219</v>
       </c>
       <c r="AP50">
-        <v>325.41130268981078</v>
+        <v>94.068792734543848</v>
       </c>
       <c r="AR50" t="s">
         <v>445</v>
@@ -14106,13 +14106,13 @@
         <v>1124</v>
       </c>
       <c r="BB50" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="BC50">
-        <v>0.98105298234439897</v>
+        <v>0.97093554889152922</v>
       </c>
       <c r="BD50">
-        <v>975.4378317707384</v>
+        <v>1098.7018960048697</v>
       </c>
     </row>
     <row r="51" spans="2:56">
@@ -14177,16 +14177,16 @@
         <v>528</v>
       </c>
       <c r="Y51" t="s">
-        <v>354</v>
+        <v>434</v>
       </c>
       <c r="Z51" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AA51">
-        <v>0.99059066767492976</v>
+        <v>0.969236873889878</v>
       </c>
       <c r="AB51">
-        <v>172.50442595962087</v>
+        <v>563.9906453522367</v>
       </c>
       <c r="AD51" t="s">
         <v>445</v>
@@ -14219,10 +14219,10 @@
         <v>656</v>
       </c>
       <c r="AO51">
-        <v>0.982419047139102</v>
+        <v>0.99698330098522958</v>
       </c>
       <c r="AP51">
-        <v>322.31746911646275</v>
+        <v>55.306148604123919</v>
       </c>
       <c r="AR51" t="s">
         <v>445</v>
@@ -14252,13 +14252,13 @@
         <v>1125</v>
       </c>
       <c r="BB51" t="s">
-        <v>652</v>
+        <v>679</v>
       </c>
       <c r="BC51">
-        <v>0.98635721678832755</v>
+        <v>0.98986511819476719</v>
       </c>
       <c r="BD51">
-        <v>910.81457546220918</v>
+        <v>868.07664332708646</v>
       </c>
     </row>
     <row r="52" spans="2:56">
@@ -14323,16 +14323,16 @@
         <v>530</v>
       </c>
       <c r="Y52" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="Z52" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="AA52">
-        <v>0.95570380597210192</v>
+        <v>0.93773368388956246</v>
       </c>
       <c r="AB52">
-        <v>812.09689051146574</v>
+        <v>1141.5491286913555</v>
       </c>
       <c r="AD52" t="s">
         <v>445</v>
@@ -14362,13 +14362,13 @@
         <v>925</v>
       </c>
       <c r="AN52" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AO52">
-        <v>0.97789502766167302</v>
+        <v>0.95884281124958637</v>
       </c>
       <c r="AP52">
-        <v>405.25782620266216</v>
+        <v>754.54846042424947</v>
       </c>
       <c r="AR52" t="s">
         <v>445</v>
@@ -14398,13 +14398,13 @@
         <v>1126</v>
       </c>
       <c r="BB52" t="s">
-        <v>644</v>
+        <v>673</v>
       </c>
       <c r="BC52">
-        <v>0.98172617970345721</v>
+        <v>0.99159294969939915</v>
       </c>
       <c r="BD52">
-        <v>967.23604394621248</v>
+        <v>786.86745907813679</v>
       </c>
     </row>
     <row r="53" spans="2:56">
@@ -14469,16 +14469,16 @@
         <v>532</v>
       </c>
       <c r="Y53" t="s">
-        <v>398</v>
+        <v>355</v>
       </c>
       <c r="Z53" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="AA53">
-        <v>0.98883273909819114</v>
+        <v>0.98418645978522035</v>
       </c>
       <c r="AB53">
-        <v>204.7331165331625</v>
+        <v>289.91490393762615</v>
       </c>
       <c r="AD53" t="s">
         <v>445</v>
@@ -14508,13 +14508,13 @@
         <v>926</v>
       </c>
       <c r="AN53" t="s">
-        <v>685</v>
+        <v>649</v>
       </c>
       <c r="AO53">
-        <v>0.99485109969932284</v>
+        <v>0.96628526147979277</v>
       </c>
       <c r="AP53">
-        <v>94.396505512414166</v>
+        <v>618.10353953713195</v>
       </c>
       <c r="AR53" t="s">
         <v>445</v>
@@ -14544,13 +14544,13 @@
         <v>1127</v>
       </c>
       <c r="BB53" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="BC53">
-        <v>0.91560080888051365</v>
+        <v>0.98080906590233208</v>
       </c>
       <c r="BD53">
-        <v>1772.8634784724095</v>
+        <v>978.40954708992126</v>
       </c>
     </row>
     <row r="54" spans="2:56">
@@ -14615,16 +14615,16 @@
         <v>534</v>
       </c>
       <c r="Y54" t="s">
-        <v>419</v>
+        <v>362</v>
       </c>
       <c r="Z54" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="AA54">
-        <v>0.98262913774151028</v>
+        <v>0.9906346744759631</v>
       </c>
       <c r="AB54">
-        <v>318.46580807231078</v>
+        <v>171.69763460734316</v>
       </c>
       <c r="AD54" t="s">
         <v>445</v>
@@ -14654,13 +14654,13 @@
         <v>927</v>
       </c>
       <c r="AN54" t="s">
-        <v>646</v>
+        <v>686</v>
       </c>
       <c r="AO54">
-        <v>0.97344873028830825</v>
+        <v>0.98449859725932043</v>
       </c>
       <c r="AP54">
-        <v>486.77327804768265</v>
+        <v>284.19238357912451</v>
       </c>
       <c r="AR54" t="s">
         <v>445</v>
@@ -14690,13 +14690,13 @@
         <v>1128</v>
       </c>
       <c r="BB54" t="s">
-        <v>686</v>
+        <v>649</v>
       </c>
       <c r="BC54">
-        <v>0.99223944103482187</v>
+        <v>0.9611655354348162</v>
       </c>
       <c r="BD54">
-        <v>745.8368089899709</v>
+        <v>1217.7332266191565</v>
       </c>
     </row>
     <row r="55" spans="2:56">
@@ -14731,7 +14731,7 @@
         <v>11.46209360111086</v>
       </c>
       <c r="M55">
-        <v>0.1872394671210959</v>
+        <v>0.16179543666542309</v>
       </c>
       <c r="O55" t="s">
         <v>445</v>
@@ -14761,16 +14761,16 @@
         <v>536</v>
       </c>
       <c r="Y55" t="s">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="Z55" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="AA55">
-        <v>0.99090558233812054</v>
+        <v>0.95915670695527311</v>
       </c>
       <c r="AB55">
-        <v>166.73099046779075</v>
+        <v>748.79370581999342</v>
       </c>
       <c r="AD55" t="s">
         <v>445</v>
@@ -14800,13 +14800,13 @@
         <v>928</v>
       </c>
       <c r="AN55" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="AO55">
-        <v>0.98192694200361774</v>
+        <v>0.981374440216361</v>
       </c>
       <c r="AP55">
-        <v>331.33939660034207</v>
+        <v>341.46859603338169</v>
       </c>
       <c r="AR55" t="s">
         <v>445</v>
@@ -14836,13 +14836,13 @@
         <v>1129</v>
       </c>
       <c r="BB55" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
       <c r="BC55">
-        <v>0.98460725799374227</v>
+        <v>0.99167399400086409</v>
       </c>
       <c r="BD55">
-        <v>932.13490677623929</v>
+        <v>781.72384741182896</v>
       </c>
     </row>
     <row r="56" spans="2:56">
@@ -14877,7 +14877,7 @@
         <v>2.5575673017713081</v>
       </c>
       <c r="M56">
-        <v>0.19402945314557199</v>
+        <v>0.14344240350087131</v>
       </c>
       <c r="O56" t="s">
         <v>445</v>
@@ -14907,16 +14907,16 @@
         <v>538</v>
       </c>
       <c r="Y56" t="s">
-        <v>440</v>
+        <v>407</v>
       </c>
       <c r="Z56" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="AA56">
-        <v>0.99144634427862732</v>
+        <v>0.98927829835282999</v>
       </c>
       <c r="AB56">
-        <v>156.81702155849862</v>
+        <v>196.56453019811752</v>
       </c>
       <c r="AD56" t="s">
         <v>445</v>
@@ -14946,13 +14946,13 @@
         <v>929</v>
       </c>
       <c r="AN56" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="AO56">
-        <v>0.98407466378375608</v>
+        <v>0.94345419131600505</v>
       </c>
       <c r="AP56">
-        <v>291.96449729780619</v>
+        <v>1036.6731592065737</v>
       </c>
       <c r="AR56" t="s">
         <v>445</v>
@@ -14985,10 +14985,10 @@
         <v>647</v>
       </c>
       <c r="BC56">
-        <v>0.99676099935070339</v>
+        <v>0.98870750020933817</v>
       </c>
       <c r="BD56">
-        <v>458.86857454202811</v>
+        <v>882.18028911622969</v>
       </c>
     </row>
     <row r="57" spans="2:56">
@@ -15023,7 +15023,7 @@
         <v>17.541373916628828</v>
       </c>
       <c r="M57">
-        <v>0.19617685635828261</v>
+        <v>0.19409687263948139</v>
       </c>
       <c r="O57" t="s">
         <v>445</v>
@@ -15053,16 +15053,16 @@
         <v>540</v>
       </c>
       <c r="Y57" t="s">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="Z57" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="AA57">
-        <v>0.96039250350097727</v>
+        <v>0.97846149456848719</v>
       </c>
       <c r="AB57">
-        <v>726.13743581541678</v>
+        <v>394.87259957773409</v>
       </c>
       <c r="AD57" t="s">
         <v>445</v>
@@ -15092,13 +15092,13 @@
         <v>930</v>
       </c>
       <c r="AN57" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="AO57">
-        <v>0.9542882304111121</v>
+        <v>0.92366037259831435</v>
       </c>
       <c r="AP57">
-        <v>838.04910912961134</v>
+        <v>1399.5598356975697</v>
       </c>
       <c r="AR57" t="s">
         <v>445</v>
@@ -15128,13 +15128,13 @@
         <v>1131</v>
       </c>
       <c r="BB57" t="s">
-        <v>670</v>
+        <v>645</v>
       </c>
       <c r="BC57">
-        <v>0.96948890259934162</v>
+        <v>0.97890667967973555</v>
       </c>
       <c r="BD57">
-        <v>1116.3268699980208</v>
+        <v>1001.5869525685553</v>
       </c>
     </row>
     <row r="58" spans="2:56">
@@ -15169,7 +15169,7 @@
         <v>140.64820956436421</v>
       </c>
       <c r="M58">
-        <v>0.2084189674494468</v>
+        <v>0.20776821596264403</v>
       </c>
       <c r="O58" t="s">
         <v>445</v>
@@ -15199,16 +15199,16 @@
         <v>542</v>
       </c>
       <c r="Y58" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="Z58" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="AA58">
-        <v>0.96501488785990974</v>
+        <v>0.98922498055164843</v>
       </c>
       <c r="AB58">
-        <v>641.39372256832166</v>
+        <v>197.54202321977883</v>
       </c>
       <c r="AD58" t="s">
         <v>445</v>
@@ -15238,13 +15238,13 @@
         <v>931</v>
       </c>
       <c r="AN58" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="AO58">
-        <v>0.99582108489984233</v>
+        <v>0.98255203569076077</v>
       </c>
       <c r="AP58">
-        <v>76.613443502890505</v>
+        <v>319.879345669386</v>
       </c>
       <c r="AR58" t="s">
         <v>445</v>
@@ -15274,13 +15274,13 @@
         <v>1132</v>
       </c>
       <c r="BB58" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="BC58">
-        <v>0.97338301712868025</v>
+        <v>0.98105298234439897</v>
       </c>
       <c r="BD58">
-        <v>1068.8835746489126</v>
+        <v>975.4378317707384</v>
       </c>
     </row>
     <row r="59" spans="2:56">
@@ -15345,16 +15345,16 @@
         <v>544</v>
       </c>
       <c r="Y59" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="Z59" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AA59">
-        <v>0.99401420652619221</v>
+        <v>0.99262576700342608</v>
       </c>
       <c r="AB59">
-        <v>109.73954701980865</v>
+        <v>135.19427160385601</v>
       </c>
       <c r="AD59" t="s">
         <v>445</v>
@@ -15384,13 +15384,13 @@
         <v>932</v>
       </c>
       <c r="AN59" t="s">
-        <v>681</v>
+        <v>660</v>
       </c>
       <c r="AO59">
-        <v>0.99800187122714112</v>
+        <v>0.98977574375304844</v>
       </c>
       <c r="AP59">
-        <v>36.632360835745096</v>
+        <v>187.44469786077892</v>
       </c>
       <c r="AR59" t="s">
         <v>445</v>
@@ -15420,13 +15420,13 @@
         <v>1133</v>
       </c>
       <c r="BB59" t="s">
-        <v>689</v>
+        <v>668</v>
       </c>
       <c r="BC59">
-        <v>0.98973750247525893</v>
+        <v>0.98635721678832755</v>
       </c>
       <c r="BD59">
-        <v>869.63142817642859</v>
+        <v>910.81457546220918</v>
       </c>
     </row>
     <row r="60" spans="2:56">
@@ -15461,7 +15461,7 @@
         <v>56.549593195147608</v>
       </c>
       <c r="M60">
-        <v>0.20337486804543919</v>
+        <v>0.19593013898546563</v>
       </c>
       <c r="O60" t="s">
         <v>445</v>
@@ -15491,16 +15491,16 @@
         <v>546</v>
       </c>
       <c r="Y60" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="Z60" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="AA60">
-        <v>0.99368555142692816</v>
+        <v>0.972129953111039</v>
       </c>
       <c r="AB60">
-        <v>115.76489050631628</v>
+        <v>510.95085963095079</v>
       </c>
       <c r="AD60" t="s">
         <v>445</v>
@@ -15530,13 +15530,13 @@
         <v>933</v>
       </c>
       <c r="AN60" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="AO60">
-        <v>0.98958136888311932</v>
+        <v>0.94216773987491098</v>
       </c>
       <c r="AP60">
-        <v>191.00823714281216</v>
+        <v>1060.2581022932995</v>
       </c>
       <c r="AR60" t="s">
         <v>445</v>
@@ -15566,13 +15566,13 @@
         <v>1134</v>
       </c>
       <c r="BB60" t="s">
-        <v>662</v>
+        <v>647</v>
       </c>
       <c r="BC60">
-        <v>0.96515942387218789</v>
+        <v>0.98172617970345721</v>
       </c>
       <c r="BD60">
-        <v>1169.0743524905106</v>
+        <v>967.23604394621248</v>
       </c>
     </row>
     <row r="61" spans="2:56">
@@ -15607,7 +15607,7 @@
         <v>1.517257960246374</v>
       </c>
       <c r="M61">
-        <v>0.18399929220051731</v>
+        <v>0.18023309962426437</v>
       </c>
       <c r="O61" t="s">
         <v>445</v>
@@ -15637,16 +15637,16 @@
         <v>548</v>
       </c>
       <c r="Y61" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="Z61" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AA61">
-        <v>0.94386714187064036</v>
+        <v>0.95402772316064421</v>
       </c>
       <c r="AB61">
-        <v>1029.10239903826</v>
+        <v>842.82507538818982</v>
       </c>
       <c r="AD61" t="s">
         <v>445</v>
@@ -15676,13 +15676,13 @@
         <v>934</v>
       </c>
       <c r="AN61" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="AO61">
-        <v>0.97298156476333331</v>
+        <v>0.99146900514737779</v>
       </c>
       <c r="AP61">
-        <v>495.337979338889</v>
+        <v>156.40157229807483</v>
       </c>
       <c r="AR61" t="s">
         <v>445</v>
@@ -15712,13 +15712,13 @@
         <v>1135</v>
       </c>
       <c r="BB61" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="BC61">
-        <v>0.95200980188478979</v>
+        <v>0.91560080888051365</v>
       </c>
       <c r="BD61">
-        <v>1329.2805803703113</v>
+        <v>1772.8634784724095</v>
       </c>
     </row>
     <row r="62" spans="2:56">
@@ -15753,7 +15753,7 @@
         <v>2.7748989458872644</v>
       </c>
       <c r="M62">
-        <v>0.18965210981791131</v>
+        <v>0.18918006848374011</v>
       </c>
       <c r="O62" t="s">
         <v>445</v>
@@ -15783,16 +15783,16 @@
         <v>550</v>
       </c>
       <c r="Y62" t="s">
-        <v>431</v>
+        <v>399</v>
       </c>
       <c r="Z62" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="AA62">
-        <v>0.92007975165213307</v>
+        <v>0.99556264479843226</v>
       </c>
       <c r="AB62">
-        <v>1465.2045530442279</v>
+        <v>81.351512028741695</v>
       </c>
       <c r="AD62" t="s">
         <v>445</v>
@@ -15822,13 +15822,13 @@
         <v>935</v>
       </c>
       <c r="AN62" t="s">
-        <v>675</v>
+        <v>647</v>
       </c>
       <c r="AO62">
-        <v>0.98449859725932043</v>
+        <v>0.97494022509165501</v>
       </c>
       <c r="AP62">
-        <v>284.19238357912451</v>
+        <v>459.42920665299067</v>
       </c>
       <c r="AR62" t="s">
         <v>445</v>
@@ -15858,13 +15858,13 @@
         <v>1136</v>
       </c>
       <c r="BB62" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="BC62">
-        <v>0.97707982144598671</v>
+        <v>0.99223944103482187</v>
       </c>
       <c r="BD62">
-        <v>1023.8441753830622</v>
+        <v>745.8368089899709</v>
       </c>
     </row>
     <row r="63" spans="2:56">
@@ -15899,7 +15899,7 @@
         <v>2.5568604295918282</v>
       </c>
       <c r="M63">
-        <v>0.1662062746973767</v>
+        <v>0.11763685142671564</v>
       </c>
       <c r="O63" t="s">
         <v>445</v>
@@ -15929,16 +15929,16 @@
         <v>552</v>
       </c>
       <c r="Y63" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="Z63" t="s">
-        <v>646</v>
+        <v>661</v>
       </c>
       <c r="AA63">
-        <v>0.96305263459297863</v>
+        <v>0.94094717156030294</v>
       </c>
       <c r="AB63">
-        <v>677.36836579539192</v>
+        <v>1082.6351880611128</v>
       </c>
       <c r="AD63" t="s">
         <v>445</v>
@@ -15968,13 +15968,13 @@
         <v>936</v>
       </c>
       <c r="AN63" t="s">
-        <v>649</v>
+        <v>679</v>
       </c>
       <c r="AO63">
-        <v>0.981374440216361</v>
+        <v>0.99342004180524168</v>
       </c>
       <c r="AP63">
-        <v>341.46859603338169</v>
+        <v>120.63256690390332</v>
       </c>
     </row>
     <row r="64" spans="2:56">
@@ -16009,7 +16009,7 @@
         <v>3.5504538561905079</v>
       </c>
       <c r="M64">
-        <v>0.16029904712052881</v>
+        <v>0.15187518960039298</v>
       </c>
       <c r="O64" t="s">
         <v>445</v>
@@ -16039,16 +16039,16 @@
         <v>554</v>
       </c>
       <c r="Y64" t="s">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="Z64" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="AA64">
-        <v>0.99459695303037288</v>
+        <v>0.96644290210447936</v>
       </c>
       <c r="AB64">
-        <v>99.055861109831142</v>
+        <v>615.21346141787853</v>
       </c>
       <c r="AD64" t="s">
         <v>445</v>
@@ -16078,13 +16078,13 @@
         <v>937</v>
       </c>
       <c r="AN64" t="s">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="AO64">
-        <v>0.94345419131600505</v>
+        <v>0.99501310191160197</v>
       </c>
       <c r="AP64">
-        <v>1036.6731592065737</v>
+        <v>91.426464953964114</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -16119,7 +16119,7 @@
         <v>29.154918866670329</v>
       </c>
       <c r="M65">
-        <v>0.2017439687898693</v>
+        <v>0.14122077815290851</v>
       </c>
       <c r="O65" t="s">
         <v>445</v>
@@ -16149,16 +16149,16 @@
         <v>556</v>
       </c>
       <c r="Y65" t="s">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="Z65" t="s">
         <v>674</v>
       </c>
       <c r="AA65">
-        <v>0.99519268990415388</v>
+        <v>0.99369895978652845</v>
       </c>
       <c r="AB65">
-        <v>88.134018423846243</v>
+        <v>115.51907058031178</v>
       </c>
       <c r="AD65" t="s">
         <v>445</v>
@@ -16188,13 +16188,13 @@
         <v>938</v>
       </c>
       <c r="AN65" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AO65">
-        <v>0.92366037259831435</v>
+        <v>0.9633630443304535</v>
       </c>
       <c r="AP65">
-        <v>1399.5598356975697</v>
+        <v>671.67752060835289</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -16259,16 +16259,16 @@
         <v>558</v>
       </c>
       <c r="Y66" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="Z66" t="s">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="AA66">
-        <v>0.98376991098916067</v>
+        <v>0.99349375112817762</v>
       </c>
       <c r="AB66">
-        <v>297.55163186538817</v>
+        <v>119.28122931674373</v>
       </c>
       <c r="AD66" t="s">
         <v>445</v>
@@ -16298,13 +16298,13 @@
         <v>939</v>
       </c>
       <c r="AN66" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="AO66">
-        <v>0.98255203569076077</v>
+        <v>0.98994878939511521</v>
       </c>
       <c r="AP66">
-        <v>319.879345669386</v>
+        <v>184.27219442288737</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -16339,7 +16339,7 @@
         <v>60.525198252848739</v>
       </c>
       <c r="M67">
-        <v>0.20776133786275169</v>
+        <v>0.14543293650392616</v>
       </c>
       <c r="O67" t="s">
         <v>445</v>
@@ -16369,16 +16369,16 @@
         <v>560</v>
       </c>
       <c r="Y67" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="Z67" t="s">
-        <v>657</v>
+        <v>676</v>
       </c>
       <c r="AA67">
-        <v>0.99221414970221189</v>
+        <v>0.99739378758993247</v>
       </c>
       <c r="AB67">
-        <v>142.74058879278186</v>
+        <v>47.780560851239088</v>
       </c>
       <c r="AD67" t="s">
         <v>445</v>
@@ -16408,13 +16408,13 @@
         <v>940</v>
       </c>
       <c r="AN67" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="AO67">
-        <v>0.98977574375304844</v>
+        <v>0.96684854231168849</v>
       </c>
       <c r="AP67">
-        <v>187.44469786077892</v>
+        <v>607.77672428571168</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -16449,7 +16449,7 @@
         <v>0.18379667725284016</v>
       </c>
       <c r="M68">
-        <v>0.18349665449971039</v>
+        <v>0.18289534321421311</v>
       </c>
       <c r="O68" t="s">
         <v>445</v>
@@ -16479,16 +16479,16 @@
         <v>562</v>
       </c>
       <c r="Y68" t="s">
-        <v>359</v>
+        <v>432</v>
       </c>
       <c r="Z68" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="AA68">
-        <v>0.98368128171218772</v>
+        <v>0.91300037935815459</v>
       </c>
       <c r="AB68">
-        <v>299.17650194322596</v>
+        <v>1594.9930451004991</v>
       </c>
       <c r="AD68" t="s">
         <v>445</v>
@@ -16518,13 +16518,13 @@
         <v>941</v>
       </c>
       <c r="AN68" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="AO68">
-        <v>0.94216773987491098</v>
+        <v>0.96378142476218853</v>
       </c>
       <c r="AP68">
-        <v>1060.2581022932995</v>
+        <v>664.00721269321059</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -16559,7 +16559,7 @@
         <v>2.1996960097232758</v>
       </c>
       <c r="M69">
-        <v>0.1705900572657362</v>
+        <v>0.16529274817425865</v>
       </c>
       <c r="O69" t="s">
         <v>445</v>
@@ -16589,16 +16589,16 @@
         <v>564</v>
       </c>
       <c r="Y69" t="s">
-        <v>374</v>
+        <v>438</v>
       </c>
       <c r="Z69" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="AA69">
-        <v>0.99448084580495932</v>
+        <v>0.96722865505135913</v>
       </c>
       <c r="AB69">
-        <v>101.18449357574643</v>
+        <v>600.80799072508239</v>
       </c>
       <c r="AD69" t="s">
         <v>445</v>
@@ -16631,10 +16631,10 @@
         <v>664</v>
       </c>
       <c r="AO69">
-        <v>0.9937640046384969</v>
+        <v>0.97998268051544435</v>
       </c>
       <c r="AP69">
-        <v>114.32658162755614</v>
+        <v>366.9841905501878</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -16669,7 +16669,7 @@
         <v>58.998302737850281</v>
       </c>
       <c r="M70">
-        <v>0.20544284328366749</v>
+        <v>0.14380999029856723</v>
       </c>
       <c r="O70" t="s">
         <v>445</v>
@@ -16699,16 +16699,16 @@
         <v>566</v>
       </c>
       <c r="Y70" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="Z70" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="AA70">
-        <v>0.98211683915529446</v>
+        <v>0.95936298088609862</v>
       </c>
       <c r="AB70">
-        <v>327.85794881960226</v>
+        <v>745.01201708819133</v>
       </c>
       <c r="AD70" t="s">
         <v>445</v>
@@ -16738,13 +16738,13 @@
         <v>943</v>
       </c>
       <c r="AN70" t="s">
-        <v>652</v>
+        <v>687</v>
       </c>
       <c r="AO70">
-        <v>0.98434157772378295</v>
+        <v>0.99273887587992471</v>
       </c>
       <c r="AP70">
-        <v>287.07107506397949</v>
+        <v>133.12060886804619</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -16779,7 +16779,7 @@
         <v>34.975274584155741</v>
       </c>
       <c r="M71">
-        <v>0.1978319238872833</v>
+        <v>0.19772688487539386</v>
       </c>
       <c r="O71" t="s">
         <v>445</v>
@@ -16809,16 +16809,16 @@
         <v>568</v>
       </c>
       <c r="Y71" t="s">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="Z71" t="s">
-        <v>655</v>
+        <v>677</v>
       </c>
       <c r="AA71">
-        <v>0.9804939638153034</v>
+        <v>0.9970088962341721</v>
       </c>
       <c r="AB71">
-        <v>357.61066338610357</v>
+        <v>54.836902373510455</v>
       </c>
       <c r="AD71" t="s">
         <v>445</v>
@@ -16848,13 +16848,13 @@
         <v>944</v>
       </c>
       <c r="AN71" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="AO71">
-        <v>0.98724240938456542</v>
+        <v>0.95931345925264233</v>
       </c>
       <c r="AP71">
-        <v>233.88916128296634</v>
+        <v>745.91991370155699</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -16889,7 +16889,7 @@
         <v>7.9955944823858998</v>
       </c>
       <c r="M72">
-        <v>0.20986347568260691</v>
+        <v>0.14690443297782482</v>
       </c>
       <c r="O72" t="s">
         <v>445</v>
@@ -16919,16 +16919,16 @@
         <v>570</v>
       </c>
       <c r="Y72" t="s">
-        <v>433</v>
+        <v>349</v>
       </c>
       <c r="Z72" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="AA72">
-        <v>0.99112806655302721</v>
+        <v>0.98828003950132159</v>
       </c>
       <c r="AB72">
-        <v>162.65211319450148</v>
+        <v>214.8659424757702</v>
       </c>
       <c r="AD72" t="s">
         <v>445</v>
@@ -16958,13 +16958,13 @@
         <v>945</v>
       </c>
       <c r="AN72" t="s">
-        <v>673</v>
+        <v>652</v>
       </c>
       <c r="AO72">
-        <v>0.99486897494175219</v>
+        <v>0.99411928823407203</v>
       </c>
       <c r="AP72">
-        <v>94.068792734543848</v>
+        <v>107.81304904201184</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16999,7 +16999,7 @@
         <v>24.67146067932309</v>
       </c>
       <c r="M73">
-        <v>0.20313391794678989</v>
+        <v>0.20266229838738631</v>
       </c>
       <c r="O73" t="s">
         <v>445</v>
@@ -17029,16 +17029,16 @@
         <v>572</v>
       </c>
       <c r="Y73" t="s">
-        <v>436</v>
+        <v>364</v>
       </c>
       <c r="Z73" t="s">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="AA73">
-        <v>0.94480589710631147</v>
+        <v>0.99382591612551541</v>
       </c>
       <c r="AB73">
-        <v>1011.8918863842907</v>
+        <v>113.1915376988852</v>
       </c>
       <c r="AD73" t="s">
         <v>445</v>
@@ -17068,13 +17068,13 @@
         <v>946</v>
       </c>
       <c r="AN73" t="s">
-        <v>679</v>
+        <v>646</v>
       </c>
       <c r="AO73">
-        <v>0.99698330098522958</v>
+        <v>0.9790694594776973</v>
       </c>
       <c r="AP73">
-        <v>55.306148604123919</v>
+        <v>383.72657624221517</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -17139,16 +17139,16 @@
         <v>574</v>
       </c>
       <c r="Y74" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="Z74" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AA74">
-        <v>0.99240501837238893</v>
+        <v>0.99482528705797657</v>
       </c>
       <c r="AB74">
-        <v>139.24132983953538</v>
+        <v>94.869737270428971</v>
       </c>
       <c r="AD74" t="s">
         <v>445</v>
@@ -17178,13 +17178,13 @@
         <v>947</v>
       </c>
       <c r="AN74" t="s">
-        <v>649</v>
+        <v>684</v>
       </c>
       <c r="AO74">
-        <v>0.95884281124958637</v>
+        <v>0.99570788786991582</v>
       </c>
       <c r="AP74">
-        <v>754.54846042424947</v>
+        <v>78.688722384876669</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -17249,16 +17249,16 @@
         <v>576</v>
       </c>
       <c r="Y75" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="Z75" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AA75">
-        <v>0.9365516394102017</v>
+        <v>0.97321507838078658</v>
       </c>
       <c r="AB75">
-        <v>1163.2199441463022</v>
+        <v>491.05689635224547</v>
       </c>
       <c r="AD75" t="s">
         <v>445</v>
@@ -17288,13 +17288,13 @@
         <v>948</v>
       </c>
       <c r="AN75" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="AO75">
-        <v>0.96628526147979277</v>
+        <v>0.98562252349041679</v>
       </c>
       <c r="AP75">
-        <v>618.10353953713195</v>
+        <v>263.58706934235943</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -17359,16 +17359,16 @@
         <v>578</v>
       </c>
       <c r="Y76" t="s">
-        <v>424</v>
+        <v>380</v>
       </c>
       <c r="Z76" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AA76">
-        <v>0.97527660765685298</v>
+        <v>0.97866893212504957</v>
       </c>
       <c r="AB76">
-        <v>453.26219295769499</v>
+        <v>391.06957770742463</v>
       </c>
       <c r="AD76" t="s">
         <v>445</v>
@@ -17398,13 +17398,13 @@
         <v>949</v>
       </c>
       <c r="AN76" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="AO76">
-        <v>0.97196184623196236</v>
+        <v>0.94920173100235461</v>
       </c>
       <c r="AP76">
-        <v>514.03281908068925</v>
+        <v>931.3015982901652</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -17469,16 +17469,16 @@
         <v>580</v>
       </c>
       <c r="Y77" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="Z77" t="s">
-        <v>678</v>
+        <v>658</v>
       </c>
       <c r="AA77">
-        <v>0.99571254852817692</v>
+        <v>0.9933008323747714</v>
       </c>
       <c r="AB77">
-        <v>78.60327698342283</v>
+        <v>122.81807312919075</v>
       </c>
       <c r="AD77" t="s">
         <v>445</v>
@@ -17508,13 +17508,13 @@
         <v>950</v>
       </c>
       <c r="AN77" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AO77">
-        <v>0.92143845786947276</v>
+        <v>0.94099051948143053</v>
       </c>
       <c r="AP77">
-        <v>1440.294939059665</v>
+        <v>1081.8404761737738</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -17579,16 +17579,16 @@
         <v>582</v>
       </c>
       <c r="Y78" t="s">
-        <v>356</v>
+        <v>403</v>
       </c>
       <c r="Z78" t="s">
-        <v>647</v>
+        <v>665</v>
       </c>
       <c r="AA78">
-        <v>0.99165895214194211</v>
+        <v>0.9771403150431911</v>
       </c>
       <c r="AB78">
-        <v>152.91921073106212</v>
+        <v>419.09422420816315</v>
       </c>
       <c r="AD78" t="s">
         <v>445</v>
@@ -17618,13 +17618,13 @@
         <v>951</v>
       </c>
       <c r="AN78" t="s">
-        <v>683</v>
+        <v>658</v>
       </c>
       <c r="AO78">
-        <v>0.99544850388702388</v>
+        <v>0.97163156886146174</v>
       </c>
       <c r="AP78">
-        <v>83.444095404561224</v>
+        <v>520.0879042065344</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -17659,7 +17659,7 @@
         <v>56.239799361911793</v>
       </c>
       <c r="M79">
-        <v>0.2002669105158062</v>
+        <v>0.19891610173338561</v>
       </c>
       <c r="O79" t="s">
         <v>445</v>
@@ -17689,16 +17689,16 @@
         <v>584</v>
       </c>
       <c r="Y79" t="s">
-        <v>365</v>
+        <v>414</v>
       </c>
       <c r="Z79" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="AA79">
-        <v>0.99664889239239962</v>
+        <v>0.96576017716725859</v>
       </c>
       <c r="AB79">
-        <v>61.436972806007184</v>
+        <v>627.73008526692502</v>
       </c>
       <c r="AD79" t="s">
         <v>445</v>
@@ -17728,13 +17728,13 @@
         <v>952</v>
       </c>
       <c r="AN79" t="s">
-        <v>657</v>
+        <v>688</v>
       </c>
       <c r="AO79">
-        <v>0.99073782529254428</v>
+        <v>0.99407790982046917</v>
       </c>
       <c r="AP79">
-        <v>169.80653630335468</v>
+        <v>108.57165329139941</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -17799,16 +17799,16 @@
         <v>586</v>
       </c>
       <c r="Y80" t="s">
-        <v>371</v>
+        <v>418</v>
       </c>
       <c r="Z80" t="s">
-        <v>680</v>
+        <v>652</v>
       </c>
       <c r="AA80">
-        <v>0.99092130604056927</v>
+        <v>0.99320659129827649</v>
       </c>
       <c r="AB80">
-        <v>166.44272258956366</v>
+        <v>124.54582619826394</v>
       </c>
       <c r="AD80" t="s">
         <v>445</v>
@@ -17838,13 +17838,13 @@
         <v>953</v>
       </c>
       <c r="AN80" t="s">
-        <v>646</v>
+        <v>661</v>
       </c>
       <c r="AO80">
-        <v>0.95849712823420175</v>
+        <v>0.97471651986393804</v>
       </c>
       <c r="AP80">
-        <v>760.8859823729681</v>
+        <v>463.53046916113516</v>
       </c>
     </row>
     <row r="81" spans="2:42">
@@ -17879,7 +17879,7 @@
         <v>74.120337453709965</v>
       </c>
       <c r="M81">
-        <v>0.20367785944499259</v>
+        <v>0.20182337922777235</v>
       </c>
       <c r="O81" t="s">
         <v>445</v>
@@ -17909,16 +17909,16 @@
         <v>588</v>
       </c>
       <c r="Y81" t="s">
-        <v>378</v>
+        <v>425</v>
       </c>
       <c r="Z81" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="AA81">
-        <v>0.95611998680969301</v>
+        <v>0.97901340677155257</v>
       </c>
       <c r="AB81">
-        <v>804.46690848896196</v>
+        <v>384.75420918820265</v>
       </c>
       <c r="AD81" t="s">
         <v>445</v>
@@ -17948,13 +17948,13 @@
         <v>954</v>
       </c>
       <c r="AN81" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="AO81">
-        <v>0.98822008409109219</v>
+        <v>0.95301935344113697</v>
       </c>
       <c r="AP81">
-        <v>215.96512499664277</v>
+        <v>861.31185357915479</v>
       </c>
     </row>
     <row r="82" spans="2:42">
@@ -17989,7 +17989,7 @@
         <v>8.4528050675863646</v>
       </c>
       <c r="M82">
-        <v>0.2016605208446671</v>
+        <v>0.20159598701952061</v>
       </c>
       <c r="O82" t="s">
         <v>445</v>
@@ -18019,16 +18019,16 @@
         <v>590</v>
       </c>
       <c r="Y82" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="Z82" t="s">
-        <v>655</v>
+        <v>681</v>
       </c>
       <c r="AA82">
-        <v>0.99055684074965455</v>
+        <v>0.99459695303037288</v>
       </c>
       <c r="AB82">
-        <v>173.12458625633352</v>
+        <v>99.055861109831142</v>
       </c>
       <c r="AD82" t="s">
         <v>445</v>
@@ -18058,13 +18058,13 @@
         <v>955</v>
       </c>
       <c r="AN82" t="s">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="AO82">
-        <v>0.99332113976407466</v>
+        <v>0.99443080330687583</v>
       </c>
       <c r="AP82">
-        <v>122.44577099196496</v>
+        <v>102.10193937394267</v>
       </c>
     </row>
     <row r="83" spans="2:42">
@@ -18099,7 +18099,7 @@
         <v>59.068455369411964</v>
       </c>
       <c r="M83">
-        <v>0.20742519634355899</v>
+        <v>0.20737196179823966</v>
       </c>
       <c r="O83" t="s">
         <v>445</v>
@@ -18129,16 +18129,16 @@
         <v>592</v>
       </c>
       <c r="Y83" t="s">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="Z83" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AA83">
-        <v>0.99723631056718209</v>
+        <v>0.99519268990415388</v>
       </c>
       <c r="AB83">
-        <v>50.667639601661186</v>
+        <v>88.134018423846243</v>
       </c>
       <c r="AD83" t="s">
         <v>445</v>
@@ -18168,13 +18168,13 @@
         <v>956</v>
       </c>
       <c r="AN83" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="AO83">
-        <v>0.99451359177835219</v>
+        <v>0.99161135964647729</v>
       </c>
       <c r="AP83">
-        <v>100.58415073020944</v>
+        <v>153.79173981458226</v>
       </c>
     </row>
     <row r="84" spans="2:42">
@@ -18209,7 +18209,7 @@
         <v>4.9244458949630907</v>
       </c>
       <c r="M84">
-        <v>0.18853018628831339</v>
+        <v>0.17547701743020053</v>
       </c>
       <c r="O84" t="s">
         <v>445</v>
@@ -18239,16 +18239,16 @@
         <v>594</v>
       </c>
       <c r="Y84" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="Z84" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="AA84">
-        <v>0.96929197405517931</v>
+        <v>0.98376991098916067</v>
       </c>
       <c r="AB84">
-        <v>562.98047565504703</v>
+        <v>297.55163186538817</v>
       </c>
       <c r="AD84" t="s">
         <v>445</v>
@@ -18278,13 +18278,13 @@
         <v>957</v>
       </c>
       <c r="AN84" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AO84">
-        <v>0.9909682810714957</v>
+        <v>0.99096791212626811</v>
       </c>
       <c r="AP84">
-        <v>165.58151368924484</v>
+        <v>165.5882776850855</v>
       </c>
     </row>
     <row r="85" spans="2:42">
@@ -18319,7 +18319,7 @@
         <v>43.396322413548354</v>
       </c>
       <c r="M85">
-        <v>0.19980451257320289</v>
+        <v>0.139863158801242</v>
       </c>
       <c r="O85" t="s">
         <v>445</v>
@@ -18349,16 +18349,16 @@
         <v>596</v>
       </c>
       <c r="Y85" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="Z85" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="AA85">
-        <v>0.98417563223370064</v>
+        <v>0.99221414970221189</v>
       </c>
       <c r="AB85">
-        <v>290.11340904882155</v>
+        <v>142.74058879278186</v>
       </c>
       <c r="AD85" t="s">
         <v>445</v>
@@ -18388,13 +18388,13 @@
         <v>958</v>
       </c>
       <c r="AN85" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AO85">
-        <v>0.97689731236523503</v>
+        <v>0.99153287968327641</v>
       </c>
       <c r="AP85">
-        <v>423.54927330402518</v>
+        <v>155.23053913993309</v>
       </c>
     </row>
     <row r="86" spans="2:42">
@@ -18429,7 +18429,7 @@
         <v>72.5473930066169</v>
       </c>
       <c r="M86">
-        <v>0.2041727547388352</v>
+        <v>0.20354412180741346</v>
       </c>
       <c r="O86" t="s">
         <v>445</v>
@@ -18459,16 +18459,16 @@
         <v>598</v>
       </c>
       <c r="Y86" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="Z86" t="s">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="AA86">
-        <v>0.98922498055164843</v>
+        <v>0.99480818130085191</v>
       </c>
       <c r="AB86">
-        <v>197.54202321977883</v>
+        <v>95.183342817714731</v>
       </c>
       <c r="AD86" t="s">
         <v>445</v>
@@ -18498,13 +18498,13 @@
         <v>959</v>
       </c>
       <c r="AN86" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="AO86">
-        <v>0.96933352809933682</v>
+        <v>0.99568711277871247</v>
       </c>
       <c r="AP86">
-        <v>562.21865151215866</v>
+        <v>79.069599056938102</v>
       </c>
     </row>
     <row r="87" spans="2:42">
@@ -18539,7 +18539,7 @@
         <v>111.90472691966944</v>
       </c>
       <c r="M87">
-        <v>0.2081628231887393</v>
+        <v>0.14571397623211749</v>
       </c>
       <c r="O87" t="s">
         <v>445</v>
@@ -18569,16 +18569,16 @@
         <v>600</v>
       </c>
       <c r="Y87" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="Z87" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="AA87">
-        <v>0.99262576700342608</v>
+        <v>0.92426797711114228</v>
       </c>
       <c r="AB87">
-        <v>135.19427160385601</v>
+        <v>1388.420419629058</v>
       </c>
       <c r="AD87" t="s">
         <v>445</v>
@@ -18608,13 +18608,13 @@
         <v>960</v>
       </c>
       <c r="AN87" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="AO87">
-        <v>0.94508652322363806</v>
+        <v>0.98225029258055574</v>
       </c>
       <c r="AP87">
-        <v>1006.7470742333013</v>
+        <v>325.41130268981078</v>
       </c>
     </row>
     <row r="88" spans="2:42">
@@ -18649,7 +18649,7 @@
         <v>30.28911159621881</v>
       </c>
       <c r="M88">
-        <v>0.20387542255148941</v>
+        <v>0.14271279578604257</v>
       </c>
       <c r="O88" t="s">
         <v>445</v>
@@ -18679,16 +18679,16 @@
         <v>602</v>
       </c>
       <c r="Y88" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="Z88" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="AA88">
-        <v>0.972129953111039</v>
+        <v>0.92861598426622882</v>
       </c>
       <c r="AB88">
-        <v>510.95085963095079</v>
+        <v>1308.7069551191387</v>
       </c>
       <c r="AD88" t="s">
         <v>445</v>
@@ -18718,13 +18718,13 @@
         <v>961</v>
       </c>
       <c r="AN88" t="s">
-        <v>647</v>
+        <v>661</v>
       </c>
       <c r="AO88">
-        <v>0.99188307586951852</v>
+        <v>0.982419047139102</v>
       </c>
       <c r="AP88">
-        <v>148.81027572549408</v>
+        <v>322.31746911646275</v>
       </c>
     </row>
     <row r="89" spans="2:42">
@@ -18789,16 +18789,16 @@
         <v>604</v>
       </c>
       <c r="Y89" t="s">
-        <v>385</v>
+        <v>352</v>
       </c>
       <c r="Z89" t="s">
-        <v>649</v>
+        <v>684</v>
       </c>
       <c r="AA89">
-        <v>0.95402772316064421</v>
+        <v>0.99521113523741833</v>
       </c>
       <c r="AB89">
-        <v>842.82507538818982</v>
+        <v>87.795853980664262</v>
       </c>
       <c r="AD89" t="s">
         <v>445</v>
@@ -18828,13 +18828,13 @@
         <v>962</v>
       </c>
       <c r="AN89" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="AO89">
-        <v>0.93449855145693639</v>
+        <v>0.97789502766167302</v>
       </c>
       <c r="AP89">
-        <v>1200.8598899561664</v>
+        <v>405.25782620266216</v>
       </c>
     </row>
     <row r="90" spans="2:42">
@@ -18869,7 +18869,7 @@
         <v>0.50085118024234676</v>
       </c>
       <c r="M90">
-        <v>0.19793035868769021</v>
+        <v>0.19387374542696106</v>
       </c>
       <c r="O90" t="s">
         <v>445</v>
@@ -18899,16 +18899,16 @@
         <v>606</v>
       </c>
       <c r="Y90" t="s">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="Z90" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AA90">
-        <v>0.99556264479843226</v>
+        <v>0.98246197339983365</v>
       </c>
       <c r="AB90">
-        <v>81.351512028741695</v>
+        <v>321.53048766971619</v>
       </c>
       <c r="AD90" t="s">
         <v>445</v>
@@ -18938,13 +18938,13 @@
         <v>963</v>
       </c>
       <c r="AN90" t="s">
-        <v>656</v>
+        <v>675</v>
       </c>
       <c r="AO90">
-        <v>0.96937670635957107</v>
+        <v>0.99485109969932284</v>
       </c>
       <c r="AP90">
-        <v>561.42705007453139</v>
+        <v>94.396505512414166</v>
       </c>
     </row>
     <row r="91" spans="2:42">
@@ -18979,7 +18979,7 @@
         <v>1.129453710093588</v>
       </c>
       <c r="M91">
-        <v>0.1813612970253643</v>
+        <v>0.1609466641249169</v>
       </c>
       <c r="O91" t="s">
         <v>445</v>
@@ -19009,16 +19009,16 @@
         <v>608</v>
       </c>
       <c r="Y91" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="Z91" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AA91">
-        <v>0.94094717156030294</v>
+        <v>0.98352964899150075</v>
       </c>
       <c r="AB91">
-        <v>1082.6351880611128</v>
+        <v>301.95643515581952</v>
       </c>
       <c r="AD91" t="s">
         <v>445</v>
@@ -19048,13 +19048,13 @@
         <v>964</v>
       </c>
       <c r="AN91" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="AO91">
-        <v>0.96461853105171591</v>
+        <v>0.97344873028830825</v>
       </c>
       <c r="AP91">
-        <v>648.66026405187517</v>
+        <v>486.77327804768265</v>
       </c>
     </row>
     <row r="92" spans="2:42">
@@ -19089,7 +19089,7 @@
         <v>0.64859160767080837</v>
       </c>
       <c r="M92">
-        <v>0.1915586927729965</v>
+        <v>0.13469932533091308</v>
       </c>
       <c r="O92" t="s">
         <v>445</v>
@@ -19119,16 +19119,16 @@
         <v>610</v>
       </c>
       <c r="Y92" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="Z92" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="AA92">
-        <v>0.96644290210447936</v>
+        <v>0.91847114692356346</v>
       </c>
       <c r="AB92">
-        <v>615.21346141787853</v>
+        <v>1494.6956397346703</v>
       </c>
       <c r="AD92" t="s">
         <v>445</v>
@@ -19158,13 +19158,13 @@
         <v>965</v>
       </c>
       <c r="AN92" t="s">
-        <v>687</v>
+        <v>649</v>
       </c>
       <c r="AO92">
-        <v>0.99347025982523174</v>
+        <v>0.98192694200361774</v>
       </c>
       <c r="AP92">
-        <v>119.71190320408562</v>
+        <v>331.33939660034207</v>
       </c>
     </row>
     <row r="93" spans="2:42">
@@ -19199,7 +19199,7 @@
         <v>6.4851879183304098</v>
       </c>
       <c r="M93">
-        <v>0.1689011220881165</v>
+        <v>0.16229821357567761</v>
       </c>
       <c r="O93" t="s">
         <v>445</v>
@@ -19229,16 +19229,16 @@
         <v>612</v>
       </c>
       <c r="Y93" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="Z93" t="s">
-        <v>684</v>
+        <v>661</v>
       </c>
       <c r="AA93">
-        <v>0.99369895978652845</v>
+        <v>0.92680423740224549</v>
       </c>
       <c r="AB93">
-        <v>115.51907058031178</v>
+        <v>1341.9223142921653</v>
       </c>
       <c r="AD93" t="s">
         <v>445</v>
@@ -19268,13 +19268,13 @@
         <v>966</v>
       </c>
       <c r="AN93" t="s">
-        <v>688</v>
+        <v>655</v>
       </c>
       <c r="AO93">
-        <v>0.99424478665673766</v>
+        <v>0.99188307586951852</v>
       </c>
       <c r="AP93">
-        <v>105.51224462647731</v>
+        <v>148.81027572549408</v>
       </c>
     </row>
     <row r="94" spans="2:42">
@@ -19309,7 +19309,7 @@
         <v>0.16172809196029012</v>
       </c>
       <c r="M94">
-        <v>0.15479515913716929</v>
+        <v>0.1083566113960185</v>
       </c>
       <c r="O94" t="s">
         <v>445</v>
@@ -19339,16 +19339,16 @@
         <v>614</v>
       </c>
       <c r="Y94" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="Z94" t="s">
-        <v>685</v>
+        <v>646</v>
       </c>
       <c r="AA94">
-        <v>0.99349375112817762</v>
+        <v>0.96447115506861258</v>
       </c>
       <c r="AB94">
-        <v>119.28122931674373</v>
+        <v>651.36215707543533</v>
       </c>
       <c r="AD94" t="s">
         <v>445</v>
@@ -19378,13 +19378,13 @@
         <v>967</v>
       </c>
       <c r="AN94" t="s">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="AO94">
-        <v>0.97867478517995188</v>
+        <v>0.93449855145693639</v>
       </c>
       <c r="AP94">
-        <v>390.96227170088139</v>
+        <v>1200.8598899561664</v>
       </c>
     </row>
     <row r="95" spans="2:42">
@@ -19449,16 +19449,16 @@
         <v>616</v>
       </c>
       <c r="Y95" t="s">
-        <v>428</v>
+        <v>359</v>
       </c>
       <c r="Z95" t="s">
         <v>686</v>
       </c>
       <c r="AA95">
-        <v>0.99739378758993247</v>
+        <v>0.98368128171218772</v>
       </c>
       <c r="AB95">
-        <v>47.780560851239088</v>
+        <v>299.17650194322596</v>
       </c>
       <c r="AD95" t="s">
         <v>445</v>
@@ -19488,13 +19488,13 @@
         <v>968</v>
       </c>
       <c r="AN95" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="AO95">
-        <v>0.95781637101189843</v>
+        <v>0.96937670635957107</v>
       </c>
       <c r="AP95">
-        <v>773.36653144852835</v>
+        <v>561.42705007453139</v>
       </c>
     </row>
     <row r="96" spans="2:42">
@@ -19529,7 +19529,7 @@
         <v>6.0465001879111799</v>
       </c>
       <c r="M96">
-        <v>0.19196008556784411</v>
+        <v>0.19005022206121128</v>
       </c>
       <c r="O96" t="s">
         <v>445</v>
@@ -19559,16 +19559,16 @@
         <v>618</v>
       </c>
       <c r="Y96" t="s">
-        <v>432</v>
+        <v>374</v>
       </c>
       <c r="Z96" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="AA96">
-        <v>0.91300037935815459</v>
+        <v>0.99448084580495932</v>
       </c>
       <c r="AB96">
-        <v>1594.9930451004991</v>
+        <v>101.18449357574643</v>
       </c>
       <c r="AD96" t="s">
         <v>445</v>
@@ -19598,13 +19598,13 @@
         <v>969</v>
       </c>
       <c r="AN96" t="s">
-        <v>668</v>
+        <v>646</v>
       </c>
       <c r="AO96">
-        <v>0.98886553660707677</v>
+        <v>0.96461853105171591</v>
       </c>
       <c r="AP96">
-        <v>204.13182887025886</v>
+        <v>648.66026405187517</v>
       </c>
     </row>
     <row r="97" spans="2:42">
@@ -19639,7 +19639,7 @@
         <v>46.796269813931573</v>
       </c>
       <c r="M97">
-        <v>0.19945819683657601</v>
+        <v>0.19916379708782467</v>
       </c>
       <c r="O97" t="s">
         <v>445</v>
@@ -19669,16 +19669,16 @@
         <v>620</v>
       </c>
       <c r="Y97" t="s">
-        <v>438</v>
+        <v>384</v>
       </c>
       <c r="Z97" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="AA97">
-        <v>0.96722865505135913</v>
+        <v>0.98211683915529446</v>
       </c>
       <c r="AB97">
-        <v>600.80799072508239</v>
+        <v>327.85794881960226</v>
       </c>
       <c r="AD97" t="s">
         <v>445</v>
@@ -19708,13 +19708,13 @@
         <v>970</v>
       </c>
       <c r="AN97" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AO97">
-        <v>0.93811411999108418</v>
+        <v>0.98407466378375608</v>
       </c>
       <c r="AP97">
-        <v>1134.5744668301231</v>
+        <v>291.96449729780619</v>
       </c>
     </row>
     <row r="98" spans="2:42">
@@ -19749,7 +19749,7 @@
         <v>125.26728427243935</v>
       </c>
       <c r="M98">
-        <v>0.1983317183255098</v>
+        <v>0.19826237089400434</v>
       </c>
       <c r="O98" t="s">
         <v>445</v>
@@ -19779,16 +19779,16 @@
         <v>622</v>
       </c>
       <c r="Y98" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="Z98" t="s">
-        <v>687</v>
+        <v>645</v>
       </c>
       <c r="AA98">
-        <v>0.99385704522942342</v>
+        <v>0.9804939638153034</v>
       </c>
       <c r="AB98">
-        <v>112.62083746056986</v>
+        <v>357.61066338610357</v>
       </c>
       <c r="AD98" t="s">
         <v>445</v>
@@ -19818,13 +19818,13 @@
         <v>971</v>
       </c>
       <c r="AN98" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="AO98">
-        <v>0.9832447093861123</v>
+        <v>0.9542882304111121</v>
       </c>
       <c r="AP98">
-        <v>307.18032792127502</v>
+        <v>838.04910912961134</v>
       </c>
     </row>
     <row r="99" spans="2:42">
@@ -19859,7 +19859,7 @@
         <v>11.350931098153549</v>
       </c>
       <c r="M99">
-        <v>0.19448671891839411</v>
+        <v>0.19443751451323907</v>
       </c>
       <c r="O99" t="s">
         <v>445</v>
@@ -19889,16 +19889,16 @@
         <v>624</v>
       </c>
       <c r="Y99" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="Z99" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="AA99">
-        <v>0.99512174530146036</v>
+        <v>0.99112806655302721</v>
       </c>
       <c r="AB99">
-        <v>89.434669473226961</v>
+        <v>162.65211319450148</v>
       </c>
       <c r="AD99" t="s">
         <v>445</v>
@@ -19928,13 +19928,13 @@
         <v>972</v>
       </c>
       <c r="AN99" t="s">
-        <v>684</v>
+        <v>665</v>
       </c>
       <c r="AO99">
-        <v>0.99401394460386272</v>
+        <v>0.99582108489984233</v>
       </c>
       <c r="AP99">
-        <v>109.74434892918245</v>
+        <v>76.613443502890505</v>
       </c>
     </row>
     <row r="100" spans="2:42">
@@ -19969,7 +19969,7 @@
         <v>146.29340009917189</v>
       </c>
       <c r="M100">
-        <v>0.19806191142622781</v>
+        <v>0.13864333799835946</v>
       </c>
       <c r="O100" t="s">
         <v>445</v>
@@ -19999,16 +19999,16 @@
         <v>626</v>
       </c>
       <c r="Y100" t="s">
-        <v>369</v>
+        <v>436</v>
       </c>
       <c r="Z100" t="s">
         <v>670</v>
       </c>
       <c r="AA100">
-        <v>0.97275257137901638</v>
+        <v>0.94480589710631147</v>
       </c>
       <c r="AB100">
-        <v>499.53619138470009</v>
+        <v>1011.8918863842907</v>
       </c>
       <c r="AD100" t="s">
         <v>445</v>
@@ -20038,13 +20038,13 @@
         <v>973</v>
       </c>
       <c r="AN100" t="s">
-        <v>686</v>
+        <v>659</v>
       </c>
       <c r="AO100">
-        <v>0.99712495361968201</v>
+        <v>0.99800187122714112</v>
       </c>
       <c r="AP100">
-        <v>52.709183639163186</v>
+        <v>36.632360835745096</v>
       </c>
     </row>
     <row r="101" spans="2:42">
@@ -20109,16 +20109,16 @@
         <v>628</v>
       </c>
       <c r="Y101" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z101" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="AA101">
-        <v>0.95322333844045537</v>
+        <v>0.96039250350097727</v>
       </c>
       <c r="AB101">
-        <v>857.57212859165099</v>
+        <v>726.13743581541678</v>
       </c>
       <c r="AD101" t="s">
         <v>445</v>
@@ -20148,13 +20148,13 @@
         <v>974</v>
       </c>
       <c r="AN101" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AO101">
-        <v>0.99728565567097416</v>
+        <v>0.98958136888311932</v>
       </c>
       <c r="AP101">
-        <v>49.762979365472916</v>
+        <v>191.00823714281216</v>
       </c>
     </row>
     <row r="102" spans="2:42">
@@ -20219,16 +20219,16 @@
         <v>630</v>
       </c>
       <c r="Y102" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Z102" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="AA102">
-        <v>0.93792673193465337</v>
+        <v>0.96501488785990974</v>
       </c>
       <c r="AB102">
-        <v>1138.0099145313559</v>
+        <v>641.39372256832166</v>
       </c>
       <c r="AD102" t="s">
         <v>445</v>
@@ -20258,13 +20258,13 @@
         <v>975</v>
       </c>
       <c r="AN102" t="s">
-        <v>646</v>
+        <v>670</v>
       </c>
       <c r="AO102">
-        <v>0.95358024529553875</v>
+        <v>0.97298156476333331</v>
       </c>
       <c r="AP102">
-        <v>851.0288362484556</v>
+        <v>495.337979338889</v>
       </c>
     </row>
     <row r="103" spans="2:42">
@@ -20329,16 +20329,16 @@
         <v>632</v>
       </c>
       <c r="Y103" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="Z103" t="s">
-        <v>661</v>
+        <v>688</v>
       </c>
       <c r="AA103">
-        <v>0.99238887682283938</v>
+        <v>0.99401420652619221</v>
       </c>
       <c r="AB103">
-        <v>139.53725824794503</v>
+        <v>109.73954701980865</v>
       </c>
       <c r="AD103" t="s">
         <v>445</v>
@@ -20368,13 +20368,13 @@
         <v>976</v>
       </c>
       <c r="AN103" t="s">
-        <v>677</v>
+        <v>658</v>
       </c>
       <c r="AO103">
-        <v>0.99223838421520194</v>
+        <v>0.97196184623196236</v>
       </c>
       <c r="AP103">
-        <v>142.29628938796495</v>
+        <v>514.03281908068925</v>
       </c>
     </row>
     <row r="104" spans="2:42">
@@ -20409,7 +20409,7 @@
         <v>13.41944237534064</v>
       </c>
       <c r="M104">
-        <v>0.19406169109879459</v>
+        <v>0.1940095018593084</v>
       </c>
       <c r="O104" t="s">
         <v>445</v>
@@ -20439,16 +20439,16 @@
         <v>634</v>
       </c>
       <c r="Y104" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="Z104" t="s">
         <v>689</v>
       </c>
       <c r="AA104">
-        <v>0.99511596204556785</v>
+        <v>0.99368555142692816</v>
       </c>
       <c r="AB104">
-        <v>89.54069583125569</v>
+        <v>115.76489050631628</v>
       </c>
       <c r="AD104" t="s">
         <v>445</v>
@@ -20478,13 +20478,13 @@
         <v>977</v>
       </c>
       <c r="AN104" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="AO104">
-        <v>0.93136449657406906</v>
+        <v>0.92143845786947276</v>
       </c>
       <c r="AP104">
-        <v>1258.3175628087345</v>
+        <v>1440.294939059665</v>
       </c>
     </row>
     <row r="105" spans="2:42">
@@ -20519,7 +20519,7 @@
         <v>90.868327533917025</v>
       </c>
       <c r="M105">
-        <v>0.1997678543338792</v>
+        <v>0.1990343507476294</v>
       </c>
       <c r="O105" t="s">
         <v>445</v>
@@ -20549,16 +20549,16 @@
         <v>636</v>
       </c>
       <c r="Y105" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Z105" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="AA105">
-        <v>0.9916566373699115</v>
+        <v>0.94386714187064036</v>
       </c>
       <c r="AB105">
-        <v>152.96164821828896</v>
+        <v>1029.10239903826</v>
       </c>
       <c r="AD105" t="s">
         <v>445</v>
@@ -20588,13 +20588,13 @@
         <v>978</v>
       </c>
       <c r="AN105" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="AO105">
-        <v>0.9340182520227388</v>
+        <v>0.99544850388702388</v>
       </c>
       <c r="AP105">
-        <v>1209.6653795831226</v>
+        <v>83.444095404561224</v>
       </c>
     </row>
     <row r="106" spans="2:42">
@@ -20659,16 +20659,16 @@
         <v>638</v>
       </c>
       <c r="Y106" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="Z106" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="AA106">
-        <v>0.98522037572241172</v>
+        <v>0.92007975165213307</v>
       </c>
       <c r="AB106">
-        <v>270.9597784224527</v>
+        <v>1465.2045530442279</v>
       </c>
       <c r="AD106" t="s">
         <v>445</v>
@@ -20701,10 +20701,10 @@
         <v>646</v>
       </c>
       <c r="AO106">
-        <v>0.9922959111510915</v>
+        <v>0.99073782529254428</v>
       </c>
       <c r="AP106">
-        <v>141.24162889665487</v>
+        <v>169.80653630335468</v>
       </c>
     </row>
     <row r="107" spans="2:42">
@@ -20739,7 +20739,7 @@
         <v>14.413610775537448</v>
       </c>
       <c r="M107">
-        <v>0.18222347611153561</v>
+        <v>0.16368090894115184</v>
       </c>
       <c r="O107" t="s">
         <v>445</v>
@@ -20769,16 +20769,16 @@
         <v>640</v>
       </c>
       <c r="Y107" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="Z107" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="AA107">
-        <v>0.98831913038449382</v>
+        <v>0.96305263459297863</v>
       </c>
       <c r="AB107">
-        <v>214.14927628428001</v>
+        <v>677.36836579539192</v>
       </c>
       <c r="AD107" t="s">
         <v>445</v>
@@ -20808,13 +20808,13 @@
         <v>980</v>
       </c>
       <c r="AN107" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AO107">
-        <v>0.97817316280665345</v>
+        <v>0.95849712823420175</v>
       </c>
       <c r="AP107">
-        <v>400.1586818780205</v>
+        <v>760.8859823729681</v>
       </c>
     </row>
   </sheetData>
@@ -20823,7 +20823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4495B621-0B6B-4F8E-BB87-2D4FC5408B66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C9A0EE-BE86-4DF3-A9CD-60C5C3A48CB4}">
   <dimension ref="B9:Z107"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20935,7 +20935,7 @@
         <v>1137</v>
       </c>
       <c r="K11" t="s">
-        <v>918</v>
+        <v>955</v>
       </c>
       <c r="L11">
         <v>0.39861308799262429</v>
@@ -20968,7 +20968,7 @@
         <v>1331</v>
       </c>
       <c r="X11" t="s">
-        <v>1121</v>
+        <v>1104</v>
       </c>
       <c r="Y11">
         <v>17.855250000000002</v>
@@ -21003,7 +21003,7 @@
         <v>1139</v>
       </c>
       <c r="K12" t="s">
-        <v>965</v>
+        <v>904</v>
       </c>
       <c r="L12">
         <v>8.3490819570661809</v>
@@ -21036,7 +21036,7 @@
         <v>1333</v>
       </c>
       <c r="X12" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="Y12">
         <v>22.539750000000002</v>
@@ -21071,7 +21071,7 @@
         <v>1141</v>
       </c>
       <c r="K13" t="s">
-        <v>954</v>
+        <v>884</v>
       </c>
       <c r="L13">
         <v>1.7523004426694913</v>
@@ -21104,7 +21104,7 @@
         <v>1335</v>
       </c>
       <c r="X13" t="s">
-        <v>1104</v>
+        <v>1090</v>
       </c>
       <c r="Y13">
         <v>56.926499999999997</v>
@@ -21139,7 +21139,7 @@
         <v>1143</v>
       </c>
       <c r="K14" t="s">
-        <v>942</v>
+        <v>920</v>
       </c>
       <c r="L14">
         <v>0.54907652770071036</v>
@@ -21172,7 +21172,7 @@
         <v>1337</v>
       </c>
       <c r="X14" t="s">
-        <v>1118</v>
+        <v>1129</v>
       </c>
       <c r="Y14">
         <v>75.277500000000003</v>
@@ -21207,7 +21207,7 @@
         <v>1145</v>
       </c>
       <c r="K15" t="s">
-        <v>966</v>
+        <v>905</v>
       </c>
       <c r="L15">
         <v>1.7694633654502361</v>
@@ -21240,7 +21240,7 @@
         <v>1339</v>
       </c>
       <c r="X15" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="Y15">
         <v>57.183750000000003</v>
@@ -21275,7 +21275,7 @@
         <v>1147</v>
       </c>
       <c r="K16" t="s">
-        <v>898</v>
+        <v>947</v>
       </c>
       <c r="L16">
         <v>3.6705701703872231</v>
@@ -21308,7 +21308,7 @@
         <v>1341</v>
       </c>
       <c r="X16" t="s">
-        <v>1089</v>
+        <v>1107</v>
       </c>
       <c r="Y16">
         <v>25.457249999999998</v>
@@ -21343,7 +21343,7 @@
         <v>1149</v>
       </c>
       <c r="K17" t="s">
-        <v>943</v>
+        <v>921</v>
       </c>
       <c r="L17">
         <v>17.939739935619471</v>
@@ -21376,7 +21376,7 @@
         <v>1343</v>
       </c>
       <c r="X17" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="Y17">
         <v>7.21875</v>
@@ -21411,7 +21411,7 @@
         <v>1151</v>
       </c>
       <c r="K18" t="s">
-        <v>911</v>
+        <v>934</v>
       </c>
       <c r="L18">
         <v>5.003019932086108</v>
@@ -21444,7 +21444,7 @@
         <v>1345</v>
       </c>
       <c r="X18" t="s">
-        <v>1129</v>
+        <v>1092</v>
       </c>
       <c r="Y18">
         <v>24.305250000000001</v>
@@ -21479,7 +21479,7 @@
         <v>1153</v>
       </c>
       <c r="K19" t="s">
-        <v>944</v>
+        <v>922</v>
       </c>
       <c r="L19">
         <v>2.5007371543803476</v>
@@ -21512,7 +21512,7 @@
         <v>1347</v>
       </c>
       <c r="X19" t="s">
-        <v>1130</v>
+        <v>1093</v>
       </c>
       <c r="Y19">
         <v>7.2749999999999995E-2</v>
@@ -21547,7 +21547,7 @@
         <v>1155</v>
       </c>
       <c r="K20" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="L20">
         <v>43.778801628691184</v>
@@ -21580,7 +21580,7 @@
         <v>1349</v>
       </c>
       <c r="X20" t="s">
-        <v>1109</v>
+        <v>1124</v>
       </c>
       <c r="Y20">
         <v>128.96625</v>
@@ -21615,7 +21615,7 @@
         <v>1157</v>
       </c>
       <c r="K21" t="s">
-        <v>976</v>
+        <v>893</v>
       </c>
       <c r="L21">
         <v>16.67304758176029</v>
@@ -21648,7 +21648,7 @@
         <v>1351</v>
       </c>
       <c r="X21" t="s">
-        <v>1119</v>
+        <v>1130</v>
       </c>
       <c r="Y21">
         <v>12.42675</v>
@@ -21683,7 +21683,7 @@
         <v>1159</v>
       </c>
       <c r="K22" t="s">
-        <v>912</v>
+        <v>935</v>
       </c>
       <c r="L22">
         <v>27.668458564541282</v>
@@ -21716,7 +21716,7 @@
         <v>1353</v>
       </c>
       <c r="X22" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="Y22">
         <v>78.813749999999999</v>
@@ -21751,7 +21751,7 @@
         <v>1161</v>
       </c>
       <c r="K23" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="L23">
         <v>11.433145121744985</v>
@@ -21784,7 +21784,7 @@
         <v>1355</v>
       </c>
       <c r="X23" t="s">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="Y23">
         <v>50.749499999999998</v>
@@ -21819,7 +21819,7 @@
         <v>1163</v>
       </c>
       <c r="K24" t="s">
-        <v>919</v>
+        <v>956</v>
       </c>
       <c r="L24">
         <v>28.004210804186364</v>
@@ -21852,7 +21852,7 @@
         <v>1357</v>
       </c>
       <c r="X24" t="s">
-        <v>1085</v>
+        <v>1116</v>
       </c>
       <c r="Y24">
         <v>46.347749999999998</v>
@@ -21887,7 +21887,7 @@
         <v>1165</v>
       </c>
       <c r="K25" t="s">
-        <v>967</v>
+        <v>906</v>
       </c>
       <c r="L25">
         <v>16.229942669977177</v>
@@ -21920,7 +21920,7 @@
         <v>1359</v>
       </c>
       <c r="X25" t="s">
-        <v>1114</v>
+        <v>1088</v>
       </c>
       <c r="Y25">
         <v>66.771000000000001</v>
@@ -21955,7 +21955,7 @@
         <v>1167</v>
       </c>
       <c r="K26" t="s">
-        <v>920</v>
+        <v>957</v>
       </c>
       <c r="L26">
         <v>27.944981415457875</v>
@@ -21988,7 +21988,7 @@
         <v>1361</v>
       </c>
       <c r="X26" t="s">
-        <v>1131</v>
+        <v>1094</v>
       </c>
       <c r="Y26">
         <v>97.8</v>
@@ -22023,7 +22023,7 @@
         <v>1169</v>
       </c>
       <c r="K27" t="s">
-        <v>945</v>
+        <v>923</v>
       </c>
       <c r="L27">
         <v>1.5549175890365936</v>
@@ -22056,7 +22056,7 @@
         <v>1363</v>
       </c>
       <c r="X27" t="s">
-        <v>1101</v>
+        <v>1085</v>
       </c>
       <c r="Y27">
         <v>107.74424999999999</v>
@@ -22091,7 +22091,7 @@
         <v>1171</v>
       </c>
       <c r="K28" t="s">
-        <v>913</v>
+        <v>936</v>
       </c>
       <c r="L28">
         <v>1.2492599133607241</v>
@@ -22124,7 +22124,7 @@
         <v>1365</v>
       </c>
       <c r="X28" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
       <c r="Y28">
         <v>51.907499999999999</v>
@@ -22159,7 +22159,7 @@
         <v>1173</v>
       </c>
       <c r="K29" t="s">
-        <v>946</v>
+        <v>924</v>
       </c>
       <c r="L29">
         <v>1.2638441295051945</v>
@@ -22192,7 +22192,7 @@
         <v>1367</v>
       </c>
       <c r="X29" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
       <c r="Y29">
         <v>82.251000000000005</v>
@@ -22227,7 +22227,7 @@
         <v>1175</v>
       </c>
       <c r="K30" t="s">
-        <v>906</v>
+        <v>888</v>
       </c>
       <c r="L30">
         <v>2.4084314808324492</v>
@@ -22260,7 +22260,7 @@
         <v>1369</v>
       </c>
       <c r="X30" t="s">
-        <v>1090</v>
+        <v>1108</v>
       </c>
       <c r="Y30">
         <v>24.861000000000001</v>
@@ -22295,7 +22295,7 @@
         <v>1177</v>
       </c>
       <c r="K31" t="s">
-        <v>892</v>
+        <v>941</v>
       </c>
       <c r="L31">
         <v>64.149379205736523</v>
@@ -22328,7 +22328,7 @@
         <v>1371</v>
       </c>
       <c r="X31" t="s">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="Y31">
         <v>24.351749999999999</v>
@@ -22363,7 +22363,7 @@
         <v>1179</v>
       </c>
       <c r="K32" t="s">
-        <v>893</v>
+        <v>942</v>
       </c>
       <c r="L32">
         <v>45.003988730231519</v>
@@ -22396,7 +22396,7 @@
         <v>1373</v>
       </c>
       <c r="X32" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="Y32">
         <v>92.853750000000005</v>
@@ -22431,7 +22431,7 @@
         <v>1181</v>
       </c>
       <c r="K33" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="L33">
         <v>2.4098384326025282</v>
@@ -22464,7 +22464,7 @@
         <v>1375</v>
       </c>
       <c r="X33" t="s">
-        <v>1115</v>
+        <v>1089</v>
       </c>
       <c r="Y33">
         <v>126.06825000000001</v>
@@ -22499,7 +22499,7 @@
         <v>1183</v>
       </c>
       <c r="K34" t="s">
-        <v>921</v>
+        <v>958</v>
       </c>
       <c r="L34">
         <v>7.719645967474376</v>
@@ -22532,7 +22532,7 @@
         <v>1377</v>
       </c>
       <c r="X34" t="s">
-        <v>1135</v>
+        <v>1112</v>
       </c>
       <c r="Y34">
         <v>39.077249999999999</v>
@@ -22567,7 +22567,7 @@
         <v>1185</v>
       </c>
       <c r="K35" t="s">
-        <v>884</v>
+        <v>915</v>
       </c>
       <c r="L35">
         <v>18.541668534317722</v>
@@ -22600,7 +22600,7 @@
         <v>1379</v>
       </c>
       <c r="X35" t="s">
-        <v>1120</v>
+        <v>1131</v>
       </c>
       <c r="Y35">
         <v>102.20099999999999</v>
@@ -22635,7 +22635,7 @@
         <v>1187</v>
       </c>
       <c r="K36" t="s">
-        <v>914</v>
+        <v>937</v>
       </c>
       <c r="L36">
         <v>1.1328532040703319</v>
@@ -22668,7 +22668,7 @@
         <v>1381</v>
       </c>
       <c r="X36" t="s">
-        <v>1091</v>
+        <v>1120</v>
       </c>
       <c r="Y36">
         <v>141.21299999999999</v>
@@ -22703,7 +22703,7 @@
         <v>1189</v>
       </c>
       <c r="K37" t="s">
-        <v>894</v>
+        <v>943</v>
       </c>
       <c r="L37">
         <v>0.98752306400324941</v>
@@ -22736,7 +22736,7 @@
         <v>1383</v>
       </c>
       <c r="X37" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="Y37">
         <v>431.52375000000001</v>
@@ -22771,7 +22771,7 @@
         <v>1191</v>
       </c>
       <c r="K38" t="s">
-        <v>929</v>
+        <v>970</v>
       </c>
       <c r="L38">
         <v>107.73017208627026</v>
@@ -22804,7 +22804,7 @@
         <v>1385</v>
       </c>
       <c r="X38" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="Y38">
         <v>137.21775</v>
@@ -22839,7 +22839,7 @@
         <v>1193</v>
       </c>
       <c r="K39" t="s">
-        <v>899</v>
+        <v>948</v>
       </c>
       <c r="L39">
         <v>144.23483288788916</v>
@@ -22872,7 +22872,7 @@
         <v>1387</v>
       </c>
       <c r="X39" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="Y39">
         <v>17.16225</v>
@@ -22907,7 +22907,7 @@
         <v>1195</v>
       </c>
       <c r="K40" t="s">
-        <v>915</v>
+        <v>938</v>
       </c>
       <c r="L40">
         <v>64.738650351652737</v>
@@ -22940,7 +22940,7 @@
         <v>1389</v>
       </c>
       <c r="X40" t="s">
-        <v>1136</v>
+        <v>1113</v>
       </c>
       <c r="Y40">
         <v>22.68825</v>
@@ -22975,7 +22975,7 @@
         <v>1197</v>
       </c>
       <c r="K41" t="s">
-        <v>907</v>
+        <v>889</v>
       </c>
       <c r="L41">
         <v>83.742151942949235</v>
@@ -23008,7 +23008,7 @@
         <v>1391</v>
       </c>
       <c r="X41" t="s">
-        <v>1111</v>
+        <v>1126</v>
       </c>
       <c r="Y41">
         <v>43.122</v>
@@ -23043,7 +23043,7 @@
         <v>1199</v>
       </c>
       <c r="K42" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="L42">
         <v>40.053209434418129</v>
@@ -23076,7 +23076,7 @@
         <v>1393</v>
       </c>
       <c r="X42" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="Y42">
         <v>63.436500000000002</v>
@@ -23111,7 +23111,7 @@
         <v>1201</v>
       </c>
       <c r="K43" t="s">
-        <v>895</v>
+        <v>944</v>
       </c>
       <c r="L43">
         <v>80.257558228094155</v>
@@ -23144,7 +23144,7 @@
         <v>1395</v>
       </c>
       <c r="X43" t="s">
-        <v>1092</v>
+        <v>1121</v>
       </c>
       <c r="Y43">
         <v>41.863500000000002</v>
@@ -23179,7 +23179,7 @@
         <v>1203</v>
       </c>
       <c r="K44" t="s">
-        <v>885</v>
+        <v>916</v>
       </c>
       <c r="L44">
         <v>108.98210875746523</v>
@@ -23212,7 +23212,7 @@
         <v>1397</v>
       </c>
       <c r="X44" t="s">
-        <v>1122</v>
+        <v>1105</v>
       </c>
       <c r="Y44">
         <v>122.985</v>
@@ -23247,7 +23247,7 @@
         <v>1205</v>
       </c>
       <c r="K45" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="L45">
         <v>76.485540774017224</v>
@@ -23280,7 +23280,7 @@
         <v>1399</v>
       </c>
       <c r="X45" t="s">
-        <v>1132</v>
+        <v>1095</v>
       </c>
       <c r="Y45">
         <v>41.619</v>
@@ -23315,7 +23315,7 @@
         <v>1207</v>
       </c>
       <c r="K46" t="s">
-        <v>977</v>
+        <v>894</v>
       </c>
       <c r="L46">
         <v>48.731974982686296</v>
@@ -23348,7 +23348,7 @@
         <v>1401</v>
       </c>
       <c r="X46" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="Y46">
         <v>4.2930000000000001</v>
@@ -23383,7 +23383,7 @@
         <v>1209</v>
       </c>
       <c r="K47" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="L47">
         <v>62.79159911093128</v>
@@ -23416,7 +23416,7 @@
         <v>1403</v>
       </c>
       <c r="X47" t="s">
-        <v>1133</v>
+        <v>1096</v>
       </c>
       <c r="Y47">
         <v>79.873500000000007</v>
@@ -23451,7 +23451,7 @@
         <v>1211</v>
       </c>
       <c r="K48" t="s">
-        <v>900</v>
+        <v>949</v>
       </c>
       <c r="L48">
         <v>65.680044471431955</v>
@@ -23484,7 +23484,7 @@
         <v>1405</v>
       </c>
       <c r="X48" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="Y48">
         <v>99.789000000000001</v>
@@ -23519,7 +23519,7 @@
         <v>1213</v>
       </c>
       <c r="K49" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="L49">
         <v>74.267839417946064</v>
@@ -23552,7 +23552,7 @@
         <v>1407</v>
       </c>
       <c r="X49" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="Y49">
         <v>104.292</v>
@@ -23587,7 +23587,7 @@
         <v>1215</v>
       </c>
       <c r="K50" t="s">
-        <v>947</v>
+        <v>925</v>
       </c>
       <c r="L50">
         <v>151.65467386640691</v>
@@ -23620,7 +23620,7 @@
         <v>1409</v>
       </c>
       <c r="X50" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="Y50">
         <v>18.36</v>
@@ -23655,7 +23655,7 @@
         <v>1217</v>
       </c>
       <c r="K51" t="s">
-        <v>901</v>
+        <v>950</v>
       </c>
       <c r="L51">
         <v>67.284600831515021</v>
@@ -23688,7 +23688,7 @@
         <v>1411</v>
       </c>
       <c r="X51" t="s">
-        <v>1134</v>
+        <v>1097</v>
       </c>
       <c r="Y51">
         <v>75.933000000000007</v>
@@ -23723,7 +23723,7 @@
         <v>1219</v>
       </c>
       <c r="K52" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="L52">
         <v>49.163937565783463</v>
@@ -23756,7 +23756,7 @@
         <v>1413</v>
       </c>
       <c r="X52" t="s">
-        <v>1093</v>
+        <v>1122</v>
       </c>
       <c r="Y52">
         <v>6.9997499999999997</v>
@@ -23791,7 +23791,7 @@
         <v>1221</v>
       </c>
       <c r="K53" t="s">
-        <v>968</v>
+        <v>907</v>
       </c>
       <c r="L53">
         <v>66.906827934341507</v>
@@ -23824,7 +23824,7 @@
         <v>1415</v>
       </c>
       <c r="X53" t="s">
-        <v>1105</v>
+        <v>1091</v>
       </c>
       <c r="Y53">
         <v>78.370500000000007</v>
@@ -23859,7 +23859,7 @@
         <v>1223</v>
       </c>
       <c r="K54" t="s">
-        <v>902</v>
+        <v>951</v>
       </c>
       <c r="L54">
         <v>88.093613990019378</v>
@@ -23892,7 +23892,7 @@
         <v>1417</v>
       </c>
       <c r="X54" t="s">
-        <v>1087</v>
+        <v>1118</v>
       </c>
       <c r="Y54">
         <v>33.83925</v>
@@ -23927,7 +23927,7 @@
         <v>1225</v>
       </c>
       <c r="K55" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="L55">
         <v>306.62374401608201</v>
@@ -23960,7 +23960,7 @@
         <v>1419</v>
       </c>
       <c r="X55" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="Y55">
         <v>32.840249999999997</v>
@@ -23995,7 +23995,7 @@
         <v>1227</v>
       </c>
       <c r="K56" t="s">
-        <v>950</v>
+        <v>977</v>
       </c>
       <c r="L56">
         <v>31.906406016589642</v>
@@ -24028,7 +24028,7 @@
         <v>1421</v>
       </c>
       <c r="X56" t="s">
-        <v>1123</v>
+        <v>1106</v>
       </c>
       <c r="Y56">
         <v>0.95399999999999996</v>
@@ -24063,7 +24063,7 @@
         <v>1229</v>
       </c>
       <c r="K57" t="s">
-        <v>958</v>
+        <v>901</v>
       </c>
       <c r="L57">
         <v>4.3112694152725819</v>
@@ -24096,7 +24096,7 @@
         <v>1423</v>
       </c>
       <c r="X57" t="s">
-        <v>1094</v>
+        <v>1123</v>
       </c>
       <c r="Y57">
         <v>58.96875</v>
@@ -24131,7 +24131,7 @@
         <v>1231</v>
       </c>
       <c r="K58" t="s">
-        <v>930</v>
+        <v>971</v>
       </c>
       <c r="L58">
         <v>22.439823618580242</v>
@@ -24164,7 +24164,7 @@
         <v>1425</v>
       </c>
       <c r="X58" t="s">
-        <v>1112</v>
+        <v>1127</v>
       </c>
       <c r="Y58">
         <v>276.46350000000001</v>
@@ -24199,7 +24199,7 @@
         <v>1233</v>
       </c>
       <c r="K59" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="L59">
         <v>2.950012771299138</v>
@@ -24232,7 +24232,7 @@
         <v>1427</v>
       </c>
       <c r="X59" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="Y59">
         <v>84.236999999999995</v>
@@ -24267,7 +24267,7 @@
         <v>1235</v>
       </c>
       <c r="K60" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="L60">
         <v>15.987623175380641</v>
@@ -24300,7 +24300,7 @@
         <v>1429</v>
       </c>
       <c r="X60" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="Y60">
         <v>101.8995</v>
@@ -24335,7 +24335,7 @@
         <v>1237</v>
       </c>
       <c r="K61" t="s">
-        <v>903</v>
+        <v>952</v>
       </c>
       <c r="L61">
         <v>0.92130801234283921</v>
@@ -24368,7 +24368,7 @@
         <v>1431</v>
       </c>
       <c r="X61" t="s">
-        <v>1088</v>
+        <v>1119</v>
       </c>
       <c r="Y61">
         <v>63.835500000000003</v>
@@ -24403,7 +24403,7 @@
         <v>1239</v>
       </c>
       <c r="K62" t="s">
-        <v>969</v>
+        <v>908</v>
       </c>
       <c r="L62">
         <v>3.3822749788348991</v>
@@ -24436,7 +24436,7 @@
         <v>1433</v>
       </c>
       <c r="X62" t="s">
-        <v>1113</v>
+        <v>1128</v>
       </c>
       <c r="Y62">
         <v>131.96250000000001</v>
@@ -24471,7 +24471,7 @@
         <v>1241</v>
       </c>
       <c r="K63" t="s">
-        <v>951</v>
+        <v>978</v>
       </c>
       <c r="L63">
         <v>4.9624795440731315</v>
@@ -24506,7 +24506,7 @@
         <v>1243</v>
       </c>
       <c r="K64" t="s">
-        <v>955</v>
+        <v>885</v>
       </c>
       <c r="L64">
         <v>5.8024432152518211</v>
@@ -24541,7 +24541,7 @@
         <v>1245</v>
       </c>
       <c r="K65" t="s">
-        <v>908</v>
+        <v>890</v>
       </c>
       <c r="L65">
         <v>30.040816717799608</v>
@@ -24576,7 +24576,7 @@
         <v>1247</v>
       </c>
       <c r="K66" t="s">
-        <v>931</v>
+        <v>972</v>
       </c>
       <c r="L66">
         <v>7.3613726419883463</v>
@@ -24611,7 +24611,7 @@
         <v>1249</v>
       </c>
       <c r="K67" t="s">
-        <v>886</v>
+        <v>917</v>
       </c>
       <c r="L67">
         <v>108.91929564165949</v>
@@ -24646,7 +24646,7 @@
         <v>1251</v>
       </c>
       <c r="K68" t="s">
-        <v>932</v>
+        <v>973</v>
       </c>
       <c r="L68">
         <v>0.15625630587072689</v>
@@ -24681,7 +24681,7 @@
         <v>1253</v>
       </c>
       <c r="K69" t="s">
-        <v>922</v>
+        <v>959</v>
       </c>
       <c r="L69">
         <v>3.3695122486871476</v>
@@ -24716,7 +24716,7 @@
         <v>1255</v>
       </c>
       <c r="K70" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="L70">
         <v>30.705835313620341</v>
@@ -24751,7 +24751,7 @@
         <v>1257</v>
       </c>
       <c r="K71" t="s">
-        <v>959</v>
+        <v>902</v>
       </c>
       <c r="L71">
         <v>64.074965136195061</v>
@@ -24786,7 +24786,7 @@
         <v>1259</v>
       </c>
       <c r="K72" t="s">
-        <v>923</v>
+        <v>960</v>
       </c>
       <c r="L72">
         <v>17.192803298674693</v>
@@ -24821,7 +24821,7 @@
         <v>1261</v>
       </c>
       <c r="K73" t="s">
-        <v>956</v>
+        <v>886</v>
       </c>
       <c r="L73">
         <v>17.258734519286374</v>
@@ -24856,7 +24856,7 @@
         <v>1263</v>
       </c>
       <c r="K74" t="s">
-        <v>960</v>
+        <v>903</v>
       </c>
       <c r="L74">
         <v>85.048994948775942</v>
@@ -24891,7 +24891,7 @@
         <v>1265</v>
       </c>
       <c r="K75" t="s">
-        <v>970</v>
+        <v>909</v>
       </c>
       <c r="L75">
         <v>66.793256267932875</v>
@@ -24926,7 +24926,7 @@
         <v>1267</v>
       </c>
       <c r="K76" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="L76">
         <v>79.890184200903121</v>
@@ -24961,7 +24961,7 @@
         <v>1269</v>
       </c>
       <c r="K77" t="s">
-        <v>904</v>
+        <v>953</v>
       </c>
       <c r="L77">
         <v>49.401067566974206</v>
@@ -24996,7 +24996,7 @@
         <v>1271</v>
       </c>
       <c r="K78" t="s">
-        <v>933</v>
+        <v>974</v>
       </c>
       <c r="L78">
         <v>42.327002358678541</v>
@@ -25031,7 +25031,7 @@
         <v>1273</v>
       </c>
       <c r="K79" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="L79">
         <v>106.28692550408161</v>
@@ -25066,7 +25066,7 @@
         <v>1275</v>
       </c>
       <c r="K80" t="s">
-        <v>924</v>
+        <v>961</v>
       </c>
       <c r="L80">
         <v>117.47590792766253</v>
@@ -25101,7 +25101,7 @@
         <v>1277</v>
       </c>
       <c r="K81" t="s">
-        <v>887</v>
+        <v>918</v>
       </c>
       <c r="L81">
         <v>30.349035200580289</v>
@@ -25136,7 +25136,7 @@
         <v>1279</v>
       </c>
       <c r="K82" t="s">
-        <v>896</v>
+        <v>945</v>
       </c>
       <c r="L82">
         <v>18.04196312682631</v>
@@ -25171,7 +25171,7 @@
         <v>1281</v>
       </c>
       <c r="K83" t="s">
-        <v>971</v>
+        <v>910</v>
       </c>
       <c r="L83">
         <v>143.70377172124182</v>
@@ -25206,7 +25206,7 @@
         <v>1283</v>
       </c>
       <c r="K84" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="L84">
         <v>4.5388067721428351</v>
@@ -25241,7 +25241,7 @@
         <v>1285</v>
       </c>
       <c r="K85" t="s">
-        <v>916</v>
+        <v>939</v>
       </c>
       <c r="L85">
         <v>61.7959751654546</v>
@@ -25276,7 +25276,7 @@
         <v>1287</v>
       </c>
       <c r="K86" t="s">
-        <v>952</v>
+        <v>979</v>
       </c>
       <c r="L86">
         <v>64.726898545060607</v>
@@ -25311,7 +25311,7 @@
         <v>1289</v>
       </c>
       <c r="K87" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="L87">
         <v>118.54300475235763</v>
@@ -25346,7 +25346,7 @@
         <v>1291</v>
       </c>
       <c r="K88" t="s">
-        <v>897</v>
+        <v>946</v>
       </c>
       <c r="L88">
         <v>40.618167251235064</v>
@@ -25381,7 +25381,7 @@
         <v>1293</v>
       </c>
       <c r="K89" t="s">
-        <v>925</v>
+        <v>962</v>
       </c>
       <c r="L89">
         <v>82.996246047592408</v>
@@ -25416,7 +25416,7 @@
         <v>1295</v>
       </c>
       <c r="K90" t="s">
-        <v>972</v>
+        <v>911</v>
       </c>
       <c r="L90">
         <v>0.46138952213474632</v>
@@ -25451,7 +25451,7 @@
         <v>1297</v>
       </c>
       <c r="K91" t="s">
-        <v>926</v>
+        <v>963</v>
       </c>
       <c r="L91">
         <v>0.76722131470466981</v>
@@ -25486,7 +25486,7 @@
         <v>1299</v>
       </c>
       <c r="K92" t="s">
-        <v>973</v>
+        <v>912</v>
       </c>
       <c r="L92">
         <v>0.69004106906673568</v>
@@ -25521,7 +25521,7 @@
         <v>1301</v>
       </c>
       <c r="K93" t="s">
-        <v>957</v>
+        <v>887</v>
       </c>
       <c r="L93">
         <v>10.04285289714629</v>
@@ -25556,7 +25556,7 @@
         <v>1303</v>
       </c>
       <c r="K94" t="s">
-        <v>974</v>
+        <v>913</v>
       </c>
       <c r="L94">
         <v>0.53797082245951966</v>
@@ -25591,7 +25591,7 @@
         <v>1305</v>
       </c>
       <c r="K95" t="s">
-        <v>917</v>
+        <v>940</v>
       </c>
       <c r="L95">
         <v>31.24013860747554</v>
@@ -25626,7 +25626,7 @@
         <v>1307</v>
       </c>
       <c r="K96" t="s">
-        <v>934</v>
+        <v>975</v>
       </c>
       <c r="L96">
         <v>182.81724421979371</v>
@@ -25661,7 +25661,7 @@
         <v>1309</v>
       </c>
       <c r="K97" t="s">
-        <v>978</v>
+        <v>895</v>
       </c>
       <c r="L97">
         <v>129.21574742491194</v>
@@ -25696,7 +25696,7 @@
         <v>1311</v>
       </c>
       <c r="K98" t="s">
-        <v>888</v>
+        <v>919</v>
       </c>
       <c r="L98">
         <v>0.3160884800353469</v>
@@ -25731,7 +25731,7 @@
         <v>1313</v>
       </c>
       <c r="K99" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="L99">
         <v>11.571846319988426</v>
@@ -25766,7 +25766,7 @@
         <v>1315</v>
       </c>
       <c r="K100" t="s">
-        <v>927</v>
+        <v>964</v>
       </c>
       <c r="L100">
         <v>66.237243466162568</v>
@@ -25801,7 +25801,7 @@
         <v>1317</v>
       </c>
       <c r="K101" t="s">
-        <v>928</v>
+        <v>965</v>
       </c>
       <c r="L101">
         <v>108.33634257446518</v>
@@ -25836,7 +25836,7 @@
         <v>1319</v>
       </c>
       <c r="K102" t="s">
-        <v>975</v>
+        <v>914</v>
       </c>
       <c r="L102">
         <v>112.56461877549133</v>
@@ -25871,7 +25871,7 @@
         <v>1321</v>
       </c>
       <c r="K103" t="s">
-        <v>905</v>
+        <v>954</v>
       </c>
       <c r="L103">
         <v>120.70970601071261</v>
@@ -25906,7 +25906,7 @@
         <v>1323</v>
       </c>
       <c r="K104" t="s">
-        <v>953</v>
+        <v>980</v>
       </c>
       <c r="L104">
         <v>33.829556694070689</v>
@@ -25941,7 +25941,7 @@
         <v>1325</v>
       </c>
       <c r="K105" t="s">
-        <v>948</v>
+        <v>926</v>
       </c>
       <c r="L105">
         <v>137.89166878057338</v>
@@ -25976,7 +25976,7 @@
         <v>1327</v>
       </c>
       <c r="K106" t="s">
-        <v>979</v>
+        <v>896</v>
       </c>
       <c r="L106">
         <v>7.7185621928607651</v>
@@ -26011,7 +26011,7 @@
         <v>1329</v>
       </c>
       <c r="K107" t="s">
-        <v>980</v>
+        <v>897</v>
       </c>
       <c r="L107">
         <v>13.260281925612457</v>
@@ -26026,7 +26026,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC43B81-D9A8-47D8-8477-A9CF03CDC2B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4326739E-7F36-4F90-88E5-183B1258C425}">
   <dimension ref="B9:Y136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEFCEAA-A050-4982-8663-5C52D3F15BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EF8B00-0838-4ECF-8F05-40794183EC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,18 +1403,72 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_AUS_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_AUS_011</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_AUS_049</t>
   </si>
   <si>
@@ -1427,6 +1481,492 @@
     <t>connecting solar to buses in cluster 78</t>
   </si>
   <si>
+    <t>distr_solelc_spv_AUS_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_AUS_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_AUS_012</t>
   </si>
   <si>
@@ -1451,688 +1991,370 @@
     <t>connecting solar to buses in cluster 97</t>
   </si>
   <si>
-    <t>distr_solelc_spv_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_AUS_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_SydneyWest_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS</t>
+  </si>
+  <si>
+    <t>e_Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>e_Para_AUS</t>
+  </si>
+  <si>
+    <t>e_OlympicDamWest_AUS</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>e_CalliopeRiver_AUS</t>
+  </si>
+  <si>
+    <t>e_WandoanSouth_AUS</t>
+  </si>
+  <si>
+    <t>e_AUS22p9S118p7E_AUS</t>
+  </si>
+  <si>
     <t>e_Robertstown_AUS</t>
   </si>
   <si>
-    <t>e_Chalumbin_AUS</t>
-  </si>
-  <si>
     <t>e_BrokenHill_AUS</t>
   </si>
   <si>
+    <t>e_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarong_AUS</t>
+  </si>
+  <si>
+    <t>e_GinGin_AUS</t>
+  </si>
+  <si>
+    <t>e_TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS</t>
+  </si>
+  <si>
+    <t>e_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>e_Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>e_Morawa_AUS</t>
+  </si>
+  <si>
+    <t>e_Balranald_AUS</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS</t>
+  </si>
+  <si>
+    <t>e_SouthMorang_AUS</t>
+  </si>
+  <si>
+    <t>e_Ballarat_AUS</t>
+  </si>
+  <si>
+    <t>e_Strathmore_AUS</t>
+  </si>
+  <si>
+    <t>e_Hazelwood_AUS</t>
+  </si>
+  <si>
+    <t>e_Wagga_AUS</t>
+  </si>
+  <si>
+    <t>e_Rowville_AUS</t>
+  </si>
+  <si>
+    <t>e_Yandin_AUS</t>
+  </si>
+  <si>
+    <t>e_CentralCoast_AUS</t>
+  </si>
+  <si>
+    <t>e_Perth_AUS</t>
+  </si>
+  <si>
+    <t>e_PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_UpperTumut_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS</t>
+  </si>
+  <si>
+    <t>e_Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>e_DarlingtonPoint_AUS</t>
+  </si>
+  <si>
+    <t>e_Canberra_AUS</t>
+  </si>
+  <si>
+    <t>e_Armidale_AUS</t>
+  </si>
+  <si>
+    <t>e_Merredin_AUS</t>
+  </si>
+  <si>
+    <t>e_Horsham_AUS</t>
+  </si>
+  <si>
+    <t>e_MountPiper_AUS</t>
+  </si>
+  <si>
+    <t>e_Murray_AUS</t>
+  </si>
+  <si>
+    <t>e_Calvale_AUS</t>
+  </si>
+  <si>
+    <t>e_BulliCreek_AUS</t>
+  </si>
+  <si>
+    <t>e_Sheffield_AUS</t>
+  </si>
+  <si>
     <t>e_Nebo_AUS</t>
   </si>
   <si>
-    <t>e_DarlingtonPoint_AUS</t>
-  </si>
-  <si>
-    <t>e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>e_Armidale_AUS</t>
-  </si>
-  <si>
-    <t>e_Merredin_AUS</t>
-  </si>
-  <si>
-    <t>e_Morawa_AUS</t>
-  </si>
-  <si>
-    <t>e_Horsham_AUS</t>
-  </si>
-  <si>
-    <t>e_SydneyWest_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS</t>
-  </si>
-  <si>
-    <t>e_Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>e_Para_AUS</t>
-  </si>
-  <si>
-    <t>e_OlympicDamWest_AUS</t>
-  </si>
-  <si>
-    <t>e_CalliopeRiver_AUS</t>
-  </si>
-  <si>
-    <t>e_WandoanSouth_AUS</t>
-  </si>
-  <si>
-    <t>e_AUS22p9S118p7E_AUS</t>
-  </si>
-  <si>
-    <t>e_SouthMorang_AUS</t>
-  </si>
-  <si>
-    <t>e_Ballarat_AUS</t>
-  </si>
-  <si>
-    <t>e_Strathmore_AUS</t>
-  </si>
-  <si>
-    <t>e_TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>e_Hazelwood_AUS</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS</t>
-  </si>
-  <si>
-    <t>e_Broadsound_AUS</t>
-  </si>
-  <si>
-    <t>e_Canberra_AUS</t>
-  </si>
-  <si>
-    <t>e_PortHedland_AUS</t>
-  </si>
-  <si>
-    <t>e_Balranald_AUS</t>
-  </si>
-  <si>
-    <t>e_Wagga_AUS</t>
-  </si>
-  <si>
-    <t>e_Rowville_AUS</t>
-  </si>
-  <si>
-    <t>e_Yandin_AUS</t>
-  </si>
-  <si>
-    <t>e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>e_Perth_AUS</t>
-  </si>
-  <si>
-    <t>e_Kingston_AUS</t>
-  </si>
-  <si>
-    <t>e_Australind_AUS</t>
-  </si>
-  <si>
-    <t>e_Ipswich_AUS</t>
-  </si>
-  <si>
-    <t>e_Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>e_Tarong_AUS</t>
-  </si>
-  <si>
-    <t>e_GinGin_AUS</t>
-  </si>
-  <si>
-    <t>e_Sheffield_AUS</t>
-  </si>
-  <si>
-    <t>e_Calvale_AUS</t>
-  </si>
-  <si>
-    <t>e_BulliCreek_AUS</t>
-  </si>
-  <si>
-    <t>e_MountPiper_AUS</t>
-  </si>
-  <si>
-    <t>e_Murray_AUS</t>
-  </si>
-  <si>
-    <t>e_UpperTumut_AUS</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS</t>
+    <t>distr_wonelc_won_AUS_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_093</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_086</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_073</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_080</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_082</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_084</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_092</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_072</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_078</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 78</t>
   </si>
   <si>
     <t>distr_wonelc_won_AUS_003</t>
@@ -2159,6 +2381,36 @@
     <t>connecting wind onshore to buses in cluster 83</t>
   </si>
   <si>
+    <t>distr_wonelc_won_AUS_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_071</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_088</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 88</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_AUS_020</t>
   </si>
   <si>
@@ -2219,136 +2471,46 @@
     <t>connecting wind onshore to buses in cluster 97</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_073</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_080</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_082</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_084</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_092</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_071</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_088</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 88</t>
+    <t>distr_wonelc_won_AUS_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_089</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 89</t>
   </si>
   <si>
     <t>distr_wonelc_won_AUS_004</t>
@@ -2393,46 +2555,124 @@
     <t>connecting wind onshore to buses in cluster 95</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_089</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 89</t>
+    <t>distr_wonelc_won_AUS_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_077</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_070</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_079</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_081</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_090</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_091</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_076</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_AUS_094</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 94</t>
   </si>
   <si>
     <t>distr_wonelc_won_AUS_008</t>
@@ -2477,244 +2717,115 @@
     <t>connecting wind onshore to buses in cluster 85</t>
   </si>
   <si>
-    <t>distr_wonelc_won_AUS_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_072</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_078</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_093</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_070</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_079</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_081</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_090</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_091</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_077</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_086</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_076</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_AUS_094</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 94</t>
+    <t>elc_won_AUS_006</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_029</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_038</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_041</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_044</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_051</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_067</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_093</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_023</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_042</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_045</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_028</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_048</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_056</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_058</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_068</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_086</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_047</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_061</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_064</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_002</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_005</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_015</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_043</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_052</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_065</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_073</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_080</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_082</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_084</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_092</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_021</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_022</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_027</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_033</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_072</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_078</t>
   </si>
   <si>
     <t>elc_won_AUS_003</t>
@@ -2729,6 +2840,21 @@
     <t>elc_won_AUS_083</t>
   </si>
   <si>
+    <t>elc_won_AUS_025</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_034</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_057</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_071</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_088</t>
+  </si>
+  <si>
     <t>elc_won_AUS_020</t>
   </si>
   <si>
@@ -2759,70 +2885,25 @@
     <t>elc_won_AUS_097</t>
   </si>
   <si>
-    <t>elc_won_AUS_023</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_042</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_045</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_047</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_061</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_064</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_002</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_005</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_015</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_043</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_052</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_065</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_073</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_080</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_082</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_084</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_092</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_025</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_034</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_057</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_071</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_088</t>
+    <t>elc_won_AUS_013</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_032</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_037</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_049</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_050</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_060</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_089</t>
   </si>
   <si>
     <t>elc_won_AUS_004</t>
@@ -2846,25 +2927,64 @@
     <t>elc_won_AUS_095</t>
   </si>
   <si>
-    <t>elc_won_AUS_013</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_032</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_037</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_049</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_050</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_060</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_089</t>
+    <t>elc_won_AUS_010</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_035</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_069</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_077</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_001</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_014</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_016</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_024</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_059</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_062</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_070</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_079</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_081</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_090</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_091</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_039</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_046</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_053</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_076</t>
+  </si>
+  <si>
+    <t>elc_won_AUS_094</t>
   </si>
   <si>
     <t>elc_won_AUS_008</t>
@@ -2888,124 +3008,244 @@
     <t>elc_won_AUS_085</t>
   </si>
   <si>
-    <t>elc_won_AUS_021</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_022</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_027</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_033</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_072</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_078</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_006</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_029</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_038</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_041</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_044</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_051</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_067</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_093</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_001</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_014</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_016</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_024</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_059</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_062</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_070</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_079</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_081</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_090</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_091</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_010</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_035</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_069</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_077</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_028</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_048</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_056</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_058</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_068</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_086</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_039</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_046</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_053</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_076</t>
-  </si>
-  <si>
-    <t>elc_won_AUS_094</t>
+    <t>distr_wofelc_wof_AUS_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_038</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_050</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_048</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_052</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_037</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_041</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_045</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_044</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_051</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_042</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_047</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_036</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_039</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_043</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 43</t>
   </si>
   <si>
     <t>distr_wofelc_wof_AUS_017</t>
@@ -3026,100 +3266,40 @@
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_043</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_037</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_041</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_036</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_039</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 39</t>
+    <t>distr_wofelc_wof_AUS_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_040</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_049</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_AUS_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
   </si>
   <si>
     <t>distr_wofelc_wof_AUS_001</t>
@@ -3140,184 +3320,124 @@
     <t>connecting wind offshore to buses in cluster 46</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_AUS_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_040</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_049</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_038</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_050</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_044</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_051</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_042</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_047</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_048</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_052</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_AUS_045</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 45</t>
+    <t>elc_wof_AUS_006</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_020</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_038</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_050</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_010</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_013</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_031</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_048</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_052</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_024</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_030</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_008</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_009</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_016</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_035</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_037</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_041</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_015</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_023</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_002</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_007</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_012</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_027</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_045</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_014</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_021</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_044</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_051</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_026</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_033</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_042</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_047</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_005</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_022</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_029</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_032</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_036</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_039</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_003</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_043</t>
   </si>
   <si>
     <t>elc_wof_AUS_017</t>
@@ -3329,52 +3449,22 @@
     <t>elc_wof_AUS_019</t>
   </si>
   <si>
-    <t>elc_wof_AUS_015</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_023</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_003</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_043</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_008</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_009</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_016</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_035</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_037</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_041</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_005</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_022</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_029</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_032</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_036</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_039</t>
+    <t>elc_wof_AUS_028</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_040</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_049</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_004</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_011</t>
+  </si>
+  <si>
+    <t>elc_wof_AUS_025</t>
   </si>
   <si>
     <t>elc_wof_AUS_001</t>
@@ -3384,96 +3474,6 @@
   </si>
   <si>
     <t>elc_wof_AUS_046</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_006</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_020</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_028</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_040</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_049</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_024</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_030</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_038</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_050</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_014</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_021</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_044</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_051</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_026</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_033</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_042</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_047</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_010</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_013</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_031</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_048</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_052</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_004</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_011</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_025</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_002</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_007</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_012</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_027</t>
-  </si>
-  <si>
-    <t>elc_wof_AUS_045</t>
   </si>
   <si>
     <t>e_won_AUS_001</t>
@@ -8099,7 +8099,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD2FB4D-97D0-4314-BA2E-908BF61EC8BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D817ABB-BD00-41FB-822D-3DFCCC51EE1A}">
   <dimension ref="B9:BD107"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8337,16 +8337,16 @@
         <v>446</v>
       </c>
       <c r="Y11" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="Z11" t="s">
         <v>644</v>
       </c>
       <c r="AA11">
-        <v>0.99240501837238893</v>
+        <v>0.99571254852817692</v>
       </c>
       <c r="AB11">
-        <v>139.24132983953538</v>
+        <v>78.60327698342283</v>
       </c>
       <c r="AD11" t="s">
         <v>445</v>
@@ -8376,13 +8376,13 @@
         <v>884</v>
       </c>
       <c r="AN11" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="AO11">
-        <v>0.98822008409109219</v>
+        <v>0.99570788786991582</v>
       </c>
       <c r="AP11">
-        <v>215.96512499664277</v>
+        <v>78.688722384876669</v>
       </c>
       <c r="AR11" t="s">
         <v>445</v>
@@ -8412,13 +8412,13 @@
         <v>1085</v>
       </c>
       <c r="BB11" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="BC11">
-        <v>0.98425930791162897</v>
+        <v>0.98870653772658501</v>
       </c>
       <c r="BD11">
-        <v>936.37409860998696</v>
+        <v>882.19201536443973</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8483,16 +8483,16 @@
         <v>450</v>
       </c>
       <c r="Y12" t="s">
-        <v>395</v>
+        <v>356</v>
       </c>
       <c r="Z12" t="s">
         <v>645</v>
       </c>
       <c r="AA12">
-        <v>0.9365516394102017</v>
+        <v>0.99165895214194211</v>
       </c>
       <c r="AB12">
-        <v>1163.2199441463022</v>
+        <v>152.91921073106212</v>
       </c>
       <c r="AD12" t="s">
         <v>445</v>
@@ -8522,13 +8522,13 @@
         <v>885</v>
       </c>
       <c r="AN12" t="s">
-        <v>689</v>
+        <v>648</v>
       </c>
       <c r="AO12">
-        <v>0.99332113976407466</v>
+        <v>0.98562252349041679</v>
       </c>
       <c r="AP12">
-        <v>122.44577099196496</v>
+        <v>263.58706934235943</v>
       </c>
       <c r="AR12" t="s">
         <v>445</v>
@@ -8558,13 +8558,13 @@
         <v>1086</v>
       </c>
       <c r="BB12" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="BC12">
-        <v>0.97983022896434013</v>
+        <v>0.9861533644012247</v>
       </c>
       <c r="BD12">
-        <v>990.33504378445582</v>
+        <v>913.29817704507911</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8599,7 +8599,7 @@
         <v>1.1750156806043059</v>
       </c>
       <c r="M13">
-        <v>0.16457070870590459</v>
+        <v>0.16462296658146586</v>
       </c>
       <c r="O13" t="s">
         <v>445</v>
@@ -8629,16 +8629,16 @@
         <v>452</v>
       </c>
       <c r="Y13" t="s">
-        <v>424</v>
+        <v>365</v>
       </c>
       <c r="Z13" t="s">
         <v>646</v>
       </c>
       <c r="AA13">
-        <v>0.97527660765685298</v>
+        <v>0.99664889239239962</v>
       </c>
       <c r="AB13">
-        <v>453.26219295769499</v>
+        <v>61.436972806007184</v>
       </c>
       <c r="AD13" t="s">
         <v>445</v>
@@ -8668,13 +8668,13 @@
         <v>886</v>
       </c>
       <c r="AN13" t="s">
-        <v>667</v>
+        <v>648</v>
       </c>
       <c r="AO13">
-        <v>0.99451359177835219</v>
+        <v>0.94920173100235461</v>
       </c>
       <c r="AP13">
-        <v>100.58415073020944</v>
+        <v>931.3015982901652</v>
       </c>
       <c r="AR13" t="s">
         <v>445</v>
@@ -8704,13 +8704,13 @@
         <v>1087</v>
       </c>
       <c r="BB13" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="BC13">
-        <v>0.98532695715711582</v>
+        <v>0.98962892741174779</v>
       </c>
       <c r="BD13">
-        <v>923.36657196913927</v>
+        <v>870.9542343668727</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8775,16 +8775,16 @@
         <v>454</v>
       </c>
       <c r="Y14" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="Z14" t="s">
         <v>647</v>
       </c>
       <c r="AA14">
-        <v>0.97630367280108865</v>
+        <v>0.99092130604056927</v>
       </c>
       <c r="AB14">
-        <v>434.43266531337389</v>
+        <v>166.44272258956366</v>
       </c>
       <c r="AD14" t="s">
         <v>445</v>
@@ -8814,13 +8814,13 @@
         <v>887</v>
       </c>
       <c r="AN14" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="AO14">
-        <v>0.9909682810714957</v>
+        <v>0.94099051948143053</v>
       </c>
       <c r="AP14">
-        <v>165.58151368924484</v>
+        <v>1081.8404761737738</v>
       </c>
       <c r="AR14" t="s">
         <v>445</v>
@@ -8850,13 +8850,13 @@
         <v>1088</v>
       </c>
       <c r="BB14" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="BC14">
-        <v>0.9827191942014929</v>
+        <v>0.93242166156261008</v>
       </c>
       <c r="BD14">
-        <v>955.13781731181223</v>
+        <v>1567.9294232955338</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8921,16 +8921,16 @@
         <v>456</v>
       </c>
       <c r="Y15" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="Z15" t="s">
         <v>648</v>
       </c>
       <c r="AA15">
-        <v>0.978447054607678</v>
+        <v>0.95611998680969301</v>
       </c>
       <c r="AB15">
-        <v>395.13733219256937</v>
+        <v>804.46690848896196</v>
       </c>
       <c r="AD15" t="s">
         <v>445</v>
@@ -8960,13 +8960,13 @@
         <v>888</v>
       </c>
       <c r="AN15" t="s">
-        <v>682</v>
+        <v>648</v>
       </c>
       <c r="AO15">
-        <v>0.99537175847221593</v>
+        <v>0.97163156886146174</v>
       </c>
       <c r="AP15">
-        <v>84.85109467604083</v>
+        <v>520.0879042065344</v>
       </c>
       <c r="AR15" t="s">
         <v>445</v>
@@ -8996,13 +8996,13 @@
         <v>1089</v>
       </c>
       <c r="BB15" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="BC15">
-        <v>0.95475709315784774</v>
+        <v>0.97093554889152922</v>
       </c>
       <c r="BD15">
-        <v>1295.8094150268885</v>
+        <v>1098.7018960048697</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9037,7 +9037,7 @@
         <v>4.567467906283377</v>
       </c>
       <c r="M16">
-        <v>0.18892535432905502</v>
+        <v>0.1889506066384119</v>
       </c>
       <c r="O16" t="s">
         <v>445</v>
@@ -9067,16 +9067,16 @@
         <v>458</v>
       </c>
       <c r="Y16" t="s">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="Z16" t="s">
         <v>649</v>
       </c>
       <c r="AA16">
-        <v>0.96307923215762514</v>
+        <v>0.99055684074965455</v>
       </c>
       <c r="AB16">
-        <v>676.88074377687337</v>
+        <v>173.12458625633352</v>
       </c>
       <c r="AD16" t="s">
         <v>445</v>
@@ -9106,13 +9106,13 @@
         <v>889</v>
       </c>
       <c r="AN16" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="AO16">
-        <v>0.95891375083366426</v>
+        <v>0.99407790982046917</v>
       </c>
       <c r="AP16">
-        <v>753.24790138282128</v>
+        <v>108.57165329139941</v>
       </c>
       <c r="AR16" t="s">
         <v>445</v>
@@ -9142,13 +9142,13 @@
         <v>1090</v>
       </c>
       <c r="BB16" t="s">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="BC16">
-        <v>0.98683737688914319</v>
+        <v>0.98986511819476719</v>
       </c>
       <c r="BD16">
-        <v>904.96462490060583</v>
+        <v>868.07664332708646</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9183,7 +9183,7 @@
         <v>21.201348678928575</v>
       </c>
       <c r="M17">
-        <v>0.19364518490898483</v>
+        <v>0.19367218184274765</v>
       </c>
       <c r="O17" t="s">
         <v>445</v>
@@ -9213,16 +9213,16 @@
         <v>460</v>
       </c>
       <c r="Y17" t="s">
-        <v>443</v>
+        <v>404</v>
       </c>
       <c r="Z17" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AA17">
-        <v>0.9793351210469925</v>
+        <v>0.99723631056718209</v>
       </c>
       <c r="AB17">
-        <v>378.85611413846999</v>
+        <v>50.667639601661186</v>
       </c>
       <c r="AD17" t="s">
         <v>445</v>
@@ -9252,13 +9252,13 @@
         <v>890</v>
       </c>
       <c r="AN17" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="AO17">
-        <v>0.97364425413724487</v>
+        <v>0.97471651986393804</v>
       </c>
       <c r="AP17">
-        <v>483.18867415051142</v>
+        <v>463.53046916113516</v>
       </c>
       <c r="AR17" t="s">
         <v>445</v>
@@ -9288,13 +9288,13 @@
         <v>1091</v>
       </c>
       <c r="BB17" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="BC17">
-        <v>0.98183502015800017</v>
+        <v>0.99159294969939915</v>
       </c>
       <c r="BD17">
-        <v>965.91000440836387</v>
+        <v>786.86745907813679</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9359,16 +9359,16 @@
         <v>462</v>
       </c>
       <c r="Y18" t="s">
-        <v>354</v>
+        <v>406</v>
       </c>
       <c r="Z18" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AA18">
-        <v>0.99059066767492976</v>
+        <v>0.96929197405517931</v>
       </c>
       <c r="AB18">
-        <v>172.50442595962087</v>
+        <v>562.98047565504703</v>
       </c>
       <c r="AD18" t="s">
         <v>445</v>
@@ -9398,13 +9398,13 @@
         <v>891</v>
       </c>
       <c r="AN18" t="s">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="AO18">
-        <v>0.95472325192752561</v>
+        <v>0.95301935344113697</v>
       </c>
       <c r="AP18">
-        <v>830.07371466203085</v>
+        <v>861.31185357915479</v>
       </c>
       <c r="AR18" t="s">
         <v>445</v>
@@ -9434,13 +9434,13 @@
         <v>1092</v>
       </c>
       <c r="BB18" t="s">
-        <v>650</v>
+        <v>674</v>
       </c>
       <c r="BC18">
-        <v>0.98460725799374227</v>
+        <v>0.98080906590233208</v>
       </c>
       <c r="BD18">
-        <v>932.13490677623929</v>
+        <v>978.40954708992126</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9475,7 +9475,7 @@
         <v>1.3432633560097478</v>
       </c>
       <c r="M19">
-        <v>0.18041783498245925</v>
+        <v>0.18044251864115426</v>
       </c>
       <c r="O19" t="s">
         <v>445</v>
@@ -9505,16 +9505,16 @@
         <v>464</v>
       </c>
       <c r="Y19" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="Z19" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="AA19">
-        <v>0.95570380597210192</v>
+        <v>0.98417563223370064</v>
       </c>
       <c r="AB19">
-        <v>812.09689051146574</v>
+        <v>290.11340904882155</v>
       </c>
       <c r="AD19" t="s">
         <v>445</v>
@@ -9547,10 +9547,10 @@
         <v>669</v>
       </c>
       <c r="AO19">
-        <v>0.99476921667660834</v>
+        <v>0.99339062123477628</v>
       </c>
       <c r="AP19">
-        <v>95.897694262180153</v>
+        <v>121.17194402910137</v>
       </c>
       <c r="AR19" t="s">
         <v>445</v>
@@ -9580,13 +9580,13 @@
         <v>1093</v>
       </c>
       <c r="BB19" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="BC19">
-        <v>0.99676099935070339</v>
+        <v>0.9611655354348162</v>
       </c>
       <c r="BD19">
-        <v>458.86857454202811</v>
+        <v>1217.7332266191565</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9621,7 +9621,7 @@
         <v>37.91472233272016</v>
       </c>
       <c r="M20">
-        <v>0.1941466361615807</v>
+        <v>0.19416770297649735</v>
       </c>
       <c r="O20" t="s">
         <v>445</v>
@@ -9651,16 +9651,16 @@
         <v>466</v>
       </c>
       <c r="Y20" t="s">
-        <v>398</v>
+        <v>357</v>
       </c>
       <c r="Z20" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AA20">
-        <v>0.98883273909819114</v>
+        <v>0.99240501837238893</v>
       </c>
       <c r="AB20">
-        <v>204.7331165331625</v>
+        <v>139.24132983953538</v>
       </c>
       <c r="AD20" t="s">
         <v>445</v>
@@ -9690,13 +9690,13 @@
         <v>893</v>
       </c>
       <c r="AN20" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="AO20">
-        <v>0.99223838421520194</v>
+        <v>0.9495926116188812</v>
       </c>
       <c r="AP20">
-        <v>142.29628938796495</v>
+        <v>924.13545365384425</v>
       </c>
       <c r="AR20" t="s">
         <v>445</v>
@@ -9726,13 +9726,13 @@
         <v>1094</v>
       </c>
       <c r="BB20" t="s">
-        <v>664</v>
+        <v>649</v>
       </c>
       <c r="BC20">
-        <v>0.96948890259934162</v>
+        <v>0.95200980188478979</v>
       </c>
       <c r="BD20">
-        <v>1116.3268699980208</v>
+        <v>1329.2805803703113</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9767,7 +9767,7 @@
         <v>14.905025922100801</v>
       </c>
       <c r="M21">
-        <v>0.19148308989241797</v>
+        <v>0.19148842363104948</v>
       </c>
       <c r="O21" t="s">
         <v>445</v>
@@ -9797,16 +9797,16 @@
         <v>468</v>
       </c>
       <c r="Y21" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="Z21" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="AA21">
-        <v>0.98262913774151028</v>
+        <v>0.9365516394102017</v>
       </c>
       <c r="AB21">
-        <v>318.46580807231078</v>
+        <v>1163.2199441463022</v>
       </c>
       <c r="AD21" t="s">
         <v>445</v>
@@ -9836,13 +9836,13 @@
         <v>894</v>
       </c>
       <c r="AN21" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="AO21">
-        <v>0.93136449657406906</v>
+        <v>0.95120262528231503</v>
       </c>
       <c r="AP21">
-        <v>1258.3175628087345</v>
+        <v>894.61853649089164</v>
       </c>
       <c r="AR21" t="s">
         <v>445</v>
@@ -9872,13 +9872,13 @@
         <v>1095</v>
       </c>
       <c r="BB21" t="s">
-        <v>659</v>
+        <v>682</v>
       </c>
       <c r="BC21">
-        <v>0.97338301712868025</v>
+        <v>0.97707982144598671</v>
       </c>
       <c r="BD21">
-        <v>1068.8835746489126</v>
+        <v>1023.8441753830622</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9913,7 +9913,7 @@
         <v>28.062880038419888</v>
       </c>
       <c r="M22">
-        <v>0.19897541486325493</v>
+        <v>0.19902760240198669</v>
       </c>
       <c r="O22" t="s">
         <v>445</v>
@@ -9943,16 +9943,16 @@
         <v>470</v>
       </c>
       <c r="Y22" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="Z22" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AA22">
-        <v>0.99090558233812054</v>
+        <v>0.97527660765685298</v>
       </c>
       <c r="AB22">
-        <v>166.73099046779075</v>
+        <v>453.26219295769499</v>
       </c>
       <c r="AD22" t="s">
         <v>445</v>
@@ -9982,13 +9982,13 @@
         <v>895</v>
       </c>
       <c r="AN22" t="s">
-        <v>670</v>
+        <v>648</v>
       </c>
       <c r="AO22">
-        <v>0.9340182520227388</v>
+        <v>0.98407466378375608</v>
       </c>
       <c r="AP22">
-        <v>1209.6653795831226</v>
+        <v>291.96449729780619</v>
       </c>
       <c r="AR22" t="s">
         <v>445</v>
@@ -10018,13 +10018,13 @@
         <v>1096</v>
       </c>
       <c r="BB22" t="s">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="BC22">
-        <v>0.98973750247525893</v>
+        <v>0.98460725799374227</v>
       </c>
       <c r="BD22">
-        <v>869.63142817642859</v>
+        <v>932.13490677623929</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10089,16 +10089,16 @@
         <v>472</v>
       </c>
       <c r="Y23" t="s">
-        <v>440</v>
+        <v>379</v>
       </c>
       <c r="Z23" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AA23">
-        <v>0.99144634427862732</v>
+        <v>0.95936298088609862</v>
       </c>
       <c r="AB23">
-        <v>156.81702155849862</v>
+        <v>745.01201708819133</v>
       </c>
       <c r="AD23" t="s">
         <v>445</v>
@@ -10131,10 +10131,10 @@
         <v>649</v>
       </c>
       <c r="AO23">
-        <v>0.9922959111510915</v>
+        <v>0.9542882304111121</v>
       </c>
       <c r="AP23">
-        <v>141.24162889665487</v>
+        <v>838.04910912961134</v>
       </c>
       <c r="AR23" t="s">
         <v>445</v>
@@ -10164,13 +10164,13 @@
         <v>1097</v>
       </c>
       <c r="BB23" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="BC23">
-        <v>0.96515942387218789</v>
+        <v>0.99676099935070339</v>
       </c>
       <c r="BD23">
-        <v>1169.0743524905106</v>
+        <v>458.86857454202811</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10235,16 +10235,16 @@
         <v>474</v>
       </c>
       <c r="Y24" t="s">
-        <v>347</v>
+        <v>430</v>
       </c>
       <c r="Z24" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AA24">
-        <v>0.99571254852817692</v>
+        <v>0.9970088962341721</v>
       </c>
       <c r="AB24">
-        <v>78.60327698342283</v>
+        <v>54.836902373510455</v>
       </c>
       <c r="AD24" t="s">
         <v>445</v>
@@ -10274,13 +10274,13 @@
         <v>897</v>
       </c>
       <c r="AN24" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="AO24">
-        <v>0.97817316280665345</v>
+        <v>0.99582108489984233</v>
       </c>
       <c r="AP24">
-        <v>400.1586818780205</v>
+        <v>76.613443502890505</v>
       </c>
       <c r="AR24" t="s">
         <v>445</v>
@@ -10310,13 +10310,13 @@
         <v>1098</v>
       </c>
       <c r="BB24" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="BC24">
-        <v>0.98624400907289522</v>
+        <v>0.96948890259934162</v>
       </c>
       <c r="BD24">
-        <v>912.19382279522597</v>
+        <v>1116.3268699980208</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10351,7 +10351,7 @@
         <v>22.160141399950017</v>
       </c>
       <c r="M25">
-        <v>0.19344088149831118</v>
+        <v>0.19345254486659699</v>
       </c>
       <c r="O25" t="s">
         <v>445</v>
@@ -10381,16 +10381,16 @@
         <v>476</v>
       </c>
       <c r="Y25" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="Z25" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AA25">
-        <v>0.99165895214194211</v>
+        <v>0.99459695303037288</v>
       </c>
       <c r="AB25">
-        <v>152.91921073106212</v>
+        <v>99.055861109831142</v>
       </c>
       <c r="AD25" t="s">
         <v>445</v>
@@ -10420,13 +10420,13 @@
         <v>898</v>
       </c>
       <c r="AN25" t="s">
-        <v>672</v>
+        <v>650</v>
       </c>
       <c r="AO25">
-        <v>0.99339062123477628</v>
+        <v>0.99800187122714112</v>
       </c>
       <c r="AP25">
-        <v>121.17194402910137</v>
+        <v>36.632360835745096</v>
       </c>
       <c r="AR25" t="s">
         <v>445</v>
@@ -10456,13 +10456,13 @@
         <v>1099</v>
       </c>
       <c r="BB25" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="BC25">
-        <v>0.96572704859346925</v>
+        <v>0.97338301712868025</v>
       </c>
       <c r="BD25">
-        <v>1162.1587913028991</v>
+        <v>1068.8835746489126</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10527,16 +10527,16 @@
         <v>478</v>
       </c>
       <c r="Y26" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Z26" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AA26">
-        <v>0.99664889239239962</v>
+        <v>0.99519268990415388</v>
       </c>
       <c r="AB26">
-        <v>61.436972806007184</v>
+        <v>88.134018423846243</v>
       </c>
       <c r="AD26" t="s">
         <v>445</v>
@@ -10566,13 +10566,13 @@
         <v>899</v>
       </c>
       <c r="AN26" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="AO26">
-        <v>0.9495926116188812</v>
+        <v>0.98958136888311932</v>
       </c>
       <c r="AP26">
-        <v>924.13545365384425</v>
+        <v>191.00823714281216</v>
       </c>
       <c r="AR26" t="s">
         <v>445</v>
@@ -10602,13 +10602,13 @@
         <v>1100</v>
       </c>
       <c r="BB26" t="s">
-        <v>688</v>
+        <v>668</v>
       </c>
       <c r="BC26">
-        <v>0.98481153677494815</v>
+        <v>0.98973750247525893</v>
       </c>
       <c r="BD26">
-        <v>929.64611029188166</v>
+        <v>869.63142817642859</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10673,16 +10673,16 @@
         <v>480</v>
       </c>
       <c r="Y27" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="Z27" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AA27">
-        <v>0.99092130604056927</v>
+        <v>0.98376991098916067</v>
       </c>
       <c r="AB27">
-        <v>166.44272258956366</v>
+        <v>297.55163186538817</v>
       </c>
       <c r="AD27" t="s">
         <v>445</v>
@@ -10712,13 +10712,13 @@
         <v>900</v>
       </c>
       <c r="AN27" t="s">
-        <v>645</v>
+        <v>674</v>
       </c>
       <c r="AO27">
-        <v>0.95120262528231503</v>
+        <v>0.97298156476333331</v>
       </c>
       <c r="AP27">
-        <v>894.61853649089164</v>
+        <v>495.337979338889</v>
       </c>
       <c r="AR27" t="s">
         <v>445</v>
@@ -10748,13 +10748,13 @@
         <v>1101</v>
       </c>
       <c r="BB27" t="s">
-        <v>689</v>
+        <v>662</v>
       </c>
       <c r="BC27">
-        <v>0.99067149991228087</v>
+        <v>0.96515942387218789</v>
       </c>
       <c r="BD27">
-        <v>845.34880556723965</v>
+        <v>1169.0743524905106</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10819,16 +10819,16 @@
         <v>482</v>
       </c>
       <c r="Y28" t="s">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="Z28" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="AA28">
-        <v>0.95611998680969301</v>
+        <v>0.99221414970221189</v>
       </c>
       <c r="AB28">
-        <v>804.46690848896196</v>
+        <v>142.74058879278186</v>
       </c>
       <c r="AD28" t="s">
         <v>445</v>
@@ -10858,7 +10858,7 @@
         <v>901</v>
       </c>
       <c r="AN28" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="AO28">
         <v>0.97689731236523503</v>
@@ -10894,13 +10894,13 @@
         <v>1102</v>
       </c>
       <c r="BB28" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="BC28">
-        <v>0.99113893512004347</v>
+        <v>0.9827191942014929</v>
       </c>
       <c r="BD28">
-        <v>815.68225104790747</v>
+        <v>955.13781731181223</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10965,16 +10965,16 @@
         <v>484</v>
       </c>
       <c r="Y29" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="Z29" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="AA29">
-        <v>0.99055684074965455</v>
+        <v>0.98828003950132159</v>
       </c>
       <c r="AB29">
-        <v>173.12458625633352</v>
+        <v>214.8659424757702</v>
       </c>
       <c r="AD29" t="s">
         <v>445</v>
@@ -11004,7 +11004,7 @@
         <v>902</v>
       </c>
       <c r="AN29" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="AO29">
         <v>0.96933352809933682</v>
@@ -11040,13 +11040,13 @@
         <v>1103</v>
       </c>
       <c r="BB29" t="s">
-        <v>667</v>
+        <v>648</v>
       </c>
       <c r="BC29">
-        <v>0.97513993579453706</v>
+        <v>0.95475709315784774</v>
       </c>
       <c r="BD29">
-        <v>1047.478448903224</v>
+        <v>1295.8094150268885</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11111,16 +11111,16 @@
         <v>486</v>
       </c>
       <c r="Y30" t="s">
-        <v>404</v>
+        <v>364</v>
       </c>
       <c r="Z30" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AA30">
-        <v>0.99723631056718209</v>
+        <v>0.99382591612551541</v>
       </c>
       <c r="AB30">
-        <v>50.667639601661186</v>
+        <v>113.1915376988852</v>
       </c>
       <c r="AD30" t="s">
         <v>445</v>
@@ -11150,7 +11150,7 @@
         <v>903</v>
       </c>
       <c r="AN30" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="AO30">
         <v>0.94508652322363806</v>
@@ -11186,13 +11186,13 @@
         <v>1104</v>
       </c>
       <c r="BB30" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="BC30">
-        <v>0.99416549953505795</v>
+        <v>0.98105298234439897</v>
       </c>
       <c r="BD30">
-        <v>623.59629617498683</v>
+        <v>975.4378317707384</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11257,16 +11257,16 @@
         <v>488</v>
       </c>
       <c r="Y31" t="s">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="Z31" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AA31">
-        <v>0.96929197405517931</v>
+        <v>0.99482528705797657</v>
       </c>
       <c r="AB31">
-        <v>562.98047565504703</v>
+        <v>94.869737270428971</v>
       </c>
       <c r="AD31" t="s">
         <v>445</v>
@@ -11296,7 +11296,7 @@
         <v>904</v>
       </c>
       <c r="AN31" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="AO31">
         <v>0.99347025982523174</v>
@@ -11332,13 +11332,13 @@
         <v>1105</v>
       </c>
       <c r="BB31" t="s">
-        <v>659</v>
+        <v>678</v>
       </c>
       <c r="BC31">
-        <v>0.98458868956887557</v>
+        <v>0.98635721678832755</v>
       </c>
       <c r="BD31">
-        <v>932.36113208586551</v>
+        <v>910.81457546220918</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11403,16 +11403,16 @@
         <v>490</v>
       </c>
       <c r="Y32" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="Z32" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="AA32">
-        <v>0.98417563223370064</v>
+        <v>0.97321507838078658</v>
       </c>
       <c r="AB32">
-        <v>290.11340904882155</v>
+        <v>491.05689635224547</v>
       </c>
       <c r="AD32" t="s">
         <v>445</v>
@@ -11442,7 +11442,7 @@
         <v>905</v>
       </c>
       <c r="AN32" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="AO32">
         <v>0.99424478665673766</v>
@@ -11478,13 +11478,13 @@
         <v>1106</v>
       </c>
       <c r="BB32" t="s">
-        <v>653</v>
+        <v>689</v>
       </c>
       <c r="BC32">
-        <v>0.98345026231369026</v>
+        <v>0.98172617970345721</v>
       </c>
       <c r="BD32">
-        <v>946.23097081154037</v>
+        <v>967.23604394621248</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11519,7 +11519,7 @@
         <v>49.344521286550219</v>
       </c>
       <c r="M33">
-        <v>0.20490009163907266</v>
+        <v>0.20511902364889514</v>
       </c>
       <c r="O33" t="s">
         <v>445</v>
@@ -11549,16 +11549,16 @@
         <v>492</v>
       </c>
       <c r="Y33" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="Z33" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="AA33">
-        <v>0.99385704522942342</v>
+        <v>0.97866893212504957</v>
       </c>
       <c r="AB33">
-        <v>112.62083746056986</v>
+        <v>391.06957770742463</v>
       </c>
       <c r="AD33" t="s">
         <v>445</v>
@@ -11588,7 +11588,7 @@
         <v>906</v>
       </c>
       <c r="AN33" t="s">
-        <v>648</v>
+        <v>679</v>
       </c>
       <c r="AO33">
         <v>0.97867478517995188</v>
@@ -11624,13 +11624,13 @@
         <v>1107</v>
       </c>
       <c r="BB33" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="BC33">
-        <v>0.98870653772658501</v>
+        <v>0.91560080888051365</v>
       </c>
       <c r="BD33">
-        <v>882.19201536443973</v>
+        <v>1772.8634784724095</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11695,16 +11695,16 @@
         <v>494</v>
       </c>
       <c r="Y34" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="Z34" t="s">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="AA34">
-        <v>0.99512174530146036</v>
+        <v>0.9933008323747714</v>
       </c>
       <c r="AB34">
-        <v>89.434669473226961</v>
+        <v>122.81807312919075</v>
       </c>
       <c r="AD34" t="s">
         <v>445</v>
@@ -11734,7 +11734,7 @@
         <v>907</v>
       </c>
       <c r="AN34" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="AO34">
         <v>0.95781637101189843</v>
@@ -11770,13 +11770,13 @@
         <v>1108</v>
       </c>
       <c r="BB34" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="BC34">
-        <v>0.9861533644012247</v>
+        <v>0.99223944103482187</v>
       </c>
       <c r="BD34">
-        <v>913.29817704507911</v>
+        <v>745.8368089899709</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11841,16 +11841,16 @@
         <v>496</v>
       </c>
       <c r="Y35" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="Z35" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="AA35">
-        <v>0.97275257137901638</v>
+        <v>0.9771403150431911</v>
       </c>
       <c r="AB35">
-        <v>499.53619138470009</v>
+        <v>419.09422420816315</v>
       </c>
       <c r="AD35" t="s">
         <v>445</v>
@@ -11880,7 +11880,7 @@
         <v>908</v>
       </c>
       <c r="AN35" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="AO35">
         <v>0.98886553660707677</v>
@@ -11916,13 +11916,13 @@
         <v>1109</v>
       </c>
       <c r="BB35" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="BC35">
-        <v>0.95190272587812108</v>
+        <v>0.98514006154561162</v>
       </c>
       <c r="BD35">
-        <v>1330.585123051558</v>
+        <v>925.6435835026324</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11957,7 +11957,7 @@
         <v>20.443718045322946</v>
       </c>
       <c r="M36">
-        <v>0.19987868500931139</v>
+        <v>0.19988352162425907</v>
       </c>
       <c r="O36" t="s">
         <v>445</v>
@@ -11987,16 +11987,16 @@
         <v>498</v>
       </c>
       <c r="Y36" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="Z36" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="AA36">
-        <v>0.95322333844045537</v>
+        <v>0.96576017716725859</v>
       </c>
       <c r="AB36">
-        <v>857.57212859165099</v>
+        <v>627.73008526692502</v>
       </c>
       <c r="AD36" t="s">
         <v>445</v>
@@ -12026,7 +12026,7 @@
         <v>909</v>
       </c>
       <c r="AN36" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="AO36">
         <v>0.93811411999108418</v>
@@ -12062,13 +12062,13 @@
         <v>1110</v>
       </c>
       <c r="BB36" t="s">
-        <v>652</v>
+        <v>685</v>
       </c>
       <c r="BC36">
-        <v>0.97560382464771223</v>
+        <v>0.9852903703395921</v>
       </c>
       <c r="BD36">
-        <v>1041.8267363753732</v>
+        <v>923.81232136263634</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -12133,16 +12133,16 @@
         <v>500</v>
       </c>
       <c r="Y37" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="Z37" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="AA37">
-        <v>0.93792673193465337</v>
+        <v>0.99320659129827649</v>
       </c>
       <c r="AB37">
-        <v>1138.0099145313559</v>
+        <v>124.54582619826394</v>
       </c>
       <c r="AD37" t="s">
         <v>445</v>
@@ -12172,7 +12172,7 @@
         <v>910</v>
       </c>
       <c r="AN37" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="AO37">
         <v>0.9832447093861123</v>
@@ -12208,13 +12208,13 @@
         <v>1111</v>
       </c>
       <c r="BB37" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="BC37">
-        <v>0.89604746025791282</v>
+        <v>0.99350055753404454</v>
       </c>
       <c r="BD37">
-        <v>2011.088442524429</v>
+        <v>665.79794850597443</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12279,16 +12279,16 @@
         <v>502</v>
       </c>
       <c r="Y38" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="Z38" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="AA38">
-        <v>0.99238887682283938</v>
+        <v>0.97901340677155257</v>
       </c>
       <c r="AB38">
-        <v>139.53725824794503</v>
+        <v>384.75420918820265</v>
       </c>
       <c r="AD38" t="s">
         <v>445</v>
@@ -12318,7 +12318,7 @@
         <v>911</v>
       </c>
       <c r="AN38" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="AO38">
         <v>0.99401394460386272</v>
@@ -12354,13 +12354,13 @@
         <v>1112</v>
       </c>
       <c r="BB38" t="s">
-        <v>645</v>
+        <v>675</v>
       </c>
       <c r="BC38">
-        <v>0.95200980188478979</v>
+        <v>0.9737385233335023</v>
       </c>
       <c r="BD38">
-        <v>1329.2805803703113</v>
+        <v>1064.5523240534972</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12395,7 +12395,7 @@
         <v>100.23792680097552</v>
       </c>
       <c r="M39">
-        <v>0.18116632231530605</v>
+        <v>0.2016402967110828</v>
       </c>
       <c r="O39" t="s">
         <v>445</v>
@@ -12425,16 +12425,16 @@
         <v>504</v>
       </c>
       <c r="Y39" t="s">
-        <v>405</v>
+        <v>355</v>
       </c>
       <c r="Z39" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="AA39">
-        <v>0.99511596204556785</v>
+        <v>0.98418645978522035</v>
       </c>
       <c r="AB39">
-        <v>89.54069583125569</v>
+        <v>289.91490393762615</v>
       </c>
       <c r="AD39" t="s">
         <v>445</v>
@@ -12464,7 +12464,7 @@
         <v>912</v>
       </c>
       <c r="AN39" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="AO39">
         <v>0.99712495361968201</v>
@@ -12500,13 +12500,13 @@
         <v>1113</v>
       </c>
       <c r="BB39" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="BC39">
-        <v>0.97707982144598671</v>
+        <v>0.946000484445496</v>
       </c>
       <c r="BD39">
-        <v>1023.8441753830622</v>
+        <v>1402.4940978390403</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12571,16 +12571,16 @@
         <v>506</v>
       </c>
       <c r="Y40" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="Z40" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="AA40">
-        <v>0.9916566373699115</v>
+        <v>0.9906346744759631</v>
       </c>
       <c r="AB40">
-        <v>152.96164821828896</v>
+        <v>171.69763460734316</v>
       </c>
       <c r="AD40" t="s">
         <v>445</v>
@@ -12610,7 +12610,7 @@
         <v>913</v>
       </c>
       <c r="AN40" t="s">
-        <v>677</v>
+        <v>655</v>
       </c>
       <c r="AO40">
         <v>0.99728565567097416</v>
@@ -12646,13 +12646,13 @@
         <v>1114</v>
       </c>
       <c r="BB40" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="BC40">
-        <v>0.98962892741174779</v>
+        <v>0.96304008712262701</v>
       </c>
       <c r="BD40">
-        <v>870.9542343668727</v>
+        <v>1194.8949385559945</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12717,16 +12717,16 @@
         <v>508</v>
       </c>
       <c r="Y41" t="s">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="Z41" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="AA41">
-        <v>0.98522037572241172</v>
+        <v>0.95915670695527311</v>
       </c>
       <c r="AB41">
-        <v>270.9597784224527</v>
+        <v>748.79370581999342</v>
       </c>
       <c r="AD41" t="s">
         <v>445</v>
@@ -12756,7 +12756,7 @@
         <v>914</v>
       </c>
       <c r="AN41" t="s">
-        <v>649</v>
+        <v>675</v>
       </c>
       <c r="AO41">
         <v>0.95358024529553875</v>
@@ -12792,13 +12792,13 @@
         <v>1115</v>
       </c>
       <c r="BB41" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="BC41">
-        <v>0.93242166156261008</v>
+        <v>0.98902339847455312</v>
       </c>
       <c r="BD41">
-        <v>1567.9294232955338</v>
+        <v>878.33159525169435</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12863,16 +12863,16 @@
         <v>510</v>
       </c>
       <c r="Y42" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="Z42" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="AA42">
-        <v>0.98831913038449382</v>
+        <v>0.98927829835282999</v>
       </c>
       <c r="AB42">
-        <v>214.14927628428001</v>
+        <v>196.56453019811752</v>
       </c>
       <c r="AD42" t="s">
         <v>445</v>
@@ -12902,13 +12902,13 @@
         <v>915</v>
       </c>
       <c r="AN42" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
       <c r="AO42">
-        <v>0.98155612527850788</v>
+        <v>0.96378142476218853</v>
       </c>
       <c r="AP42">
-        <v>338.13770322735616</v>
+        <v>664.00721269321059</v>
       </c>
       <c r="AR42" t="s">
         <v>445</v>
@@ -12938,13 +12938,13 @@
         <v>1116</v>
       </c>
       <c r="BB42" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="BC42">
-        <v>0.98514006154561162</v>
+        <v>0.99181397642123026</v>
       </c>
       <c r="BD42">
-        <v>925.6435835026324</v>
+        <v>772.83962979925604</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -13009,16 +13009,16 @@
         <v>512</v>
       </c>
       <c r="Y43" t="s">
-        <v>353</v>
+        <v>408</v>
       </c>
       <c r="Z43" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="AA43">
-        <v>0.98522854207859256</v>
+        <v>0.97846149456848719</v>
       </c>
       <c r="AB43">
-        <v>270.81006189247</v>
+        <v>394.87259957773409</v>
       </c>
       <c r="AD43" t="s">
         <v>445</v>
@@ -13048,13 +13048,13 @@
         <v>916</v>
       </c>
       <c r="AN43" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="AO43">
-        <v>0.92201529031984186</v>
+        <v>0.97998268051544435</v>
       </c>
       <c r="AP43">
-        <v>1429.719677469566</v>
+        <v>366.9841905501878</v>
       </c>
       <c r="AR43" t="s">
         <v>445</v>
@@ -13084,13 +13084,13 @@
         <v>1117</v>
       </c>
       <c r="BB43" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="BC43">
-        <v>0.9852903703395921</v>
+        <v>0.98624400907289522</v>
       </c>
       <c r="BD43">
-        <v>923.81232136263634</v>
+        <v>912.19382279522597</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -13125,7 +13125,7 @@
         <v>17.455188698838782</v>
       </c>
       <c r="M44">
-        <v>0.1609687803389015</v>
+        <v>0.1637262892375024</v>
       </c>
       <c r="O44" t="s">
         <v>445</v>
@@ -13155,16 +13155,16 @@
         <v>514</v>
       </c>
       <c r="Y44" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="Z44" t="s">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="AA44">
-        <v>0.99185644171670617</v>
+        <v>0.99385704522942342</v>
       </c>
       <c r="AB44">
-        <v>149.29856852705402</v>
+        <v>112.62083746056986</v>
       </c>
       <c r="AD44" t="s">
         <v>445</v>
@@ -13194,13 +13194,13 @@
         <v>917</v>
       </c>
       <c r="AN44" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="AO44">
-        <v>0.98335963574413709</v>
+        <v>0.99273887587992471</v>
       </c>
       <c r="AP44">
-        <v>305.07334469081934</v>
+        <v>133.12060886804619</v>
       </c>
       <c r="AR44" t="s">
         <v>445</v>
@@ -13230,13 +13230,13 @@
         <v>1118</v>
       </c>
       <c r="BB44" t="s">
-        <v>675</v>
+        <v>648</v>
       </c>
       <c r="BC44">
-        <v>0.99350055753404454</v>
+        <v>0.96572704859346925</v>
       </c>
       <c r="BD44">
-        <v>665.79794850597443</v>
+        <v>1162.1587913028991</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13271,7 +13271,7 @@
         <v>37.0118256629992</v>
       </c>
       <c r="M45">
-        <v>0.19874837763123138</v>
+        <v>0.1990685230369556</v>
       </c>
       <c r="O45" t="s">
         <v>445</v>
@@ -13301,16 +13301,16 @@
         <v>516</v>
       </c>
       <c r="Y45" t="s">
-        <v>387</v>
+        <v>351</v>
       </c>
       <c r="Z45" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="AA45">
-        <v>0.94189846566095958</v>
+        <v>0.99512174530146036</v>
       </c>
       <c r="AB45">
-        <v>1065.1947962157406</v>
+        <v>89.434669473226961</v>
       </c>
       <c r="AD45" t="s">
         <v>445</v>
@@ -13340,13 +13340,13 @@
         <v>918</v>
       </c>
       <c r="AN45" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="AO45">
-        <v>0.98001801309124148</v>
+        <v>0.95931345925264233</v>
       </c>
       <c r="AP45">
-        <v>366.33642666057369</v>
+        <v>745.91991370155699</v>
       </c>
       <c r="AR45" t="s">
         <v>445</v>
@@ -13376,13 +13376,13 @@
         <v>1119</v>
       </c>
       <c r="BB45" t="s">
-        <v>649</v>
+        <v>676</v>
       </c>
       <c r="BC45">
-        <v>0.9737385233335023</v>
+        <v>0.98481153677494815</v>
       </c>
       <c r="BD45">
-        <v>1064.5523240534972</v>
+        <v>929.64611029188166</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13417,7 +13417,7 @@
         <v>57.04947416201933</v>
       </c>
       <c r="M46">
-        <v>0.13505975949083393</v>
+        <v>0.19294251355833419</v>
       </c>
       <c r="O46" t="s">
         <v>445</v>
@@ -13447,16 +13447,16 @@
         <v>518</v>
       </c>
       <c r="Y46" t="s">
-        <v>439</v>
+        <v>369</v>
       </c>
       <c r="Z46" t="s">
-        <v>649</v>
+        <v>667</v>
       </c>
       <c r="AA46">
-        <v>0.95001627981732095</v>
+        <v>0.97275257137901638</v>
       </c>
       <c r="AB46">
-        <v>916.36820334911533</v>
+        <v>499.53619138470009</v>
       </c>
       <c r="AD46" t="s">
         <v>445</v>
@@ -13486,13 +13486,13 @@
         <v>919</v>
       </c>
       <c r="AN46" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="AO46">
-        <v>0.91475976979271756</v>
+        <v>0.99411928823407203</v>
       </c>
       <c r="AP46">
-        <v>1562.7375538001788</v>
+        <v>107.81304904201184</v>
       </c>
       <c r="AR46" t="s">
         <v>445</v>
@@ -13522,13 +13522,13 @@
         <v>1120</v>
       </c>
       <c r="BB46" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="BC46">
-        <v>0.946000484445496</v>
+        <v>0.99067149991228087</v>
       </c>
       <c r="BD46">
-        <v>1402.4940978390403</v>
+        <v>845.34880556723965</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13563,7 +13563,7 @@
         <v>73.263486534558155</v>
       </c>
       <c r="M47">
-        <v>0.14626407043642911</v>
+        <v>0.2089486720520416</v>
       </c>
       <c r="O47" t="s">
         <v>445</v>
@@ -13593,16 +13593,16 @@
         <v>520</v>
       </c>
       <c r="Y47" t="s">
-        <v>441</v>
+        <v>375</v>
       </c>
       <c r="Z47" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AA47">
-        <v>0.98042178820377779</v>
+        <v>0.95322333844045537</v>
       </c>
       <c r="AB47">
-        <v>358.93388293074008</v>
+        <v>857.57212859165099</v>
       </c>
       <c r="AD47" t="s">
         <v>445</v>
@@ -13632,13 +13632,13 @@
         <v>920</v>
       </c>
       <c r="AN47" t="s">
-        <v>683</v>
+        <v>654</v>
       </c>
       <c r="AO47">
-        <v>0.9937640046384969</v>
+        <v>0.9790694594776973</v>
       </c>
       <c r="AP47">
-        <v>114.32658162755614</v>
+        <v>383.72657624221517</v>
       </c>
       <c r="AR47" t="s">
         <v>445</v>
@@ -13668,13 +13668,13 @@
         <v>1121</v>
       </c>
       <c r="BB47" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="BC47">
-        <v>0.96304008712262701</v>
+        <v>0.99113893512004347</v>
       </c>
       <c r="BD47">
-        <v>1194.8949385559945</v>
+        <v>815.68225104790747</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13739,16 +13739,16 @@
         <v>522</v>
       </c>
       <c r="Y48" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Z48" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="AA48">
-        <v>0.95808092951199286</v>
+        <v>0.93792673193465337</v>
       </c>
       <c r="AB48">
-        <v>768.51629228013144</v>
+        <v>1138.0099145313559</v>
       </c>
       <c r="AD48" t="s">
         <v>445</v>
@@ -13778,13 +13778,13 @@
         <v>921</v>
       </c>
       <c r="AN48" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="AO48">
-        <v>0.98434157772378295</v>
+        <v>0.98822008409109219</v>
       </c>
       <c r="AP48">
-        <v>287.07107506397949</v>
+        <v>215.96512499664277</v>
       </c>
       <c r="AR48" t="s">
         <v>445</v>
@@ -13814,13 +13814,13 @@
         <v>1122</v>
       </c>
       <c r="BB48" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="BC48">
-        <v>0.98902339847455312</v>
+        <v>0.97513993579453706</v>
       </c>
       <c r="BD48">
-        <v>878.33159525169435</v>
+        <v>1047.478448903224</v>
       </c>
     </row>
     <row r="49" spans="2:56">
@@ -13855,7 +13855,7 @@
         <v>87.23926107037741</v>
       </c>
       <c r="M49">
-        <v>0.14714843352802712</v>
+        <v>0.21021204789718159</v>
       </c>
       <c r="O49" t="s">
         <v>445</v>
@@ -13885,16 +13885,16 @@
         <v>524</v>
       </c>
       <c r="Y49" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="Z49" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="AA49">
-        <v>0.98362353815347903</v>
+        <v>0.99238887682283938</v>
       </c>
       <c r="AB49">
-        <v>300.23513385288544</v>
+        <v>139.53725824794503</v>
       </c>
       <c r="AD49" t="s">
         <v>445</v>
@@ -13924,13 +13924,13 @@
         <v>922</v>
       </c>
       <c r="AN49" t="s">
-        <v>655</v>
+        <v>677</v>
       </c>
       <c r="AO49">
-        <v>0.98724240938456542</v>
+        <v>0.99332113976407466</v>
       </c>
       <c r="AP49">
-        <v>233.88916128296634</v>
+        <v>122.44577099196496</v>
       </c>
       <c r="AR49" t="s">
         <v>445</v>
@@ -13960,13 +13960,13 @@
         <v>1123</v>
       </c>
       <c r="BB49" t="s">
-        <v>677</v>
+        <v>659</v>
       </c>
       <c r="BC49">
-        <v>0.99181397642123026</v>
+        <v>0.98683737688914319</v>
       </c>
       <c r="BD49">
-        <v>772.83962979925604</v>
+        <v>904.96462490060583</v>
       </c>
     </row>
     <row r="50" spans="2:56">
@@ -14001,7 +14001,7 @@
         <v>174.30633413429078</v>
       </c>
       <c r="M50">
-        <v>0.15412160122752708</v>
+        <v>0.15432348562346257</v>
       </c>
       <c r="O50" t="s">
         <v>445</v>
@@ -14031,16 +14031,16 @@
         <v>526</v>
       </c>
       <c r="Y50" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="Z50" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA50">
-        <v>0.99495707351657814</v>
+        <v>0.99511596204556785</v>
       </c>
       <c r="AB50">
-        <v>92.453652196066486</v>
+        <v>89.54069583125569</v>
       </c>
       <c r="AD50" t="s">
         <v>445</v>
@@ -14070,13 +14070,13 @@
         <v>923</v>
       </c>
       <c r="AN50" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="AO50">
-        <v>0.99486897494175219</v>
+        <v>0.99451359177835219</v>
       </c>
       <c r="AP50">
-        <v>94.068792734543848</v>
+        <v>100.58415073020944</v>
       </c>
       <c r="AR50" t="s">
         <v>445</v>
@@ -14106,13 +14106,13 @@
         <v>1124</v>
       </c>
       <c r="BB50" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
       <c r="BC50">
-        <v>0.97093554889152922</v>
+        <v>0.98183502015800017</v>
       </c>
       <c r="BD50">
-        <v>1098.7018960048697</v>
+        <v>965.91000440836387</v>
       </c>
     </row>
     <row r="51" spans="2:56">
@@ -14177,16 +14177,16 @@
         <v>528</v>
       </c>
       <c r="Y51" t="s">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="Z51" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="AA51">
-        <v>0.969236873889878</v>
+        <v>0.9916566373699115</v>
       </c>
       <c r="AB51">
-        <v>563.9906453522367</v>
+        <v>152.96164821828896</v>
       </c>
       <c r="AD51" t="s">
         <v>445</v>
@@ -14216,13 +14216,13 @@
         <v>924</v>
       </c>
       <c r="AN51" t="s">
-        <v>656</v>
+        <v>683</v>
       </c>
       <c r="AO51">
-        <v>0.99698330098522958</v>
+        <v>0.9909682810714957</v>
       </c>
       <c r="AP51">
-        <v>55.306148604123919</v>
+        <v>165.58151368924484</v>
       </c>
       <c r="AR51" t="s">
         <v>445</v>
@@ -14252,13 +14252,13 @@
         <v>1125</v>
       </c>
       <c r="BB51" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="BC51">
-        <v>0.98986511819476719</v>
+        <v>0.98425930791162897</v>
       </c>
       <c r="BD51">
-        <v>868.07664332708646</v>
+        <v>936.37409860998696</v>
       </c>
     </row>
     <row r="52" spans="2:56">
@@ -14323,16 +14323,16 @@
         <v>530</v>
       </c>
       <c r="Y52" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="Z52" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="AA52">
-        <v>0.93773368388956246</v>
+        <v>0.98522037572241172</v>
       </c>
       <c r="AB52">
-        <v>1141.5491286913555</v>
+        <v>270.9597784224527</v>
       </c>
       <c r="AD52" t="s">
         <v>445</v>
@@ -14362,13 +14362,13 @@
         <v>925</v>
       </c>
       <c r="AN52" t="s">
-        <v>658</v>
+        <v>687</v>
       </c>
       <c r="AO52">
-        <v>0.95884281124958637</v>
+        <v>0.98155612527850788</v>
       </c>
       <c r="AP52">
-        <v>754.54846042424947</v>
+        <v>338.13770322735616</v>
       </c>
       <c r="AR52" t="s">
         <v>445</v>
@@ -14398,13 +14398,13 @@
         <v>1126</v>
       </c>
       <c r="BB52" t="s">
-        <v>673</v>
+        <v>647</v>
       </c>
       <c r="BC52">
-        <v>0.99159294969939915</v>
+        <v>0.97983022896434013</v>
       </c>
       <c r="BD52">
-        <v>786.86745907813679</v>
+        <v>990.33504378445582</v>
       </c>
     </row>
     <row r="53" spans="2:56">
@@ -14469,16 +14469,16 @@
         <v>532</v>
       </c>
       <c r="Y53" t="s">
-        <v>355</v>
+        <v>422</v>
       </c>
       <c r="Z53" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AA53">
-        <v>0.98418645978522035</v>
+        <v>0.98831913038449382</v>
       </c>
       <c r="AB53">
-        <v>289.91490393762615</v>
+        <v>214.14927628428001</v>
       </c>
       <c r="AD53" t="s">
         <v>445</v>
@@ -14508,13 +14508,13 @@
         <v>926</v>
       </c>
       <c r="AN53" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AO53">
-        <v>0.96628526147979277</v>
+        <v>0.92201529031984186</v>
       </c>
       <c r="AP53">
-        <v>618.10353953713195</v>
+        <v>1429.719677469566</v>
       </c>
       <c r="AR53" t="s">
         <v>445</v>
@@ -14544,13 +14544,13 @@
         <v>1127</v>
       </c>
       <c r="BB53" t="s">
-        <v>670</v>
+        <v>647</v>
       </c>
       <c r="BC53">
-        <v>0.98080906590233208</v>
+        <v>0.98532695715711582</v>
       </c>
       <c r="BD53">
-        <v>978.40954708992126</v>
+        <v>923.36657196913927</v>
       </c>
     </row>
     <row r="54" spans="2:56">
@@ -14615,16 +14615,16 @@
         <v>534</v>
       </c>
       <c r="Y54" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="Z54" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="AA54">
-        <v>0.9906346744759631</v>
+        <v>0.98922498055164843</v>
       </c>
       <c r="AB54">
-        <v>171.69763460734316</v>
+        <v>197.54202321977883</v>
       </c>
       <c r="AD54" t="s">
         <v>445</v>
@@ -14654,13 +14654,13 @@
         <v>927</v>
       </c>
       <c r="AN54" t="s">
-        <v>686</v>
+        <v>658</v>
       </c>
       <c r="AO54">
-        <v>0.98449859725932043</v>
+        <v>0.98335963574413709</v>
       </c>
       <c r="AP54">
-        <v>284.19238357912451</v>
+        <v>305.07334469081934</v>
       </c>
       <c r="AR54" t="s">
         <v>445</v>
@@ -14693,10 +14693,10 @@
         <v>649</v>
       </c>
       <c r="BC54">
-        <v>0.9611655354348162</v>
+        <v>0.95190272587812108</v>
       </c>
       <c r="BD54">
-        <v>1217.7332266191565</v>
+        <v>1330.585123051558</v>
       </c>
     </row>
     <row r="55" spans="2:56">
@@ -14761,16 +14761,16 @@
         <v>536</v>
       </c>
       <c r="Y55" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z55" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="AA55">
-        <v>0.95915670695527311</v>
+        <v>0.99262576700342608</v>
       </c>
       <c r="AB55">
-        <v>748.79370581999342</v>
+        <v>135.19427160385601</v>
       </c>
       <c r="AD55" t="s">
         <v>445</v>
@@ -14800,13 +14800,13 @@
         <v>928</v>
       </c>
       <c r="AN55" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="AO55">
-        <v>0.981374440216361</v>
+        <v>0.98001801309124148</v>
       </c>
       <c r="AP55">
-        <v>341.46859603338169</v>
+        <v>366.33642666057369</v>
       </c>
       <c r="AR55" t="s">
         <v>445</v>
@@ -14836,13 +14836,13 @@
         <v>1129</v>
       </c>
       <c r="BB55" t="s">
-        <v>683</v>
+        <v>662</v>
       </c>
       <c r="BC55">
-        <v>0.99167399400086409</v>
+        <v>0.97560382464771223</v>
       </c>
       <c r="BD55">
-        <v>781.72384741182896</v>
+        <v>1041.8267363753732</v>
       </c>
     </row>
     <row r="56" spans="2:56">
@@ -14907,16 +14907,16 @@
         <v>538</v>
       </c>
       <c r="Y56" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="Z56" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="AA56">
-        <v>0.98927829835282999</v>
+        <v>0.972129953111039</v>
       </c>
       <c r="AB56">
-        <v>196.56453019811752</v>
+        <v>510.95085963095079</v>
       </c>
       <c r="AD56" t="s">
         <v>445</v>
@@ -14946,13 +14946,13 @@
         <v>929</v>
       </c>
       <c r="AN56" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
       <c r="AO56">
-        <v>0.94345419131600505</v>
+        <v>0.91475976979271756</v>
       </c>
       <c r="AP56">
-        <v>1036.6731592065737</v>
+        <v>1562.7375538001788</v>
       </c>
       <c r="AR56" t="s">
         <v>445</v>
@@ -14982,13 +14982,13 @@
         <v>1130</v>
       </c>
       <c r="BB56" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="BC56">
-        <v>0.98870750020933817</v>
+        <v>0.89604746025791282</v>
       </c>
       <c r="BD56">
-        <v>882.18028911622969</v>
+        <v>2011.088442524429</v>
       </c>
     </row>
     <row r="57" spans="2:56">
@@ -15023,7 +15023,7 @@
         <v>17.541373916628828</v>
       </c>
       <c r="M57">
-        <v>0.19409687263948139</v>
+        <v>0.19446425617479213</v>
       </c>
       <c r="O57" t="s">
         <v>445</v>
@@ -15053,16 +15053,16 @@
         <v>540</v>
       </c>
       <c r="Y57" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="Z57" t="s">
-        <v>667</v>
+        <v>648</v>
       </c>
       <c r="AA57">
-        <v>0.97846149456848719</v>
+        <v>0.95402772316064421</v>
       </c>
       <c r="AB57">
-        <v>394.87259957773409</v>
+        <v>842.82507538818982</v>
       </c>
       <c r="AD57" t="s">
         <v>445</v>
@@ -15092,13 +15092,13 @@
         <v>930</v>
       </c>
       <c r="AN57" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="AO57">
-        <v>0.92366037259831435</v>
+        <v>0.99537175847221593</v>
       </c>
       <c r="AP57">
-        <v>1399.5598356975697</v>
+        <v>84.85109467604083</v>
       </c>
       <c r="AR57" t="s">
         <v>445</v>
@@ -15128,13 +15128,13 @@
         <v>1131</v>
       </c>
       <c r="BB57" t="s">
-        <v>645</v>
+        <v>688</v>
       </c>
       <c r="BC57">
-        <v>0.97890667967973555</v>
+        <v>0.99167399400086409</v>
       </c>
       <c r="BD57">
-        <v>1001.5869525685553</v>
+        <v>781.72384741182896</v>
       </c>
     </row>
     <row r="58" spans="2:56">
@@ -15169,7 +15169,7 @@
         <v>140.64820956436421</v>
       </c>
       <c r="M58">
-        <v>0.20776821596264403</v>
+        <v>0.20788559204216223</v>
       </c>
       <c r="O58" t="s">
         <v>445</v>
@@ -15199,16 +15199,16 @@
         <v>542</v>
       </c>
       <c r="Y58" t="s">
-        <v>367</v>
+        <v>399</v>
       </c>
       <c r="Z58" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="AA58">
-        <v>0.98922498055164843</v>
+        <v>0.99556264479843226</v>
       </c>
       <c r="AB58">
-        <v>197.54202321977883</v>
+        <v>81.351512028741695</v>
       </c>
       <c r="AD58" t="s">
         <v>445</v>
@@ -15238,13 +15238,13 @@
         <v>931</v>
       </c>
       <c r="AN58" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AO58">
-        <v>0.98255203569076077</v>
+        <v>0.95891375083366426</v>
       </c>
       <c r="AP58">
-        <v>319.879345669386</v>
+        <v>753.24790138282128</v>
       </c>
       <c r="AR58" t="s">
         <v>445</v>
@@ -15274,13 +15274,13 @@
         <v>1132</v>
       </c>
       <c r="BB58" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="BC58">
-        <v>0.98105298234439897</v>
+        <v>0.98870750020933817</v>
       </c>
       <c r="BD58">
-        <v>975.4378317707384</v>
+        <v>882.18028911622969</v>
       </c>
     </row>
     <row r="59" spans="2:56">
@@ -15345,16 +15345,16 @@
         <v>544</v>
       </c>
       <c r="Y59" t="s">
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="Z59" t="s">
-        <v>672</v>
+        <v>652</v>
       </c>
       <c r="AA59">
-        <v>0.99262576700342608</v>
+        <v>0.94094717156030294</v>
       </c>
       <c r="AB59">
-        <v>135.19427160385601</v>
+        <v>1082.6351880611128</v>
       </c>
       <c r="AD59" t="s">
         <v>445</v>
@@ -15384,13 +15384,13 @@
         <v>932</v>
       </c>
       <c r="AN59" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AO59">
-        <v>0.98977574375304844</v>
+        <v>0.97364425413724487</v>
       </c>
       <c r="AP59">
-        <v>187.44469786077892</v>
+        <v>483.18867415051142</v>
       </c>
       <c r="AR59" t="s">
         <v>445</v>
@@ -15420,13 +15420,13 @@
         <v>1133</v>
       </c>
       <c r="BB59" t="s">
-        <v>668</v>
+        <v>649</v>
       </c>
       <c r="BC59">
-        <v>0.98635721678832755</v>
+        <v>0.97890667967973555</v>
       </c>
       <c r="BD59">
-        <v>910.81457546220918</v>
+        <v>1001.5869525685553</v>
       </c>
     </row>
     <row r="60" spans="2:56">
@@ -15461,7 +15461,7 @@
         <v>56.549593195147608</v>
       </c>
       <c r="M60">
-        <v>0.19593013898546563</v>
+        <v>0.20337486804543919</v>
       </c>
       <c r="O60" t="s">
         <v>445</v>
@@ -15491,16 +15491,16 @@
         <v>546</v>
       </c>
       <c r="Y60" t="s">
-        <v>383</v>
+        <v>416</v>
       </c>
       <c r="Z60" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="AA60">
-        <v>0.972129953111039</v>
+        <v>0.96644290210447936</v>
       </c>
       <c r="AB60">
-        <v>510.95085963095079</v>
+        <v>615.21346141787853</v>
       </c>
       <c r="AD60" t="s">
         <v>445</v>
@@ -15530,13 +15530,13 @@
         <v>933</v>
       </c>
       <c r="AN60" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="AO60">
-        <v>0.94216773987491098</v>
+        <v>0.95472325192752561</v>
       </c>
       <c r="AP60">
-        <v>1060.2581022932995</v>
+        <v>830.07371466203085</v>
       </c>
       <c r="AR60" t="s">
         <v>445</v>
@@ -15566,13 +15566,13 @@
         <v>1134</v>
       </c>
       <c r="BB60" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="BC60">
-        <v>0.98172617970345721</v>
+        <v>0.99416549953505795</v>
       </c>
       <c r="BD60">
-        <v>967.23604394621248</v>
+        <v>623.59629617498683</v>
       </c>
     </row>
     <row r="61" spans="2:56">
@@ -15607,7 +15607,7 @@
         <v>1.517257960246374</v>
       </c>
       <c r="M61">
-        <v>0.18023309962426437</v>
+        <v>0.1803261519416787</v>
       </c>
       <c r="O61" t="s">
         <v>445</v>
@@ -15637,16 +15637,16 @@
         <v>548</v>
       </c>
       <c r="Y61" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="Z61" t="s">
-        <v>658</v>
+        <v>671</v>
       </c>
       <c r="AA61">
-        <v>0.95402772316064421</v>
+        <v>0.99369895978652845</v>
       </c>
       <c r="AB61">
-        <v>842.82507538818982</v>
+        <v>115.51907058031178</v>
       </c>
       <c r="AD61" t="s">
         <v>445</v>
@@ -15676,13 +15676,13 @@
         <v>934</v>
       </c>
       <c r="AN61" t="s">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="AO61">
-        <v>0.99146900514737779</v>
+        <v>0.99476921667660834</v>
       </c>
       <c r="AP61">
-        <v>156.40157229807483</v>
+        <v>95.897694262180153</v>
       </c>
       <c r="AR61" t="s">
         <v>445</v>
@@ -15712,13 +15712,13 @@
         <v>1135</v>
       </c>
       <c r="BB61" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="BC61">
-        <v>0.91560080888051365</v>
+        <v>0.98458868956887557</v>
       </c>
       <c r="BD61">
-        <v>1772.8634784724095</v>
+        <v>932.36113208586551</v>
       </c>
     </row>
     <row r="62" spans="2:56">
@@ -15753,7 +15753,7 @@
         <v>2.7748989458872644</v>
       </c>
       <c r="M62">
-        <v>0.18918006848374011</v>
+        <v>0.18926535942103342</v>
       </c>
       <c r="O62" t="s">
         <v>445</v>
@@ -15783,16 +15783,16 @@
         <v>550</v>
       </c>
       <c r="Y62" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="Z62" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AA62">
-        <v>0.99556264479843226</v>
+        <v>0.99349375112817762</v>
       </c>
       <c r="AB62">
-        <v>81.351512028741695</v>
+        <v>119.28122931674373</v>
       </c>
       <c r="AD62" t="s">
         <v>445</v>
@@ -15822,13 +15822,13 @@
         <v>935</v>
       </c>
       <c r="AN62" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="AO62">
-        <v>0.97494022509165501</v>
+        <v>0.99223838421520194</v>
       </c>
       <c r="AP62">
-        <v>459.42920665299067</v>
+        <v>142.29628938796495</v>
       </c>
       <c r="AR62" t="s">
         <v>445</v>
@@ -15858,13 +15858,13 @@
         <v>1136</v>
       </c>
       <c r="BB62" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="BC62">
-        <v>0.99223944103482187</v>
+        <v>0.98345026231369026</v>
       </c>
       <c r="BD62">
-        <v>745.8368089899709</v>
+        <v>946.23097081154037</v>
       </c>
     </row>
     <row r="63" spans="2:56">
@@ -15899,7 +15899,7 @@
         <v>2.5568604295918282</v>
       </c>
       <c r="M63">
-        <v>0.11763685142671564</v>
+        <v>0.11763151100879637</v>
       </c>
       <c r="O63" t="s">
         <v>445</v>
@@ -15929,16 +15929,16 @@
         <v>552</v>
       </c>
       <c r="Y63" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="Z63" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="AA63">
-        <v>0.94094717156030294</v>
+        <v>0.99739378758993247</v>
       </c>
       <c r="AB63">
-        <v>1082.6351880611128</v>
+        <v>47.780560851239088</v>
       </c>
       <c r="AD63" t="s">
         <v>445</v>
@@ -15968,13 +15968,13 @@
         <v>936</v>
       </c>
       <c r="AN63" t="s">
-        <v>679</v>
+        <v>648</v>
       </c>
       <c r="AO63">
-        <v>0.99342004180524168</v>
+        <v>0.93136449657406906</v>
       </c>
       <c r="AP63">
-        <v>120.63256690390332</v>
+        <v>1258.3175628087345</v>
       </c>
     </row>
     <row r="64" spans="2:56">
@@ -16039,16 +16039,16 @@
         <v>554</v>
       </c>
       <c r="Y64" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="Z64" t="s">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="AA64">
-        <v>0.96644290210447936</v>
+        <v>0.91300037935815459</v>
       </c>
       <c r="AB64">
-        <v>615.21346141787853</v>
+        <v>1594.9930451004991</v>
       </c>
       <c r="AD64" t="s">
         <v>445</v>
@@ -16078,13 +16078,13 @@
         <v>937</v>
       </c>
       <c r="AN64" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="AO64">
-        <v>0.99501310191160197</v>
+        <v>0.9340182520227388</v>
       </c>
       <c r="AP64">
-        <v>91.426464953964114</v>
+        <v>1209.6653795831226</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -16149,16 +16149,16 @@
         <v>556</v>
       </c>
       <c r="Y65" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="Z65" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AA65">
-        <v>0.99369895978652845</v>
+        <v>0.96722865505135913</v>
       </c>
       <c r="AB65">
-        <v>115.51907058031178</v>
+        <v>600.80799072508239</v>
       </c>
       <c r="AD65" t="s">
         <v>445</v>
@@ -16188,13 +16188,13 @@
         <v>938</v>
       </c>
       <c r="AN65" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="AO65">
-        <v>0.9633630443304535</v>
+        <v>0.9922959111510915</v>
       </c>
       <c r="AP65">
-        <v>671.67752060835289</v>
+        <v>141.24162889665487</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -16259,16 +16259,16 @@
         <v>558</v>
       </c>
       <c r="Y66" t="s">
-        <v>427</v>
+        <v>368</v>
       </c>
       <c r="Z66" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="AA66">
-        <v>0.99349375112817762</v>
+        <v>0.96039250350097727</v>
       </c>
       <c r="AB66">
-        <v>119.28122931674373</v>
+        <v>726.13743581541678</v>
       </c>
       <c r="AD66" t="s">
         <v>445</v>
@@ -16298,13 +16298,13 @@
         <v>939</v>
       </c>
       <c r="AN66" t="s">
-        <v>646</v>
+        <v>675</v>
       </c>
       <c r="AO66">
-        <v>0.98994878939511521</v>
+        <v>0.97817316280665345</v>
       </c>
       <c r="AP66">
-        <v>184.27219442288737</v>
+        <v>400.1586818780205</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -16339,7 +16339,7 @@
         <v>60.525198252848739</v>
       </c>
       <c r="M67">
-        <v>0.14543293650392616</v>
+        <v>0.20776133786275169</v>
       </c>
       <c r="O67" t="s">
         <v>445</v>
@@ -16369,16 +16369,16 @@
         <v>560</v>
       </c>
       <c r="Y67" t="s">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="Z67" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="AA67">
-        <v>0.99739378758993247</v>
+        <v>0.96501488785990974</v>
       </c>
       <c r="AB67">
-        <v>47.780560851239088</v>
+        <v>641.39372256832166</v>
       </c>
       <c r="AD67" t="s">
         <v>445</v>
@@ -16408,13 +16408,13 @@
         <v>940</v>
       </c>
       <c r="AN67" t="s">
-        <v>670</v>
+        <v>684</v>
       </c>
       <c r="AO67">
-        <v>0.96684854231168849</v>
+        <v>0.98449859725932043</v>
       </c>
       <c r="AP67">
-        <v>607.77672428571168</v>
+        <v>284.19238357912451</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -16449,7 +16449,7 @@
         <v>0.18379667725284016</v>
       </c>
       <c r="M68">
-        <v>0.18289534321421311</v>
+        <v>0.18291108975429096</v>
       </c>
       <c r="O68" t="s">
         <v>445</v>
@@ -16479,16 +16479,16 @@
         <v>562</v>
       </c>
       <c r="Y68" t="s">
-        <v>432</v>
+        <v>397</v>
       </c>
       <c r="Z68" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="AA68">
-        <v>0.91300037935815459</v>
+        <v>0.99401420652619221</v>
       </c>
       <c r="AB68">
-        <v>1594.9930451004991</v>
+        <v>109.73954701980865</v>
       </c>
       <c r="AD68" t="s">
         <v>445</v>
@@ -16518,13 +16518,13 @@
         <v>941</v>
       </c>
       <c r="AN68" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="AO68">
-        <v>0.96378142476218853</v>
+        <v>0.981374440216361</v>
       </c>
       <c r="AP68">
-        <v>664.00721269321059</v>
+        <v>341.46859603338169</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -16589,16 +16589,16 @@
         <v>564</v>
       </c>
       <c r="Y69" t="s">
-        <v>438</v>
+        <v>400</v>
       </c>
       <c r="Z69" t="s">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="AA69">
-        <v>0.96722865505135913</v>
+        <v>0.99368555142692816</v>
       </c>
       <c r="AB69">
-        <v>600.80799072508239</v>
+        <v>115.76489050631628</v>
       </c>
       <c r="AD69" t="s">
         <v>445</v>
@@ -16628,13 +16628,13 @@
         <v>942</v>
       </c>
       <c r="AN69" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="AO69">
-        <v>0.97998268051544435</v>
+        <v>0.94345419131600505</v>
       </c>
       <c r="AP69">
-        <v>366.9841905501878</v>
+        <v>1036.6731592065737</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -16699,16 +16699,16 @@
         <v>566</v>
       </c>
       <c r="Y70" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="Z70" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="AA70">
-        <v>0.95936298088609862</v>
+        <v>0.94386714187064036</v>
       </c>
       <c r="AB70">
-        <v>745.01201708819133</v>
+        <v>1029.10239903826</v>
       </c>
       <c r="AD70" t="s">
         <v>445</v>
@@ -16738,13 +16738,13 @@
         <v>943</v>
       </c>
       <c r="AN70" t="s">
-        <v>687</v>
+        <v>649</v>
       </c>
       <c r="AO70">
-        <v>0.99273887587992471</v>
+        <v>0.92366037259831435</v>
       </c>
       <c r="AP70">
-        <v>133.12060886804619</v>
+        <v>1399.5598356975697</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -16779,7 +16779,7 @@
         <v>34.975274584155741</v>
       </c>
       <c r="M71">
-        <v>0.19772688487539386</v>
+        <v>0.19772966031545994</v>
       </c>
       <c r="O71" t="s">
         <v>445</v>
@@ -16809,16 +16809,16 @@
         <v>568</v>
       </c>
       <c r="Y71" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z71" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="AA71">
-        <v>0.9970088962341721</v>
+        <v>0.92007975165213307</v>
       </c>
       <c r="AB71">
-        <v>54.836902373510455</v>
+        <v>1465.2045530442279</v>
       </c>
       <c r="AD71" t="s">
         <v>445</v>
@@ -16848,13 +16848,13 @@
         <v>944</v>
       </c>
       <c r="AN71" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="AO71">
-        <v>0.95931345925264233</v>
+        <v>0.98255203569076077</v>
       </c>
       <c r="AP71">
-        <v>745.91991370155699</v>
+        <v>319.879345669386</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -16919,16 +16919,16 @@
         <v>570</v>
       </c>
       <c r="Y72" t="s">
-        <v>349</v>
+        <v>437</v>
       </c>
       <c r="Z72" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="AA72">
-        <v>0.98828003950132159</v>
+        <v>0.96305263459297863</v>
       </c>
       <c r="AB72">
-        <v>214.8659424757702</v>
+        <v>677.36836579539192</v>
       </c>
       <c r="AD72" t="s">
         <v>445</v>
@@ -16958,13 +16958,13 @@
         <v>945</v>
       </c>
       <c r="AN72" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AO72">
-        <v>0.99411928823407203</v>
+        <v>0.98977574375304844</v>
       </c>
       <c r="AP72">
-        <v>107.81304904201184</v>
+        <v>187.44469786077892</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -16999,7 +16999,7 @@
         <v>24.67146067932309</v>
       </c>
       <c r="M73">
-        <v>0.20266229838738631</v>
+        <v>0.20267468740491282</v>
       </c>
       <c r="O73" t="s">
         <v>445</v>
@@ -17029,16 +17029,16 @@
         <v>572</v>
       </c>
       <c r="Y73" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="Z73" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AA73">
-        <v>0.99382591612551541</v>
+        <v>0.98522854207859256</v>
       </c>
       <c r="AB73">
-        <v>113.1915376988852</v>
+        <v>270.81006189247</v>
       </c>
       <c r="AD73" t="s">
         <v>445</v>
@@ -17068,13 +17068,13 @@
         <v>946</v>
       </c>
       <c r="AN73" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="AO73">
-        <v>0.9790694594776973</v>
+        <v>0.94216773987491098</v>
       </c>
       <c r="AP73">
-        <v>383.72657624221517</v>
+        <v>1060.2581022932995</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -17139,16 +17139,16 @@
         <v>574</v>
       </c>
       <c r="Y74" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="Z74" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA74">
-        <v>0.99482528705797657</v>
+        <v>0.99185644171670617</v>
       </c>
       <c r="AB74">
-        <v>94.869737270428971</v>
+        <v>149.29856852705402</v>
       </c>
       <c r="AD74" t="s">
         <v>445</v>
@@ -17178,13 +17178,13 @@
         <v>947</v>
       </c>
       <c r="AN74" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="AO74">
-        <v>0.99570788786991582</v>
+        <v>0.9937640046384969</v>
       </c>
       <c r="AP74">
-        <v>78.688722384876669</v>
+        <v>114.32658162755614</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -17249,16 +17249,16 @@
         <v>576</v>
       </c>
       <c r="Y75" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="Z75" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="AA75">
-        <v>0.97321507838078658</v>
+        <v>0.94189846566095958</v>
       </c>
       <c r="AB75">
-        <v>491.05689635224547</v>
+        <v>1065.1947962157406</v>
       </c>
       <c r="AD75" t="s">
         <v>445</v>
@@ -17288,13 +17288,13 @@
         <v>948</v>
       </c>
       <c r="AN75" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="AO75">
-        <v>0.98562252349041679</v>
+        <v>0.98434157772378295</v>
       </c>
       <c r="AP75">
-        <v>263.58706934235943</v>
+        <v>287.07107506397949</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -17359,16 +17359,16 @@
         <v>578</v>
       </c>
       <c r="Y76" t="s">
-        <v>380</v>
+        <v>439</v>
       </c>
       <c r="Z76" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="AA76">
-        <v>0.97866893212504957</v>
+        <v>0.95001627981732095</v>
       </c>
       <c r="AB76">
-        <v>391.06957770742463</v>
+        <v>916.36820334911533</v>
       </c>
       <c r="AD76" t="s">
         <v>445</v>
@@ -17398,13 +17398,13 @@
         <v>949</v>
       </c>
       <c r="AN76" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="AO76">
-        <v>0.94920173100235461</v>
+        <v>0.98724240938456542</v>
       </c>
       <c r="AP76">
-        <v>931.3015982901652</v>
+        <v>233.88916128296634</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -17469,16 +17469,16 @@
         <v>580</v>
       </c>
       <c r="Y77" t="s">
-        <v>381</v>
+        <v>441</v>
       </c>
       <c r="Z77" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="AA77">
-        <v>0.9933008323747714</v>
+        <v>0.98042178820377779</v>
       </c>
       <c r="AB77">
-        <v>122.81807312919075</v>
+        <v>358.93388293074008</v>
       </c>
       <c r="AD77" t="s">
         <v>445</v>
@@ -17508,13 +17508,13 @@
         <v>950</v>
       </c>
       <c r="AN77" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AO77">
-        <v>0.94099051948143053</v>
+        <v>0.99486897494175219</v>
       </c>
       <c r="AP77">
-        <v>1081.8404761737738</v>
+        <v>94.068792734543848</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -17579,16 +17579,16 @@
         <v>582</v>
       </c>
       <c r="Y78" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="Z78" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="AA78">
-        <v>0.9771403150431911</v>
+        <v>0.95808092951199286</v>
       </c>
       <c r="AB78">
-        <v>419.09422420816315</v>
+        <v>768.51629228013144</v>
       </c>
       <c r="AD78" t="s">
         <v>445</v>
@@ -17618,13 +17618,13 @@
         <v>951</v>
       </c>
       <c r="AN78" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="AO78">
-        <v>0.97163156886146174</v>
+        <v>0.99698330098522958</v>
       </c>
       <c r="AP78">
-        <v>520.0879042065344</v>
+        <v>55.306148604123919</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -17659,7 +17659,7 @@
         <v>56.239799361911793</v>
       </c>
       <c r="M79">
-        <v>0.19891610173338561</v>
+        <v>0.19895107262484735</v>
       </c>
       <c r="O79" t="s">
         <v>445</v>
@@ -17689,16 +17689,16 @@
         <v>584</v>
       </c>
       <c r="Y79" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Z79" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AA79">
-        <v>0.96576017716725859</v>
+        <v>0.98362353815347903</v>
       </c>
       <c r="AB79">
-        <v>627.73008526692502</v>
+        <v>300.23513385288544</v>
       </c>
       <c r="AD79" t="s">
         <v>445</v>
@@ -17728,13 +17728,13 @@
         <v>952</v>
       </c>
       <c r="AN79" t="s">
-        <v>688</v>
+        <v>648</v>
       </c>
       <c r="AO79">
-        <v>0.99407790982046917</v>
+        <v>0.95884281124958637</v>
       </c>
       <c r="AP79">
-        <v>108.57165329139941</v>
+        <v>754.54846042424947</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -17799,16 +17799,16 @@
         <v>586</v>
       </c>
       <c r="Y80" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Z80" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="AA80">
-        <v>0.99320659129827649</v>
+        <v>0.99495707351657814</v>
       </c>
       <c r="AB80">
-        <v>124.54582619826394</v>
+        <v>92.453652196066486</v>
       </c>
       <c r="AD80" t="s">
         <v>445</v>
@@ -17838,13 +17838,13 @@
         <v>953</v>
       </c>
       <c r="AN80" t="s">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="AO80">
-        <v>0.97471651986393804</v>
+        <v>0.96628526147979277</v>
       </c>
       <c r="AP80">
-        <v>463.53046916113516</v>
+        <v>618.10353953713195</v>
       </c>
     </row>
     <row r="81" spans="2:42">
@@ -17879,7 +17879,7 @@
         <v>74.120337453709965</v>
       </c>
       <c r="M81">
-        <v>0.20182337922777235</v>
+        <v>0.20367785944499259</v>
       </c>
       <c r="O81" t="s">
         <v>445</v>
@@ -17909,16 +17909,16 @@
         <v>588</v>
       </c>
       <c r="Y81" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="Z81" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="AA81">
-        <v>0.97901340677155257</v>
+        <v>0.969236873889878</v>
       </c>
       <c r="AB81">
-        <v>384.75420918820265</v>
+        <v>563.9906453522367</v>
       </c>
       <c r="AD81" t="s">
         <v>445</v>
@@ -17948,13 +17948,13 @@
         <v>954</v>
       </c>
       <c r="AN81" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="AO81">
-        <v>0.95301935344113697</v>
+        <v>0.99188307586951852</v>
       </c>
       <c r="AP81">
-        <v>861.31185357915479</v>
+        <v>148.81027572549408</v>
       </c>
     </row>
     <row r="82" spans="2:42">
@@ -17989,7 +17989,7 @@
         <v>8.4528050675863646</v>
       </c>
       <c r="M82">
-        <v>0.20159598701952061</v>
+        <v>0.2016605208446671</v>
       </c>
       <c r="O82" t="s">
         <v>445</v>
@@ -18019,16 +18019,16 @@
         <v>590</v>
       </c>
       <c r="Y82" t="s">
-        <v>363</v>
+        <v>435</v>
       </c>
       <c r="Z82" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="AA82">
-        <v>0.99459695303037288</v>
+        <v>0.93773368388956246</v>
       </c>
       <c r="AB82">
-        <v>99.055861109831142</v>
+        <v>1141.5491286913555</v>
       </c>
       <c r="AD82" t="s">
         <v>445</v>
@@ -18058,13 +18058,13 @@
         <v>955</v>
       </c>
       <c r="AN82" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="AO82">
-        <v>0.99443080330687583</v>
+        <v>0.93449855145693639</v>
       </c>
       <c r="AP82">
-        <v>102.10193937394267</v>
+        <v>1200.8598899561664</v>
       </c>
     </row>
     <row r="83" spans="2:42">
@@ -18099,7 +18099,7 @@
         <v>59.068455369411964</v>
       </c>
       <c r="M83">
-        <v>0.20737196179823966</v>
+        <v>0.20738163955106215</v>
       </c>
       <c r="O83" t="s">
         <v>445</v>
@@ -18129,16 +18129,16 @@
         <v>592</v>
       </c>
       <c r="Y83" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="Z83" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AA83">
-        <v>0.99519268990415388</v>
+        <v>0.99059066767492976</v>
       </c>
       <c r="AB83">
-        <v>88.134018423846243</v>
+        <v>172.50442595962087</v>
       </c>
       <c r="AD83" t="s">
         <v>445</v>
@@ -18168,13 +18168,13 @@
         <v>956</v>
       </c>
       <c r="AN83" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="AO83">
-        <v>0.99161135964647729</v>
+        <v>0.96937670635957107</v>
       </c>
       <c r="AP83">
-        <v>153.79173981458226</v>
+        <v>561.42705007453139</v>
       </c>
     </row>
     <row r="84" spans="2:42">
@@ -18239,16 +18239,16 @@
         <v>594</v>
       </c>
       <c r="Y84" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="Z84" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="AA84">
-        <v>0.98376991098916067</v>
+        <v>0.95570380597210192</v>
       </c>
       <c r="AB84">
-        <v>297.55163186538817</v>
+        <v>812.09689051146574</v>
       </c>
       <c r="AD84" t="s">
         <v>445</v>
@@ -18278,13 +18278,13 @@
         <v>957</v>
       </c>
       <c r="AN84" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="AO84">
-        <v>0.99096791212626811</v>
+        <v>0.96461853105171591</v>
       </c>
       <c r="AP84">
-        <v>165.5882776850855</v>
+        <v>648.66026405187517</v>
       </c>
     </row>
     <row r="85" spans="2:42">
@@ -18349,16 +18349,16 @@
         <v>596</v>
       </c>
       <c r="Y85" t="s">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="Z85" t="s">
-        <v>646</v>
+        <v>682</v>
       </c>
       <c r="AA85">
-        <v>0.99221414970221189</v>
+        <v>0.98883273909819114</v>
       </c>
       <c r="AB85">
-        <v>142.74058879278186</v>
+        <v>204.7331165331625</v>
       </c>
       <c r="AD85" t="s">
         <v>445</v>
@@ -18388,13 +18388,13 @@
         <v>958</v>
       </c>
       <c r="AN85" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="AO85">
-        <v>0.99153287968327641</v>
+        <v>0.99443080330687583</v>
       </c>
       <c r="AP85">
-        <v>155.23053913993309</v>
+        <v>102.10193937394267</v>
       </c>
     </row>
     <row r="86" spans="2:42">
@@ -18429,7 +18429,7 @@
         <v>72.5473930066169</v>
       </c>
       <c r="M86">
-        <v>0.20354412180741346</v>
+        <v>0.2041727547388352</v>
       </c>
       <c r="O86" t="s">
         <v>445</v>
@@ -18459,16 +18459,16 @@
         <v>598</v>
       </c>
       <c r="Y86" t="s">
-        <v>350</v>
+        <v>419</v>
       </c>
       <c r="Z86" t="s">
-        <v>683</v>
+        <v>662</v>
       </c>
       <c r="AA86">
-        <v>0.99480818130085191</v>
+        <v>0.98262913774151028</v>
       </c>
       <c r="AB86">
-        <v>95.183342817714731</v>
+        <v>318.46580807231078</v>
       </c>
       <c r="AD86" t="s">
         <v>445</v>
@@ -18498,13 +18498,13 @@
         <v>959</v>
       </c>
       <c r="AN86" t="s">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="AO86">
-        <v>0.99568711277871247</v>
+        <v>0.99161135964647729</v>
       </c>
       <c r="AP86">
-        <v>79.069599056938102</v>
+        <v>153.79173981458226</v>
       </c>
     </row>
     <row r="87" spans="2:42">
@@ -18539,7 +18539,7 @@
         <v>111.90472691966944</v>
       </c>
       <c r="M87">
-        <v>0.14571397623211749</v>
+        <v>0.2081628231887393</v>
       </c>
       <c r="O87" t="s">
         <v>445</v>
@@ -18569,16 +18569,16 @@
         <v>600</v>
       </c>
       <c r="Y87" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
       <c r="Z87" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="AA87">
-        <v>0.92426797711114228</v>
+        <v>0.99090558233812054</v>
       </c>
       <c r="AB87">
-        <v>1388.420419629058</v>
+        <v>166.73099046779075</v>
       </c>
       <c r="AD87" t="s">
         <v>445</v>
@@ -18608,13 +18608,13 @@
         <v>960</v>
       </c>
       <c r="AN87" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="AO87">
-        <v>0.98225029258055574</v>
+        <v>0.99096791212626811</v>
       </c>
       <c r="AP87">
-        <v>325.41130268981078</v>
+        <v>165.5882776850855</v>
       </c>
     </row>
     <row r="88" spans="2:42">
@@ -18679,16 +18679,16 @@
         <v>602</v>
       </c>
       <c r="Y88" t="s">
-        <v>389</v>
+        <v>440</v>
       </c>
       <c r="Z88" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="AA88">
-        <v>0.92861598426622882</v>
+        <v>0.99144634427862732</v>
       </c>
       <c r="AB88">
-        <v>1308.7069551191387</v>
+        <v>156.81702155849862</v>
       </c>
       <c r="AD88" t="s">
         <v>445</v>
@@ -18718,13 +18718,13 @@
         <v>961</v>
       </c>
       <c r="AN88" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="AO88">
-        <v>0.982419047139102</v>
+        <v>0.99153287968327641</v>
       </c>
       <c r="AP88">
-        <v>322.31746911646275</v>
+        <v>155.23053913993309</v>
       </c>
     </row>
     <row r="89" spans="2:42">
@@ -18789,16 +18789,16 @@
         <v>604</v>
       </c>
       <c r="Y89" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="Z89" t="s">
         <v>684</v>
       </c>
       <c r="AA89">
-        <v>0.99521113523741833</v>
+        <v>0.98368128171218772</v>
       </c>
       <c r="AB89">
-        <v>87.795853980664262</v>
+        <v>299.17650194322596</v>
       </c>
       <c r="AD89" t="s">
         <v>445</v>
@@ -18828,13 +18828,13 @@
         <v>962</v>
       </c>
       <c r="AN89" t="s">
-        <v>646</v>
+        <v>668</v>
       </c>
       <c r="AO89">
-        <v>0.97789502766167302</v>
+        <v>0.99568711277871247</v>
       </c>
       <c r="AP89">
-        <v>405.25782620266216</v>
+        <v>79.069599056938102</v>
       </c>
     </row>
     <row r="90" spans="2:42">
@@ -18869,7 +18869,7 @@
         <v>0.50085118024234676</v>
       </c>
       <c r="M90">
-        <v>0.19387374542696106</v>
+        <v>0.19397396392996696</v>
       </c>
       <c r="O90" t="s">
         <v>445</v>
@@ -18899,16 +18899,16 @@
         <v>606</v>
       </c>
       <c r="Y90" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Z90" t="s">
         <v>685</v>
       </c>
       <c r="AA90">
-        <v>0.98246197339983365</v>
+        <v>0.99448084580495932</v>
       </c>
       <c r="AB90">
-        <v>321.53048766971619</v>
+        <v>101.18449357574643</v>
       </c>
       <c r="AD90" t="s">
         <v>445</v>
@@ -18938,13 +18938,13 @@
         <v>963</v>
       </c>
       <c r="AN90" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="AO90">
-        <v>0.99485109969932284</v>
+        <v>0.98225029258055574</v>
       </c>
       <c r="AP90">
-        <v>94.396505512414166</v>
+        <v>325.41130268981078</v>
       </c>
     </row>
     <row r="91" spans="2:42">
@@ -19009,16 +19009,16 @@
         <v>608</v>
       </c>
       <c r="Y91" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Z91" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="AA91">
-        <v>0.98352964899150075</v>
+        <v>0.98211683915529446</v>
       </c>
       <c r="AB91">
-        <v>301.95643515581952</v>
+        <v>327.85794881960226</v>
       </c>
       <c r="AD91" t="s">
         <v>445</v>
@@ -19048,13 +19048,13 @@
         <v>964</v>
       </c>
       <c r="AN91" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="AO91">
-        <v>0.97344873028830825</v>
+        <v>0.982419047139102</v>
       </c>
       <c r="AP91">
-        <v>486.77327804768265</v>
+        <v>322.31746911646275</v>
       </c>
     </row>
     <row r="92" spans="2:42">
@@ -19119,16 +19119,16 @@
         <v>610</v>
       </c>
       <c r="Y92" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Z92" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="AA92">
-        <v>0.91847114692356346</v>
+        <v>0.9804939638153034</v>
       </c>
       <c r="AB92">
-        <v>1494.6956397346703</v>
+        <v>357.61066338610357</v>
       </c>
       <c r="AD92" t="s">
         <v>445</v>
@@ -19158,13 +19158,13 @@
         <v>965</v>
       </c>
       <c r="AN92" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="AO92">
-        <v>0.98192694200361774</v>
+        <v>0.97789502766167302</v>
       </c>
       <c r="AP92">
-        <v>331.33939660034207</v>
+        <v>405.25782620266216</v>
       </c>
     </row>
     <row r="93" spans="2:42">
@@ -19199,7 +19199,7 @@
         <v>6.4851879183304098</v>
       </c>
       <c r="M93">
-        <v>0.16229821357567761</v>
+        <v>0.16245073467312587</v>
       </c>
       <c r="O93" t="s">
         <v>445</v>
@@ -19229,16 +19229,16 @@
         <v>612</v>
       </c>
       <c r="Y93" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="Z93" t="s">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="AA93">
-        <v>0.92680423740224549</v>
+        <v>0.99112806655302721</v>
       </c>
       <c r="AB93">
-        <v>1341.9223142921653</v>
+        <v>162.65211319450148</v>
       </c>
       <c r="AD93" t="s">
         <v>445</v>
@@ -19268,13 +19268,13 @@
         <v>966</v>
       </c>
       <c r="AN93" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="AO93">
-        <v>0.99188307586951852</v>
+        <v>0.99485109969932284</v>
       </c>
       <c r="AP93">
-        <v>148.81027572549408</v>
+        <v>94.396505512414166</v>
       </c>
     </row>
     <row r="94" spans="2:42">
@@ -19339,16 +19339,16 @@
         <v>614</v>
       </c>
       <c r="Y94" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="Z94" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="AA94">
-        <v>0.96447115506861258</v>
+        <v>0.94480589710631147</v>
       </c>
       <c r="AB94">
-        <v>651.36215707543533</v>
+        <v>1011.8918863842907</v>
       </c>
       <c r="AD94" t="s">
         <v>445</v>
@@ -19378,13 +19378,13 @@
         <v>967</v>
       </c>
       <c r="AN94" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="AO94">
-        <v>0.93449855145693639</v>
+        <v>0.97344873028830825</v>
       </c>
       <c r="AP94">
-        <v>1200.8598899561664</v>
+        <v>486.77327804768265</v>
       </c>
     </row>
     <row r="95" spans="2:42">
@@ -19449,16 +19449,16 @@
         <v>616</v>
       </c>
       <c r="Y95" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="Z95" t="s">
         <v>686</v>
       </c>
       <c r="AA95">
-        <v>0.98368128171218772</v>
+        <v>0.99521113523741833</v>
       </c>
       <c r="AB95">
-        <v>299.17650194322596</v>
+        <v>87.795853980664262</v>
       </c>
       <c r="AD95" t="s">
         <v>445</v>
@@ -19488,13 +19488,13 @@
         <v>968</v>
       </c>
       <c r="AN95" t="s">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="AO95">
-        <v>0.96937670635957107</v>
+        <v>0.98192694200361774</v>
       </c>
       <c r="AP95">
-        <v>561.42705007453139</v>
+        <v>331.33939660034207</v>
       </c>
     </row>
     <row r="96" spans="2:42">
@@ -19559,16 +19559,16 @@
         <v>618</v>
       </c>
       <c r="Y96" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="Z96" t="s">
         <v>687</v>
       </c>
       <c r="AA96">
-        <v>0.99448084580495932</v>
+        <v>0.98246197339983365</v>
       </c>
       <c r="AB96">
-        <v>101.18449357574643</v>
+        <v>321.53048766971619</v>
       </c>
       <c r="AD96" t="s">
         <v>445</v>
@@ -19598,13 +19598,13 @@
         <v>969</v>
       </c>
       <c r="AN96" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AO96">
-        <v>0.96461853105171591</v>
+        <v>0.97196184623196236</v>
       </c>
       <c r="AP96">
-        <v>648.66026405187517</v>
+        <v>514.03281908068925</v>
       </c>
     </row>
     <row r="97" spans="2:42">
@@ -19639,7 +19639,7 @@
         <v>46.796269813931573</v>
       </c>
       <c r="M97">
-        <v>0.19916379708782467</v>
+        <v>0.19921713910064925</v>
       </c>
       <c r="O97" t="s">
         <v>445</v>
@@ -19669,16 +19669,16 @@
         <v>620</v>
       </c>
       <c r="Y97" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="Z97" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="AA97">
-        <v>0.98211683915529446</v>
+        <v>0.98352964899150075</v>
       </c>
       <c r="AB97">
-        <v>327.85794881960226</v>
+        <v>301.95643515581952</v>
       </c>
       <c r="AD97" t="s">
         <v>445</v>
@@ -19708,13 +19708,13 @@
         <v>970</v>
       </c>
       <c r="AN97" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="AO97">
-        <v>0.98407466378375608</v>
+        <v>0.92143845786947276</v>
       </c>
       <c r="AP97">
-        <v>291.96449729780619</v>
+        <v>1440.294939059665</v>
       </c>
     </row>
     <row r="98" spans="2:42">
@@ -19749,7 +19749,7 @@
         <v>125.26728427243935</v>
       </c>
       <c r="M98">
-        <v>0.19826237089400434</v>
+        <v>0.19826420433736899</v>
       </c>
       <c r="O98" t="s">
         <v>445</v>
@@ -19779,16 +19779,16 @@
         <v>622</v>
       </c>
       <c r="Y98" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z98" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="AA98">
-        <v>0.9804939638153034</v>
+        <v>0.91847114692356346</v>
       </c>
       <c r="AB98">
-        <v>357.61066338610357</v>
+        <v>1494.6956397346703</v>
       </c>
       <c r="AD98" t="s">
         <v>445</v>
@@ -19818,13 +19818,13 @@
         <v>971</v>
       </c>
       <c r="AN98" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="AO98">
-        <v>0.9542882304111121</v>
+        <v>0.99544850388702388</v>
       </c>
       <c r="AP98">
-        <v>838.04910912961134</v>
+        <v>83.444095404561224</v>
       </c>
     </row>
     <row r="99" spans="2:42">
@@ -19859,7 +19859,7 @@
         <v>11.350931098153549</v>
       </c>
       <c r="M99">
-        <v>0.19443751451323907</v>
+        <v>0.19448671891839411</v>
       </c>
       <c r="O99" t="s">
         <v>445</v>
@@ -19889,16 +19889,16 @@
         <v>624</v>
       </c>
       <c r="Y99" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="Z99" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="AA99">
-        <v>0.99112806655302721</v>
+        <v>0.92680423740224549</v>
       </c>
       <c r="AB99">
-        <v>162.65211319450148</v>
+        <v>1341.9223142921653</v>
       </c>
       <c r="AD99" t="s">
         <v>445</v>
@@ -19928,13 +19928,13 @@
         <v>972</v>
       </c>
       <c r="AN99" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="AO99">
-        <v>0.99582108489984233</v>
+        <v>0.99073782529254428</v>
       </c>
       <c r="AP99">
-        <v>76.613443502890505</v>
+        <v>169.80653630335468</v>
       </c>
     </row>
     <row r="100" spans="2:42">
@@ -19999,16 +19999,16 @@
         <v>626</v>
       </c>
       <c r="Y100" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="Z100" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="AA100">
-        <v>0.94480589710631147</v>
+        <v>0.96447115506861258</v>
       </c>
       <c r="AB100">
-        <v>1011.8918863842907</v>
+        <v>651.36215707543533</v>
       </c>
       <c r="AD100" t="s">
         <v>445</v>
@@ -20038,13 +20038,13 @@
         <v>973</v>
       </c>
       <c r="AN100" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
       <c r="AO100">
-        <v>0.99800187122714112</v>
+        <v>0.95849712823420175</v>
       </c>
       <c r="AP100">
-        <v>36.632360835745096</v>
+        <v>760.8859823729681</v>
       </c>
     </row>
     <row r="101" spans="2:42">
@@ -20109,16 +20109,16 @@
         <v>628</v>
       </c>
       <c r="Y101" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="Z101" t="s">
-        <v>664</v>
+        <v>688</v>
       </c>
       <c r="AA101">
-        <v>0.96039250350097727</v>
+        <v>0.99480818130085191</v>
       </c>
       <c r="AB101">
-        <v>726.13743581541678</v>
+        <v>95.183342817714731</v>
       </c>
       <c r="AD101" t="s">
         <v>445</v>
@@ -20148,13 +20148,13 @@
         <v>974</v>
       </c>
       <c r="AN101" t="s">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="AO101">
-        <v>0.98958136888311932</v>
+        <v>0.99146900514737779</v>
       </c>
       <c r="AP101">
-        <v>191.00823714281216</v>
+        <v>156.40157229807483</v>
       </c>
     </row>
     <row r="102" spans="2:42">
@@ -20219,16 +20219,16 @@
         <v>630</v>
       </c>
       <c r="Y102" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="Z102" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AA102">
-        <v>0.96501488785990974</v>
+        <v>0.92426797711114228</v>
       </c>
       <c r="AB102">
-        <v>641.39372256832166</v>
+        <v>1388.420419629058</v>
       </c>
       <c r="AD102" t="s">
         <v>445</v>
@@ -20258,13 +20258,13 @@
         <v>975</v>
       </c>
       <c r="AN102" t="s">
-        <v>670</v>
+        <v>689</v>
       </c>
       <c r="AO102">
-        <v>0.97298156476333331</v>
+        <v>0.97494022509165501</v>
       </c>
       <c r="AP102">
-        <v>495.337979338889</v>
+        <v>459.42920665299067</v>
       </c>
     </row>
     <row r="103" spans="2:42">
@@ -20329,16 +20329,16 @@
         <v>632</v>
       </c>
       <c r="Y103" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="Z103" t="s">
-        <v>688</v>
+        <v>648</v>
       </c>
       <c r="AA103">
-        <v>0.99401420652619221</v>
+        <v>0.92861598426622882</v>
       </c>
       <c r="AB103">
-        <v>109.73954701980865</v>
+        <v>1308.7069551191387</v>
       </c>
       <c r="AD103" t="s">
         <v>445</v>
@@ -20368,13 +20368,13 @@
         <v>976</v>
       </c>
       <c r="AN103" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AO103">
-        <v>0.97196184623196236</v>
+        <v>0.99342004180524168</v>
       </c>
       <c r="AP103">
-        <v>514.03281908068925</v>
+        <v>120.63256690390332</v>
       </c>
     </row>
     <row r="104" spans="2:42">
@@ -20409,7 +20409,7 @@
         <v>13.41944237534064</v>
       </c>
       <c r="M104">
-        <v>0.1940095018593084</v>
+        <v>0.19401088202736752</v>
       </c>
       <c r="O104" t="s">
         <v>445</v>
@@ -20439,16 +20439,16 @@
         <v>634</v>
       </c>
       <c r="Y104" t="s">
-        <v>400</v>
+        <v>358</v>
       </c>
       <c r="Z104" t="s">
         <v>689</v>
       </c>
       <c r="AA104">
-        <v>0.99368555142692816</v>
+        <v>0.97630367280108865</v>
       </c>
       <c r="AB104">
-        <v>115.76489050631628</v>
+        <v>434.43266531337389</v>
       </c>
       <c r="AD104" t="s">
         <v>445</v>
@@ -20478,13 +20478,13 @@
         <v>977</v>
       </c>
       <c r="AN104" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="AO104">
-        <v>0.92143845786947276</v>
+        <v>0.99501310191160197</v>
       </c>
       <c r="AP104">
-        <v>1440.294939059665</v>
+        <v>91.426464953964114</v>
       </c>
     </row>
     <row r="105" spans="2:42">
@@ -20519,7 +20519,7 @@
         <v>90.868327533917025</v>
       </c>
       <c r="M105">
-        <v>0.1990343507476294</v>
+        <v>0.19916645206402311</v>
       </c>
       <c r="O105" t="s">
         <v>445</v>
@@ -20549,16 +20549,16 @@
         <v>636</v>
       </c>
       <c r="Y105" t="s">
-        <v>411</v>
+        <v>360</v>
       </c>
       <c r="Z105" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="AA105">
-        <v>0.94386714187064036</v>
+        <v>0.978447054607678</v>
       </c>
       <c r="AB105">
-        <v>1029.10239903826</v>
+        <v>395.13733219256937</v>
       </c>
       <c r="AD105" t="s">
         <v>445</v>
@@ -20588,13 +20588,13 @@
         <v>978</v>
       </c>
       <c r="AN105" t="s">
-        <v>673</v>
+        <v>648</v>
       </c>
       <c r="AO105">
-        <v>0.99544850388702388</v>
+        <v>0.9633630443304535</v>
       </c>
       <c r="AP105">
-        <v>83.444095404561224</v>
+        <v>671.67752060835289</v>
       </c>
     </row>
     <row r="106" spans="2:42">
@@ -20659,16 +20659,16 @@
         <v>638</v>
       </c>
       <c r="Y106" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="Z106" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="AA106">
-        <v>0.92007975165213307</v>
+        <v>0.96307923215762514</v>
       </c>
       <c r="AB106">
-        <v>1465.2045530442279</v>
+        <v>676.88074377687337</v>
       </c>
       <c r="AD106" t="s">
         <v>445</v>
@@ -20698,13 +20698,13 @@
         <v>979</v>
       </c>
       <c r="AN106" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="AO106">
-        <v>0.99073782529254428</v>
+        <v>0.98994878939511521</v>
       </c>
       <c r="AP106">
-        <v>169.80653630335468</v>
+        <v>184.27219442288737</v>
       </c>
     </row>
     <row r="107" spans="2:42">
@@ -20739,7 +20739,7 @@
         <v>14.413610775537448</v>
       </c>
       <c r="M107">
-        <v>0.16368090894115184</v>
+        <v>0.16400816875645291</v>
       </c>
       <c r="O107" t="s">
         <v>445</v>
@@ -20769,16 +20769,16 @@
         <v>640</v>
       </c>
       <c r="Y107" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="Z107" t="s">
-        <v>649</v>
+        <v>675</v>
       </c>
       <c r="AA107">
-        <v>0.96305263459297863</v>
+        <v>0.9793351210469925</v>
       </c>
       <c r="AB107">
-        <v>677.36836579539192</v>
+        <v>378.85611413846999</v>
       </c>
       <c r="AD107" t="s">
         <v>445</v>
@@ -20808,13 +20808,13 @@
         <v>980</v>
       </c>
       <c r="AN107" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="AO107">
-        <v>0.95849712823420175</v>
+        <v>0.96684854231168849</v>
       </c>
       <c r="AP107">
-        <v>760.8859823729681</v>
+        <v>607.77672428571168</v>
       </c>
     </row>
   </sheetData>
@@ -20823,7 +20823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C9A0EE-BE86-4DF3-A9CD-60C5C3A48CB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2BF19BD-815F-433D-B5C8-B191E7D545DA}">
   <dimension ref="B9:Z107"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20935,7 +20935,7 @@
         <v>1137</v>
       </c>
       <c r="K11" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="L11">
         <v>0.39861308799262429</v>
@@ -20968,7 +20968,7 @@
         <v>1331</v>
       </c>
       <c r="X11" t="s">
-        <v>1104</v>
+        <v>1134</v>
       </c>
       <c r="Y11">
         <v>17.855250000000002</v>
@@ -21036,7 +21036,7 @@
         <v>1333</v>
       </c>
       <c r="X12" t="s">
-        <v>1132</v>
+        <v>1104</v>
       </c>
       <c r="Y12">
         <v>22.539750000000002</v>
@@ -21071,7 +21071,7 @@
         <v>1141</v>
       </c>
       <c r="K13" t="s">
-        <v>884</v>
+        <v>921</v>
       </c>
       <c r="L13">
         <v>1.7523004426694913</v>
@@ -21104,7 +21104,7 @@
         <v>1335</v>
       </c>
       <c r="X13" t="s">
-        <v>1090</v>
+        <v>1123</v>
       </c>
       <c r="Y13">
         <v>56.926499999999997</v>
@@ -21139,7 +21139,7 @@
         <v>1143</v>
       </c>
       <c r="K14" t="s">
-        <v>920</v>
+        <v>947</v>
       </c>
       <c r="L14">
         <v>0.54907652770071036</v>
@@ -21172,7 +21172,7 @@
         <v>1337</v>
       </c>
       <c r="X14" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="Y14">
         <v>75.277500000000003</v>
@@ -21240,7 +21240,7 @@
         <v>1339</v>
       </c>
       <c r="X15" t="s">
-        <v>1098</v>
+        <v>1117</v>
       </c>
       <c r="Y15">
         <v>57.183750000000003</v>
@@ -21275,7 +21275,7 @@
         <v>1147</v>
       </c>
       <c r="K16" t="s">
-        <v>947</v>
+        <v>884</v>
       </c>
       <c r="L16">
         <v>3.6705701703872231</v>
@@ -21308,7 +21308,7 @@
         <v>1341</v>
       </c>
       <c r="X16" t="s">
-        <v>1107</v>
+        <v>1085</v>
       </c>
       <c r="Y16">
         <v>25.457249999999998</v>
@@ -21343,7 +21343,7 @@
         <v>1149</v>
       </c>
       <c r="K17" t="s">
-        <v>921</v>
+        <v>948</v>
       </c>
       <c r="L17">
         <v>17.939739935619471</v>
@@ -21376,7 +21376,7 @@
         <v>1343</v>
       </c>
       <c r="X17" t="s">
-        <v>1133</v>
+        <v>1105</v>
       </c>
       <c r="Y17">
         <v>7.21875</v>
@@ -21411,7 +21411,7 @@
         <v>1151</v>
       </c>
       <c r="K18" t="s">
-        <v>934</v>
+        <v>974</v>
       </c>
       <c r="L18">
         <v>5.003019932086108</v>
@@ -21444,7 +21444,7 @@
         <v>1345</v>
       </c>
       <c r="X18" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="Y18">
         <v>24.305250000000001</v>
@@ -21479,7 +21479,7 @@
         <v>1153</v>
       </c>
       <c r="K19" t="s">
-        <v>922</v>
+        <v>949</v>
       </c>
       <c r="L19">
         <v>2.5007371543803476</v>
@@ -21512,7 +21512,7 @@
         <v>1347</v>
       </c>
       <c r="X19" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="Y19">
         <v>7.2749999999999995E-2</v>
@@ -21547,7 +21547,7 @@
         <v>1155</v>
       </c>
       <c r="K20" t="s">
-        <v>966</v>
+        <v>954</v>
       </c>
       <c r="L20">
         <v>43.778801628691184</v>
@@ -21580,7 +21580,7 @@
         <v>1349</v>
       </c>
       <c r="X20" t="s">
-        <v>1124</v>
+        <v>1089</v>
       </c>
       <c r="Y20">
         <v>128.96625</v>
@@ -21615,7 +21615,7 @@
         <v>1157</v>
       </c>
       <c r="K21" t="s">
-        <v>893</v>
+        <v>935</v>
       </c>
       <c r="L21">
         <v>16.67304758176029</v>
@@ -21648,7 +21648,7 @@
         <v>1351</v>
       </c>
       <c r="X21" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="Y21">
         <v>12.42675</v>
@@ -21683,7 +21683,7 @@
         <v>1159</v>
       </c>
       <c r="K22" t="s">
-        <v>935</v>
+        <v>975</v>
       </c>
       <c r="L22">
         <v>27.668458564541282</v>
@@ -21716,7 +21716,7 @@
         <v>1353</v>
       </c>
       <c r="X22" t="s">
-        <v>1134</v>
+        <v>1106</v>
       </c>
       <c r="Y22">
         <v>78.813749999999999</v>
@@ -21751,7 +21751,7 @@
         <v>1161</v>
       </c>
       <c r="K23" t="s">
-        <v>927</v>
+        <v>940</v>
       </c>
       <c r="L23">
         <v>11.433145121744985</v>
@@ -21784,7 +21784,7 @@
         <v>1355</v>
       </c>
       <c r="X23" t="s">
-        <v>1125</v>
+        <v>1090</v>
       </c>
       <c r="Y23">
         <v>50.749499999999998</v>
@@ -21819,7 +21819,7 @@
         <v>1163</v>
       </c>
       <c r="K24" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="L24">
         <v>28.004210804186364</v>
@@ -21852,7 +21852,7 @@
         <v>1357</v>
       </c>
       <c r="X24" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="Y24">
         <v>46.347749999999998</v>
@@ -21920,7 +21920,7 @@
         <v>1359</v>
       </c>
       <c r="X25" t="s">
-        <v>1088</v>
+        <v>1102</v>
       </c>
       <c r="Y25">
         <v>66.771000000000001</v>
@@ -21955,7 +21955,7 @@
         <v>1167</v>
       </c>
       <c r="K26" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="L26">
         <v>27.944981415457875</v>
@@ -21988,7 +21988,7 @@
         <v>1361</v>
       </c>
       <c r="X26" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="Y26">
         <v>97.8</v>
@@ -22023,7 +22023,7 @@
         <v>1169</v>
       </c>
       <c r="K27" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="L27">
         <v>1.5549175890365936</v>
@@ -22056,7 +22056,7 @@
         <v>1363</v>
       </c>
       <c r="X27" t="s">
-        <v>1085</v>
+        <v>1125</v>
       </c>
       <c r="Y27">
         <v>107.74424999999999</v>
@@ -22091,7 +22091,7 @@
         <v>1171</v>
       </c>
       <c r="K28" t="s">
-        <v>936</v>
+        <v>976</v>
       </c>
       <c r="L28">
         <v>1.2492599133607241</v>
@@ -22124,7 +22124,7 @@
         <v>1365</v>
       </c>
       <c r="X28" t="s">
-        <v>1086</v>
+        <v>1126</v>
       </c>
       <c r="Y28">
         <v>51.907499999999999</v>
@@ -22159,7 +22159,7 @@
         <v>1173</v>
       </c>
       <c r="K29" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="L29">
         <v>1.2638441295051945</v>
@@ -22192,7 +22192,7 @@
         <v>1367</v>
       </c>
       <c r="X29" t="s">
-        <v>1087</v>
+        <v>1127</v>
       </c>
       <c r="Y29">
         <v>82.251000000000005</v>
@@ -22227,7 +22227,7 @@
         <v>1175</v>
       </c>
       <c r="K30" t="s">
-        <v>888</v>
+        <v>930</v>
       </c>
       <c r="L30">
         <v>2.4084314808324492</v>
@@ -22260,7 +22260,7 @@
         <v>1369</v>
       </c>
       <c r="X30" t="s">
-        <v>1108</v>
+        <v>1086</v>
       </c>
       <c r="Y30">
         <v>24.861000000000001</v>
@@ -22295,7 +22295,7 @@
         <v>1177</v>
       </c>
       <c r="K31" t="s">
-        <v>941</v>
+        <v>915</v>
       </c>
       <c r="L31">
         <v>64.149379205736523</v>
@@ -22328,7 +22328,7 @@
         <v>1371</v>
       </c>
       <c r="X31" t="s">
-        <v>1117</v>
+        <v>1110</v>
       </c>
       <c r="Y31">
         <v>24.351749999999999</v>
@@ -22363,7 +22363,7 @@
         <v>1179</v>
       </c>
       <c r="K32" t="s">
-        <v>942</v>
+        <v>916</v>
       </c>
       <c r="L32">
         <v>45.003988730231519</v>
@@ -22396,7 +22396,7 @@
         <v>1373</v>
       </c>
       <c r="X32" t="s">
-        <v>1099</v>
+        <v>1118</v>
       </c>
       <c r="Y32">
         <v>92.853750000000005</v>
@@ -22431,7 +22431,7 @@
         <v>1181</v>
       </c>
       <c r="K33" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="L33">
         <v>2.4098384326025282</v>
@@ -22464,7 +22464,7 @@
         <v>1375</v>
       </c>
       <c r="X33" t="s">
-        <v>1089</v>
+        <v>1103</v>
       </c>
       <c r="Y33">
         <v>126.06825000000001</v>
@@ -22499,7 +22499,7 @@
         <v>1183</v>
       </c>
       <c r="K34" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="L34">
         <v>7.719645967474376</v>
@@ -22532,7 +22532,7 @@
         <v>1377</v>
       </c>
       <c r="X34" t="s">
-        <v>1112</v>
+        <v>1094</v>
       </c>
       <c r="Y34">
         <v>39.077249999999999</v>
@@ -22567,7 +22567,7 @@
         <v>1185</v>
       </c>
       <c r="K35" t="s">
-        <v>915</v>
+        <v>925</v>
       </c>
       <c r="L35">
         <v>18.541668534317722</v>
@@ -22600,7 +22600,7 @@
         <v>1379</v>
       </c>
       <c r="X35" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="Y35">
         <v>102.20099999999999</v>
@@ -22635,7 +22635,7 @@
         <v>1187</v>
       </c>
       <c r="K36" t="s">
-        <v>937</v>
+        <v>977</v>
       </c>
       <c r="L36">
         <v>1.1328532040703319</v>
@@ -22668,7 +22668,7 @@
         <v>1381</v>
       </c>
       <c r="X36" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
       <c r="Y36">
         <v>141.21299999999999</v>
@@ -22703,7 +22703,7 @@
         <v>1189</v>
       </c>
       <c r="K37" t="s">
-        <v>943</v>
+        <v>917</v>
       </c>
       <c r="L37">
         <v>0.98752306400324941</v>
@@ -22736,7 +22736,7 @@
         <v>1383</v>
       </c>
       <c r="X37" t="s">
-        <v>1135</v>
+        <v>1107</v>
       </c>
       <c r="Y37">
         <v>431.52375000000001</v>
@@ -22771,7 +22771,7 @@
         <v>1191</v>
       </c>
       <c r="K38" t="s">
-        <v>970</v>
+        <v>895</v>
       </c>
       <c r="L38">
         <v>107.73017208627026</v>
@@ -22804,7 +22804,7 @@
         <v>1385</v>
       </c>
       <c r="X38" t="s">
-        <v>1109</v>
+        <v>1128</v>
       </c>
       <c r="Y38">
         <v>137.21775</v>
@@ -22839,7 +22839,7 @@
         <v>1193</v>
       </c>
       <c r="K39" t="s">
-        <v>948</v>
+        <v>885</v>
       </c>
       <c r="L39">
         <v>144.23483288788916</v>
@@ -22872,7 +22872,7 @@
         <v>1387</v>
       </c>
       <c r="X39" t="s">
-        <v>1100</v>
+        <v>1119</v>
       </c>
       <c r="Y39">
         <v>17.16225</v>
@@ -22907,7 +22907,7 @@
         <v>1195</v>
       </c>
       <c r="K40" t="s">
-        <v>938</v>
+        <v>978</v>
       </c>
       <c r="L40">
         <v>64.738650351652737</v>
@@ -22940,7 +22940,7 @@
         <v>1389</v>
       </c>
       <c r="X40" t="s">
-        <v>1113</v>
+        <v>1095</v>
       </c>
       <c r="Y40">
         <v>22.68825</v>
@@ -22975,7 +22975,7 @@
         <v>1197</v>
       </c>
       <c r="K41" t="s">
-        <v>889</v>
+        <v>931</v>
       </c>
       <c r="L41">
         <v>83.742151942949235</v>
@@ -23008,7 +23008,7 @@
         <v>1391</v>
       </c>
       <c r="X41" t="s">
-        <v>1126</v>
+        <v>1091</v>
       </c>
       <c r="Y41">
         <v>43.122</v>
@@ -23043,7 +23043,7 @@
         <v>1199</v>
       </c>
       <c r="K42" t="s">
-        <v>928</v>
+        <v>941</v>
       </c>
       <c r="L42">
         <v>40.053209434418129</v>
@@ -23076,7 +23076,7 @@
         <v>1393</v>
       </c>
       <c r="X42" t="s">
-        <v>1101</v>
+        <v>1120</v>
       </c>
       <c r="Y42">
         <v>63.436500000000002</v>
@@ -23111,7 +23111,7 @@
         <v>1201</v>
       </c>
       <c r="K43" t="s">
-        <v>944</v>
+        <v>918</v>
       </c>
       <c r="L43">
         <v>80.257558228094155</v>
@@ -23144,7 +23144,7 @@
         <v>1395</v>
       </c>
       <c r="X43" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
       <c r="Y43">
         <v>41.863500000000002</v>
@@ -23179,7 +23179,7 @@
         <v>1203</v>
       </c>
       <c r="K44" t="s">
-        <v>916</v>
+        <v>926</v>
       </c>
       <c r="L44">
         <v>108.98210875746523</v>
@@ -23212,7 +23212,7 @@
         <v>1397</v>
       </c>
       <c r="X44" t="s">
-        <v>1105</v>
+        <v>1135</v>
       </c>
       <c r="Y44">
         <v>122.985</v>
@@ -23247,7 +23247,7 @@
         <v>1205</v>
       </c>
       <c r="K45" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
       <c r="L45">
         <v>76.485540774017224</v>
@@ -23280,7 +23280,7 @@
         <v>1399</v>
       </c>
       <c r="X45" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="Y45">
         <v>41.619</v>
@@ -23315,7 +23315,7 @@
         <v>1207</v>
       </c>
       <c r="K46" t="s">
-        <v>894</v>
+        <v>936</v>
       </c>
       <c r="L46">
         <v>48.731974982686296</v>
@@ -23348,7 +23348,7 @@
         <v>1401</v>
       </c>
       <c r="X46" t="s">
-        <v>1102</v>
+        <v>1121</v>
       </c>
       <c r="Y46">
         <v>4.2930000000000001</v>
@@ -23383,7 +23383,7 @@
         <v>1209</v>
       </c>
       <c r="K47" t="s">
-        <v>929</v>
+        <v>942</v>
       </c>
       <c r="L47">
         <v>62.79159911093128</v>
@@ -23416,7 +23416,7 @@
         <v>1403</v>
       </c>
       <c r="X47" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="Y47">
         <v>79.873500000000007</v>
@@ -23451,7 +23451,7 @@
         <v>1211</v>
       </c>
       <c r="K48" t="s">
-        <v>949</v>
+        <v>886</v>
       </c>
       <c r="L48">
         <v>65.680044471431955</v>
@@ -23484,7 +23484,7 @@
         <v>1405</v>
       </c>
       <c r="X48" t="s">
-        <v>1114</v>
+        <v>1087</v>
       </c>
       <c r="Y48">
         <v>99.789000000000001</v>
@@ -23519,7 +23519,7 @@
         <v>1213</v>
       </c>
       <c r="K49" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="L49">
         <v>74.267839417946064</v>
@@ -23552,7 +23552,7 @@
         <v>1407</v>
       </c>
       <c r="X49" t="s">
-        <v>1103</v>
+        <v>1122</v>
       </c>
       <c r="Y49">
         <v>104.292</v>
@@ -23587,7 +23587,7 @@
         <v>1215</v>
       </c>
       <c r="K50" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="L50">
         <v>151.65467386640691</v>
@@ -23620,7 +23620,7 @@
         <v>1409</v>
       </c>
       <c r="X50" t="s">
-        <v>1110</v>
+        <v>1129</v>
       </c>
       <c r="Y50">
         <v>18.36</v>
@@ -23655,7 +23655,7 @@
         <v>1217</v>
       </c>
       <c r="K51" t="s">
-        <v>950</v>
+        <v>887</v>
       </c>
       <c r="L51">
         <v>67.284600831515021</v>
@@ -23688,7 +23688,7 @@
         <v>1411</v>
       </c>
       <c r="X51" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="Y51">
         <v>75.933000000000007</v>
@@ -23723,7 +23723,7 @@
         <v>1219</v>
       </c>
       <c r="K52" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="L52">
         <v>49.163937565783463</v>
@@ -23756,7 +23756,7 @@
         <v>1413</v>
       </c>
       <c r="X52" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="Y52">
         <v>6.9997499999999997</v>
@@ -23824,7 +23824,7 @@
         <v>1415</v>
       </c>
       <c r="X53" t="s">
-        <v>1091</v>
+        <v>1124</v>
       </c>
       <c r="Y53">
         <v>78.370500000000007</v>
@@ -23859,7 +23859,7 @@
         <v>1223</v>
       </c>
       <c r="K54" t="s">
-        <v>951</v>
+        <v>888</v>
       </c>
       <c r="L54">
         <v>88.093613990019378</v>
@@ -23892,7 +23892,7 @@
         <v>1417</v>
       </c>
       <c r="X54" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
       <c r="Y54">
         <v>33.83925</v>
@@ -23927,7 +23927,7 @@
         <v>1225</v>
       </c>
       <c r="K55" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="L55">
         <v>306.62374401608201</v>
@@ -23960,7 +23960,7 @@
         <v>1419</v>
       </c>
       <c r="X55" t="s">
-        <v>1136</v>
+        <v>1108</v>
       </c>
       <c r="Y55">
         <v>32.840249999999997</v>
@@ -23995,7 +23995,7 @@
         <v>1227</v>
       </c>
       <c r="K56" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="L56">
         <v>31.906406016589642</v>
@@ -24028,7 +24028,7 @@
         <v>1421</v>
       </c>
       <c r="X56" t="s">
-        <v>1106</v>
+        <v>1136</v>
       </c>
       <c r="Y56">
         <v>0.95399999999999996</v>
@@ -24096,7 +24096,7 @@
         <v>1423</v>
       </c>
       <c r="X57" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="Y57">
         <v>58.96875</v>
@@ -24131,7 +24131,7 @@
         <v>1231</v>
       </c>
       <c r="K58" t="s">
-        <v>971</v>
+        <v>896</v>
       </c>
       <c r="L58">
         <v>22.439823618580242</v>
@@ -24164,7 +24164,7 @@
         <v>1425</v>
       </c>
       <c r="X58" t="s">
-        <v>1127</v>
+        <v>1092</v>
       </c>
       <c r="Y58">
         <v>276.46350000000001</v>
@@ -24199,7 +24199,7 @@
         <v>1233</v>
       </c>
       <c r="K59" t="s">
-        <v>930</v>
+        <v>943</v>
       </c>
       <c r="L59">
         <v>2.950012771299138</v>
@@ -24232,7 +24232,7 @@
         <v>1427</v>
       </c>
       <c r="X59" t="s">
-        <v>1111</v>
+        <v>1130</v>
       </c>
       <c r="Y59">
         <v>84.236999999999995</v>
@@ -24267,7 +24267,7 @@
         <v>1235</v>
       </c>
       <c r="K60" t="s">
-        <v>931</v>
+        <v>944</v>
       </c>
       <c r="L60">
         <v>15.987623175380641</v>
@@ -24300,7 +24300,7 @@
         <v>1429</v>
       </c>
       <c r="X60" t="s">
-        <v>1115</v>
+        <v>1088</v>
       </c>
       <c r="Y60">
         <v>101.8995</v>
@@ -24335,7 +24335,7 @@
         <v>1237</v>
       </c>
       <c r="K61" t="s">
-        <v>952</v>
+        <v>889</v>
       </c>
       <c r="L61">
         <v>0.92130801234283921</v>
@@ -24368,7 +24368,7 @@
         <v>1431</v>
       </c>
       <c r="X61" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="Y61">
         <v>63.835500000000003</v>
@@ -24436,7 +24436,7 @@
         <v>1433</v>
       </c>
       <c r="X62" t="s">
-        <v>1128</v>
+        <v>1093</v>
       </c>
       <c r="Y62">
         <v>131.96250000000001</v>
@@ -24471,7 +24471,7 @@
         <v>1241</v>
       </c>
       <c r="K63" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="L63">
         <v>4.9624795440731315</v>
@@ -24506,7 +24506,7 @@
         <v>1243</v>
       </c>
       <c r="K64" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="L64">
         <v>5.8024432152518211</v>
@@ -24541,7 +24541,7 @@
         <v>1245</v>
       </c>
       <c r="K65" t="s">
-        <v>890</v>
+        <v>932</v>
       </c>
       <c r="L65">
         <v>30.040816717799608</v>
@@ -24576,7 +24576,7 @@
         <v>1247</v>
       </c>
       <c r="K66" t="s">
-        <v>972</v>
+        <v>897</v>
       </c>
       <c r="L66">
         <v>7.3613726419883463</v>
@@ -24611,7 +24611,7 @@
         <v>1249</v>
       </c>
       <c r="K67" t="s">
-        <v>917</v>
+        <v>927</v>
       </c>
       <c r="L67">
         <v>108.91929564165949</v>
@@ -24646,7 +24646,7 @@
         <v>1251</v>
       </c>
       <c r="K68" t="s">
-        <v>973</v>
+        <v>898</v>
       </c>
       <c r="L68">
         <v>0.15625630587072689</v>
@@ -24681,7 +24681,7 @@
         <v>1253</v>
       </c>
       <c r="K69" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="L69">
         <v>3.3695122486871476</v>
@@ -24716,7 +24716,7 @@
         <v>1255</v>
       </c>
       <c r="K70" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="L70">
         <v>30.705835313620341</v>
@@ -24786,7 +24786,7 @@
         <v>1259</v>
       </c>
       <c r="K72" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="L72">
         <v>17.192803298674693</v>
@@ -24821,7 +24821,7 @@
         <v>1261</v>
       </c>
       <c r="K73" t="s">
-        <v>886</v>
+        <v>923</v>
       </c>
       <c r="L73">
         <v>17.258734519286374</v>
@@ -24926,7 +24926,7 @@
         <v>1267</v>
       </c>
       <c r="K76" t="s">
-        <v>891</v>
+        <v>933</v>
       </c>
       <c r="L76">
         <v>79.890184200903121</v>
@@ -24961,7 +24961,7 @@
         <v>1269</v>
       </c>
       <c r="K77" t="s">
-        <v>953</v>
+        <v>890</v>
       </c>
       <c r="L77">
         <v>49.401067566974206</v>
@@ -24996,7 +24996,7 @@
         <v>1271</v>
       </c>
       <c r="K78" t="s">
-        <v>974</v>
+        <v>899</v>
       </c>
       <c r="L78">
         <v>42.327002358678541</v>
@@ -25031,7 +25031,7 @@
         <v>1273</v>
       </c>
       <c r="K79" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="L79">
         <v>106.28692550408161</v>
@@ -25066,7 +25066,7 @@
         <v>1275</v>
       </c>
       <c r="K80" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="L80">
         <v>117.47590792766253</v>
@@ -25101,7 +25101,7 @@
         <v>1277</v>
       </c>
       <c r="K81" t="s">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="L81">
         <v>30.349035200580289</v>
@@ -25136,7 +25136,7 @@
         <v>1279</v>
       </c>
       <c r="K82" t="s">
-        <v>945</v>
+        <v>919</v>
       </c>
       <c r="L82">
         <v>18.04196312682631</v>
@@ -25206,7 +25206,7 @@
         <v>1283</v>
       </c>
       <c r="K84" t="s">
-        <v>892</v>
+        <v>934</v>
       </c>
       <c r="L84">
         <v>4.5388067721428351</v>
@@ -25241,7 +25241,7 @@
         <v>1285</v>
       </c>
       <c r="K85" t="s">
-        <v>939</v>
+        <v>979</v>
       </c>
       <c r="L85">
         <v>61.7959751654546</v>
@@ -25276,7 +25276,7 @@
         <v>1287</v>
       </c>
       <c r="K86" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="L86">
         <v>64.726898545060607</v>
@@ -25311,7 +25311,7 @@
         <v>1289</v>
       </c>
       <c r="K87" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="L87">
         <v>118.54300475235763</v>
@@ -25346,7 +25346,7 @@
         <v>1291</v>
       </c>
       <c r="K88" t="s">
-        <v>946</v>
+        <v>920</v>
       </c>
       <c r="L88">
         <v>40.618167251235064</v>
@@ -25381,7 +25381,7 @@
         <v>1293</v>
       </c>
       <c r="K89" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="L89">
         <v>82.996246047592408</v>
@@ -25451,7 +25451,7 @@
         <v>1297</v>
       </c>
       <c r="K91" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="L91">
         <v>0.76722131470466981</v>
@@ -25521,7 +25521,7 @@
         <v>1301</v>
       </c>
       <c r="K93" t="s">
-        <v>887</v>
+        <v>924</v>
       </c>
       <c r="L93">
         <v>10.04285289714629</v>
@@ -25591,7 +25591,7 @@
         <v>1305</v>
       </c>
       <c r="K95" t="s">
-        <v>940</v>
+        <v>980</v>
       </c>
       <c r="L95">
         <v>31.24013860747554</v>
@@ -25626,7 +25626,7 @@
         <v>1307</v>
       </c>
       <c r="K96" t="s">
-        <v>975</v>
+        <v>900</v>
       </c>
       <c r="L96">
         <v>182.81724421979371</v>
@@ -25661,7 +25661,7 @@
         <v>1309</v>
       </c>
       <c r="K97" t="s">
-        <v>895</v>
+        <v>937</v>
       </c>
       <c r="L97">
         <v>129.21574742491194</v>
@@ -25696,7 +25696,7 @@
         <v>1311</v>
       </c>
       <c r="K98" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="L98">
         <v>0.3160884800353469</v>
@@ -25731,7 +25731,7 @@
         <v>1313</v>
       </c>
       <c r="K99" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="L99">
         <v>11.571846319988426</v>
@@ -25766,7 +25766,7 @@
         <v>1315</v>
       </c>
       <c r="K100" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="L100">
         <v>66.237243466162568</v>
@@ -25801,7 +25801,7 @@
         <v>1317</v>
       </c>
       <c r="K101" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="L101">
         <v>108.33634257446518</v>
@@ -25871,7 +25871,7 @@
         <v>1321</v>
       </c>
       <c r="K103" t="s">
-        <v>954</v>
+        <v>891</v>
       </c>
       <c r="L103">
         <v>120.70970601071261</v>
@@ -25906,7 +25906,7 @@
         <v>1323</v>
       </c>
       <c r="K104" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="L104">
         <v>33.829556694070689</v>
@@ -25941,7 +25941,7 @@
         <v>1325</v>
       </c>
       <c r="K105" t="s">
-        <v>926</v>
+        <v>953</v>
       </c>
       <c r="L105">
         <v>137.89166878057338</v>
@@ -25976,7 +25976,7 @@
         <v>1327</v>
       </c>
       <c r="K106" t="s">
-        <v>896</v>
+        <v>938</v>
       </c>
       <c r="L106">
         <v>7.7185621928607651</v>
@@ -26011,7 +26011,7 @@
         <v>1329</v>
       </c>
       <c r="K107" t="s">
-        <v>897</v>
+        <v>939</v>
       </c>
       <c r="L107">
         <v>13.260281925612457</v>
@@ -26026,7 +26026,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4326739E-7F36-4F90-88E5-183B1258C425}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CE3A50-ADB6-4F74-BA58-9219480FDFBA}">
   <dimension ref="B9:Y136"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
